--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col width="10.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1273,6 +1273,187 @@
         <v>158.5</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>102.107</v>
+      </c>
+      <c r="D5" t="n">
+        <v>142.16</v>
+      </c>
+      <c r="E5" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>103</v>
+      </c>
+      <c r="H5" t="n">
+        <v>120.01</v>
+      </c>
+      <c r="I5" t="n">
+        <v>108.74</v>
+      </c>
+      <c r="J5" t="n">
+        <v>122.95</v>
+      </c>
+      <c r="K5" t="n">
+        <v>116</v>
+      </c>
+      <c r="L5" t="n">
+        <v>139.54</v>
+      </c>
+      <c r="M5" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>119.19</v>
+      </c>
+      <c r="O5" t="n">
+        <v>122.631</v>
+      </c>
+      <c r="P5" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>387.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>161.55</v>
+      </c>
+      <c r="T5" t="n">
+        <v>284.55</v>
+      </c>
+      <c r="U5" t="n">
+        <v>209.9</v>
+      </c>
+      <c r="V5" t="n">
+        <v>115.95</v>
+      </c>
+      <c r="W5" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="X5" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>332.4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>89.91</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>122.449</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>114.55</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>104</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>140230</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>139650</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>135060</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>122190</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>95.34</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>81.38</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>73.68000000000001</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>65.42</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>85.12</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>75.34999999999999</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>90.64</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>87.45</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>159.25</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>158.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP8"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2133,6 +2133,211 @@
         <v>102.8</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>102.486</v>
+      </c>
+      <c r="D9" t="n">
+        <v>142.65</v>
+      </c>
+      <c r="E9" t="n">
+        <v>105.11</v>
+      </c>
+      <c r="F9" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="G9" t="n">
+        <v>103.33</v>
+      </c>
+      <c r="H9" t="n">
+        <v>120.298</v>
+      </c>
+      <c r="I9" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>138.851</v>
+      </c>
+      <c r="M9" t="n">
+        <v>126.249</v>
+      </c>
+      <c r="N9" t="n">
+        <v>119.18</v>
+      </c>
+      <c r="O9" t="n">
+        <v>123.289</v>
+      </c>
+      <c r="P9" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="R9" t="n">
+        <v>388.95</v>
+      </c>
+      <c r="S9" t="n">
+        <v>162.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>286.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>211.35</v>
+      </c>
+      <c r="V9" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="W9" t="n">
+        <v>376.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>265.45</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>122.87</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>108</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>143000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>142600</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>137510</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>125100</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>64.28</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>93.48999999999999</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>64.27</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>79.13</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>74.20999999999999</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>65.77</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>65.45</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>81.69</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>85.63</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>73.15000000000001</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>101</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>91</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>159.15</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>100.38</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>142700</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>138110</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>101</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>105.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2543,6 +2543,208 @@
         <v>105.65</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>102.731</v>
+      </c>
+      <c r="D11" t="n">
+        <v>143.07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>105.53</v>
+      </c>
+      <c r="F11" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>121</v>
+      </c>
+      <c r="I11" t="n">
+        <v>109.309</v>
+      </c>
+      <c r="J11" t="n">
+        <v>123.749</v>
+      </c>
+      <c r="K11" t="n">
+        <v>116.955</v>
+      </c>
+      <c r="L11" t="n">
+        <v>139.6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>126.72</v>
+      </c>
+      <c r="N11" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="O11" t="n">
+        <v>123</v>
+      </c>
+      <c r="P11" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="R11" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="S11" t="n">
+        <v>162.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>212.1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>379.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>336.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>88.68000000000001</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>115</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>143430</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>142800</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>138590</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>126000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>93.23999999999999</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>78.89</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>73.84999999999999</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>65.87</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>81.36</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>85.08</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>75.41</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>102</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>95.56</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>159.7</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>100.77</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>143190</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>140400</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>105.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP13"/>
+  <dimension ref="A1:BP14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3149,6 +3149,208 @@
         <v>105.8</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>102.904</v>
+      </c>
+      <c r="D14" t="n">
+        <v>143.425</v>
+      </c>
+      <c r="E14" t="n">
+        <v>105.765</v>
+      </c>
+      <c r="F14" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="G14" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="J14" t="n">
+        <v>124.74</v>
+      </c>
+      <c r="K14" t="n">
+        <v>117.13</v>
+      </c>
+      <c r="L14" t="n">
+        <v>140.95</v>
+      </c>
+      <c r="M14" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="N14" t="n">
+        <v>120.649</v>
+      </c>
+      <c r="O14" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="P14" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>390.85</v>
+      </c>
+      <c r="S14" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>288.2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>379.8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>266.85</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>97</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>338.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>88</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>143040</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>142690</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>139450</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>126400</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>64.16</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>93.27</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>63.83</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>78.26000000000001</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>80.83</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>73.61</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>80.93000000000001</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>84.73</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>72.78</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>88.70999999999999</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>160.75</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>160.7</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>101.39</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>142600</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>139400</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>111.05</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>105.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP14"/>
+  <dimension ref="A1:BP15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3351,6 +3351,205 @@
         <v>105.45</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>143.475</v>
+      </c>
+      <c r="E15" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>114.67</v>
+      </c>
+      <c r="G15" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>110.07</v>
+      </c>
+      <c r="J15" t="n">
+        <v>124.771</v>
+      </c>
+      <c r="K15" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>141.509</v>
+      </c>
+      <c r="M15" t="n">
+        <v>128.55</v>
+      </c>
+      <c r="N15" t="n">
+        <v>120.96</v>
+      </c>
+      <c r="O15" t="n">
+        <v>124.95</v>
+      </c>
+      <c r="P15" t="n">
+        <v>99.62</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>391</v>
+      </c>
+      <c r="S15" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>288.3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>213.45</v>
+      </c>
+      <c r="V15" t="n">
+        <v>117.55</v>
+      </c>
+      <c r="W15" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="X15" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>340.3</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>88.06999999999999</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>142390</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>141880</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>139000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>125150</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>96.16</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>65.38</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>75.47</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>65.95999999999999</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>87.45</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>77.56999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>92</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>89.65000000000001</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>160.7</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>160.35</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>101.408</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>142150</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>138800</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>105.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP15"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3550,6 +3550,205 @@
         <v>105.25</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>143.75</v>
+      </c>
+      <c r="E16" t="n">
+        <v>105.999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>114.86</v>
+      </c>
+      <c r="G16" t="n">
+        <v>104.36</v>
+      </c>
+      <c r="H16" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>110.285</v>
+      </c>
+      <c r="J16" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>118.201</v>
+      </c>
+      <c r="L16" t="n">
+        <v>141.95</v>
+      </c>
+      <c r="M16" t="n">
+        <v>128.745</v>
+      </c>
+      <c r="N16" t="n">
+        <v>121.35</v>
+      </c>
+      <c r="O16" t="n">
+        <v>125</v>
+      </c>
+      <c r="P16" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>391.75</v>
+      </c>
+      <c r="S16" t="n">
+        <v>163.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>288.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>213.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>382.35</v>
+      </c>
+      <c r="X16" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>88.31</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>111</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>103</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>142300</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>141510</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>138800</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>124500</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>65.12</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>64.56999999999999</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>83.31</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>75.47</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>66.22</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>83.86</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>88</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>78.43000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>75.14</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>92.08</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>161.05</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>142300</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>139800</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>104</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>112</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>105.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU18"/>
+  <dimension ref="A1:BU19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4232,6 +4232,220 @@
         <v>79.7</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>143.825</v>
+      </c>
+      <c r="E19" t="n">
+        <v>106.049</v>
+      </c>
+      <c r="F19" t="n">
+        <v>114.72</v>
+      </c>
+      <c r="G19" t="n">
+        <v>104.33</v>
+      </c>
+      <c r="H19" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>110.19</v>
+      </c>
+      <c r="J19" t="n">
+        <v>125.125</v>
+      </c>
+      <c r="K19" t="n">
+        <v>118</v>
+      </c>
+      <c r="L19" t="n">
+        <v>141.75</v>
+      </c>
+      <c r="M19" t="n">
+        <v>128.84</v>
+      </c>
+      <c r="N19" t="n">
+        <v>121.656</v>
+      </c>
+      <c r="O19" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>110</v>
+      </c>
+      <c r="R19" t="n">
+        <v>392</v>
+      </c>
+      <c r="S19" t="n">
+        <v>163.15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>287.3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>212.9</v>
+      </c>
+      <c r="V19" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>380.65</v>
+      </c>
+      <c r="X19" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>268</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>88.29000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>123.89</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>111</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>143800</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>143040</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>139650</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>125140</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>94.47</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>80.59</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>83.52</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>65.91</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>83.19</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>88</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>92.45999999999999</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>161.15</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>160.55</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>101.463</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>143750</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>140950</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>106</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>142700</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>119200</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>83</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>79.09999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU19"/>
+  <dimension ref="A1:BU20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4446,6 +4446,220 @@
         <v>79.09999999999999</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>143.92</v>
+      </c>
+      <c r="E20" t="n">
+        <v>106.125</v>
+      </c>
+      <c r="F20" t="n">
+        <v>114.802</v>
+      </c>
+      <c r="G20" t="n">
+        <v>104.489</v>
+      </c>
+      <c r="H20" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>110.28</v>
+      </c>
+      <c r="J20" t="n">
+        <v>125.19</v>
+      </c>
+      <c r="K20" t="n">
+        <v>117.989</v>
+      </c>
+      <c r="L20" t="n">
+        <v>141.98</v>
+      </c>
+      <c r="M20" t="n">
+        <v>128.85</v>
+      </c>
+      <c r="N20" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="O20" t="n">
+        <v>124</v>
+      </c>
+      <c r="P20" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="R20" t="n">
+        <v>392.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>163.95</v>
+      </c>
+      <c r="T20" t="n">
+        <v>287</v>
+      </c>
+      <c r="U20" t="n">
+        <v>213.1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>380.25</v>
+      </c>
+      <c r="X20" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>267.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>97</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>340.6</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>123.94</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>103</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>144640</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>144110</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>142090</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>125900</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>65.88</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>84.05</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>102</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>91.56</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>161.35</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>160.65</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>144190</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>141900</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>144390</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>119550</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>82.73</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>79.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU21"/>
+  <dimension ref="A1:BU22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4874,6 +4874,220 @@
         <v>79.08</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>144.272</v>
+      </c>
+      <c r="E22" t="n">
+        <v>106.49</v>
+      </c>
+      <c r="F22" t="n">
+        <v>115.09</v>
+      </c>
+      <c r="G22" t="n">
+        <v>104.776</v>
+      </c>
+      <c r="H22" t="n">
+        <v>121.962</v>
+      </c>
+      <c r="I22" t="n">
+        <v>110.553</v>
+      </c>
+      <c r="J22" t="n">
+        <v>125.3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="M22" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>122.21</v>
+      </c>
+      <c r="O22" t="n">
+        <v>125</v>
+      </c>
+      <c r="P22" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>393.35</v>
+      </c>
+      <c r="S22" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>119</v>
+      </c>
+      <c r="W22" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="X22" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>340</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>89</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>124.35</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>145550</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>144700</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>142800</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>126100</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>97</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>95.28</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>81.33</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>84.09</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>76.42</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>66.01000000000001</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>84.19</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>87.98999999999999</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>75.34999999999999</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>92</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>161.05</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>145200</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>143330</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>144950</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>119700</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>79.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU25"/>
+  <dimension ref="A1:BU26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5730,6 +5730,220 @@
         <v>79.2</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>144.795</v>
+      </c>
+      <c r="E26" t="n">
+        <v>106.73</v>
+      </c>
+      <c r="F26" t="n">
+        <v>115.38</v>
+      </c>
+      <c r="G26" t="n">
+        <v>104.94</v>
+      </c>
+      <c r="H26" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>125.06</v>
+      </c>
+      <c r="K26" t="n">
+        <v>118.11</v>
+      </c>
+      <c r="L26" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="M26" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>122.8</v>
+      </c>
+      <c r="O26" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>394.65</v>
+      </c>
+      <c r="S26" t="n">
+        <v>163.75</v>
+      </c>
+      <c r="T26" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>116.65</v>
+      </c>
+      <c r="W26" t="n">
+        <v>375.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>266.75</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>337.85</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>124.48</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>147610</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>146670</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>145180</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>126800</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>95.29000000000001</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>81.83</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>77</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>66.03</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>84.63</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>78.78</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>92.66</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>89</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>161.55</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>147000</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>144500</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>146500</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>121400</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>90</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>79.40000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU26"/>
+  <dimension ref="A1:BY27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -787,6 +787,26 @@
           <t>TXMJ0</t>
         </is>
       </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>S13N6</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>TZXO7</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>TZXD8</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>TML27</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -5942,6 +5962,208 @@
       </c>
       <c r="BU26" t="n">
         <v>79.40000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106.83</v>
+      </c>
+      <c r="F27" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="G27" t="n">
+        <v>105.234</v>
+      </c>
+      <c r="H27" t="n">
+        <v>122.53</v>
+      </c>
+      <c r="I27" t="n">
+        <v>110.96</v>
+      </c>
+      <c r="J27" t="n">
+        <v>125.502</v>
+      </c>
+      <c r="K27" t="n">
+        <v>118.555</v>
+      </c>
+      <c r="L27" t="n">
+        <v>142.25</v>
+      </c>
+      <c r="M27" t="n">
+        <v>129.839</v>
+      </c>
+      <c r="N27" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="O27" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="P27" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>164.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>288.2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>212.75</v>
+      </c>
+      <c r="V27" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>377.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>88.23999999999999</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>124.86</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>147200</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>146400</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>126900</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>64.31</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>81.47</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>84.23999999999999</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>84.89</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>75.95999999999999</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>92.52</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>161.75</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>102.201</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>146990</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>146200</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>146680</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>121550</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>90</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>79.8</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY27"/>
+  <dimension ref="A1:BY28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6166,6 +6166,220 @@
         <v>79.8</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106.91</v>
+      </c>
+      <c r="F28" t="n">
+        <v>115.655</v>
+      </c>
+      <c r="G28" t="n">
+        <v>105.23</v>
+      </c>
+      <c r="H28" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="J28" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>142.84</v>
+      </c>
+      <c r="M28" t="n">
+        <v>130.189</v>
+      </c>
+      <c r="N28" t="n">
+        <v>123.06</v>
+      </c>
+      <c r="O28" t="n">
+        <v>125.645</v>
+      </c>
+      <c r="P28" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>212.85</v>
+      </c>
+      <c r="V28" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="W28" t="n">
+        <v>377.7</v>
+      </c>
+      <c r="X28" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>267</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>337.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>87.98</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>125</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>106</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>148250</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>147500</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>127930</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>81.16</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>83.97</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>77.29000000000001</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>66.33</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>65.95999999999999</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>84.66</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>93.97</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>89.45</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>102.37</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>147600</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>147150</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>102</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>147390</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>121850</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>90</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>100.645</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>81.93000000000001</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>101.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY29"/>
+  <dimension ref="A1:BY30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6594,6 +6594,220 @@
         <v>101.6</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>107.06</v>
+      </c>
+      <c r="F30" t="n">
+        <v>115.83</v>
+      </c>
+      <c r="G30" t="n">
+        <v>105.351</v>
+      </c>
+      <c r="H30" t="n">
+        <v>122.701</v>
+      </c>
+      <c r="I30" t="n">
+        <v>111.28</v>
+      </c>
+      <c r="J30" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>143.249</v>
+      </c>
+      <c r="M30" t="n">
+        <v>130.55</v>
+      </c>
+      <c r="N30" t="n">
+        <v>123.45</v>
+      </c>
+      <c r="O30" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="S30" t="n">
+        <v>164.3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>289.25</v>
+      </c>
+      <c r="U30" t="n">
+        <v>213.1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="W30" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="X30" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>266.3</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>338.75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>88.15000000000001</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>125.12</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>111</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>104</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>146950</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>146500</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>128150</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>95.33</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>64.33</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>81.58</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>78.42</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>162.15</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>102.48</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>147900</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>146500</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>112</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>147600</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>122750</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>100.855</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>101.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY31"/>
+  <dimension ref="A1:BY32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7022,6 +7022,220 @@
         <v>102.3</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>107.308</v>
+      </c>
+      <c r="F32" t="n">
+        <v>116.15</v>
+      </c>
+      <c r="G32" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="H32" t="n">
+        <v>123.18</v>
+      </c>
+      <c r="I32" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>126.252</v>
+      </c>
+      <c r="K32" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>123.999</v>
+      </c>
+      <c r="O32" t="n">
+        <v>125.9</v>
+      </c>
+      <c r="P32" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>165.05</v>
+      </c>
+      <c r="T32" t="n">
+        <v>290.25</v>
+      </c>
+      <c r="U32" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="W32" t="n">
+        <v>382.8</v>
+      </c>
+      <c r="X32" t="n">
+        <v>103</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>268.35</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>342.45</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>93</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>125.51</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>147250</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>146020</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>127900</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>97.26000000000001</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>81.36</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>84.73</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>78.45999999999999</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>66.01000000000001</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>66.19</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>89.45</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>76.59</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>96.34999999999999</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>162.6</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>102.864</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>147700</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>145300</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>147300</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>122700</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>91</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>84.23999999999999</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>101.385</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>102.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY36"/>
+  <dimension ref="A1:BY37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8092,6 +8092,220 @@
         <v>104</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>107.718</v>
+      </c>
+      <c r="F37" t="n">
+        <v>116.44</v>
+      </c>
+      <c r="G37" t="n">
+        <v>106.02</v>
+      </c>
+      <c r="H37" t="n">
+        <v>123.45</v>
+      </c>
+      <c r="I37" t="n">
+        <v>111.999</v>
+      </c>
+      <c r="J37" t="n">
+        <v>126.65</v>
+      </c>
+      <c r="K37" t="n">
+        <v>119.39</v>
+      </c>
+      <c r="L37" t="n">
+        <v>144.32</v>
+      </c>
+      <c r="M37" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="N37" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>126.81</v>
+      </c>
+      <c r="P37" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="S37" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="T37" t="n">
+        <v>291.3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>215.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>119</v>
+      </c>
+      <c r="W37" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="X37" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>268.4</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>342.75</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>89.47</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>125.911</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>117</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>106</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>146800</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>144400</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>127660</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>95.73999999999999</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>77.02</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>83</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>92.69</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>163.15</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>103.101</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>147460</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>145880</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>147500</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>122490</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>81.55</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>101.56</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>102.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY39"/>
+  <dimension ref="A1:BY40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8734,6 +8734,217 @@
         <v>103.75</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>116.775</v>
+      </c>
+      <c r="G40" t="n">
+        <v>106.205</v>
+      </c>
+      <c r="H40" t="n">
+        <v>123.68</v>
+      </c>
+      <c r="I40" t="n">
+        <v>112.21</v>
+      </c>
+      <c r="J40" t="n">
+        <v>126.651</v>
+      </c>
+      <c r="K40" t="n">
+        <v>119.263</v>
+      </c>
+      <c r="L40" t="n">
+        <v>143.8</v>
+      </c>
+      <c r="M40" t="n">
+        <v>131.499</v>
+      </c>
+      <c r="N40" t="n">
+        <v>124.32</v>
+      </c>
+      <c r="O40" t="n">
+        <v>127</v>
+      </c>
+      <c r="P40" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="S40" t="n">
+        <v>166</v>
+      </c>
+      <c r="T40" t="n">
+        <v>292</v>
+      </c>
+      <c r="U40" t="n">
+        <v>215.35</v>
+      </c>
+      <c r="V40" t="n">
+        <v>119.05</v>
+      </c>
+      <c r="W40" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="X40" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>268.45</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>343.1</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>126.241</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>116.95</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>107</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>145850</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>143550</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>126400</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>98</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>55.26</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>97</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>56.43</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>77.03</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>78.37</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>92.76000000000001</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>92.45999999999999</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>103.281</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>146800</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>144890</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>104</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>146400</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>120100</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>84.73999999999999</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>101.77</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>103.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA41"/>
+  <dimension ref="A1:CE41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -817,6 +817,26 @@
           <t>AO29D</t>
         </is>
       </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>TZXY7</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>X30N6</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>X31L6</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>X30S6</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -1038,6 +1058,9 @@
       <c r="BU2" t="n">
         <v>79.59999999999999</v>
       </c>
+      <c r="CC2" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1222,6 +1245,18 @@
       <c r="BH3" t="n">
         <v>158.7</v>
       </c>
+      <c r="CB3" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>117.15</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>108.801</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1406,6 +1441,18 @@
       <c r="BH4" t="n">
         <v>158.5</v>
       </c>
+      <c r="CB4" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>108.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1587,6 +1634,18 @@
       <c r="BH5" t="n">
         <v>158.6</v>
       </c>
+      <c r="CB5" t="n">
+        <v>114</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>117.295</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1792,6 +1851,18 @@
       <c r="BP6" t="n">
         <v>109</v>
       </c>
+      <c r="CB6" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>109.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1997,6 +2068,18 @@
       <c r="BP7" t="n">
         <v>105.3</v>
       </c>
+      <c r="CB7" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>109.37</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2202,6 +2285,18 @@
       <c r="BP8" t="n">
         <v>102.8</v>
       </c>
+      <c r="CB8" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>117.815</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>109.32</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2407,6 +2502,18 @@
       <c r="BP9" t="n">
         <v>105.1</v>
       </c>
+      <c r="CB9" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>109.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2612,6 +2719,18 @@
       <c r="BP10" t="n">
         <v>105.65</v>
       </c>
+      <c r="CB10" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>117.76</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>114.225</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>109.45</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2814,6 +2933,18 @@
       <c r="BP11" t="n">
         <v>105.55</v>
       </c>
+      <c r="CB11" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>114.452</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>109.65</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3016,6 +3147,18 @@
       <c r="BP12" t="n">
         <v>105.9</v>
       </c>
+      <c r="CB12" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>118.34</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>109.71</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3218,6 +3361,18 @@
       <c r="BP13" t="n">
         <v>105.8</v>
       </c>
+      <c r="CB13" t="n">
+        <v>116</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3420,6 +3575,18 @@
       <c r="BP14" t="n">
         <v>105.45</v>
       </c>
+      <c r="CB14" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>118.775</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>114.727</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>110.25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3619,6 +3786,18 @@
       <c r="BP15" t="n">
         <v>105.25</v>
       </c>
+      <c r="CB15" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>110.25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3833,6 +4012,18 @@
       <c r="BU16" t="n">
         <v>79.59999999999999</v>
       </c>
+      <c r="CB16" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>118.65</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>110.25</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4261,6 +4452,18 @@
       <c r="BU18" t="n">
         <v>79.7</v>
       </c>
+      <c r="CB18" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>110.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4475,6 +4678,18 @@
       <c r="BU19" t="n">
         <v>79.09999999999999</v>
       </c>
+      <c r="CB19" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>110.1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4689,6 +4904,18 @@
       <c r="BU20" t="n">
         <v>79.05</v>
       </c>
+      <c r="CB20" t="n">
+        <v>116</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>118.35</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>114.88</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>110.25</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4903,6 +5130,18 @@
       <c r="BU21" t="n">
         <v>79.08</v>
       </c>
+      <c r="CB21" t="n">
+        <v>116</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>118.301</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>115.21</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>110.35</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5117,6 +5356,18 @@
       <c r="BU22" t="n">
         <v>79.14</v>
       </c>
+      <c r="CB22" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="CC22" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="CD22" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="CE22" t="n">
+        <v>110.499</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5331,6 +5582,18 @@
       <c r="BU23" t="n">
         <v>79.09</v>
       </c>
+      <c r="CB23" t="n">
+        <v>116</v>
+      </c>
+      <c r="CC23" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="CD23" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="CE23" t="n">
+        <v>110.4</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5545,6 +5808,18 @@
       <c r="BU24" t="n">
         <v>79.63</v>
       </c>
+      <c r="CB24" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="CC24" t="n">
+        <v>118.38</v>
+      </c>
+      <c r="CD24" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="CE24" t="n">
+        <v>110.45</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5759,6 +6034,18 @@
       <c r="BU25" t="n">
         <v>79.2</v>
       </c>
+      <c r="CB25" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="CC25" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="CD25" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="CE25" t="n">
+        <v>110.45</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5973,6 +6260,18 @@
       <c r="BU26" t="n">
         <v>79.40000000000001</v>
       </c>
+      <c r="CB26" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="CC26" t="n">
+        <v>118.55</v>
+      </c>
+      <c r="CD26" t="n">
+        <v>115.52</v>
+      </c>
+      <c r="CE26" t="n">
+        <v>110.55</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6175,6 +6474,18 @@
       <c r="BU27" t="n">
         <v>79.8</v>
       </c>
+      <c r="CB27" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="CC27" t="n">
+        <v>118.77</v>
+      </c>
+      <c r="CD27" t="n">
+        <v>115.65</v>
+      </c>
+      <c r="CE27" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6389,6 +6700,18 @@
       <c r="BY28" t="n">
         <v>101.7</v>
       </c>
+      <c r="CB28" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="CC28" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="CD28" t="n">
+        <v>115.852</v>
+      </c>
+      <c r="CE28" t="n">
+        <v>110.93</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6603,6 +6926,18 @@
       <c r="BY29" t="n">
         <v>101.6</v>
       </c>
+      <c r="CB29" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="CC29" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="CD29" t="n">
+        <v>116.04</v>
+      </c>
+      <c r="CE29" t="n">
+        <v>111.05</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6817,6 +7152,18 @@
       <c r="BY30" t="n">
         <v>101.7</v>
       </c>
+      <c r="CB30" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="CC30" t="n">
+        <v>119.07</v>
+      </c>
+      <c r="CD30" t="n">
+        <v>116.031</v>
+      </c>
+      <c r="CE30" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7031,6 +7378,18 @@
       <c r="BY31" t="n">
         <v>102.3</v>
       </c>
+      <c r="CB31" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="CC31" t="n">
+        <v>119.412</v>
+      </c>
+      <c r="CD31" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="CE31" t="n">
+        <v>111.15</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7245,6 +7604,18 @@
       <c r="BY32" t="n">
         <v>102.5</v>
       </c>
+      <c r="CB32" t="n">
+        <v>116.15</v>
+      </c>
+      <c r="CC32" t="n">
+        <v>119.675</v>
+      </c>
+      <c r="CD32" t="n">
+        <v>116.35</v>
+      </c>
+      <c r="CE32" t="n">
+        <v>111.4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7459,6 +7830,18 @@
       <c r="BY33" t="n">
         <v>102.8</v>
       </c>
+      <c r="CB33" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>119.6</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>116.39</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>111.4</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7673,6 +8056,18 @@
       <c r="BY34" t="n">
         <v>102.9</v>
       </c>
+      <c r="CB34" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="CC34" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="CD34" t="n">
+        <v>116.71</v>
+      </c>
+      <c r="CE34" t="n">
+        <v>111.52</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8101,6 +8496,18 @@
       <c r="BY36" t="n">
         <v>104</v>
       </c>
+      <c r="CB36" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="CC36" t="n">
+        <v>120.112</v>
+      </c>
+      <c r="CD36" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="CE36" t="n">
+        <v>111.989</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8315,6 +8722,18 @@
       <c r="BY37" t="n">
         <v>102.9</v>
       </c>
+      <c r="CB37" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="CC37" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="CE37" t="n">
+        <v>111.749</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8529,6 +8948,18 @@
       <c r="BY38" t="n">
         <v>103</v>
       </c>
+      <c r="CB38" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="CC38" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="CD38" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="CE38" t="n">
+        <v>111.78</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8743,6 +9174,18 @@
       <c r="BY39" t="n">
         <v>103.75</v>
       </c>
+      <c r="CB39" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="CC39" t="n">
+        <v>119.871</v>
+      </c>
+      <c r="CD39" t="n">
+        <v>117</v>
+      </c>
+      <c r="CE39" t="n">
+        <v>111.95</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8954,6 +9397,18 @@
       <c r="BY40" t="n">
         <v>103.3</v>
       </c>
+      <c r="CB40" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="CC40" t="n">
+        <v>120.14</v>
+      </c>
+      <c r="CD40" t="n">
+        <v>117.01</v>
+      </c>
+      <c r="CE40" t="n">
+        <v>112.049</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9170,6 +9625,18 @@
       </c>
       <c r="CA41" t="n">
         <v>94.64000000000001</v>
+      </c>
+      <c r="CB41" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="CC41" t="n">
+        <v>120.36</v>
+      </c>
+      <c r="CD41" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="CE41" t="n">
+        <v>112.19</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE41"/>
+  <dimension ref="A1:CE42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9639,6 +9639,232 @@
         <v>112.19</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>106.48</v>
+      </c>
+      <c r="H42" t="n">
+        <v>124</v>
+      </c>
+      <c r="I42" t="n">
+        <v>112.599</v>
+      </c>
+      <c r="J42" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="K42" t="n">
+        <v>119.64</v>
+      </c>
+      <c r="L42" t="n">
+        <v>144.34</v>
+      </c>
+      <c r="M42" t="n">
+        <v>131.72</v>
+      </c>
+      <c r="N42" t="n">
+        <v>124.45</v>
+      </c>
+      <c r="O42" t="n">
+        <v>126.19</v>
+      </c>
+      <c r="P42" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="S42" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>215.7</v>
+      </c>
+      <c r="V42" t="n">
+        <v>119.45</v>
+      </c>
+      <c r="W42" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>268.7</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>344.05</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>126.53</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>146550</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>144700</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>126840</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>97.89</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>80.81999999999999</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>55.95</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>77.98</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>72.06999999999999</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>93.09</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>103.59</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>147290</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>145540</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>104</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>105</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>108</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>146750</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>120500</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>85.09</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>102.06</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>94.64</v>
+      </c>
+      <c r="CB42" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="CC42" t="n">
+        <v>120.36</v>
+      </c>
+      <c r="CE42" t="n">
+        <v>112.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE42"/>
+  <dimension ref="A1:CE41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9639,232 +9639,6 @@
         <v>112.19</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>117.1</v>
-      </c>
-      <c r="G42" t="n">
-        <v>106.48</v>
-      </c>
-      <c r="H42" t="n">
-        <v>124</v>
-      </c>
-      <c r="I42" t="n">
-        <v>112.599</v>
-      </c>
-      <c r="J42" t="n">
-        <v>127.25</v>
-      </c>
-      <c r="K42" t="n">
-        <v>119.64</v>
-      </c>
-      <c r="L42" t="n">
-        <v>144.34</v>
-      </c>
-      <c r="M42" t="n">
-        <v>131.72</v>
-      </c>
-      <c r="N42" t="n">
-        <v>124.45</v>
-      </c>
-      <c r="O42" t="n">
-        <v>126.19</v>
-      </c>
-      <c r="P42" t="n">
-        <v>102</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="S42" t="n">
-        <v>166.3</v>
-      </c>
-      <c r="T42" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="U42" t="n">
-        <v>215.7</v>
-      </c>
-      <c r="V42" t="n">
-        <v>119.45</v>
-      </c>
-      <c r="W42" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="X42" t="n">
-        <v>103.55</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>268.7</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>97.34999999999999</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>344.05</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>93.45999999999999</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>89.89</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>126.53</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>107.45</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>104.1</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>146550</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>144700</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>126840</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>102.7</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>97.89</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>55.37</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>97.15000000000001</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>56.47</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>80.81999999999999</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>83.64</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>76.91</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>55.95</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>57.99</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>83.56999999999999</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>86.89</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>77.98</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>72.06999999999999</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>102.65</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>102.6</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>93.09</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>96.65000000000001</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="BH42" t="n">
-        <v>163.8</v>
-      </c>
-      <c r="BI42" t="n">
-        <v>103.59</v>
-      </c>
-      <c r="BJ42" t="n">
-        <v>147290</v>
-      </c>
-      <c r="BK42" t="n">
-        <v>145540</v>
-      </c>
-      <c r="BM42" t="n">
-        <v>104</v>
-      </c>
-      <c r="BN42" t="n">
-        <v>105</v>
-      </c>
-      <c r="BO42" t="n">
-        <v>112.7</v>
-      </c>
-      <c r="BP42" t="n">
-        <v>108</v>
-      </c>
-      <c r="BQ42" t="n">
-        <v>146750</v>
-      </c>
-      <c r="BR42" t="n">
-        <v>120500</v>
-      </c>
-      <c r="BS42" t="n">
-        <v>92.05</v>
-      </c>
-      <c r="BT42" t="n">
-        <v>85.09</v>
-      </c>
-      <c r="BU42" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="BV42" t="n">
-        <v>102.06</v>
-      </c>
-      <c r="BW42" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="BX42" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="BY42" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="BZ42" t="n">
-        <v>146600</v>
-      </c>
-      <c r="CA42" t="n">
-        <v>94.64</v>
-      </c>
-      <c r="CB42" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="CC42" t="n">
-        <v>120.36</v>
-      </c>
-      <c r="CE42" t="n">
-        <v>112.19</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE41"/>
+  <dimension ref="A1:CE42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9639,6 +9639,232 @@
         <v>112.19</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="G42" t="n">
+        <v>106.535</v>
+      </c>
+      <c r="H42" t="n">
+        <v>124.08</v>
+      </c>
+      <c r="I42" t="n">
+        <v>112.599</v>
+      </c>
+      <c r="J42" t="n">
+        <v>127.369</v>
+      </c>
+      <c r="K42" t="n">
+        <v>119.679</v>
+      </c>
+      <c r="L42" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>124.37</v>
+      </c>
+      <c r="O42" t="n">
+        <v>126</v>
+      </c>
+      <c r="P42" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>166.4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="U42" t="n">
+        <v>216.05</v>
+      </c>
+      <c r="V42" t="n">
+        <v>119.05</v>
+      </c>
+      <c r="W42" t="n">
+        <v>385.25</v>
+      </c>
+      <c r="X42" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>344.85</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>104</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>146490</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>144250</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>126650</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>97.45999999999999</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>78.23999999999999</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>94</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>103.68</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>147590</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>144160</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>103</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>146780</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>120500</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>92</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>102.119</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>146420</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>94.98</v>
+      </c>
+      <c r="CB42" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="CC42" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="CE42" t="n">
+        <v>112.275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE41"/>
+  <dimension ref="A1:CG41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -837,6 +837,16 @@
           <t>X30S6</t>
         </is>
       </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>BPA7D</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>BPB7D</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -1061,6 +1071,12 @@
       <c r="CC2" t="n">
         <v>94</v>
       </c>
+      <c r="CF2" t="n">
+        <v>100</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>99.11999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1257,6 +1273,12 @@
       <c r="CE3" t="n">
         <v>108.801</v>
       </c>
+      <c r="CF3" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>100.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1453,6 +1475,12 @@
       <c r="CE4" t="n">
         <v>108.95</v>
       </c>
+      <c r="CF4" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>100.6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1646,6 +1674,12 @@
       <c r="CE5" t="n">
         <v>109</v>
       </c>
+      <c r="CF5" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>100.55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1863,6 +1897,12 @@
       <c r="CE6" t="n">
         <v>109.3</v>
       </c>
+      <c r="CF6" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>100.6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2080,6 +2120,12 @@
       <c r="CE7" t="n">
         <v>109.37</v>
       </c>
+      <c r="CF7" t="n">
+        <v>101</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>100.75</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2297,6 +2343,12 @@
       <c r="CE8" t="n">
         <v>109.32</v>
       </c>
+      <c r="CF8" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>101.05</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2514,6 +2566,12 @@
       <c r="CE9" t="n">
         <v>109.3</v>
       </c>
+      <c r="CF9" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>101.1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2731,6 +2789,12 @@
       <c r="CE10" t="n">
         <v>109.45</v>
       </c>
+      <c r="CF10" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>101.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2945,6 +3009,12 @@
       <c r="CE11" t="n">
         <v>109.65</v>
       </c>
+      <c r="CF11" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>101.7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3159,6 +3229,12 @@
       <c r="CE12" t="n">
         <v>109.71</v>
       </c>
+      <c r="CF12" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3373,6 +3449,12 @@
       <c r="CE13" t="n">
         <v>111</v>
       </c>
+      <c r="CF13" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3587,6 +3669,12 @@
       <c r="CE14" t="n">
         <v>110.25</v>
       </c>
+      <c r="CF14" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>102.05</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3798,6 +3886,12 @@
       <c r="CE15" t="n">
         <v>110.25</v>
       </c>
+      <c r="CF15" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>101.85</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4024,6 +4118,12 @@
       <c r="CE16" t="n">
         <v>110.25</v>
       </c>
+      <c r="CF16" t="n">
+        <v>102</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>101.85</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4464,6 +4564,12 @@
       <c r="CE18" t="n">
         <v>110.1</v>
       </c>
+      <c r="CF18" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4690,6 +4796,12 @@
       <c r="CE19" t="n">
         <v>110.1</v>
       </c>
+      <c r="CF19" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4916,6 +5028,12 @@
       <c r="CE20" t="n">
         <v>110.25</v>
       </c>
+      <c r="CF20" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>101.9</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5142,6 +5260,12 @@
       <c r="CE21" t="n">
         <v>110.35</v>
       </c>
+      <c r="CF21" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>101.8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5368,6 +5492,12 @@
       <c r="CE22" t="n">
         <v>110.499</v>
       </c>
+      <c r="CF22" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="CG22" t="n">
+        <v>101.85</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5594,6 +5724,12 @@
       <c r="CE23" t="n">
         <v>110.4</v>
       </c>
+      <c r="CF23" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="CG23" t="n">
+        <v>101.85</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5820,6 +5956,12 @@
       <c r="CE24" t="n">
         <v>110.45</v>
       </c>
+      <c r="CF24" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="CG24" t="n">
+        <v>102.2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6046,6 +6188,12 @@
       <c r="CE25" t="n">
         <v>110.45</v>
       </c>
+      <c r="CF25" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>102.25</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6272,6 +6420,12 @@
       <c r="CE26" t="n">
         <v>110.55</v>
       </c>
+      <c r="CF26" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6486,6 +6640,12 @@
       <c r="CE27" t="n">
         <v>111</v>
       </c>
+      <c r="CF27" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="CG27" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6712,6 +6872,12 @@
       <c r="CE28" t="n">
         <v>110.93</v>
       </c>
+      <c r="CF28" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="CG28" t="n">
+        <v>101.8</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6938,6 +7104,12 @@
       <c r="CE29" t="n">
         <v>111.05</v>
       </c>
+      <c r="CF29" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>102.1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7164,6 +7336,12 @@
       <c r="CE30" t="n">
         <v>111</v>
       </c>
+      <c r="CF30" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7390,6 +7568,12 @@
       <c r="CE31" t="n">
         <v>111.15</v>
       </c>
+      <c r="CF31" t="n">
+        <v>102</v>
+      </c>
+      <c r="CG31" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7616,6 +7800,12 @@
       <c r="CE32" t="n">
         <v>111.4</v>
       </c>
+      <c r="CF32" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="CG32" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7842,6 +8032,12 @@
       <c r="CE33" t="n">
         <v>111.4</v>
       </c>
+      <c r="CF33" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>101.9</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8068,6 +8264,12 @@
       <c r="CE34" t="n">
         <v>111.52</v>
       </c>
+      <c r="CF34" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="CG34" t="n">
+        <v>101.85</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8508,6 +8710,12 @@
       <c r="CE36" t="n">
         <v>111.989</v>
       </c>
+      <c r="CF36" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="CG36" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8734,6 +8942,12 @@
       <c r="CE37" t="n">
         <v>111.749</v>
       </c>
+      <c r="CF37" t="n">
+        <v>102</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8960,6 +9174,12 @@
       <c r="CE38" t="n">
         <v>111.78</v>
       </c>
+      <c r="CF38" t="n">
+        <v>102</v>
+      </c>
+      <c r="CG38" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9186,6 +9406,12 @@
       <c r="CE39" t="n">
         <v>111.95</v>
       </c>
+      <c r="CF39" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="CG39" t="n">
+        <v>102.15</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9409,6 +9635,12 @@
       <c r="CE40" t="n">
         <v>112.049</v>
       </c>
+      <c r="CF40" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="CG40" t="n">
+        <v>102.35</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9637,6 +9869,12 @@
       </c>
       <c r="CE41" t="n">
         <v>112.19</v>
+      </c>
+      <c r="CF41" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="CG41" t="n">
+        <v>102.4</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG42"/>
+  <dimension ref="A1:DG43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -847,6 +847,136 @@
           <t>BPB7D</t>
         </is>
       </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>JUS22</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>Bueair27</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>CO24</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>Muni27</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>SF27D</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>SA24D</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>CH24D</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>RIF25</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>RND25</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>ERF25</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>CO27</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>PMM29</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>PUL26</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>TFU27</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>NDT25</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>NDT11</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>CO32</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>ERM33</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>BDC33</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>SFD34</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>CO35</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>PUA36</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>BDC36</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>BA37D</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>BB37D</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>BC37D</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -10107,6 +10237,295 @@
       </c>
       <c r="CG42" t="n">
         <v>102.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>117.139</v>
+      </c>
+      <c r="G43" t="n">
+        <v>106.57</v>
+      </c>
+      <c r="H43" t="n">
+        <v>124.13</v>
+      </c>
+      <c r="I43" t="n">
+        <v>112.625</v>
+      </c>
+      <c r="J43" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>119.643</v>
+      </c>
+      <c r="L43" t="n">
+        <v>144</v>
+      </c>
+      <c r="M43" t="n">
+        <v>131.62</v>
+      </c>
+      <c r="N43" t="n">
+        <v>124.29</v>
+      </c>
+      <c r="O43" t="n">
+        <v>125.88</v>
+      </c>
+      <c r="P43" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="S43" t="n">
+        <v>166.65</v>
+      </c>
+      <c r="T43" t="n">
+        <v>293.1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>216.35</v>
+      </c>
+      <c r="V43" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>270.4</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>344.9</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>107</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>146250</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>144500</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>126300</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>103</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>98.16</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>56.87999999999999</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>83.39</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>78.12</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>92.68999999999998</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>164.25</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>103.68</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>147260</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>144200</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>146420</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>120200</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>92</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>85.02</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="CB43" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="CC43" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="CE43" t="n">
+        <v>112.399</v>
+      </c>
+      <c r="CF43" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="CG43" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="CH43" t="n">
+        <v>32014.25</v>
+      </c>
+      <c r="CM43" t="n">
+        <v>59000</v>
+      </c>
+      <c r="CN43" t="n">
+        <v>29754.62</v>
+      </c>
+      <c r="CQ43" t="n">
+        <v>74450</v>
+      </c>
+      <c r="CS43" t="n">
+        <v>71800</v>
+      </c>
+      <c r="CT43" t="n">
+        <v>54213.425</v>
+      </c>
+      <c r="CU43" t="n">
+        <v>41575.111</v>
+      </c>
+      <c r="CV43" t="n">
+        <v>98500</v>
+      </c>
+      <c r="CW43" t="n">
+        <v>36128.597</v>
+      </c>
+      <c r="CX43" t="n">
+        <v>168100</v>
+      </c>
+      <c r="CY43" t="n">
+        <v>159000</v>
+      </c>
+      <c r="CZ43" t="n">
+        <v>167660</v>
+      </c>
+      <c r="DA43" t="n">
+        <v>159650</v>
+      </c>
+      <c r="DB43" t="n">
+        <v>163500</v>
+      </c>
+      <c r="DC43" t="n">
+        <v>171910</v>
+      </c>
+      <c r="DD43" t="n">
+        <v>156100</v>
+      </c>
+      <c r="DE43" t="n">
+        <v>121370</v>
+      </c>
+      <c r="DF43" t="n">
+        <v>122820</v>
+      </c>
+      <c r="DG43" t="n">
+        <v>123200</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG42"/>
+  <dimension ref="A1:EZ42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -847,6 +847,361 @@
           <t>BPB7D</t>
         </is>
       </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>BYCHD</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>BACHD</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>CP38D</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>DNC7D</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>DNCAD</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>MR46D</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>IRCFD</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>IRCPD</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>RUCDD</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>EAC4D</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>MGCMD</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>MGCOD</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>MGCRD</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>PN43D</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>PLC5D</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>PLC4D</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>PLC7D</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>TTCDD</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>TLCMD</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>TLCTD</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>TSC3D</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>TSC4D</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>VSCVD</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>VSCTD</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>VSCXD</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>YMCID</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>YMCXD</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>YMCJD</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>YM34D</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>YFCJD</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>OLC5D</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>OLC6D</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>OLC7D</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>PN38D</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>PN41D</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>PN35D</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>PN36D</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>MGCQD</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>MGCTD</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>MCC1D</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>MCC3D</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>PLC6D</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>PLC2D</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>VSCRD</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>YM37D</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>YM38D</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>YMCYD</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>YM42D</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>YM43D</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>YM39D</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>BYCVD</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>BF37D</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>CICAD</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>HJCID</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>HJCLD</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>T662D</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>LOC5D</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>MIC6D</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>PFC2D</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>CACDD</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>NPCCD</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>NPCDD</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>OZC3D</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>DNC3D</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>DNC5D</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>DNCBD</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>TLCUD</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>TLCWD</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>CS52D</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>CS48D</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>CS47D</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -1077,6 +1432,153 @@
       <c r="CG2" t="n">
         <v>99.11999999999999</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>106</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>104</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>106</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>107</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>104</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>102</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>105</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>101</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>100</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>106</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>104</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>100</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1279,6 +1781,195 @@
       <c r="CG3" t="n">
         <v>100.7</v>
       </c>
+      <c r="CH3" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>114.05</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>99.99999999999999</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>105</v>
+      </c>
+      <c r="EB3" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EC3" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="ED3" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="EE3" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="EF3" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="EH3" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="EI3" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="EK3" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="EL3" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="EN3" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="EO3" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="EP3" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="EQ3" t="n">
+        <v>99.99999999999999</v>
+      </c>
+      <c r="ER3" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="ES3" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="ET3" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="EV3" t="n">
+        <v>103</v>
+      </c>
+      <c r="EX3" t="n">
+        <v>99.95000000000002</v>
+      </c>
+      <c r="EY3" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="EZ3" t="n">
+        <v>102.65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1481,6 +2172,192 @@
       <c r="CG4" t="n">
         <v>100.6</v>
       </c>
+      <c r="CH4" t="n">
+        <v>108</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>105</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>108</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>106</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>101</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>106</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>108</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>102.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1680,6 +2557,198 @@
       <c r="CG5" t="n">
         <v>100.55</v>
       </c>
+      <c r="CH5" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>111.05</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>107</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>108</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>106</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>99.95000000000002</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>103</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>99.74999999999999</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>105</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>99.99999999999999</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>102.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1903,6 +2972,195 @@
       <c r="CG6" t="n">
         <v>100.6</v>
       </c>
+      <c r="CH6" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>70.89</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>111</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>107</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>115</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>107</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>115</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>106</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>99.55000000000001</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>105</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>99.74999999999999</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2126,6 +3384,201 @@
       <c r="CG7" t="n">
         <v>100.75</v>
       </c>
+      <c r="CH7" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>111</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>107</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>115</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>106</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>99.57000000000001</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>105</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>100</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>99.94999999999999</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>102.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2349,6 +3802,198 @@
       <c r="CG8" t="n">
         <v>101.05</v>
       </c>
+      <c r="CH8" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>103</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>112.85</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>102</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>107</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>102.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2572,6 +4217,204 @@
       <c r="CG9" t="n">
         <v>101.1</v>
       </c>
+      <c r="CH9" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>108</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>109</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>114</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>108</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>104</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>100</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>102.6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2795,6 +4638,204 @@
       <c r="CG10" t="n">
         <v>101.7</v>
       </c>
+      <c r="CH10" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>105</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>115.15</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>111</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>112.95</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>105</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>108</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>107</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>104</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>105</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>113.15</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>103</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>98.26999999999998</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>102.95</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3015,6 +5056,201 @@
       <c r="CG11" t="n">
         <v>101.7</v>
       </c>
+      <c r="CH11" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>109</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>115.45</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>114</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>116.35</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>112</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>108</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>105</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>100</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>102.95</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3235,6 +5471,198 @@
       <c r="CG12" t="n">
         <v>102</v>
       </c>
+      <c r="CH12" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>108</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>106</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>99.95000000000002</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>101</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>100</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>100</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>103.15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3455,6 +5883,207 @@
       <c r="CG13" t="n">
         <v>101.95</v>
       </c>
+      <c r="CH13" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>71.06</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>111</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>112.05</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>106</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>101</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>100</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3675,6 +6304,207 @@
       <c r="CG14" t="n">
         <v>102.05</v>
       </c>
+      <c r="CH14" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>111</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>111.05</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>113</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>108</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>101</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>99.97999999999999</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>102</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>99.99999999999999</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>99.99999999999999</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>106</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>102</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>101</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>103.75</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3892,6 +6722,204 @@
       <c r="CG15" t="n">
         <v>101.85</v>
       </c>
+      <c r="CH15" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>108</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>71.73</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>109</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>115.55</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>106</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>107</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>108</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>108</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>102</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>105</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>99.75000000000001</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>102</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>102</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>106</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>101</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>100</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>107</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>103.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4124,6 +7152,207 @@
       <c r="CG16" t="n">
         <v>101.85</v>
       </c>
+      <c r="CH16" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>106</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>107</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>107</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>100</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>100</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>100</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>103.3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4570,6 +7799,204 @@
       <c r="CG18" t="n">
         <v>101.95</v>
       </c>
+      <c r="CH18" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>109</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>109</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>71.98</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>108</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>115.55</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>114</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>109</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>102</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>110</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>102</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>103</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>99.89999999999999</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>103.15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4802,6 +8229,204 @@
       <c r="CG19" t="n">
         <v>101.95</v>
       </c>
+      <c r="CH19" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>109</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>109</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>71.84</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>105</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>115.65</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>112</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>113</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>105</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>108</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>104</v>
+      </c>
+      <c r="DX19" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="DY19" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="DZ19" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="EB19" t="n">
+        <v>104</v>
+      </c>
+      <c r="EC19" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="ED19" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EE19" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="EF19" t="n">
+        <v>104</v>
+      </c>
+      <c r="EH19" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="EI19" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="EJ19" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="EK19" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="EL19" t="n">
+        <v>107</v>
+      </c>
+      <c r="EM19" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="EN19" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="EO19" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EP19" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="EQ19" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="ER19" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="ES19" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="ET19" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="EV19" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="EW19" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EX19" t="n">
+        <v>100</v>
+      </c>
+      <c r="EY19" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="EZ19" t="n">
+        <v>103.05</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5034,6 +8659,207 @@
       <c r="CG20" t="n">
         <v>101.9</v>
       </c>
+      <c r="CH20" t="n">
+        <v>108</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>107</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>71</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>111.05</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="CU20" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>108</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="DI20" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="DK20" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DL20" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DM20" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DN20" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="DO20" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="DP20" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="DQ20" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="DR20" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DS20" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DT20" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="DU20" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="DV20" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="DW20" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="DX20" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="DY20" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="DZ20" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EA20" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="EB20" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EC20" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="ED20" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EE20" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="EF20" t="n">
+        <v>104</v>
+      </c>
+      <c r="EG20" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="EH20" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="EI20" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="EJ20" t="n">
+        <v>101</v>
+      </c>
+      <c r="EK20" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="EL20" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="EM20" t="n">
+        <v>101</v>
+      </c>
+      <c r="EN20" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="EP20" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="EQ20" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="ER20" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="ES20" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="ET20" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="EV20" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EW20" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="EX20" t="n">
+        <v>98.61000000000001</v>
+      </c>
+      <c r="EY20" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="EZ20" t="n">
+        <v>103.4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5266,6 +9092,204 @@
       <c r="CG21" t="n">
         <v>101.8</v>
       </c>
+      <c r="CH21" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>107</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="CQ21" t="n">
+        <v>103</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="CU21" t="n">
+        <v>111</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="CY21" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="DA21" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="DB21" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="DC21" t="n">
+        <v>108</v>
+      </c>
+      <c r="DD21" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>108</v>
+      </c>
+      <c r="DF21" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="DH21" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="DI21" t="n">
+        <v>107</v>
+      </c>
+      <c r="DJ21" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="DK21" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DL21" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DM21" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="DN21" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="DO21" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DP21" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="DQ21" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="DR21" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DS21" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DT21" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="DU21" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DV21" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="DW21" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="DX21" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="DY21" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="DZ21" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EA21" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="EB21" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EC21" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="ED21" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="EE21" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="EF21" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EH21" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EI21" t="n">
+        <v>102</v>
+      </c>
+      <c r="EJ21" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="EK21" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="EL21" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="EM21" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="EN21" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EP21" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="EQ21" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="ER21" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="ES21" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="ET21" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="EV21" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EW21" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="EX21" t="n">
+        <v>100</v>
+      </c>
+      <c r="EY21" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="EZ21" t="n">
+        <v>103.4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5498,6 +9522,207 @@
       <c r="CG22" t="n">
         <v>101.85</v>
       </c>
+      <c r="CH22" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="CI22" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="CJ22" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>109</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="CN22" t="n">
+        <v>51.24999999999999</v>
+      </c>
+      <c r="CO22" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="CP22" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="CQ22" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="CR22" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="CS22" t="n">
+        <v>108</v>
+      </c>
+      <c r="CT22" t="n">
+        <v>107</v>
+      </c>
+      <c r="CU22" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="CV22" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="CW22" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="CY22" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="CZ22" t="n">
+        <v>115.55</v>
+      </c>
+      <c r="DA22" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="DC22" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="DF22" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="DI22" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="DJ22" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="DK22" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DL22" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="DM22" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="DN22" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DO22" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="DP22" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="DQ22" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="DR22" t="n">
+        <v>108</v>
+      </c>
+      <c r="DS22" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DT22" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DU22" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="DV22" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="DW22" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="DX22" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="DY22" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="DZ22" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EA22" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="EB22" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EC22" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="ED22" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="EE22" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="EF22" t="n">
+        <v>103</v>
+      </c>
+      <c r="EH22" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="EI22" t="n">
+        <v>102</v>
+      </c>
+      <c r="EJ22" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="EK22" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="EL22" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="EM22" t="n">
+        <v>99.90000000000002</v>
+      </c>
+      <c r="EN22" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="EO22" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EP22" t="n">
+        <v>108</v>
+      </c>
+      <c r="EQ22" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="ER22" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="ES22" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="ET22" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="EV22" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EW22" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="EX22" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="EY22" t="n">
+        <v>108</v>
+      </c>
+      <c r="EZ22" t="n">
+        <v>103.55</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5730,6 +9955,207 @@
       <c r="CG23" t="n">
         <v>101.85</v>
       </c>
+      <c r="CH23" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="CI23" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="CJ23" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CK23" t="n">
+        <v>109</v>
+      </c>
+      <c r="CL23" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="CN23" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="CO23" t="n">
+        <v>109</v>
+      </c>
+      <c r="CP23" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="CQ23" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="CR23" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="CS23" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="CT23" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="CU23" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="CV23" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="CW23" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="CY23" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CZ23" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="DA23" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DJ23" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="DK23" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="DL23" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="DM23" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="DN23" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="DO23" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DP23" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DQ23" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="DR23" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="DS23" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DT23" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="DU23" t="n">
+        <v>105</v>
+      </c>
+      <c r="DV23" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="DW23" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DX23" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="DY23" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="DZ23" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EA23" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EB23" t="n">
+        <v>104</v>
+      </c>
+      <c r="EC23" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="ED23" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="EE23" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="EF23" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EH23" t="n">
+        <v>102</v>
+      </c>
+      <c r="EI23" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="EJ23" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="EK23" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="EL23" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="EM23" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="EN23" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="EO23" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="EP23" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="EQ23" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="ER23" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="ES23" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="ET23" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="EV23" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EW23" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EX23" t="n">
+        <v>99</v>
+      </c>
+      <c r="EY23" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="EZ23" t="n">
+        <v>103.15</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5962,6 +10388,207 @@
       <c r="CG24" t="n">
         <v>102.2</v>
       </c>
+      <c r="CI24" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="CJ24" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="CK24" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="CL24" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="CN24" t="n">
+        <v>51</v>
+      </c>
+      <c r="CO24" t="n">
+        <v>109</v>
+      </c>
+      <c r="CP24" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="CQ24" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="CR24" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="CS24" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="CT24" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="CU24" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="CV24" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="CW24" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="CY24" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="CZ24" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="DA24" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="DB24" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="DC24" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DD24" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="DE24" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DF24" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="DG24" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="DH24" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="DI24" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="DJ24" t="n">
+        <v>112</v>
+      </c>
+      <c r="DK24" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DL24" t="n">
+        <v>108</v>
+      </c>
+      <c r="DM24" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DN24" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DO24" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="DP24" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="DQ24" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="DR24" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DS24" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="DT24" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="DU24" t="n">
+        <v>105</v>
+      </c>
+      <c r="DV24" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="DW24" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DX24" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DY24" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="DZ24" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EA24" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="EB24" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EC24" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="ED24" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EE24" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="EF24" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EG24" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="EH24" t="n">
+        <v>101</v>
+      </c>
+      <c r="EI24" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EJ24" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="EK24" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="EL24" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="EM24" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="EN24" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="EO24" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="EP24" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="EQ24" t="n">
+        <v>101</v>
+      </c>
+      <c r="ER24" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="ES24" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="ET24" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="EV24" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EW24" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="EX24" t="n">
+        <v>98.99999999999999</v>
+      </c>
+      <c r="EY24" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="EZ24" t="n">
+        <v>103.6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6194,6 +10821,210 @@
       <c r="CG25" t="n">
         <v>102.25</v>
       </c>
+      <c r="CH25" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CI25" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="CJ25" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="CL25" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="CM25" t="n">
+        <v>74</v>
+      </c>
+      <c r="CN25" t="n">
+        <v>50.52999999999999</v>
+      </c>
+      <c r="CO25" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="CP25" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="CQ25" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="CR25" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="CS25" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="CT25" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="CU25" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="CV25" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="CW25" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CY25" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="CZ25" t="n">
+        <v>116</v>
+      </c>
+      <c r="DA25" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DB25" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="DC25" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DD25" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="DE25" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="DF25" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DG25" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="DH25" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="DI25" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="DJ25" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="DK25" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DL25" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="DM25" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="DN25" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="DO25" t="n">
+        <v>108</v>
+      </c>
+      <c r="DP25" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DQ25" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="DR25" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="DS25" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DT25" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="DU25" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DV25" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="DW25" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DX25" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DY25" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DZ25" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EA25" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EB25" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="EC25" t="n">
+        <v>105</v>
+      </c>
+      <c r="ED25" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="EE25" t="n">
+        <v>114</v>
+      </c>
+      <c r="EF25" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EH25" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="EI25" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="EJ25" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EK25" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EL25" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="EM25" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="EN25" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="EO25" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="EP25" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="EQ25" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="ER25" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="ES25" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="ET25" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="EV25" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EW25" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EX25" t="n">
+        <v>100</v>
+      </c>
+      <c r="EY25" t="n">
+        <v>108</v>
+      </c>
+      <c r="EZ25" t="n">
+        <v>103.75</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6426,6 +11257,207 @@
       <c r="CG26" t="n">
         <v>102</v>
       </c>
+      <c r="CH26" t="n">
+        <v>108</v>
+      </c>
+      <c r="CI26" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="CJ26" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="CL26" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="CM26" t="n">
+        <v>82.04000000000001</v>
+      </c>
+      <c r="CN26" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="CO26" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="CP26" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="CQ26" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="CR26" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="CS26" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CT26" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="CU26" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="CV26" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="CW26" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CY26" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="CZ26" t="n">
+        <v>115.95</v>
+      </c>
+      <c r="DA26" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="DC26" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DD26" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="DE26" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="DF26" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="DG26" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="DH26" t="n">
+        <v>113</v>
+      </c>
+      <c r="DI26" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="DJ26" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="DK26" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DL26" t="n">
+        <v>105</v>
+      </c>
+      <c r="DM26" t="n">
+        <v>106</v>
+      </c>
+      <c r="DN26" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="DO26" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="DP26" t="n">
+        <v>109</v>
+      </c>
+      <c r="DQ26" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="DR26" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="DS26" t="n">
+        <v>108</v>
+      </c>
+      <c r="DT26" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="DU26" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="DV26" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="DW26" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DX26" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="DY26" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DZ26" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EA26" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EB26" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EC26" t="n">
+        <v>105</v>
+      </c>
+      <c r="ED26" t="n">
+        <v>100</v>
+      </c>
+      <c r="EE26" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="EF26" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EH26" t="n">
+        <v>102</v>
+      </c>
+      <c r="EI26" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="EJ26" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="EK26" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="EL26" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="EM26" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="EN26" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="EO26" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EP26" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="EQ26" t="n">
+        <v>101</v>
+      </c>
+      <c r="ER26" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="ES26" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="ET26" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="EV26" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EW26" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="EY26" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="EZ26" t="n">
+        <v>103.3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6646,6 +11678,213 @@
       <c r="CG27" t="n">
         <v>101.95</v>
       </c>
+      <c r="CH27" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="CI27" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="CJ27" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="CK27" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="CL27" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="CM27" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="CN27" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="CO27" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="CP27" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="CQ27" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="CR27" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="CS27" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="CT27" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="CU27" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="CV27" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="CW27" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CY27" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="CZ27" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="DA27" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="DB27" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="DC27" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DD27" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="DE27" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="DF27" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="DG27" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="DH27" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="DI27" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="DJ27" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DK27" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="DL27" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="DM27" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="DN27" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="DO27" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DP27" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="DQ27" t="n">
+        <v>107</v>
+      </c>
+      <c r="DR27" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="DS27" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DT27" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="DU27" t="n">
+        <v>104</v>
+      </c>
+      <c r="DV27" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="DW27" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="DX27" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="DY27" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="DZ27" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EA27" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="EB27" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="EC27" t="n">
+        <v>106</v>
+      </c>
+      <c r="ED27" t="n">
+        <v>101</v>
+      </c>
+      <c r="EE27" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="EF27" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="EG27" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="EH27" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="EI27" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EJ27" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="EK27" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EL27" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="EM27" t="n">
+        <v>100</v>
+      </c>
+      <c r="EN27" t="n">
+        <v>106</v>
+      </c>
+      <c r="EO27" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EP27" t="n">
+        <v>109</v>
+      </c>
+      <c r="EQ27" t="n">
+        <v>101</v>
+      </c>
+      <c r="ER27" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="ES27" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="ET27" t="n">
+        <v>109</v>
+      </c>
+      <c r="EV27" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EW27" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EX27" t="n">
+        <v>98.16999999999999</v>
+      </c>
+      <c r="EY27" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="EZ27" t="n">
+        <v>104.3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6878,6 +12117,207 @@
       <c r="CG28" t="n">
         <v>101.8</v>
       </c>
+      <c r="CH28" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="CI28" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="CJ28" t="n">
+        <v>107</v>
+      </c>
+      <c r="CK28" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="CL28" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="CM28" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="CN28" t="n">
+        <v>50.92000000000001</v>
+      </c>
+      <c r="CO28" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="CP28" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="CQ28" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="CR28" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="CS28" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="CT28" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="CU28" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="CV28" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="CW28" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="CY28" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="CZ28" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="DA28" t="n">
+        <v>112</v>
+      </c>
+      <c r="DB28" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="DC28" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DD28" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="DE28" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DF28" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="DG28" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="DH28" t="n">
+        <v>113</v>
+      </c>
+      <c r="DI28" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="DJ28" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="DK28" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="DL28" t="n">
+        <v>106</v>
+      </c>
+      <c r="DM28" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="DN28" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="DO28" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DP28" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DQ28" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="DR28" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DS28" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DT28" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="DU28" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="DV28" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="DW28" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DX28" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DY28" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DZ28" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="EA28" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EB28" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="EC28" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="ED28" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="EE28" t="n">
+        <v>114.05</v>
+      </c>
+      <c r="EG28" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="EH28" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="EI28" t="n">
+        <v>103</v>
+      </c>
+      <c r="EJ28" t="n">
+        <v>100</v>
+      </c>
+      <c r="EK28" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="EL28" t="n">
+        <v>107</v>
+      </c>
+      <c r="EM28" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="EN28" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EO28" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="EP28" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="EQ28" t="n">
+        <v>101</v>
+      </c>
+      <c r="ER28" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="ES28" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="ET28" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="EV28" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EW28" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="EY28" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="EZ28" t="n">
+        <v>103.6</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7110,6 +12550,213 @@
       <c r="CG29" t="n">
         <v>102.1</v>
       </c>
+      <c r="CH29" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="CI29" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="CJ29" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="CM29" t="n">
+        <v>85</v>
+      </c>
+      <c r="CN29" t="n">
+        <v>51</v>
+      </c>
+      <c r="CO29" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="CP29" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="CQ29" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="CR29" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="CS29" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="CT29" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="CU29" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="CW29" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="CX29" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="CY29" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CZ29" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="DA29" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="DC29" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="DE29" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="DF29" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DG29" t="n">
+        <v>92.44999999999999</v>
+      </c>
+      <c r="DH29" t="n">
+        <v>114</v>
+      </c>
+      <c r="DI29" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="DJ29" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="DK29" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DL29" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="DM29" t="n">
+        <v>106</v>
+      </c>
+      <c r="DN29" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DO29" t="n">
+        <v>109</v>
+      </c>
+      <c r="DP29" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="DQ29" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="DR29" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DS29" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="DT29" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="DU29" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="DV29" t="n">
+        <v>101</v>
+      </c>
+      <c r="DW29" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="DX29" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="DY29" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DZ29" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="EA29" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EB29" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="EC29" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="ED29" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="EE29" t="n">
+        <v>114.05</v>
+      </c>
+      <c r="EF29" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="EH29" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="EI29" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="EJ29" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EK29" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="EL29" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="EM29" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EN29" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="EO29" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="EP29" t="n">
+        <v>109</v>
+      </c>
+      <c r="EQ29" t="n">
+        <v>101</v>
+      </c>
+      <c r="ER29" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="ES29" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="ET29" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="EV29" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="EW29" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="EX29" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="EY29" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="EZ29" t="n">
+        <v>103.85</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7342,6 +12989,216 @@
       <c r="CG30" t="n">
         <v>102</v>
       </c>
+      <c r="CH30" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="CI30" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="CJ30" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="CN30" t="n">
+        <v>50.74999999999999</v>
+      </c>
+      <c r="CO30" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="CP30" t="n">
+        <v>107</v>
+      </c>
+      <c r="CQ30" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="CW30" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="CX30" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="CY30" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CZ30" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="DE30" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DF30" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>113</v>
+      </c>
+      <c r="DI30" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="DJ30" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="DK30" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="DL30" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="DM30" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="DN30" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="DO30" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DP30" t="n">
+        <v>109</v>
+      </c>
+      <c r="DQ30" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="DR30" t="n">
+        <v>108</v>
+      </c>
+      <c r="DS30" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="DT30" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="DU30" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DV30" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="DW30" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DX30" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DY30" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="DZ30" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="EA30" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="EB30" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="EC30" t="n">
+        <v>106</v>
+      </c>
+      <c r="ED30" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="EE30" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="EF30" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EG30" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="EH30" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="EI30" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EJ30" t="n">
+        <v>101</v>
+      </c>
+      <c r="EK30" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="EL30" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="EM30" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="EN30" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="EO30" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="EP30" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="EQ30" t="n">
+        <v>101</v>
+      </c>
+      <c r="ER30" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="ES30" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="ET30" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="EV30" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EW30" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="EX30" t="n">
+        <v>99.69999999999999</v>
+      </c>
+      <c r="EY30" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="EZ30" t="n">
+        <v>103.8</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7574,6 +13431,219 @@
       <c r="CG31" t="n">
         <v>101.95</v>
       </c>
+      <c r="CH31" t="n">
+        <v>108</v>
+      </c>
+      <c r="CI31" t="n">
+        <v>110</v>
+      </c>
+      <c r="CJ31" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="CK31" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="CL31" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="CM31" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="CN31" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="CO31" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="CP31" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="CQ31" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="CR31" t="n">
+        <v>112</v>
+      </c>
+      <c r="CS31" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="CT31" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="CU31" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="CV31" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="CW31" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="CX31" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="CY31" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CZ31" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="DA31" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="DB31" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="DC31" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DD31" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DE31" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DF31" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="DG31" t="n">
+        <v>95.39</v>
+      </c>
+      <c r="DH31" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="DI31" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DJ31" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="DK31" t="n">
+        <v>108</v>
+      </c>
+      <c r="DL31" t="n">
+        <v>107</v>
+      </c>
+      <c r="DM31" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DN31" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="DO31" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DP31" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DQ31" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="DR31" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DS31" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="DT31" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="DU31" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="DV31" t="n">
+        <v>101</v>
+      </c>
+      <c r="DW31" t="n">
+        <v>105</v>
+      </c>
+      <c r="DX31" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="DY31" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="DZ31" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="EA31" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="EB31" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EC31" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="ED31" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="EE31" t="n">
+        <v>114.05</v>
+      </c>
+      <c r="EF31" t="n">
+        <v>103</v>
+      </c>
+      <c r="EG31" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="EH31" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="EI31" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="EJ31" t="n">
+        <v>100</v>
+      </c>
+      <c r="EK31" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EL31" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="EM31" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EN31" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="EO31" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="EP31" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="EQ31" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="ER31" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="ES31" t="n">
+        <v>103</v>
+      </c>
+      <c r="ET31" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="EU31" t="n">
+        <v>100</v>
+      </c>
+      <c r="EV31" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EW31" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="EX31" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="EY31" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="EZ31" t="n">
+        <v>103.8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7806,6 +13876,219 @@
       <c r="CG32" t="n">
         <v>101.95</v>
       </c>
+      <c r="CH32" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="CI32" t="n">
+        <v>110</v>
+      </c>
+      <c r="CJ32" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="CK32" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="CL32" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="CM32" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="CN32" t="n">
+        <v>50.90999999999999</v>
+      </c>
+      <c r="CO32" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="CP32" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CQ32" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="CR32" t="n">
+        <v>111.05</v>
+      </c>
+      <c r="CS32" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="CT32" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="CU32" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="CV32" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CW32" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="CX32" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="CY32" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="CZ32" t="n">
+        <v>117</v>
+      </c>
+      <c r="DA32" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="DB32" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="DC32" t="n">
+        <v>108</v>
+      </c>
+      <c r="DD32" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="DE32" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="DF32" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="DG32" t="n">
+        <v>93.70000000000002</v>
+      </c>
+      <c r="DH32" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="DI32" t="n">
+        <v>107</v>
+      </c>
+      <c r="DJ32" t="n">
+        <v>112</v>
+      </c>
+      <c r="DK32" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DL32" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="DM32" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DN32" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="DO32" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DP32" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="DQ32" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="DR32" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DS32" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DT32" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="DU32" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DV32" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="DW32" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="DX32" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="DY32" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DZ32" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EA32" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EB32" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="EC32" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="ED32" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="EE32" t="n">
+        <v>114</v>
+      </c>
+      <c r="EF32" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EG32" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EH32" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="EI32" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EJ32" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="EK32" t="n">
+        <v>102</v>
+      </c>
+      <c r="EL32" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="EM32" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="EN32" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="EO32" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="EP32" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="EQ32" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="ER32" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="ES32" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="ET32" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="EU32" t="n">
+        <v>99.99000000000001</v>
+      </c>
+      <c r="EV32" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EW32" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="EX32" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="EY32" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="EZ32" t="n">
+        <v>103.45</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8038,6 +14321,213 @@
       <c r="CG33" t="n">
         <v>101.9</v>
       </c>
+      <c r="CH33" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>110</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>51.04999999999999</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>112</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="CY33" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="CZ33" t="n">
+        <v>116.05</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="DB33" t="n">
+        <v>113</v>
+      </c>
+      <c r="DC33" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="DD33" t="n">
+        <v>111</v>
+      </c>
+      <c r="DE33" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DF33" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DG33" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="DH33" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="DI33" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DJ33" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="DK33" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DL33" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="DM33" t="n">
+        <v>106</v>
+      </c>
+      <c r="DN33" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="DO33" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DP33" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DQ33" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DR33" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DS33" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="DT33" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="DU33" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="DV33" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="DW33" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="DX33" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="DY33" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DZ33" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EA33" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="EB33" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="EC33" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="ED33" t="n">
+        <v>101</v>
+      </c>
+      <c r="EE33" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="EF33" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EH33" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EI33" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EJ33" t="n">
+        <v>100</v>
+      </c>
+      <c r="EK33" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EL33" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="EM33" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="EN33" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="EO33" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="EP33" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="EQ33" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="ER33" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="ES33" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="ET33" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="EU33" t="n">
+        <v>99.89</v>
+      </c>
+      <c r="EV33" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EW33" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="EY33" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="EZ33" t="n">
+        <v>103.8</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8270,6 +14760,219 @@
       <c r="CG34" t="n">
         <v>101.85</v>
       </c>
+      <c r="CH34" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="CI34" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="CJ34" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="CK34" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="CL34" t="n">
+        <v>106</v>
+      </c>
+      <c r="CM34" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="CN34" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="CO34" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="CP34" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="CQ34" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="CR34" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="CS34" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CT34" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="CU34" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="CV34" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="CW34" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="CX34" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="CY34" t="n">
+        <v>108</v>
+      </c>
+      <c r="CZ34" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DB34" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="DC34" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DD34" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="DE34" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DF34" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DG34" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="DH34" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="DI34" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="DJ34" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="DK34" t="n">
+        <v>108</v>
+      </c>
+      <c r="DL34" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="DM34" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="DN34" t="n">
+        <v>105</v>
+      </c>
+      <c r="DO34" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="DP34" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DQ34" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="DR34" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DS34" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DT34" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="DU34" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="DV34" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="DW34" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DX34" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="DY34" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="DZ34" t="n">
+        <v>104</v>
+      </c>
+      <c r="EA34" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="EB34" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="EC34" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="ED34" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="EE34" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="EF34" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EG34" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EH34" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EI34" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EJ34" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EK34" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="EL34" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="EM34" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="EN34" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="EO34" t="n">
+        <v>103</v>
+      </c>
+      <c r="EP34" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="EQ34" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="ER34" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="ES34" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="ET34" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="EU34" t="n">
+        <v>100</v>
+      </c>
+      <c r="EV34" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="EW34" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="EX34" t="n">
+        <v>99.79999999999998</v>
+      </c>
+      <c r="EY34" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EZ34" t="n">
+        <v>103.4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8716,6 +15419,171 @@
       <c r="CG36" t="n">
         <v>102</v>
       </c>
+      <c r="CH36" t="n">
+        <v>108</v>
+      </c>
+      <c r="CJ36" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="CK36" t="n">
+        <v>109</v>
+      </c>
+      <c r="CL36" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="CM36" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="CN36" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="CO36" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="CP36" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="CQ36" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="CT36" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="CU36" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="CV36" t="n">
+        <v>108</v>
+      </c>
+      <c r="CW36" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="CX36" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="CZ36" t="n">
+        <v>117</v>
+      </c>
+      <c r="DA36" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="DC36" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="DD36" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DF36" t="n">
+        <v>109</v>
+      </c>
+      <c r="DG36" t="n">
+        <v>92.90000000000002</v>
+      </c>
+      <c r="DH36" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="DI36" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="DJ36" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="DK36" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DL36" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DM36" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="DN36" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="DP36" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DQ36" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="DR36" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DS36" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="DT36" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="DU36" t="n">
+        <v>105</v>
+      </c>
+      <c r="DV36" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="DX36" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DY36" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="DZ36" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="EA36" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="EB36" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EC36" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="ED36" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="EE36" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="EH36" t="n">
+        <v>103</v>
+      </c>
+      <c r="EJ36" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="EL36" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="EM36" t="n">
+        <v>100</v>
+      </c>
+      <c r="EO36" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EP36" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="EQ36" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="ER36" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="ES36" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="ET36" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="EU36" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="EY36" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="EZ36" t="n">
+        <v>103.8</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8948,6 +15816,216 @@
       <c r="CG37" t="n">
         <v>101.95</v>
       </c>
+      <c r="CH37" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="CI37" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="CJ37" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="CK37" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="CL37" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="CM37" t="n">
+        <v>84.81999999999999</v>
+      </c>
+      <c r="CN37" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="CO37" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="CP37" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CQ37" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="CR37" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="CS37" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CT37" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="CU37" t="n">
+        <v>111</v>
+      </c>
+      <c r="CV37" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CW37" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="CX37" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="CY37" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="CZ37" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="DA37" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="DB37" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="DC37" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DD37" t="n">
+        <v>110</v>
+      </c>
+      <c r="DE37" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DF37" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DG37" t="n">
+        <v>93.29000000000001</v>
+      </c>
+      <c r="DH37" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="DI37" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DJ37" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="DK37" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DL37" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="DM37" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="DN37" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DO37" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="DP37" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="DQ37" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DR37" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DS37" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="DT37" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DU37" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DV37" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="DW37" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="DX37" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="DY37" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="DZ37" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="EA37" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="EB37" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="EC37" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="ED37" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="EE37" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="EF37" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EG37" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EH37" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EI37" t="n">
+        <v>103</v>
+      </c>
+      <c r="EJ37" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="EK37" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EL37" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="EM37" t="n">
+        <v>100</v>
+      </c>
+      <c r="EO37" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EP37" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="EQ37" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="ER37" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="ES37" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="ET37" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="EU37" t="n">
+        <v>99.93999999999998</v>
+      </c>
+      <c r="EV37" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="EW37" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="EX37" t="n">
+        <v>100</v>
+      </c>
+      <c r="EY37" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="EZ37" t="n">
+        <v>103.65</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9180,6 +16258,216 @@
       <c r="CG38" t="n">
         <v>102</v>
       </c>
+      <c r="CH38" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="CI38" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="CJ38" t="n">
+        <v>107</v>
+      </c>
+      <c r="CK38" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="CL38" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="CM38" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="CN38" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="CO38" t="n">
+        <v>110</v>
+      </c>
+      <c r="CP38" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="CQ38" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="CR38" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="CS38" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="CT38" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="CU38" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="CV38" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="CW38" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="CX38" t="n">
+        <v>102</v>
+      </c>
+      <c r="CY38" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="CZ38" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="DA38" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="DB38" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="DC38" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DD38" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="DE38" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DF38" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="DG38" t="n">
+        <v>93</v>
+      </c>
+      <c r="DH38" t="n">
+        <v>113.15</v>
+      </c>
+      <c r="DI38" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DJ38" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="DK38" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DL38" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="DM38" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="DN38" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="DO38" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DP38" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="DQ38" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DR38" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="DS38" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="DT38" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="DU38" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="DV38" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="DW38" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="DX38" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="DY38" t="n">
+        <v>109</v>
+      </c>
+      <c r="DZ38" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EA38" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="EB38" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="EC38" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="ED38" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="EE38" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="EF38" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EH38" t="n">
+        <v>102</v>
+      </c>
+      <c r="EI38" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EJ38" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="EK38" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="EL38" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="EM38" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="EN38" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="EO38" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EP38" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="EQ38" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="ER38" t="n">
+        <v>102</v>
+      </c>
+      <c r="ES38" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="ET38" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="EU38" t="n">
+        <v>100</v>
+      </c>
+      <c r="EV38" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="EW38" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="EX38" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="EY38" t="n">
+        <v>105</v>
+      </c>
+      <c r="EZ38" t="n">
+        <v>103.9</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9412,6 +16700,216 @@
       <c r="CG39" t="n">
         <v>102.15</v>
       </c>
+      <c r="CH39" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="CI39" t="n">
+        <v>111</v>
+      </c>
+      <c r="CJ39" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="CK39" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="CL39" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="CM39" t="n">
+        <v>84.56</v>
+      </c>
+      <c r="CN39" t="n">
+        <v>51.47999999999999</v>
+      </c>
+      <c r="CO39" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="CP39" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="CQ39" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="CR39" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="CS39" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="CT39" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="CU39" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CV39" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="CW39" t="n">
+        <v>110</v>
+      </c>
+      <c r="CX39" t="n">
+        <v>102</v>
+      </c>
+      <c r="CY39" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="CZ39" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="DA39" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="DB39" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="DC39" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DD39" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="DE39" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="DF39" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DG39" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="DH39" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="DI39" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DJ39" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="DK39" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="DL39" t="n">
+        <v>107</v>
+      </c>
+      <c r="DM39" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="DN39" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="DO39" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DP39" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DQ39" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DR39" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DS39" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="DT39" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DV39" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="DW39" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DX39" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DY39" t="n">
+        <v>110</v>
+      </c>
+      <c r="DZ39" t="n">
+        <v>104</v>
+      </c>
+      <c r="EA39" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="EB39" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="EC39" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="ED39" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="EE39" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="EF39" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EG39" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EH39" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EI39" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="EJ39" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EK39" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="EL39" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="EM39" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="EN39" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="EO39" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EP39" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="EQ39" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="ER39" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="ES39" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="ET39" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="EU39" t="n">
+        <v>100</v>
+      </c>
+      <c r="EV39" t="n">
+        <v>105</v>
+      </c>
+      <c r="EW39" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="EX39" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="EY39" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="EZ39" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9641,6 +17139,216 @@
       <c r="CG40" t="n">
         <v>102.35</v>
       </c>
+      <c r="CH40" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="CI40" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="CJ40" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="CK40" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="CL40" t="n">
+        <v>106</v>
+      </c>
+      <c r="CM40" t="n">
+        <v>85</v>
+      </c>
+      <c r="CN40" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="CO40" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="CP40" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="CQ40" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="CR40" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="CS40" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="CT40" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="CU40" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="CW40" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="CX40" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="CY40" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="CZ40" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="DA40" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="DB40" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="DC40" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="DD40" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="DE40" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="DF40" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="DG40" t="n">
+        <v>93.06999999999998</v>
+      </c>
+      <c r="DH40" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="DI40" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DJ40" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DK40" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="DL40" t="n">
+        <v>106</v>
+      </c>
+      <c r="DM40" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DN40" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DO40" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DP40" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="DQ40" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DR40" t="n">
+        <v>109</v>
+      </c>
+      <c r="DS40" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="DT40" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DU40" t="n">
+        <v>105</v>
+      </c>
+      <c r="DV40" t="n">
+        <v>102</v>
+      </c>
+      <c r="DW40" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DX40" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DY40" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="DZ40" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="EA40" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="EB40" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="EC40" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="ED40" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="EE40" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="EF40" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EH40" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="EI40" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="EJ40" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="EK40" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="EL40" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="EM40" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="EN40" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="EO40" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="EP40" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="EQ40" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="ER40" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="ES40" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="ET40" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="EU40" t="n">
+        <v>100</v>
+      </c>
+      <c r="EV40" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="EW40" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="EX40" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="EY40" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EZ40" t="n">
+        <v>103.95</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9876,6 +17584,219 @@
       <c r="CG41" t="n">
         <v>102.4</v>
       </c>
+      <c r="CH41" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="CI41" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="CJ41" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CK41" t="n">
+        <v>110</v>
+      </c>
+      <c r="CL41" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="CM41" t="n">
+        <v>85.45999999999999</v>
+      </c>
+      <c r="CN41" t="n">
+        <v>51.20999999999999</v>
+      </c>
+      <c r="CO41" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="CP41" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="CQ41" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="CR41" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="CS41" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="CT41" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="CU41" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="CV41" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="CW41" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="CX41" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="CY41" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="CZ41" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="DA41" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DB41" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="DC41" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="DD41" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="DE41" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="DF41" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DG41" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="DH41" t="n">
+        <v>114</v>
+      </c>
+      <c r="DI41" t="n">
+        <v>108</v>
+      </c>
+      <c r="DJ41" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DK41" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DL41" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="DM41" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="DN41" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="DO41" t="n">
+        <v>109</v>
+      </c>
+      <c r="DP41" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="DQ41" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DR41" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DS41" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="DT41" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DU41" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="DV41" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DW41" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="DX41" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="DY41" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DZ41" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="EA41" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="EB41" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EC41" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="ED41" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="EE41" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="EF41" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EG41" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EH41" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="EI41" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="EJ41" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="EK41" t="n">
+        <v>102</v>
+      </c>
+      <c r="EL41" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="EM41" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="EN41" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="EO41" t="n">
+        <v>103</v>
+      </c>
+      <c r="EP41" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="EQ41" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="ER41" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="ES41" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="ET41" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="EU41" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="EV41" t="n">
+        <v>105</v>
+      </c>
+      <c r="EW41" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="EX41" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="EY41" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EZ41" t="n">
+        <v>104.3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -10107,6 +18028,219 @@
       </c>
       <c r="CG42" t="n">
         <v>102.9</v>
+      </c>
+      <c r="CH42" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="CI42" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="CJ42" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="CK42" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="CL42" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="CM42" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="CN42" t="n">
+        <v>51.39999999999999</v>
+      </c>
+      <c r="CO42" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="CP42" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="CQ42" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="CR42" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="CS42" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="CT42" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="CU42" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="CV42" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="CW42" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="CX42" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="CY42" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="CZ42" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="DA42" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="DB42" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="DC42" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="DD42" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="DE42" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="DF42" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DG42" t="n">
+        <v>93.00000000000001</v>
+      </c>
+      <c r="DH42" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="DI42" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DJ42" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="DK42" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DL42" t="n">
+        <v>106</v>
+      </c>
+      <c r="DM42" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="DN42" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="DO42" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="DP42" t="n">
+        <v>110</v>
+      </c>
+      <c r="DQ42" t="n">
+        <v>108</v>
+      </c>
+      <c r="DR42" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="DS42" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="DT42" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DU42" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="DV42" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="DW42" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="DX42" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DY42" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="DZ42" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="EA42" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="EB42" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EC42" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="ED42" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="EE42" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="EF42" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EG42" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EH42" t="n">
+        <v>102</v>
+      </c>
+      <c r="EI42" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EJ42" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="EK42" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EL42" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="EM42" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="EN42" t="n">
+        <v>103</v>
+      </c>
+      <c r="EO42" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="EP42" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="EQ42" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="ER42" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="ES42" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="ET42" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="EU42" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="EV42" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="EW42" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="EX42" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="EY42" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="EZ42" t="n">
+        <v>105.5</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FZ43"/>
+  <dimension ref="A1:FZ44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18875,6 +18875,508 @@
         <v>105.15</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>117.154</v>
+      </c>
+      <c r="G44" t="n">
+        <v>106.592</v>
+      </c>
+      <c r="H44" t="n">
+        <v>124.18</v>
+      </c>
+      <c r="I44" t="n">
+        <v>112.63</v>
+      </c>
+      <c r="J44" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="K44" t="n">
+        <v>119.65</v>
+      </c>
+      <c r="L44" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>131.498</v>
+      </c>
+      <c r="N44" t="n">
+        <v>124.099</v>
+      </c>
+      <c r="O44" t="n">
+        <v>125.65</v>
+      </c>
+      <c r="P44" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="S44" t="n">
+        <v>166.75</v>
+      </c>
+      <c r="T44" t="n">
+        <v>293.35</v>
+      </c>
+      <c r="U44" t="n">
+        <v>216.45</v>
+      </c>
+      <c r="V44" t="n">
+        <v>119.6</v>
+      </c>
+      <c r="W44" t="n">
+        <v>386.45</v>
+      </c>
+      <c r="X44" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>270.85</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>345.2</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>146900</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>144390</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>126290</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>55.38000000000001</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>81.34</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>56</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>93.64999999999999</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>91.04000000000001</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>164.35</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>103.73</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>147450</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>144800</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>146900</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>120100</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>92.05</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>85</v>
+      </c>
+      <c r="BU44" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="BV44" t="n">
+        <v>102.115</v>
+      </c>
+      <c r="BW44" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="BX44" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="BY44" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="BZ44" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA44" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="CB44" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="CC44" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="CE44" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="CF44" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="CG44" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="CH44" t="n">
+        <v>32014.25</v>
+      </c>
+      <c r="CM44" t="n">
+        <v>60850</v>
+      </c>
+      <c r="CN44" t="n">
+        <v>29754.62</v>
+      </c>
+      <c r="CQ44" t="n">
+        <v>74400</v>
+      </c>
+      <c r="CS44" t="n">
+        <v>71900</v>
+      </c>
+      <c r="CT44" t="n">
+        <v>54213.425</v>
+      </c>
+      <c r="CU44" t="n">
+        <v>41575.111</v>
+      </c>
+      <c r="CV44" t="n">
+        <v>97710</v>
+      </c>
+      <c r="CW44" t="n">
+        <v>36128.597</v>
+      </c>
+      <c r="CX44" t="n">
+        <v>168850</v>
+      </c>
+      <c r="CY44" t="n">
+        <v>160350</v>
+      </c>
+      <c r="CZ44" t="n">
+        <v>168350</v>
+      </c>
+      <c r="DA44" t="n">
+        <v>159500</v>
+      </c>
+      <c r="DB44" t="n">
+        <v>164000</v>
+      </c>
+      <c r="DC44" t="n">
+        <v>171200</v>
+      </c>
+      <c r="DD44" t="n">
+        <v>156900</v>
+      </c>
+      <c r="DE44" t="n">
+        <v>121100</v>
+      </c>
+      <c r="DF44" t="n">
+        <v>124000</v>
+      </c>
+      <c r="DG44" t="n">
+        <v>122980</v>
+      </c>
+      <c r="DH44" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="DI44" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="DJ44" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DK44" t="n">
+        <v>110</v>
+      </c>
+      <c r="DL44" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="DM44" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="DN44" t="n">
+        <v>51.47999999999999</v>
+      </c>
+      <c r="DO44" t="n">
+        <v>111</v>
+      </c>
+      <c r="DP44" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="DQ44" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="DR44" t="n">
+        <v>112</v>
+      </c>
+      <c r="DS44" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DT44" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DU44" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DV44" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DW44" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DX44" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="DY44" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="DZ44" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="EA44" t="n">
+        <v>110</v>
+      </c>
+      <c r="EB44" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="EC44" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="ED44" t="n">
+        <v>112.05</v>
+      </c>
+      <c r="EE44" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="EF44" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="EG44" t="n">
+        <v>93.97000000000001</v>
+      </c>
+      <c r="EH44" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="EI44" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="EJ44" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="EK44" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="EL44" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EM44" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="EN44" t="n">
+        <v>106</v>
+      </c>
+      <c r="EO44" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="EP44" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="EQ44" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="ER44" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="ES44" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="ET44" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="EU44" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="EV44" t="n">
+        <v>104</v>
+      </c>
+      <c r="EW44" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="EX44" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="EY44" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="EZ44" t="n">
+        <v>104</v>
+      </c>
+      <c r="FA44" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="FB44" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="FC44" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="FD44" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="FE44" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="FF44" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FG44" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="FH44" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="FI44" t="n">
+        <v>103</v>
+      </c>
+      <c r="FJ44" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="FK44" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="FL44" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="FM44" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="FN44" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FO44" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FP44" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="FQ44" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="FR44" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="FS44" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="FT44" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="FU44" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FV44" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="FW44" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FX44" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="FY44" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="FZ44" t="n">
+        <v>104.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FZ44"/>
+  <dimension ref="A1:FZ45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -19377,6 +19377,508 @@
         <v>104.8</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>106.64</v>
+      </c>
+      <c r="H45" t="n">
+        <v>124.19</v>
+      </c>
+      <c r="I45" t="n">
+        <v>112.601</v>
+      </c>
+      <c r="J45" t="n">
+        <v>127.45</v>
+      </c>
+      <c r="K45" t="n">
+        <v>119.65</v>
+      </c>
+      <c r="L45" t="n">
+        <v>144.139</v>
+      </c>
+      <c r="M45" t="n">
+        <v>131.28</v>
+      </c>
+      <c r="N45" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="O45" t="n">
+        <v>125.35</v>
+      </c>
+      <c r="P45" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>113</v>
+      </c>
+      <c r="S45" t="n">
+        <v>166.85</v>
+      </c>
+      <c r="T45" t="n">
+        <v>293.65</v>
+      </c>
+      <c r="U45" t="n">
+        <v>216.75</v>
+      </c>
+      <c r="V45" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="W45" t="n">
+        <v>386.6</v>
+      </c>
+      <c r="X45" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>270.75</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>97.65000000000001</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>345.55</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>127</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>147400</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>145400</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>126590</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>98.27</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>55.78999999999998</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>82.44</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>71.06999999999999</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>103.72</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>148350</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>144990</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>114</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>147640</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>120410</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>92.04000000000001</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>81.84999999999999</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>102.145</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>146600</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="CB45" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="CC45" t="n">
+        <v>120.95</v>
+      </c>
+      <c r="CE45" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="CF45" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="CG45" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="CH45" t="n">
+        <v>32014.25</v>
+      </c>
+      <c r="CM45" t="n">
+        <v>59980</v>
+      </c>
+      <c r="CN45" t="n">
+        <v>29754.62</v>
+      </c>
+      <c r="CQ45" t="n">
+        <v>73450</v>
+      </c>
+      <c r="CS45" t="n">
+        <v>72000</v>
+      </c>
+      <c r="CT45" t="n">
+        <v>54213.425</v>
+      </c>
+      <c r="CU45" t="n">
+        <v>41575.111</v>
+      </c>
+      <c r="CV45" t="n">
+        <v>97600</v>
+      </c>
+      <c r="CW45" t="n">
+        <v>36128.597</v>
+      </c>
+      <c r="CX45" t="n">
+        <v>170000</v>
+      </c>
+      <c r="CY45" t="n">
+        <v>160350</v>
+      </c>
+      <c r="CZ45" t="n">
+        <v>167650</v>
+      </c>
+      <c r="DA45" t="n">
+        <v>160700</v>
+      </c>
+      <c r="DB45" t="n">
+        <v>166000</v>
+      </c>
+      <c r="DC45" t="n">
+        <v>172990</v>
+      </c>
+      <c r="DD45" t="n">
+        <v>158000</v>
+      </c>
+      <c r="DE45" t="n">
+        <v>120650</v>
+      </c>
+      <c r="DF45" t="n">
+        <v>123500</v>
+      </c>
+      <c r="DG45" t="n">
+        <v>122980</v>
+      </c>
+      <c r="DH45" t="n">
+        <v>110</v>
+      </c>
+      <c r="DI45" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="DJ45" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DK45" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="DL45" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="DM45" t="n">
+        <v>85.19</v>
+      </c>
+      <c r="DN45" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="DO45" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="DP45" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DQ45" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="DR45" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="DS45" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DT45" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="DU45" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DV45" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DW45" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="DX45" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="DY45" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="DZ45" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="EA45" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="EB45" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="EC45" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="ED45" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="EE45" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="EF45" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="EG45" t="n">
+        <v>93.91</v>
+      </c>
+      <c r="EH45" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="EI45" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="EJ45" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="EK45" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="EL45" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="EM45" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="EN45" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EO45" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="EP45" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="EQ45" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="ER45" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="ES45" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="ET45" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="EU45" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="EV45" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EW45" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="EX45" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="EY45" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="EZ45" t="n">
+        <v>104</v>
+      </c>
+      <c r="FA45" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="FB45" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="FC45" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="FD45" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="FE45" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="FF45" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FG45" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="FH45" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="FI45" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="FJ45" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="FK45" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="FL45" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FM45" t="n">
+        <v>101</v>
+      </c>
+      <c r="FN45" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="FO45" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="FP45" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="FQ45" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="FR45" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="FS45" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FT45" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="FU45" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="FV45" t="n">
+        <v>106</v>
+      </c>
+      <c r="FW45" t="n">
+        <v>102</v>
+      </c>
+      <c r="FX45" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="FY45" t="n">
+        <v>106</v>
+      </c>
+      <c r="FZ45" t="n">
+        <v>104.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FZ45"/>
+  <dimension ref="A1:GA45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1332,6 +1332,11 @@
           <t>CS47D</t>
         </is>
       </c>
+      <c r="GA1" t="inlineStr">
+        <is>
+          <t>PFC3D</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -2100,6 +2105,9 @@
       <c r="FZ3" t="n">
         <v>102.65</v>
       </c>
+      <c r="GA3" t="n">
+        <v>99.59999999999998</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2488,6 +2496,9 @@
       <c r="FZ4" t="n">
         <v>102.95</v>
       </c>
+      <c r="GA4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2879,6 +2890,9 @@
       <c r="FZ5" t="n">
         <v>102.9</v>
       </c>
+      <c r="GA5" t="n">
+        <v>99.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3291,6 +3305,9 @@
       <c r="FZ6" t="n">
         <v>103</v>
       </c>
+      <c r="GA6" t="n">
+        <v>99.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3709,6 +3726,9 @@
       <c r="FZ7" t="n">
         <v>102.7</v>
       </c>
+      <c r="GA7" t="n">
+        <v>99.98999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4124,6 +4144,9 @@
       <c r="FZ8" t="n">
         <v>102.8</v>
       </c>
+      <c r="GA8" t="n">
+        <v>99.79000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4545,6 +4568,9 @@
       <c r="FZ9" t="n">
         <v>102.6</v>
       </c>
+      <c r="GA9" t="n">
+        <v>100.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4966,6 +4992,9 @@
       <c r="FZ10" t="n">
         <v>102.95</v>
       </c>
+      <c r="GA10" t="n">
+        <v>100.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5381,6 +5410,9 @@
       <c r="FZ11" t="n">
         <v>102.95</v>
       </c>
+      <c r="GA11" t="n">
+        <v>100.45</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5793,6 +5825,9 @@
       <c r="FZ12" t="n">
         <v>103.15</v>
       </c>
+      <c r="GA12" t="n">
+        <v>100.3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6635,6 +6670,9 @@
       <c r="FZ14" t="n">
         <v>103.75</v>
       </c>
+      <c r="GA14" t="n">
+        <v>100.15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7050,6 +7088,9 @@
       <c r="FZ15" t="n">
         <v>103.2</v>
       </c>
+      <c r="GA15" t="n">
+        <v>100.95</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7483,6 +7524,9 @@
       <c r="FZ16" t="n">
         <v>103.3</v>
       </c>
+      <c r="GA16" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8127,6 +8171,9 @@
       <c r="FZ18" t="n">
         <v>103.15</v>
       </c>
+      <c r="GA18" t="n">
+        <v>100.4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8557,6 +8604,9 @@
       <c r="FZ19" t="n">
         <v>103.05</v>
       </c>
+      <c r="GA19" t="n">
+        <v>100.5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8990,6 +9040,9 @@
       <c r="FZ20" t="n">
         <v>103.4</v>
       </c>
+      <c r="GA20" t="n">
+        <v>100.05</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9420,6 +9473,9 @@
       <c r="FZ21" t="n">
         <v>103.4</v>
       </c>
+      <c r="GA21" t="n">
+        <v>100.3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9853,6 +9909,9 @@
       <c r="FZ22" t="n">
         <v>103.55</v>
       </c>
+      <c r="GA22" t="n">
+        <v>100.5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10286,6 +10345,9 @@
       <c r="FZ23" t="n">
         <v>103.15</v>
       </c>
+      <c r="GA23" t="n">
+        <v>100.5</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10719,6 +10781,9 @@
       <c r="FZ24" t="n">
         <v>103.6</v>
       </c>
+      <c r="GA24" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11155,6 +11220,9 @@
       <c r="FZ25" t="n">
         <v>103.75</v>
       </c>
+      <c r="GA25" t="n">
+        <v>100.3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11588,6 +11656,9 @@
       <c r="FZ26" t="n">
         <v>103.3</v>
       </c>
+      <c r="GA26" t="n">
+        <v>100.75</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12015,6 +12086,9 @@
       <c r="FZ27" t="n">
         <v>104.3</v>
       </c>
+      <c r="GA27" t="n">
+        <v>101.25</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12448,6 +12522,9 @@
       <c r="FZ28" t="n">
         <v>103.6</v>
       </c>
+      <c r="GA28" t="n">
+        <v>101.2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12887,6 +12964,9 @@
       <c r="FZ29" t="n">
         <v>103.85</v>
       </c>
+      <c r="GA29" t="n">
+        <v>100.7</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13329,6 +13409,9 @@
       <c r="FZ30" t="n">
         <v>103.8</v>
       </c>
+      <c r="GA30" t="n">
+        <v>101.1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13774,6 +13857,9 @@
       <c r="FZ31" t="n">
         <v>103.8</v>
       </c>
+      <c r="GA31" t="n">
+        <v>101.4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14219,6 +14305,9 @@
       <c r="FZ32" t="n">
         <v>103.45</v>
       </c>
+      <c r="GA32" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -14658,6 +14747,9 @@
       <c r="FZ33" t="n">
         <v>103.8</v>
       </c>
+      <c r="GA33" t="n">
+        <v>100.5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15103,6 +15195,9 @@
       <c r="FZ34" t="n">
         <v>103.4</v>
       </c>
+      <c r="GA34" t="n">
+        <v>101.25</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15714,6 +15809,9 @@
       <c r="FZ36" t="n">
         <v>103.8</v>
       </c>
+      <c r="GA36" t="n">
+        <v>101.5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16156,6 +16254,9 @@
       <c r="FZ37" t="n">
         <v>103.65</v>
       </c>
+      <c r="GA37" t="n">
+        <v>101.6</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -16598,6 +16699,9 @@
       <c r="FZ38" t="n">
         <v>103.9</v>
       </c>
+      <c r="GA38" t="n">
+        <v>101.5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -17479,6 +17583,9 @@
       <c r="FZ40" t="n">
         <v>103.95</v>
       </c>
+      <c r="GA40" t="n">
+        <v>100.55</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -17927,6 +18034,9 @@
       <c r="FZ41" t="n">
         <v>104.3</v>
       </c>
+      <c r="GA41" t="n">
+        <v>101.9</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -18372,6 +18482,9 @@
       <c r="FZ42" t="n">
         <v>105.5</v>
       </c>
+      <c r="GA42" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18874,6 +18987,9 @@
       <c r="FZ43" t="n">
         <v>105.15</v>
       </c>
+      <c r="GA43" t="n">
+        <v>101.05</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -19376,6 +19492,9 @@
       <c r="FZ44" t="n">
         <v>104.8</v>
       </c>
+      <c r="GA44" t="n">
+        <v>101.05</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -19877,6 +19996,9 @@
       </c>
       <c r="FZ45" t="n">
         <v>104.65</v>
+      </c>
+      <c r="GA45" t="n">
+        <v>101.85</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GA45"/>
+  <dimension ref="A1:GD45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1337,6 +1337,21 @@
           <t>PFC3D</t>
         </is>
       </c>
+      <c r="GB1" t="inlineStr">
+        <is>
+          <t>RC2CD</t>
+        </is>
+      </c>
+      <c r="GC1" t="inlineStr">
+        <is>
+          <t>YM35D</t>
+        </is>
+      </c>
+      <c r="GD1" t="inlineStr">
+        <is>
+          <t>YFCMD</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -1714,6 +1729,12 @@
       <c r="FZ2" t="n">
         <v>102</v>
       </c>
+      <c r="GC2" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>103.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2108,6 +2129,15 @@
       <c r="GA3" t="n">
         <v>99.59999999999998</v>
       </c>
+      <c r="GB3" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GC3" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="GD3" t="n">
+        <v>102.4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2499,6 +2529,15 @@
       <c r="GA4" t="n">
         <v>100</v>
       </c>
+      <c r="GB4" t="n">
+        <v>102</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>102.45</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2893,6 +2932,15 @@
       <c r="GA5" t="n">
         <v>99.8</v>
       </c>
+      <c r="GB5" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>102.55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3308,6 +3356,15 @@
       <c r="GA6" t="n">
         <v>99.8</v>
       </c>
+      <c r="GB6" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>102.35</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3729,6 +3786,15 @@
       <c r="GA7" t="n">
         <v>99.98999999999999</v>
       </c>
+      <c r="GB7" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>103.15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4147,6 +4213,15 @@
       <c r="GA8" t="n">
         <v>99.79000000000001</v>
       </c>
+      <c r="GB8" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>102.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4571,6 +4646,15 @@
       <c r="GA9" t="n">
         <v>100.5</v>
       </c>
+      <c r="GB9" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>102.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4995,6 +5079,15 @@
       <c r="GA10" t="n">
         <v>100.2</v>
       </c>
+      <c r="GB10" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5413,6 +5506,15 @@
       <c r="GA11" t="n">
         <v>100.45</v>
       </c>
+      <c r="GB11" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>102.45</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5828,6 +5930,15 @@
       <c r="GA12" t="n">
         <v>100.3</v>
       </c>
+      <c r="GB12" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>102</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>103.05</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6249,6 +6360,15 @@
       <c r="FZ13" t="n">
         <v>103</v>
       </c>
+      <c r="GB13" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>102.3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6673,6 +6793,15 @@
       <c r="GA14" t="n">
         <v>100.15</v>
       </c>
+      <c r="GB14" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7091,6 +7220,15 @@
       <c r="GA15" t="n">
         <v>100.95</v>
       </c>
+      <c r="GB15" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>103.25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7527,6 +7665,15 @@
       <c r="GA16" t="n">
         <v>101</v>
       </c>
+      <c r="GB16" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>103.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8174,6 +8321,15 @@
       <c r="GA18" t="n">
         <v>100.4</v>
       </c>
+      <c r="GB18" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>102.9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8607,6 +8763,15 @@
       <c r="GA19" t="n">
         <v>100.5</v>
       </c>
+      <c r="GB19" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="GC19" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="GD19" t="n">
+        <v>103.3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9043,6 +9208,15 @@
       <c r="GA20" t="n">
         <v>100.05</v>
       </c>
+      <c r="GB20" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GC20" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="GD20" t="n">
+        <v>102.6</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9476,6 +9650,12 @@
       <c r="GA21" t="n">
         <v>100.3</v>
       </c>
+      <c r="GC21" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="GD21" t="n">
+        <v>103.3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9912,6 +10092,15 @@
       <c r="GA22" t="n">
         <v>100.5</v>
       </c>
+      <c r="GB22" t="n">
+        <v>102</v>
+      </c>
+      <c r="GC22" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="GD22" t="n">
+        <v>102.85</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10348,6 +10537,15 @@
       <c r="GA23" t="n">
         <v>100.5</v>
       </c>
+      <c r="GB23" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GC23" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="GD23" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10784,6 +10982,15 @@
       <c r="GA24" t="n">
         <v>101</v>
       </c>
+      <c r="GB24" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GC24" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GD24" t="n">
+        <v>103.3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11223,6 +11430,15 @@
       <c r="GA25" t="n">
         <v>100.3</v>
       </c>
+      <c r="GB25" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GC25" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GD25" t="n">
+        <v>103.05</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11659,6 +11875,15 @@
       <c r="GA26" t="n">
         <v>100.75</v>
       </c>
+      <c r="GB26" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="GC26" t="n">
+        <v>103</v>
+      </c>
+      <c r="GD26" t="n">
+        <v>102.85</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12089,6 +12314,15 @@
       <c r="GA27" t="n">
         <v>101.25</v>
       </c>
+      <c r="GB27" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="GC27" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GD27" t="n">
+        <v>103.45</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12525,6 +12759,12 @@
       <c r="GA28" t="n">
         <v>101.2</v>
       </c>
+      <c r="GC28" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GD28" t="n">
+        <v>103.3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12967,6 +13207,15 @@
       <c r="GA29" t="n">
         <v>100.7</v>
       </c>
+      <c r="GB29" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="GC29" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GD29" t="n">
+        <v>103.4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13412,6 +13661,15 @@
       <c r="GA30" t="n">
         <v>101.1</v>
       </c>
+      <c r="GB30" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="GC30" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="GD30" t="n">
+        <v>103.6</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13860,6 +14118,15 @@
       <c r="GA31" t="n">
         <v>101.4</v>
       </c>
+      <c r="GB31" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="GC31" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="GD31" t="n">
+        <v>103.8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14308,6 +14575,15 @@
       <c r="GA32" t="n">
         <v>101</v>
       </c>
+      <c r="GB32" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="GC32" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="GD32" t="n">
+        <v>104.5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -14750,6 +15026,15 @@
       <c r="GA33" t="n">
         <v>100.5</v>
       </c>
+      <c r="GB33" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="GC33" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GD33" t="n">
+        <v>102.65</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15198,6 +15483,15 @@
       <c r="GA34" t="n">
         <v>101.25</v>
       </c>
+      <c r="GB34" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GC34" t="n">
+        <v>103</v>
+      </c>
+      <c r="GD34" t="n">
+        <v>103.65</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15812,6 +16106,15 @@
       <c r="GA36" t="n">
         <v>101.5</v>
       </c>
+      <c r="GB36" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GC36" t="n">
+        <v>103</v>
+      </c>
+      <c r="GD36" t="n">
+        <v>104.95</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16257,6 +16560,15 @@
       <c r="GA37" t="n">
         <v>101.6</v>
       </c>
+      <c r="GB37" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="GC37" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="GD37" t="n">
+        <v>104.45</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -16702,6 +17014,15 @@
       <c r="GA38" t="n">
         <v>101.5</v>
       </c>
+      <c r="GB38" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="GC38" t="n">
+        <v>103</v>
+      </c>
+      <c r="GD38" t="n">
+        <v>103.55</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -17144,6 +17465,15 @@
       <c r="FZ39" t="n">
         <v>104</v>
       </c>
+      <c r="GB39" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="GC39" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="GD39" t="n">
+        <v>103.25</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -17586,6 +17916,15 @@
       <c r="GA40" t="n">
         <v>100.55</v>
       </c>
+      <c r="GB40" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GC40" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="GD40" t="n">
+        <v>103.6</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18037,6 +18376,15 @@
       <c r="GA41" t="n">
         <v>101.9</v>
       </c>
+      <c r="GB41" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GC41" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="GD41" t="n">
+        <v>103.6</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -18485,6 +18833,15 @@
       <c r="GA42" t="n">
         <v>101.95</v>
       </c>
+      <c r="GB42" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GC42" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GD42" t="n">
+        <v>104.5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18990,6 +19347,15 @@
       <c r="GA43" t="n">
         <v>101.05</v>
       </c>
+      <c r="GB43" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GC43" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="GD43" t="n">
+        <v>104.5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -19495,6 +19861,15 @@
       <c r="GA44" t="n">
         <v>101.05</v>
       </c>
+      <c r="GB44" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GC44" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="GD44" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -19999,6 +20374,15 @@
       </c>
       <c r="GA45" t="n">
         <v>101.85</v>
+      </c>
+      <c r="GB45" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="GC45" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GD45" t="n">
+        <v>104.25</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GD45"/>
+  <dimension ref="A1:GG45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1352,6 +1352,21 @@
           <t>YFCMD</t>
         </is>
       </c>
+      <c r="GE1" t="inlineStr">
+        <is>
+          <t>LUC5D</t>
+        </is>
+      </c>
+      <c r="GF1" t="inlineStr">
+        <is>
+          <t>STCFD</t>
+        </is>
+      </c>
+      <c r="GG1" t="inlineStr">
+        <is>
+          <t>WBS3D</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -1582,6 +1597,21 @@
       <c r="CG2" t="n">
         <v>99.11999999999999</v>
       </c>
+      <c r="CS2" t="n">
+        <v>53.60000000000001</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>109</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>75.11</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>71</v>
+      </c>
       <c r="DJ2" t="n">
         <v>103.6</v>
       </c>
@@ -1937,6 +1967,27 @@
       <c r="CG3" t="n">
         <v>100.7</v>
       </c>
+      <c r="CS3" t="n">
+        <v>47.09999999999999</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>75.81999999999999</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>75.59</v>
+      </c>
       <c r="DH3" t="n">
         <v>107.9</v>
       </c>
@@ -2137,6 +2188,9 @@
       </c>
       <c r="GD3" t="n">
         <v>102.4</v>
+      </c>
+      <c r="GE3" t="n">
+        <v>101.8</v>
       </c>
     </row>
     <row r="4">
@@ -2340,6 +2394,27 @@
       <c r="CG4" t="n">
         <v>100.6</v>
       </c>
+      <c r="CS4" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>63.41</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>76.19</v>
+      </c>
       <c r="DH4" t="n">
         <v>108</v>
       </c>
@@ -2537,6 +2612,12 @@
       </c>
       <c r="GD4" t="n">
         <v>102.45</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>102</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>100.3</v>
       </c>
     </row>
     <row r="5">
@@ -2737,6 +2818,30 @@
       <c r="CG5" t="n">
         <v>100.55</v>
       </c>
+      <c r="CS5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>74.23</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>75.98999999999999</v>
+      </c>
       <c r="DH5" t="n">
         <v>107.7</v>
       </c>
@@ -2940,6 +3045,9 @@
       </c>
       <c r="GD5" t="n">
         <v>102.55</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>101.5</v>
       </c>
     </row>
     <row r="6">
@@ -3164,6 +3272,24 @@
       <c r="CG6" t="n">
         <v>100.6</v>
       </c>
+      <c r="CS6" t="n">
+        <v>47.69</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>63.41</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>75.31</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>75</v>
+      </c>
       <c r="DH6" t="n">
         <v>107.45</v>
       </c>
@@ -3364,6 +3490,9 @@
       </c>
       <c r="GD6" t="n">
         <v>102.35</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>101.4</v>
       </c>
     </row>
     <row r="7">
@@ -3588,6 +3717,30 @@
       <c r="CG7" t="n">
         <v>100.75</v>
       </c>
+      <c r="CS7" t="n">
+        <v>47.01</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>112</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>75</v>
+      </c>
       <c r="DH7" t="n">
         <v>107.9</v>
       </c>
@@ -3794,6 +3947,9 @@
       </c>
       <c r="GD7" t="n">
         <v>103.15</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>102.2</v>
       </c>
     </row>
     <row r="8">
@@ -4018,6 +4174,27 @@
       <c r="CG8" t="n">
         <v>101.05</v>
       </c>
+      <c r="CS8" t="n">
+        <v>46.981</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>104</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>101</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>75.89</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>76.34</v>
+      </c>
       <c r="DH8" t="n">
         <v>107.95</v>
       </c>
@@ -4221,6 +4398,9 @@
       </c>
       <c r="GD8" t="n">
         <v>102.7</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>101.3</v>
       </c>
     </row>
     <row r="9">
@@ -4445,6 +4625,27 @@
       <c r="CG9" t="n">
         <v>101.1</v>
       </c>
+      <c r="CS9" t="n">
+        <v>46.78000000000001</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>64.19</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>101</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>76.5</v>
+      </c>
       <c r="DH9" t="n">
         <v>108.1</v>
       </c>
@@ -4654,6 +4855,9 @@
       </c>
       <c r="GD9" t="n">
         <v>102.5</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>101.95</v>
       </c>
     </row>
     <row r="10">
@@ -4878,6 +5082,30 @@
       <c r="CG10" t="n">
         <v>101.7</v>
       </c>
+      <c r="CS10" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>113.95</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>76.17</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>76.5</v>
+      </c>
       <c r="DH10" t="n">
         <v>108.6</v>
       </c>
@@ -5087,6 +5315,9 @@
       </c>
       <c r="GD10" t="n">
         <v>103</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -5308,6 +5539,27 @@
       <c r="CG11" t="n">
         <v>101.7</v>
       </c>
+      <c r="CS11" t="n">
+        <v>46.77999999999999</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>103</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>75.14</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>76.59999999999999</v>
+      </c>
       <c r="DH11" t="n">
         <v>108.05</v>
       </c>
@@ -5514,6 +5766,9 @@
       </c>
       <c r="GD11" t="n">
         <v>102.45</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>101.5</v>
       </c>
     </row>
     <row r="12">
@@ -5735,6 +5990,27 @@
       <c r="CG12" t="n">
         <v>102</v>
       </c>
+      <c r="CS12" t="n">
+        <v>46.61</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>76.40000000000001</v>
+      </c>
       <c r="DH12" t="n">
         <v>108.15</v>
       </c>
@@ -5938,6 +6214,9 @@
       </c>
       <c r="GD12" t="n">
         <v>103.05</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>102.25</v>
       </c>
     </row>
     <row r="13">
@@ -6159,6 +6438,30 @@
       <c r="CG13" t="n">
         <v>101.95</v>
       </c>
+      <c r="CS13" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>75.16</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>75.47</v>
+      </c>
       <c r="DH13" t="n">
         <v>108.95</v>
       </c>
@@ -6368,6 +6671,12 @@
       </c>
       <c r="GD13" t="n">
         <v>102.3</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>98.55</v>
       </c>
     </row>
     <row r="14">
@@ -6589,6 +6898,30 @@
       <c r="CG14" t="n">
         <v>102.05</v>
       </c>
+      <c r="CS14" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>103</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>76.36</v>
+      </c>
       <c r="DH14" t="n">
         <v>108.2</v>
       </c>
@@ -6801,6 +7134,9 @@
       </c>
       <c r="GD14" t="n">
         <v>103</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>102.5</v>
       </c>
     </row>
     <row r="15">
@@ -7019,6 +7355,24 @@
       <c r="CG15" t="n">
         <v>101.85</v>
       </c>
+      <c r="CS15" t="n">
+        <v>46.90000000000001</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>77</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>77.44</v>
+      </c>
       <c r="DH15" t="n">
         <v>107.8</v>
       </c>
@@ -7228,6 +7582,12 @@
       </c>
       <c r="GD15" t="n">
         <v>103.25</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>98.75</v>
       </c>
     </row>
     <row r="16">
@@ -7461,6 +7821,27 @@
       <c r="CG16" t="n">
         <v>101.85</v>
       </c>
+      <c r="CS16" t="n">
+        <v>47</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>77.59999999999999</v>
+      </c>
       <c r="DH16" t="n">
         <v>108.2</v>
       </c>
@@ -7673,6 +8054,9 @@
       </c>
       <c r="GD16" t="n">
         <v>103.2</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>102.75</v>
       </c>
     </row>
     <row r="17">
@@ -8120,6 +8504,27 @@
       <c r="CG18" t="n">
         <v>101.95</v>
       </c>
+      <c r="CS18" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>63.01999999999999</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>77.2</v>
+      </c>
       <c r="DH18" t="n">
         <v>107.7</v>
       </c>
@@ -8329,6 +8734,9 @@
       </c>
       <c r="GD18" t="n">
         <v>102.9</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>102.7</v>
       </c>
     </row>
     <row r="19">
@@ -8562,6 +8970,24 @@
       <c r="CG19" t="n">
         <v>101.95</v>
       </c>
+      <c r="CS19" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>63.27</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>78</v>
+      </c>
       <c r="DH19" t="n">
         <v>107.6</v>
       </c>
@@ -8771,6 +9197,9 @@
       </c>
       <c r="GD19" t="n">
         <v>103.3</v>
+      </c>
+      <c r="GE19" t="n">
+        <v>102.75</v>
       </c>
     </row>
     <row r="20">
@@ -9004,6 +9433,30 @@
       <c r="CG20" t="n">
         <v>101.9</v>
       </c>
+      <c r="CS20" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>63.12</v>
+      </c>
+      <c r="CX20" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>77.59</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>78.5</v>
+      </c>
       <c r="DH20" t="n">
         <v>108</v>
       </c>
@@ -9216,6 +9669,9 @@
       </c>
       <c r="GD20" t="n">
         <v>102.6</v>
+      </c>
+      <c r="GE20" t="n">
+        <v>102.75</v>
       </c>
     </row>
     <row r="21">
@@ -9449,6 +9905,30 @@
       <c r="CG21" t="n">
         <v>101.8</v>
       </c>
+      <c r="CS21" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="CY21" t="n">
+        <v>103</v>
+      </c>
+      <c r="DB21" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="DD21" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>78.09</v>
+      </c>
+      <c r="DF21" t="n">
+        <v>78.40000000000001</v>
+      </c>
       <c r="DH21" t="n">
         <v>107.7</v>
       </c>
@@ -9655,6 +10135,9 @@
       </c>
       <c r="GD21" t="n">
         <v>103.3</v>
+      </c>
+      <c r="GE21" t="n">
+        <v>102.6</v>
       </c>
     </row>
     <row r="22">
@@ -9888,6 +10371,27 @@
       <c r="CG22" t="n">
         <v>101.85</v>
       </c>
+      <c r="CS22" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="CV22" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="CX22" t="n">
+        <v>115</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>77.63</v>
+      </c>
+      <c r="DF22" t="n">
+        <v>78</v>
+      </c>
       <c r="DH22" t="n">
         <v>107.3</v>
       </c>
@@ -10100,6 +10604,9 @@
       </c>
       <c r="GD22" t="n">
         <v>102.85</v>
+      </c>
+      <c r="GE22" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="23">
@@ -10333,6 +10840,30 @@
       <c r="CG23" t="n">
         <v>101.85</v>
       </c>
+      <c r="CS23" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="CV23" t="n">
+        <v>63.45</v>
+      </c>
+      <c r="CX23" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="CY23" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>78.39</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>78</v>
+      </c>
       <c r="DH23" t="n">
         <v>107.5</v>
       </c>
@@ -10545,6 +11076,9 @@
       </c>
       <c r="GD23" t="n">
         <v>103</v>
+      </c>
+      <c r="GE23" t="n">
+        <v>102.5</v>
       </c>
     </row>
     <row r="24">
@@ -10778,6 +11312,27 @@
       <c r="CG24" t="n">
         <v>102.2</v>
       </c>
+      <c r="CS24" t="n">
+        <v>46.911</v>
+      </c>
+      <c r="CV24" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="CX24" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="DB24" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DD24" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="DE24" t="n">
+        <v>77.53</v>
+      </c>
+      <c r="DF24" t="n">
+        <v>77.59999999999999</v>
+      </c>
       <c r="DI24" t="n">
         <v>109.55</v>
       </c>
@@ -10990,6 +11545,9 @@
       </c>
       <c r="GD24" t="n">
         <v>103.3</v>
+      </c>
+      <c r="GE24" t="n">
+        <v>102.7</v>
       </c>
     </row>
     <row r="25">
@@ -11223,6 +11781,27 @@
       <c r="CG25" t="n">
         <v>102.25</v>
       </c>
+      <c r="CS25" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="CV25" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="CX25" t="n">
+        <v>115</v>
+      </c>
+      <c r="DB25" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DD25" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="DE25" t="n">
+        <v>77.34</v>
+      </c>
+      <c r="DF25" t="n">
+        <v>78</v>
+      </c>
       <c r="DH25" t="n">
         <v>107.9</v>
       </c>
@@ -11438,6 +12017,9 @@
       </c>
       <c r="GD25" t="n">
         <v>103.05</v>
+      </c>
+      <c r="GE25" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="26">
@@ -11671,6 +12253,27 @@
       <c r="CG26" t="n">
         <v>102</v>
       </c>
+      <c r="CS26" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="CV26" t="n">
+        <v>63.63999999999999</v>
+      </c>
+      <c r="CX26" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DD26" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="DE26" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="DF26" t="n">
+        <v>77.90000000000001</v>
+      </c>
       <c r="DH26" t="n">
         <v>108</v>
       </c>
@@ -11883,6 +12486,9 @@
       </c>
       <c r="GD26" t="n">
         <v>102.85</v>
+      </c>
+      <c r="GE26" t="n">
+        <v>102.9</v>
       </c>
     </row>
     <row r="27">
@@ -12104,6 +12710,27 @@
       <c r="CG27" t="n">
         <v>101.95</v>
       </c>
+      <c r="CS27" t="n">
+        <v>46.99999999999999</v>
+      </c>
+      <c r="CV27" t="n">
+        <v>63.49999999999999</v>
+      </c>
+      <c r="CX27" t="n">
+        <v>115</v>
+      </c>
+      <c r="DB27" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="DD27" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="DE27" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="DF27" t="n">
+        <v>79.5</v>
+      </c>
       <c r="DH27" t="n">
         <v>107.6</v>
       </c>
@@ -12322,6 +12949,9 @@
       </c>
       <c r="GD27" t="n">
         <v>103.45</v>
+      </c>
+      <c r="GE27" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="28">
@@ -12555,6 +13185,27 @@
       <c r="CG28" t="n">
         <v>101.8</v>
       </c>
+      <c r="CS28" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="CV28" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="CX28" t="n">
+        <v>115</v>
+      </c>
+      <c r="DB28" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="DD28" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="DE28" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="DF28" t="n">
+        <v>78.34999999999999</v>
+      </c>
       <c r="DH28" t="n">
         <v>108.05</v>
       </c>
@@ -12764,6 +13415,9 @@
       </c>
       <c r="GD28" t="n">
         <v>103.3</v>
+      </c>
+      <c r="GE28" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="29">
@@ -12997,6 +13651,24 @@
       <c r="CG29" t="n">
         <v>102.1</v>
       </c>
+      <c r="CS29" t="n">
+        <v>47.39000000000001</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DE29" t="n">
+        <v>78.20999999999999</v>
+      </c>
+      <c r="DF29" t="n">
+        <v>79.3</v>
+      </c>
       <c r="DH29" t="n">
         <v>107.4</v>
       </c>
@@ -13215,6 +13887,9 @@
       </c>
       <c r="GD29" t="n">
         <v>103.4</v>
+      </c>
+      <c r="GE29" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="30">
@@ -13448,6 +14123,27 @@
       <c r="CG30" t="n">
         <v>102</v>
       </c>
+      <c r="CS30" t="n">
+        <v>47</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>63.35999999999999</v>
+      </c>
+      <c r="CX30" t="n">
+        <v>112</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>102</v>
+      </c>
+      <c r="DE30" t="n">
+        <v>78.20999999999999</v>
+      </c>
+      <c r="DF30" t="n">
+        <v>79.90000000000001</v>
+      </c>
       <c r="DH30" t="n">
         <v>107.95</v>
       </c>
@@ -13669,6 +14365,9 @@
       </c>
       <c r="GD30" t="n">
         <v>103.6</v>
+      </c>
+      <c r="GE30" t="n">
+        <v>102.5</v>
       </c>
     </row>
     <row r="31">
@@ -13902,6 +14601,24 @@
       <c r="CG31" t="n">
         <v>101.95</v>
       </c>
+      <c r="CS31" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="CV31" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="DB31" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DD31" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="DE31" t="n">
+        <v>78.27</v>
+      </c>
+      <c r="DF31" t="n">
+        <v>80.2</v>
+      </c>
       <c r="DH31" t="n">
         <v>108</v>
       </c>
@@ -14126,6 +14843,12 @@
       </c>
       <c r="GD31" t="n">
         <v>103.8</v>
+      </c>
+      <c r="GE31" t="n">
+        <v>103</v>
+      </c>
+      <c r="GG31" t="n">
+        <v>100.1</v>
       </c>
     </row>
     <row r="32">
@@ -14359,6 +15082,30 @@
       <c r="CG32" t="n">
         <v>101.95</v>
       </c>
+      <c r="CS32" t="n">
+        <v>47</v>
+      </c>
+      <c r="CV32" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="CX32" t="n">
+        <v>111</v>
+      </c>
+      <c r="CY32" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="DB32" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DD32" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="DE32" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="DF32" t="n">
+        <v>79.8</v>
+      </c>
       <c r="DH32" t="n">
         <v>108.05</v>
       </c>
@@ -14583,6 +15330,9 @@
       </c>
       <c r="GD32" t="n">
         <v>104.5</v>
+      </c>
+      <c r="GE32" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="33">
@@ -14816,6 +15566,27 @@
       <c r="CG33" t="n">
         <v>101.9</v>
       </c>
+      <c r="CS33" t="n">
+        <v>47</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>63.71999999999999</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>111</v>
+      </c>
+      <c r="DB33" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="DD33" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="DE33" t="n">
+        <v>78.68000000000001</v>
+      </c>
+      <c r="DF33" t="n">
+        <v>81</v>
+      </c>
       <c r="DH33" t="n">
         <v>108.65</v>
       </c>
@@ -15034,6 +15805,9 @@
       </c>
       <c r="GD33" t="n">
         <v>102.65</v>
+      </c>
+      <c r="GE33" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="34">
@@ -15267,6 +16041,30 @@
       <c r="CG34" t="n">
         <v>101.85</v>
       </c>
+      <c r="CS34" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="CV34" t="n">
+        <v>63.74999999999999</v>
+      </c>
+      <c r="CX34" t="n">
+        <v>111</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="DB34" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DD34" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="DE34" t="n">
+        <v>79.47</v>
+      </c>
+      <c r="DF34" t="n">
+        <v>80</v>
+      </c>
       <c r="DH34" t="n">
         <v>109.1</v>
       </c>
@@ -15491,6 +16289,9 @@
       </c>
       <c r="GD34" t="n">
         <v>103.65</v>
+      </c>
+      <c r="GE34" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="35">
@@ -15938,6 +16739,18 @@
       <c r="CG36" t="n">
         <v>102</v>
       </c>
+      <c r="CV36" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="DA36" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DE36" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="DF36" t="n">
+        <v>81.48999999999999</v>
+      </c>
       <c r="DH36" t="n">
         <v>108</v>
       </c>
@@ -16114,6 +16927,9 @@
       </c>
       <c r="GD36" t="n">
         <v>104.95</v>
+      </c>
+      <c r="GE36" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="37">
@@ -16347,6 +17163,33 @@
       <c r="CG37" t="n">
         <v>101.95</v>
       </c>
+      <c r="CS37" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="CV37" t="n">
+        <v>63.97999999999999</v>
+      </c>
+      <c r="CX37" t="n">
+        <v>112</v>
+      </c>
+      <c r="CY37" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="DA37" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="DB37" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DD37" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="DE37" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="DF37" t="n">
+        <v>81.5</v>
+      </c>
       <c r="DH37" t="n">
         <v>108.1</v>
       </c>
@@ -16568,6 +17411,9 @@
       </c>
       <c r="GD37" t="n">
         <v>104.45</v>
+      </c>
+      <c r="GE37" t="n">
+        <v>103.25</v>
       </c>
     </row>
     <row r="38">
@@ -16801,6 +17647,30 @@
       <c r="CG38" t="n">
         <v>102</v>
       </c>
+      <c r="CS38" t="n">
+        <v>47.09999999999999</v>
+      </c>
+      <c r="CV38" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="CX38" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="DA38" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DB38" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DD38" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="DE38" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="DF38" t="n">
+        <v>81.5</v>
+      </c>
       <c r="DH38" t="n">
         <v>108.2</v>
       </c>
@@ -17022,6 +17892,12 @@
       </c>
       <c r="GD38" t="n">
         <v>103.55</v>
+      </c>
+      <c r="GE38" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GG38" t="n">
+        <v>100.4</v>
       </c>
     </row>
     <row r="39">
@@ -17255,6 +18131,33 @@
       <c r="CG39" t="n">
         <v>102.15</v>
       </c>
+      <c r="CS39" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="CV39" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="CX39" t="n">
+        <v>112</v>
+      </c>
+      <c r="CY39" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="DA39" t="n">
+        <v>107</v>
+      </c>
+      <c r="DB39" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DD39" t="n">
+        <v>104</v>
+      </c>
+      <c r="DE39" t="n">
+        <v>79.77</v>
+      </c>
+      <c r="DF39" t="n">
+        <v>81.79000000000001</v>
+      </c>
       <c r="DH39" t="n">
         <v>108.65</v>
       </c>
@@ -17473,6 +18376,9 @@
       </c>
       <c r="GD39" t="n">
         <v>103.25</v>
+      </c>
+      <c r="GE39" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="40">
@@ -17703,6 +18609,30 @@
       <c r="CG40" t="n">
         <v>102.35</v>
       </c>
+      <c r="CV40" t="n">
+        <v>65</v>
+      </c>
+      <c r="CX40" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="CY40" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DA40" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="DB40" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DD40" t="n">
+        <v>103</v>
+      </c>
+      <c r="DE40" t="n">
+        <v>79.64</v>
+      </c>
+      <c r="DF40" t="n">
+        <v>81.98999999999999</v>
+      </c>
       <c r="DH40" t="n">
         <v>108.6</v>
       </c>
@@ -17924,6 +18854,12 @@
       </c>
       <c r="GD40" t="n">
         <v>103.6</v>
+      </c>
+      <c r="GE40" t="n">
+        <v>105</v>
+      </c>
+      <c r="GG40" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="41">
@@ -18160,6 +19096,30 @@
       <c r="CG41" t="n">
         <v>102.4</v>
       </c>
+      <c r="CS41" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="CV41" t="n">
+        <v>65</v>
+      </c>
+      <c r="CX41" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DA41" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="DB41" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DD41" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="DE41" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="DF41" t="n">
+        <v>81.67</v>
+      </c>
       <c r="DH41" t="n">
         <v>108.8</v>
       </c>
@@ -18384,6 +19344,12 @@
       </c>
       <c r="GD41" t="n">
         <v>103.6</v>
+      </c>
+      <c r="GE41" t="n">
+        <v>105</v>
+      </c>
+      <c r="GG41" t="n">
+        <v>100.4</v>
       </c>
     </row>
     <row r="42">
@@ -18617,6 +19583,27 @@
       <c r="CG42" t="n">
         <v>102.9</v>
       </c>
+      <c r="CS42" t="n">
+        <v>47.60000000000001</v>
+      </c>
+      <c r="CV42" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="CX42" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="DA42" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DB42" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DE42" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="DF42" t="n">
+        <v>81.79000000000001</v>
+      </c>
       <c r="DH42" t="n">
         <v>109.65</v>
       </c>
@@ -18841,6 +19828,12 @@
       </c>
       <c r="GD42" t="n">
         <v>104.5</v>
+      </c>
+      <c r="GE42" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GG42" t="n">
+        <v>100.35</v>
       </c>
     </row>
     <row r="43">
@@ -19087,7 +20080,7 @@
         <v>74450</v>
       </c>
       <c r="CS43" t="n">
-        <v>71800</v>
+        <v>47.7</v>
       </c>
       <c r="CT43" t="n">
         <v>54213.425</v>
@@ -19096,37 +20089,34 @@
         <v>41575.111</v>
       </c>
       <c r="CV43" t="n">
-        <v>98500</v>
+        <v>64.58</v>
       </c>
       <c r="CW43" t="n">
         <v>36128.597</v>
       </c>
       <c r="CX43" t="n">
-        <v>168100</v>
-      </c>
-      <c r="CY43" t="n">
-        <v>159000</v>
+        <v>111.9</v>
       </c>
       <c r="CZ43" t="n">
         <v>167660</v>
       </c>
       <c r="DA43" t="n">
-        <v>159650</v>
+        <v>105.6</v>
       </c>
       <c r="DB43" t="n">
-        <v>163500</v>
+        <v>108.4</v>
       </c>
       <c r="DC43" t="n">
         <v>171910</v>
       </c>
       <c r="DD43" t="n">
-        <v>156100</v>
+        <v>103.4</v>
       </c>
       <c r="DE43" t="n">
-        <v>121370</v>
+        <v>80.5</v>
       </c>
       <c r="DF43" t="n">
-        <v>122820</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="DG43" t="n">
         <v>123200</v>
@@ -19355,6 +20345,15 @@
       </c>
       <c r="GD43" t="n">
         <v>104.5</v>
+      </c>
+      <c r="GE43" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="GF43" t="n">
+        <v>102</v>
+      </c>
+      <c r="GG43" t="n">
+        <v>100.4</v>
       </c>
     </row>
     <row r="44">
@@ -19601,7 +20600,7 @@
         <v>74400</v>
       </c>
       <c r="CS44" t="n">
-        <v>71900</v>
+        <v>47.36</v>
       </c>
       <c r="CT44" t="n">
         <v>54213.425</v>
@@ -19610,37 +20609,34 @@
         <v>41575.111</v>
       </c>
       <c r="CV44" t="n">
-        <v>97710</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="CW44" t="n">
         <v>36128.597</v>
       </c>
       <c r="CX44" t="n">
-        <v>168850</v>
-      </c>
-      <c r="CY44" t="n">
-        <v>160350</v>
+        <v>112</v>
       </c>
       <c r="CZ44" t="n">
         <v>168350</v>
       </c>
       <c r="DA44" t="n">
-        <v>159500</v>
+        <v>105.6</v>
       </c>
       <c r="DB44" t="n">
-        <v>164000</v>
+        <v>108.6</v>
       </c>
       <c r="DC44" t="n">
         <v>171200</v>
       </c>
       <c r="DD44" t="n">
-        <v>156900</v>
+        <v>103.45</v>
       </c>
       <c r="DE44" t="n">
-        <v>121100</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="DF44" t="n">
-        <v>124000</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="DG44" t="n">
         <v>122980</v>
@@ -19869,6 +20865,12 @@
       </c>
       <c r="GD44" t="n">
         <v>104</v>
+      </c>
+      <c r="GE44" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="GG44" t="n">
+        <v>100.05</v>
       </c>
     </row>
     <row r="45">
@@ -20115,7 +21117,7 @@
         <v>73450</v>
       </c>
       <c r="CS45" t="n">
-        <v>72000</v>
+        <v>47.29999999999999</v>
       </c>
       <c r="CT45" t="n">
         <v>54213.425</v>
@@ -20124,37 +21126,34 @@
         <v>41575.111</v>
       </c>
       <c r="CV45" t="n">
-        <v>97600</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="CW45" t="n">
         <v>36128.597</v>
       </c>
       <c r="CX45" t="n">
-        <v>170000</v>
-      </c>
-      <c r="CY45" t="n">
-        <v>160350</v>
+        <v>111.9</v>
       </c>
       <c r="CZ45" t="n">
         <v>167650</v>
       </c>
       <c r="DA45" t="n">
-        <v>160700</v>
+        <v>105.75</v>
       </c>
       <c r="DB45" t="n">
-        <v>166000</v>
+        <v>108.8</v>
       </c>
       <c r="DC45" t="n">
         <v>172990</v>
       </c>
       <c r="DD45" t="n">
-        <v>158000</v>
+        <v>104</v>
       </c>
       <c r="DE45" t="n">
-        <v>120650</v>
+        <v>79.59</v>
       </c>
       <c r="DF45" t="n">
-        <v>123500</v>
+        <v>81.5</v>
       </c>
       <c r="DG45" t="n">
         <v>122980</v>
@@ -20383,6 +21382,12 @@
       </c>
       <c r="GD45" t="n">
         <v>104.25</v>
+      </c>
+      <c r="GE45" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="GF45" t="n">
+        <v>103.9</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GP53"/>
+  <dimension ref="A1:GP54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -25261,6 +25261,532 @@
         <v>136700</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>107.48</v>
+      </c>
+      <c r="H54" t="n">
+        <v>125.12</v>
+      </c>
+      <c r="I54" t="n">
+        <v>113.28</v>
+      </c>
+      <c r="J54" t="n">
+        <v>128.049</v>
+      </c>
+      <c r="K54" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>144.207</v>
+      </c>
+      <c r="M54" t="n">
+        <v>131.176</v>
+      </c>
+      <c r="N54" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="O54" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="P54" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="S54" t="n">
+        <v>167.55</v>
+      </c>
+      <c r="T54" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>217</v>
+      </c>
+      <c r="V54" t="n">
+        <v>119.65</v>
+      </c>
+      <c r="W54" t="n">
+        <v>387.9</v>
+      </c>
+      <c r="X54" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>270.05</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>346</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>93.55</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>89</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>118</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>106</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>147900</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>146800</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>126400</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>96.44</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>56.89999999999999</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>75.34999999999999</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>82.59</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>92.61</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>145710</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>148500</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>120190</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="BU54" t="n">
+        <v>81.04000000000001</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>102.579</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="BY54" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="CB54" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="CC54" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="CE54" t="n">
+        <v>112.901</v>
+      </c>
+      <c r="CF54" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="CG54" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="CH54" t="n">
+        <v>32014.25</v>
+      </c>
+      <c r="CM54" t="n">
+        <v>58050</v>
+      </c>
+      <c r="CN54" t="n">
+        <v>29754.62</v>
+      </c>
+      <c r="CQ54" t="n">
+        <v>73880</v>
+      </c>
+      <c r="CS54" t="n">
+        <v>47.799</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>47281.86</v>
+      </c>
+      <c r="CU54" t="n">
+        <v>41575.111</v>
+      </c>
+      <c r="CV54" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="CW54" t="n">
+        <v>36128.597</v>
+      </c>
+      <c r="CX54" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="CZ54" t="n">
+        <v>166380</v>
+      </c>
+      <c r="DA54" t="n">
+        <v>106</v>
+      </c>
+      <c r="DB54" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="DC54" t="n">
+        <v>168440</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>104</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>80.15000000000001</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>81</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>122000</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>109</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DJ54" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DK54" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="DL54" t="n">
+        <v>107</v>
+      </c>
+      <c r="DM54" t="n">
+        <v>85</v>
+      </c>
+      <c r="DN54" t="n">
+        <v>51.45000000000001</v>
+      </c>
+      <c r="DO54" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="DP54" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DQ54" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="DR54" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="DS54" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="DT54" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="DU54" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="DV54" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="DW54" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="DX54" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="DY54" t="n">
+        <v>109</v>
+      </c>
+      <c r="DZ54" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="EA54" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="EB54" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="EC54" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="ED54" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="EF54" t="n">
+        <v>110</v>
+      </c>
+      <c r="EG54" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="EH54" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="EI54" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="EJ54" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="EK54" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="EL54" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="EM54" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="EN54" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="EO54" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="EP54" t="n">
+        <v>110</v>
+      </c>
+      <c r="EQ54" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="ER54" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="ES54" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="ET54" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EU54" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="EV54" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="EW54" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="EX54" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="EY54" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="EZ54" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="FA54" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="FB54" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="FC54" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="FD54" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="FE54" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="FF54" t="n">
+        <v>103</v>
+      </c>
+      <c r="FG54" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="FH54" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="FI54" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="FJ54" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="FK54" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="FL54" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="FM54" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FN54" t="n">
+        <v>103</v>
+      </c>
+      <c r="FO54" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FP54" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="FQ54" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FR54" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="FS54" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="FT54" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FU54" t="n">
+        <v>100</v>
+      </c>
+      <c r="FV54" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="FW54" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="FY54" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="FZ54" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="GA54" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="GB54" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GC54" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="GD54" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="GE54" t="n">
+        <v>106</v>
+      </c>
+      <c r="GH54" t="n">
+        <v>100.341</v>
+      </c>
+      <c r="GI54" t="n">
+        <v>147000</v>
+      </c>
+      <c r="GJ54" t="n">
+        <v>136420</v>
+      </c>
+      <c r="GL54" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="GM54" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="GN54" t="n">
+        <v>102</v>
+      </c>
+      <c r="GO54" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GP54" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GP54"/>
+  <dimension ref="A1:GP55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -25787,6 +25787,535 @@
         <v>26.2</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>107.56</v>
+      </c>
+      <c r="H55" t="n">
+        <v>125.18</v>
+      </c>
+      <c r="I55" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="J55" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="K55" t="n">
+        <v>120.05</v>
+      </c>
+      <c r="L55" t="n">
+        <v>144.24</v>
+      </c>
+      <c r="M55" t="n">
+        <v>131</v>
+      </c>
+      <c r="N55" t="n">
+        <v>123.249</v>
+      </c>
+      <c r="O55" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="P55" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="S55" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="T55" t="n">
+        <v>295.05</v>
+      </c>
+      <c r="U55" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="V55" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="W55" t="n">
+        <v>388</v>
+      </c>
+      <c r="X55" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>98</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>344.8</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>127.78</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>148100</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>148000</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>126600</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>96.70999999999999</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>54.70999999999999</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>55.77000000000001</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>81.70999999999999</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>76.31</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>92.34999999999998</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>104.49</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>147300</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>148700</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>120280</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>80.84</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>102.48</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>83.05</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="BZ55" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA55" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="CB55" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="CC55" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="CE55" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="CF55" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="CG55" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="CH55" t="n">
+        <v>32014.25</v>
+      </c>
+      <c r="CM55" t="n">
+        <v>59400</v>
+      </c>
+      <c r="CN55" t="n">
+        <v>29754.62</v>
+      </c>
+      <c r="CQ55" t="n">
+        <v>73950</v>
+      </c>
+      <c r="CS55" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="CT55" t="n">
+        <v>47281.86</v>
+      </c>
+      <c r="CU55" t="n">
+        <v>41575.111</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>36128.597</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="CZ55" t="n">
+        <v>167740</v>
+      </c>
+      <c r="DA55" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DB55" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="DC55" t="n">
+        <v>168300</v>
+      </c>
+      <c r="DD55" t="n">
+        <v>104</v>
+      </c>
+      <c r="DE55" t="n">
+        <v>79.88</v>
+      </c>
+      <c r="DF55" t="n">
+        <v>81.01000000000001</v>
+      </c>
+      <c r="DG55" t="n">
+        <v>117010</v>
+      </c>
+      <c r="DH55" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="DI55" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DJ55" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DK55" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="DL55" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="DM55" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="DN55" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="DO55" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="DP55" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DQ55" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="DR55" t="n">
+        <v>112</v>
+      </c>
+      <c r="DS55" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DT55" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DU55" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="DV55" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="DW55" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="DX55" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="DY55" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="DZ55" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="EA55" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="EB55" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="EC55" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="ED55" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="EE55" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="EF55" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="EG55" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="EH55" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="EI55" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="EJ55" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="EK55" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="EL55" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="EM55" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="EN55" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="EO55" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="EP55" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="EQ55" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="ER55" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="ES55" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="ET55" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="EU55" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="EV55" t="n">
+        <v>104</v>
+      </c>
+      <c r="EW55" t="n">
+        <v>106</v>
+      </c>
+      <c r="EX55" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="EY55" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="EZ55" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FA55" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FB55" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="FC55" t="n">
+        <v>106</v>
+      </c>
+      <c r="FD55" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="FE55" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="FF55" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FG55" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="FH55" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="FI55" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="FJ55" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="FK55" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="FL55" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="FM55" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="FN55" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FO55" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="FP55" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="FQ55" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FR55" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="FS55" t="n">
+        <v>103</v>
+      </c>
+      <c r="FT55" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="FU55" t="n">
+        <v>99.99000000000001</v>
+      </c>
+      <c r="FV55" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="FW55" t="n">
+        <v>103</v>
+      </c>
+      <c r="FX55" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FY55" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="FZ55" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GA55" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GB55" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GC55" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="GD55" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="GE55" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="GH55" t="n">
+        <v>100.345</v>
+      </c>
+      <c r="GI55" t="n">
+        <v>147950</v>
+      </c>
+      <c r="GJ55" t="n">
+        <v>136450</v>
+      </c>
+      <c r="GL55" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="GM55" t="n">
+        <v>99.99999999999999</v>
+      </c>
+      <c r="GO55" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="GP55" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -15,9 +15,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,11 +49,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FY54"/>
+  <dimension ref="A1:FY56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -25402,6 +25404,1000 @@
         <v>26.2</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G55" t="n">
+        <v>107.56</v>
+      </c>
+      <c r="H55" t="n">
+        <v>125.18</v>
+      </c>
+      <c r="I55" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="J55" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="K55" t="n">
+        <v>120.05</v>
+      </c>
+      <c r="L55" t="n">
+        <v>144.24</v>
+      </c>
+      <c r="M55" t="n">
+        <v>131</v>
+      </c>
+      <c r="N55" t="n">
+        <v>123.249</v>
+      </c>
+      <c r="O55" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="P55" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="S55" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="T55" t="n">
+        <v>295.05</v>
+      </c>
+      <c r="U55" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="V55" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="W55" t="n">
+        <v>388</v>
+      </c>
+      <c r="X55" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>98</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>344.8</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>127.78</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>148100</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>148000</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>126600</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>96.70999999999999</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>54.70999999999999</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>55.77000000000001</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>81.70999999999999</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>76.31</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>92.34999999999998</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>104.49</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>147300</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>148700</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>120280</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>80.84</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>102.48</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>83.05</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="BZ55" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA55" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="CB55" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="CC55" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="CE55" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="CF55" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="CG55" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="CH55" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="CI55" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="CJ55" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="CL55" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="CM55" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="CN55" t="n">
+        <v>104</v>
+      </c>
+      <c r="CO55" t="n">
+        <v>79.88</v>
+      </c>
+      <c r="CP55" t="n">
+        <v>81.01000000000001</v>
+      </c>
+      <c r="CQ55" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="CR55" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="CS55" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="CT55" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="CU55" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="CY55" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="CZ55" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="DA55" t="n">
+        <v>112</v>
+      </c>
+      <c r="DB55" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DC55" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DD55" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="DE55" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="DF55" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="DG55" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="DH55" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="DI55" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="DJ55" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DK55" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="DL55" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="DM55" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DN55" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DO55" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="DP55" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="DQ55" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="DR55" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DS55" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="DT55" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="DU55" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="DV55" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="DW55" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DX55" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="DY55" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="DZ55" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="EA55" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="EB55" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="EC55" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="ED55" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="EE55" t="n">
+        <v>104</v>
+      </c>
+      <c r="EF55" t="n">
+        <v>106</v>
+      </c>
+      <c r="EG55" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="EH55" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="EI55" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EJ55" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EK55" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EL55" t="n">
+        <v>106</v>
+      </c>
+      <c r="EM55" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="EN55" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="EO55" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EP55" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="EQ55" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="ER55" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="ES55" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="ET55" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="EU55" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EV55" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="EW55" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EX55" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="EY55" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="EZ55" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FA55" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="FB55" t="n">
+        <v>103</v>
+      </c>
+      <c r="FC55" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="FD55" t="n">
+        <v>99.99000000000001</v>
+      </c>
+      <c r="FE55" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="FF55" t="n">
+        <v>103</v>
+      </c>
+      <c r="FG55" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FH55" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="FI55" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FJ55" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="FK55" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FL55" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="FM55" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="FN55" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="FQ55" t="n">
+        <v>100.345</v>
+      </c>
+      <c r="FR55" t="n">
+        <v>147950</v>
+      </c>
+      <c r="FS55" t="n">
+        <v>136450</v>
+      </c>
+      <c r="FU55" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FV55" t="n">
+        <v>99.99999999999999</v>
+      </c>
+      <c r="FX55" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="FY55" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G56" t="n">
+        <v>107.74</v>
+      </c>
+      <c r="H56" t="n">
+        <v>125.44</v>
+      </c>
+      <c r="I56" t="n">
+        <v>113.58</v>
+      </c>
+      <c r="J56" t="n">
+        <v>128.18</v>
+      </c>
+      <c r="K56" t="n">
+        <v>120.35</v>
+      </c>
+      <c r="L56" t="n">
+        <v>144.199</v>
+      </c>
+      <c r="M56" t="n">
+        <v>130.89</v>
+      </c>
+      <c r="N56" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>125.486</v>
+      </c>
+      <c r="P56" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>112.95</v>
+      </c>
+      <c r="S56" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="T56" t="n">
+        <v>295.65</v>
+      </c>
+      <c r="U56" t="n">
+        <v>218.15</v>
+      </c>
+      <c r="V56" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="W56" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="X56" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>271.25</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>93.87</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>148240</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>149400</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>126500</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>96.62999999999998</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>95.79999999999998</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>56.49999999999999</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>78.43000000000001</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>56.13000000000001</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>58.11999999999999</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>81.41</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>75.97</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>69.39</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>165.95</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>147290</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>108</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>148800</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>120300</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>80.95</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="BY56" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="CA56" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="CB56" t="n">
+        <v>118.05</v>
+      </c>
+      <c r="CC56" t="n">
+        <v>121.85</v>
+      </c>
+      <c r="CE56" t="n">
+        <v>113.579</v>
+      </c>
+      <c r="CF56" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="CG56" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="CH56" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="CI56" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="CJ56" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="CK56" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="CL56" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="CM56" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="CN56" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="CO56" t="n">
+        <v>79.26000000000001</v>
+      </c>
+      <c r="CP56" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="CQ56" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="CR56" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="CS56" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="CT56" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="CU56" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="CW56" t="n">
+        <v>51.45000000000001</v>
+      </c>
+      <c r="CX56" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="CY56" t="n">
+        <v>108</v>
+      </c>
+      <c r="CZ56" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="DA56" t="n">
+        <v>112</v>
+      </c>
+      <c r="DB56" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="DC56" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DD56" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="DE56" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="DF56" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="DG56" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="DH56" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DI56" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="DJ56" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="DK56" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="DL56" t="n">
+        <v>109</v>
+      </c>
+      <c r="DM56" t="n">
+        <v>112.05</v>
+      </c>
+      <c r="DN56" t="n">
+        <v>109</v>
+      </c>
+      <c r="DO56" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="DP56" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="DQ56" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="DR56" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DS56" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="DT56" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="DU56" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="DV56" t="n">
+        <v>106</v>
+      </c>
+      <c r="DW56" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DX56" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DY56" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DZ56" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="EA56" t="n">
+        <v>109</v>
+      </c>
+      <c r="EB56" t="n">
+        <v>107</v>
+      </c>
+      <c r="EC56" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="ED56" t="n">
+        <v>107</v>
+      </c>
+      <c r="EE56" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EF56" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="EG56" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="EH56" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="EI56" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="EJ56" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EK56" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="EL56" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="EM56" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="EN56" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="EO56" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EP56" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="EQ56" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="ER56" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="ES56" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="ET56" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="EU56" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EV56" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="EW56" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EX56" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="EY56" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="EZ56" t="n">
+        <v>102</v>
+      </c>
+      <c r="FA56" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="FB56" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="FC56" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="FD56" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="FE56" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="FF56" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="FG56" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FH56" t="n">
+        <v>105</v>
+      </c>
+      <c r="FI56" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FJ56" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="FK56" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="FL56" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="FM56" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FN56" t="n">
+        <v>105</v>
+      </c>
+      <c r="FQ56" t="n">
+        <v>100.54</v>
+      </c>
+      <c r="FR56" t="n">
+        <v>148000</v>
+      </c>
+      <c r="FS56" t="n">
+        <v>137030</v>
+      </c>
+      <c r="FU56" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="FV56" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="FX56" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FY56" t="n">
+        <v>25.511</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FY56"/>
+  <dimension ref="A1:GA56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1332,6 +1332,16 @@
           <t>MR44D</t>
         </is>
       </c>
+      <c r="FZ1" t="inlineStr">
+        <is>
+          <t>PUA36</t>
+        </is>
+      </c>
+      <c r="GA1" t="inlineStr">
+        <is>
+          <t>NDG34</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -2157,6 +2167,9 @@
       <c r="FN3" t="n">
         <v>101.8</v>
       </c>
+      <c r="FZ3" t="n">
+        <v>108.8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2584,6 +2597,9 @@
       <c r="FO4" t="n">
         <v>100.3</v>
       </c>
+      <c r="FZ4" t="n">
+        <v>108.45</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3014,6 +3030,9 @@
       <c r="FN5" t="n">
         <v>101.5</v>
       </c>
+      <c r="FZ5" t="n">
+        <v>108.4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3459,6 +3478,9 @@
       <c r="FN6" t="n">
         <v>101.4</v>
       </c>
+      <c r="FZ6" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3916,6 +3938,9 @@
       <c r="FN7" t="n">
         <v>102.2</v>
       </c>
+      <c r="FZ7" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4367,6 +4392,9 @@
       <c r="FN8" t="n">
         <v>101.3</v>
       </c>
+      <c r="FZ8" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4824,6 +4852,9 @@
       <c r="FN9" t="n">
         <v>101.95</v>
       </c>
+      <c r="FZ9" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5284,6 +5315,9 @@
       <c r="FN10" t="n">
         <v>102</v>
       </c>
+      <c r="FZ10" t="n">
+        <v>110.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6643,6 +6677,9 @@
       <c r="FO13" t="n">
         <v>98.55</v>
       </c>
+      <c r="FZ13" t="n">
+        <v>111.65</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7103,6 +7140,9 @@
       <c r="FN14" t="n">
         <v>102.5</v>
       </c>
+      <c r="FZ14" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8023,6 +8063,9 @@
       <c r="FN16" t="n">
         <v>102.75</v>
       </c>
+      <c r="FZ16" t="n">
+        <v>112.55</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8703,6 +8746,9 @@
       <c r="FN18" t="n">
         <v>102.7</v>
       </c>
+      <c r="FZ18" t="n">
+        <v>113.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10104,6 +10150,9 @@
       <c r="FN21" t="n">
         <v>102.6</v>
       </c>
+      <c r="FZ21" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11045,6 +11094,9 @@
       <c r="FN23" t="n">
         <v>102.5</v>
       </c>
+      <c r="FZ23" t="n">
+        <v>112.55</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11514,6 +11566,9 @@
       <c r="FN24" t="n">
         <v>102.7</v>
       </c>
+      <c r="FZ24" t="n">
+        <v>112.55</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11986,6 +12041,9 @@
       <c r="FN25" t="n">
         <v>103</v>
       </c>
+      <c r="FZ25" t="n">
+        <v>112.3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12455,6 +12513,9 @@
       <c r="FN26" t="n">
         <v>102.9</v>
       </c>
+      <c r="FZ26" t="n">
+        <v>112.45</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12918,6 +12979,9 @@
       <c r="FN27" t="n">
         <v>103</v>
       </c>
+      <c r="FZ27" t="n">
+        <v>112.55</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13384,6 +13448,9 @@
       <c r="FN28" t="n">
         <v>103</v>
       </c>
+      <c r="FZ28" t="n">
+        <v>112.15</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14334,6 +14401,9 @@
       <c r="FN30" t="n">
         <v>102.5</v>
       </c>
+      <c r="FZ30" t="n">
+        <v>112.85</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14815,6 +14885,9 @@
       <c r="FP31" t="n">
         <v>100.1</v>
       </c>
+      <c r="FZ31" t="n">
+        <v>112.8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15299,6 +15372,9 @@
       <c r="FN32" t="n">
         <v>103</v>
       </c>
+      <c r="FZ32" t="n">
+        <v>112.8</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15774,6 +15850,9 @@
       <c r="FN33" t="n">
         <v>103</v>
       </c>
+      <c r="FZ33" t="n">
+        <v>111.85</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16258,6 +16337,9 @@
       <c r="FN34" t="n">
         <v>103</v>
       </c>
+      <c r="FZ34" t="n">
+        <v>112.8</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -17380,6 +17462,9 @@
       <c r="FN37" t="n">
         <v>103.25</v>
       </c>
+      <c r="FZ37" t="n">
+        <v>112.8</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -17864,6 +17949,9 @@
       <c r="FP38" t="n">
         <v>100.4</v>
       </c>
+      <c r="FZ38" t="n">
+        <v>112.85</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -18345,6 +18433,9 @@
       <c r="FN39" t="n">
         <v>103</v>
       </c>
+      <c r="FZ39" t="n">
+        <v>112.9</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -18826,6 +18917,9 @@
       <c r="FP40" t="n">
         <v>100</v>
       </c>
+      <c r="FZ40" t="n">
+        <v>112.9</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -19316,6 +19410,9 @@
       <c r="FP41" t="n">
         <v>100.4</v>
       </c>
+      <c r="FZ41" t="n">
+        <v>113.65</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -19800,6 +19897,9 @@
       <c r="FP42" t="n">
         <v>100.35</v>
       </c>
+      <c r="FZ42" t="n">
+        <v>113.95</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -21264,6 +21364,9 @@
       <c r="FO45" t="n">
         <v>103.9</v>
       </c>
+      <c r="FZ45" t="n">
+        <v>114.2</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -21754,6 +21857,9 @@
       <c r="FP46" t="n">
         <v>100.05</v>
       </c>
+      <c r="FZ46" t="n">
+        <v>114.4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -22244,6 +22350,9 @@
       <c r="FP47" t="n">
         <v>100.55</v>
       </c>
+      <c r="FZ47" t="n">
+        <v>114.45</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -22734,6 +22843,9 @@
       <c r="FP48" t="n">
         <v>100.75</v>
       </c>
+      <c r="FZ48" t="n">
+        <v>111.45</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -23227,6 +23339,9 @@
       <c r="FP49" t="n">
         <v>100.75</v>
       </c>
+      <c r="FZ49" t="n">
+        <v>111.4</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -23703,6 +23818,9 @@
       <c r="FN50" t="n">
         <v>103.75</v>
       </c>
+      <c r="FZ50" t="n">
+        <v>110.95</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -24178,6 +24296,12 @@
       </c>
       <c r="FP51" t="n">
         <v>100.6</v>
+      </c>
+      <c r="FZ51" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="GA51" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="52">
@@ -24684,6 +24808,12 @@
       <c r="FY52" t="n">
         <v>25.499</v>
       </c>
+      <c r="FZ52" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="GA52" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -24907,6 +25037,12 @@
       <c r="FS53" t="n">
         <v>136700</v>
       </c>
+      <c r="FZ53" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="GA53" t="n">
+        <v>103.1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -25403,6 +25539,12 @@
       <c r="FY54" t="n">
         <v>26.2</v>
       </c>
+      <c r="FZ54" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="GA54" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -25900,6 +26042,12 @@
       <c r="FY55" t="n">
         <v>25.9</v>
       </c>
+      <c r="FZ55" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="GA55" t="n">
+        <v>104.05</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -26396,6 +26544,12 @@
       </c>
       <c r="FY56" t="n">
         <v>25.511</v>
+      </c>
+      <c r="FZ56" t="n">
+        <v>111.05</v>
+      </c>
+      <c r="GA56" t="n">
+        <v>104.25</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GA56"/>
+  <dimension ref="A1:GB57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1342,6 +1342,11 @@
           <t>NDG34</t>
         </is>
       </c>
+      <c r="GB1" t="inlineStr">
+        <is>
+          <t>AEC3D</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -26552,6 +26557,508 @@
         <v>104.25</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>107.829</v>
+      </c>
+      <c r="H57" t="n">
+        <v>125.46</v>
+      </c>
+      <c r="I57" t="n">
+        <v>113.69</v>
+      </c>
+      <c r="J57" t="n">
+        <v>128.31</v>
+      </c>
+      <c r="K57" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="L57" t="n">
+        <v>144.4</v>
+      </c>
+      <c r="M57" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>123.45</v>
+      </c>
+      <c r="O57" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="P57" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>113</v>
+      </c>
+      <c r="S57" t="n">
+        <v>168.6</v>
+      </c>
+      <c r="T57" t="n">
+        <v>296.35</v>
+      </c>
+      <c r="U57" t="n">
+        <v>218.8</v>
+      </c>
+      <c r="V57" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="W57" t="n">
+        <v>388.35</v>
+      </c>
+      <c r="X57" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>272.5</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>347.85</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>90.22</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>128.24</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>114</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>148110</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>148700</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>126480</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>54.40000000000001</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>55.50000000000001</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>75.51000000000001</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>92.50000000000001</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>98</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>104.839</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>146800</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>148650</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>120450</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="BU57" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="BV57" t="n">
+        <v>102.725</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="BZ57" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA57" t="n">
+        <v>94.10000000000001</v>
+      </c>
+      <c r="CB57" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="CC57" t="n">
+        <v>122.05</v>
+      </c>
+      <c r="CE57" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="CF57" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="CG57" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="CH57" t="n">
+        <v>48</v>
+      </c>
+      <c r="CI57" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="CL57" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="CM57" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="CN57" t="n">
+        <v>104</v>
+      </c>
+      <c r="CO57" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="CP57" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="CQ57" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="CR57" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="CS57" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="CT57" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="CU57" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="CV57" t="n">
+        <v>85.02</v>
+      </c>
+      <c r="CW57" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="CX57" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="CY57" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DA57" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="DB57" t="n">
+        <v>110</v>
+      </c>
+      <c r="DC57" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DD57" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DE57" t="n">
+        <v>110</v>
+      </c>
+      <c r="DF57" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="DG57" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="DH57" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DI57" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="DJ57" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="DK57" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="DL57" t="n">
+        <v>109</v>
+      </c>
+      <c r="DM57" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="DN57" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DO57" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="DP57" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="DQ57" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="DR57" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DS57" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="DT57" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DU57" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="DV57" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="DW57" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DX57" t="n">
+        <v>105</v>
+      </c>
+      <c r="DY57" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DZ57" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="EA57" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="EB57" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="EC57" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="ED57" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="EE57" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="EF57" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="EG57" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="EH57" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="EI57" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="EJ57" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EK57" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EL57" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="EM57" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="EN57" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="EP57" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="EQ57" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="ER57" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="ES57" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="ET57" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="EU57" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="EV57" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="EW57" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="EX57" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="EY57" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="EZ57" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="FA57" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="FB57" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="FC57" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="FD57" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="FE57" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="FF57" t="n">
+        <v>104</v>
+      </c>
+      <c r="FG57" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FH57" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="FI57" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="FJ57" t="n">
+        <v>104</v>
+      </c>
+      <c r="FK57" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FL57" t="n">
+        <v>102</v>
+      </c>
+      <c r="FM57" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="FN57" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="FP57" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="FQ57" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="FS57" t="n">
+        <v>137100</v>
+      </c>
+      <c r="FU57" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="FV57" t="n">
+        <v>100</v>
+      </c>
+      <c r="FW57" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="FX57" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="FY57" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="FZ57" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="GA57" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GB57" t="n">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GB57"/>
+  <dimension ref="A1:GB58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -27059,6 +27059,514 @@
         <v>101</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>107.895</v>
+      </c>
+      <c r="H58" t="n">
+        <v>125.575</v>
+      </c>
+      <c r="I58" t="n">
+        <v>113.82</v>
+      </c>
+      <c r="J58" t="n">
+        <v>128.45</v>
+      </c>
+      <c r="K58" t="n">
+        <v>120.375</v>
+      </c>
+      <c r="L58" t="n">
+        <v>144.451</v>
+      </c>
+      <c r="M58" t="n">
+        <v>131</v>
+      </c>
+      <c r="N58" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="O58" t="n">
+        <v>125.3</v>
+      </c>
+      <c r="P58" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="S58" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="T58" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="V58" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="W58" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="X58" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>272.5</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>347.6</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>90.12</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>119.05</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>147690</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>149010</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>126200</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>54.40000000000001</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>56.43</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>57.99999999999999</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>84.86</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>76.01000000000001</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>69</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>93.01000000000001</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>166.25</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>104.89</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>146500</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>148400</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>120300</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="BU58" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="BV58" t="n">
+        <v>102.899</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="BZ58" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>94</v>
+      </c>
+      <c r="CB58" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="CC58" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="CE58" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="CF58" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="CG58" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="CH58" t="n">
+        <v>48</v>
+      </c>
+      <c r="CI58" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="CJ58" t="n">
+        <v>112</v>
+      </c>
+      <c r="CL58" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="CM58" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="CN58" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="CO58" t="n">
+        <v>78.61</v>
+      </c>
+      <c r="CP58" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="CQ58" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="CR58" t="n">
+        <v>109</v>
+      </c>
+      <c r="CS58" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="CT58" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="CU58" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="CV58" t="n">
+        <v>84.95999999999999</v>
+      </c>
+      <c r="CW58" t="n">
+        <v>51.99</v>
+      </c>
+      <c r="CX58" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="CY58" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="CZ58" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="DA58" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="DB58" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DC58" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DD58" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DE58" t="n">
+        <v>110</v>
+      </c>
+      <c r="DF58" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="DG58" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="DH58" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="DI58" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="DJ58" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DK58" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="DL58" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="DM58" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="DN58" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DO58" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="DP58" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="DQ58" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="DR58" t="n">
+        <v>108</v>
+      </c>
+      <c r="DS58" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="DT58" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DU58" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="DV58" t="n">
+        <v>107</v>
+      </c>
+      <c r="DW58" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="DX58" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="DY58" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DZ58" t="n">
+        <v>108</v>
+      </c>
+      <c r="EA58" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="EB58" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EC58" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="ED58" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="EE58" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="EF58" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="EG58" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="EH58" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="EI58" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="EJ58" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EK58" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EL58" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="EM58" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="EN58" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="EO58" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="EQ58" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="ER58" t="n">
+        <v>104</v>
+      </c>
+      <c r="ES58" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="ET58" t="n">
+        <v>102</v>
+      </c>
+      <c r="EU58" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EV58" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="EW58" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EX58" t="n">
+        <v>105</v>
+      </c>
+      <c r="EY58" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="EZ58" t="n">
+        <v>102</v>
+      </c>
+      <c r="FA58" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="FB58" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FC58" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FD58" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="FE58" t="n">
+        <v>105</v>
+      </c>
+      <c r="FF58" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="FG58" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="FH58" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="FI58" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FJ58" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="FK58" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FL58" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="FM58" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="FN58" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="FP58" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FQ58" t="n">
+        <v>100.77</v>
+      </c>
+      <c r="FS58" t="n">
+        <v>136900</v>
+      </c>
+      <c r="FU58" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="FV58" t="n">
+        <v>99.89999999999999</v>
+      </c>
+      <c r="FW58" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="FX58" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="FY58" t="n">
+        <v>26</v>
+      </c>
+      <c r="FZ58" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="GA58" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GB58" t="n">
+        <v>100.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GB58"/>
+  <dimension ref="A1:GB59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -27567,6 +27567,226 @@
         <v>100.85</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>107.96</v>
+      </c>
+      <c r="H59" t="n">
+        <v>125.605</v>
+      </c>
+      <c r="I59" t="n">
+        <v>113.885</v>
+      </c>
+      <c r="J59" t="n">
+        <v>128.53</v>
+      </c>
+      <c r="K59" t="n">
+        <v>120.551</v>
+      </c>
+      <c r="L59" t="n">
+        <v>144.55</v>
+      </c>
+      <c r="M59" t="n">
+        <v>131.15</v>
+      </c>
+      <c r="N59" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="O59" t="n">
+        <v>125.3</v>
+      </c>
+      <c r="P59" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="S59" t="n">
+        <v>169</v>
+      </c>
+      <c r="T59" t="n">
+        <v>297.85</v>
+      </c>
+      <c r="U59" t="n">
+        <v>219.15</v>
+      </c>
+      <c r="V59" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="W59" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="X59" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>272.65</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>347</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>94.23</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>128.35</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>107</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>104</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>148100</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>149000</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>126290</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>96.20999999999999</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>54.45</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>77.61</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>80.29000000000001</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>84.66</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>75.56999999999999</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>93.29000000000001</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="BI59" t="n">
+        <v>104.91</v>
+      </c>
+      <c r="BK59" t="n">
+        <v>146700</v>
+      </c>
+      <c r="BQ59" t="n">
+        <v>148400</v>
+      </c>
+      <c r="BR59" t="n">
+        <v>120300</v>
+      </c>
+      <c r="BS59" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="BT59" t="n">
+        <v>84.55</v>
+      </c>
+      <c r="BU59" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="BV59" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>94.76000000000001</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>84.89</v>
+      </c>
+      <c r="BY59" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="BZ59" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA59" t="n">
+        <v>93.69</v>
+      </c>
+      <c r="CB59" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="CC59" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="CE59" t="n">
+        <v>113.82</v>
+      </c>
+      <c r="CF59" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="CG59" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="FQ59" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="FS59" t="n">
+        <v>136890</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GB59"/>
+  <dimension ref="A1:GB60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -27787,6 +27787,505 @@
         <v>136890</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>125.71</v>
+      </c>
+      <c r="I60" t="n">
+        <v>113.919</v>
+      </c>
+      <c r="J60" t="n">
+        <v>128.65</v>
+      </c>
+      <c r="K60" t="n">
+        <v>120.831</v>
+      </c>
+      <c r="L60" t="n">
+        <v>144.79</v>
+      </c>
+      <c r="M60" t="n">
+        <v>131.17</v>
+      </c>
+      <c r="N60" t="n">
+        <v>123.57</v>
+      </c>
+      <c r="O60" t="n">
+        <v>125.85</v>
+      </c>
+      <c r="P60" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="S60" t="n">
+        <v>169.35</v>
+      </c>
+      <c r="T60" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>219.55</v>
+      </c>
+      <c r="V60" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="W60" t="n">
+        <v>388.35</v>
+      </c>
+      <c r="X60" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>272.9</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>346.8</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>89.81999999999999</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>128.45</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>119.15</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>115.65</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>147850</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>147570</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>126260</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>77.52</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>80.28</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>72.20999999999999</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>58.22999999999999</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>92.75000000000001</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>166.45</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>105</v>
+      </c>
+      <c r="BK60" t="n">
+        <v>146500</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>113.95</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>148400</v>
+      </c>
+      <c r="BR60" t="n">
+        <v>119870</v>
+      </c>
+      <c r="BS60" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="BT60" t="n">
+        <v>84.29000000000001</v>
+      </c>
+      <c r="BU60" t="n">
+        <v>81.29000000000001</v>
+      </c>
+      <c r="BV60" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>95.48999999999999</v>
+      </c>
+      <c r="BX60" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="BY60" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="BZ60" t="n">
+        <v>146800</v>
+      </c>
+      <c r="CA60" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="CB60" t="n">
+        <v>118.95</v>
+      </c>
+      <c r="CC60" t="n">
+        <v>122.49</v>
+      </c>
+      <c r="CE60" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="CF60" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="CG60" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="CH60" t="n">
+        <v>48</v>
+      </c>
+      <c r="CI60" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="CJ60" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="CL60" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="CM60" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="CN60" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="CO60" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="CP60" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="CQ60" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="CR60" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="CS60" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="CT60" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="CU60" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="CV60" t="n">
+        <v>85.03</v>
+      </c>
+      <c r="CW60" t="n">
+        <v>51.46999999999999</v>
+      </c>
+      <c r="CX60" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="CY60" t="n">
+        <v>108</v>
+      </c>
+      <c r="CZ60" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="DA60" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="DB60" t="n">
+        <v>110</v>
+      </c>
+      <c r="DC60" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DD60" t="n">
+        <v>108</v>
+      </c>
+      <c r="DE60" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DF60" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="DG60" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DH60" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DI60" t="n">
+        <v>113.15</v>
+      </c>
+      <c r="DJ60" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="DK60" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="DL60" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DM60" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="DN60" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DO60" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="DP60" t="n">
+        <v>93.69</v>
+      </c>
+      <c r="DQ60" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="DR60" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DS60" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="DT60" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="DU60" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="DV60" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="DW60" t="n">
+        <v>107</v>
+      </c>
+      <c r="DX60" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DY60" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="DZ60" t="n">
+        <v>108</v>
+      </c>
+      <c r="EA60" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="EB60" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="EC60" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="ED60" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="EE60" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EF60" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="EG60" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="EH60" t="n">
+        <v>112</v>
+      </c>
+      <c r="EI60" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="EJ60" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EK60" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EL60" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="EM60" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="EN60" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="EO60" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EQ60" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="ER60" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="ES60" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="ET60" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="EU60" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EV60" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EW60" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EX60" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EY60" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="EZ60" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="FA60" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="FB60" t="n">
+        <v>104</v>
+      </c>
+      <c r="FC60" t="n">
+        <v>105</v>
+      </c>
+      <c r="FD60" t="n">
+        <v>100</v>
+      </c>
+      <c r="FE60" t="n">
+        <v>105</v>
+      </c>
+      <c r="FF60" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FG60" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="FH60" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="FI60" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="FJ60" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="FK60" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="FL60" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="FM60" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="FN60" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FQ60" t="n">
+        <v>100.999</v>
+      </c>
+      <c r="FS60" t="n">
+        <v>136690</v>
+      </c>
+      <c r="FU60" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="FV60" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="FX60" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="FY60" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="FZ60" t="n">
+        <v>109</v>
+      </c>
+      <c r="GA60" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="GB60" t="n">
+        <v>100.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GB60"/>
+  <dimension ref="A1:GB61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -28286,6 +28286,223 @@
         <v>100.45</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>126</v>
+      </c>
+      <c r="I61" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>128.92</v>
+      </c>
+      <c r="K61" t="n">
+        <v>121.045</v>
+      </c>
+      <c r="L61" t="n">
+        <v>145.3</v>
+      </c>
+      <c r="M61" t="n">
+        <v>131.451</v>
+      </c>
+      <c r="N61" t="n">
+        <v>123.88</v>
+      </c>
+      <c r="O61" t="n">
+        <v>125.84</v>
+      </c>
+      <c r="P61" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="S61" t="n">
+        <v>169.65</v>
+      </c>
+      <c r="T61" t="n">
+        <v>297.95</v>
+      </c>
+      <c r="U61" t="n">
+        <v>219.5</v>
+      </c>
+      <c r="V61" t="n">
+        <v>120.75</v>
+      </c>
+      <c r="W61" t="n">
+        <v>388.9</v>
+      </c>
+      <c r="X61" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>273.15</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>90</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>119.25</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>147750</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>147500</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>125800</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>54.42</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>93.93000000000001</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>71.42</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>80.89</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>75.31999999999999</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>69</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>97</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>90.06</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>105.24</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>145600</v>
+      </c>
+      <c r="BQ61" t="n">
+        <v>148380</v>
+      </c>
+      <c r="BR61" t="n">
+        <v>120000</v>
+      </c>
+      <c r="BS61" t="n">
+        <v>91.48999999999999</v>
+      </c>
+      <c r="BT61" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="BU61" t="n">
+        <v>80.95</v>
+      </c>
+      <c r="BV61" t="n">
+        <v>103.22</v>
+      </c>
+      <c r="BW61" t="n">
+        <v>95</v>
+      </c>
+      <c r="BX61" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY61" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="BZ61" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA61" t="n">
+        <v>93.48999999999999</v>
+      </c>
+      <c r="CB61" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="CC61" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="CE61" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="CF61" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="CG61" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FQ61" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="FS61" t="n">
+        <v>136740</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -24985,6 +24985,18 @@
       <c r="BK53" t="n">
         <v>146500</v>
       </c>
+      <c r="BM53" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>108.1</v>
+      </c>
       <c r="BQ53" t="n">
         <v>148450</v>
       </c>
@@ -25033,6 +25045,252 @@
       <c r="CG53" t="n">
         <v>102.4</v>
       </c>
+      <c r="CH53" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>109</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="CY53" t="n">
+        <v>108</v>
+      </c>
+      <c r="CZ53" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="DA53" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="DB53" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DC53" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="DJ53" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DK53" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="DL53" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DM53" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="DO53" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="DP53" t="n">
+        <v>93.37</v>
+      </c>
+      <c r="DQ53" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="DR53" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DS53" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="DT53" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="DU53" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="DV53" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="DW53" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="DX53" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="DY53" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="DZ53" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="EA53" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="EB53" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="EC53" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="ED53" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="EE53" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="EF53" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="EG53" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="EH53" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="EI53" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="EJ53" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EK53" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EL53" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="EM53" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="EN53" t="n">
+        <v>112</v>
+      </c>
+      <c r="EO53" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EP53" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EQ53" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="ER53" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="ES53" t="n">
+        <v>102</v>
+      </c>
+      <c r="ET53" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="EU53" t="n">
+        <v>104</v>
+      </c>
+      <c r="EV53" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="EW53" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="EX53" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EY53" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="EZ53" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="FA53" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FB53" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="FC53" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="FD53" t="n">
+        <v>100</v>
+      </c>
+      <c r="FE53" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="FF53" t="n">
+        <v>104</v>
+      </c>
+      <c r="FH53" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="FI53" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="FJ53" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="FK53" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FL53" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="FM53" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="FN53" t="n">
+        <v>106</v>
+      </c>
       <c r="FQ53" t="n">
         <v>100.369</v>
       </c>
@@ -25041,6 +25299,21 @@
       </c>
       <c r="FS53" t="n">
         <v>136700</v>
+      </c>
+      <c r="FU53" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FV53" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="FW53" t="n">
+        <v>102</v>
+      </c>
+      <c r="FX53" t="n">
+        <v>103</v>
+      </c>
+      <c r="FY53" t="n">
+        <v>25.95</v>
       </c>
       <c r="FZ53" t="n">
         <v>110.85</v>
@@ -27732,6 +28005,18 @@
       <c r="BK59" t="n">
         <v>146700</v>
       </c>
+      <c r="BM59" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>108.2</v>
+      </c>
       <c r="BQ59" t="n">
         <v>148400</v>
       </c>
@@ -27780,11 +28065,281 @@
       <c r="CG59" t="n">
         <v>102.6</v>
       </c>
+      <c r="CH59" t="n">
+        <v>47.99999999999999</v>
+      </c>
+      <c r="CI59" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="CJ59" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="CL59" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="CM59" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="CN59" t="n">
+        <v>105</v>
+      </c>
+      <c r="CO59" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="CP59" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="CQ59" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="CR59" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="CS59" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="CT59" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="CU59" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="CV59" t="n">
+        <v>84.62</v>
+      </c>
+      <c r="CW59" t="n">
+        <v>51.46999999999998</v>
+      </c>
+      <c r="CX59" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="CY59" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="CZ59" t="n">
+        <v>104</v>
+      </c>
+      <c r="DA59" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="DB59" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DC59" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="DD59" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DE59" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="DF59" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="DG59" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="DH59" t="n">
+        <v>109</v>
+      </c>
+      <c r="DI59" t="n">
+        <v>113</v>
+      </c>
+      <c r="DJ59" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="DK59" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="DL59" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="DM59" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="DN59" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DO59" t="n">
+        <v>110</v>
+      </c>
+      <c r="DP59" t="n">
+        <v>93.55</v>
+      </c>
+      <c r="DQ59" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="DR59" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DS59" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="DT59" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="DU59" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="DV59" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="DW59" t="n">
+        <v>108</v>
+      </c>
+      <c r="DX59" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="DY59" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="DZ59" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="EA59" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="EB59" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="EC59" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="ED59" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="EE59" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EF59" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="EG59" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="EH59" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="EI59" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="EJ59" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EK59" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EL59" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="EM59" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="EN59" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="EO59" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EQ59" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="ER59" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="ES59" t="n">
+        <v>102</v>
+      </c>
+      <c r="ET59" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="EU59" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="EV59" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EW59" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EX59" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EY59" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="EZ59" t="n">
+        <v>102</v>
+      </c>
+      <c r="FA59" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FB59" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FC59" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="FD59" t="n">
+        <v>99.99999999999999</v>
+      </c>
+      <c r="FE59" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="FF59" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FG59" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FH59" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="FI59" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FJ59" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="FK59" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FL59" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="FM59" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="FN59" t="n">
+        <v>106.2</v>
+      </c>
       <c r="FQ59" t="n">
         <v>100.9</v>
       </c>
       <c r="FS59" t="n">
         <v>136890</v>
+      </c>
+      <c r="FU59" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="FV59" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="FX59" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="FY59" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="FZ59" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="GA59" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GB59" t="n">
+        <v>100.85</v>
       </c>
     </row>
     <row r="60">
@@ -28448,6 +29003,18 @@
       <c r="BK61" t="n">
         <v>145600</v>
       </c>
+      <c r="BM61" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>108.55</v>
+      </c>
       <c r="BQ61" t="n">
         <v>148380</v>
       </c>
@@ -28496,11 +29063,278 @@
       <c r="CG61" t="n">
         <v>102.8</v>
       </c>
+      <c r="CH61" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="CI61" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="CJ61" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="CL61" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="CM61" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="CN61" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="CO61" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="CP61" t="n">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="CQ61" t="n">
+        <v>110</v>
+      </c>
+      <c r="CR61" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="CS61" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="CT61" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="CU61" t="n">
+        <v>107</v>
+      </c>
+      <c r="CV61" t="n">
+        <v>84.26000000000001</v>
+      </c>
+      <c r="CW61" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="CX61" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="CY61" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="CZ61" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="DA61" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="DB61" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="DC61" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DD61" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="DE61" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="DF61" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="DG61" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DH61" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DI61" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="DJ61" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="DK61" t="n">
+        <v>111</v>
+      </c>
+      <c r="DL61" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DM61" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="DN61" t="n">
+        <v>109</v>
+      </c>
+      <c r="DO61" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="DP61" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="DQ61" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="DR61" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DS61" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="DT61" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="DU61" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="DV61" t="n">
+        <v>107</v>
+      </c>
+      <c r="DW61" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DX61" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="DY61" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="DZ61" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="EA61" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="EB61" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="EC61" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="ED61" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="EE61" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="EF61" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="EG61" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="EH61" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="EI61" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="EJ61" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EK61" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EL61" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="EM61" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="EN61" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="EQ61" t="n">
+        <v>104</v>
+      </c>
+      <c r="ER61" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="ES61" t="n">
+        <v>102</v>
+      </c>
+      <c r="ET61" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="EU61" t="n">
+        <v>104</v>
+      </c>
+      <c r="EV61" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EW61" t="n">
+        <v>103</v>
+      </c>
+      <c r="EX61" t="n">
+        <v>107</v>
+      </c>
+      <c r="EY61" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="EZ61" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="FA61" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="FB61" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="FC61" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="FD61" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="FE61" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="FF61" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="FG61" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="FH61" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="FI61" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="FJ61" t="n">
+        <v>103</v>
+      </c>
+      <c r="FK61" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="FL61" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="FM61" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="FN61" t="n">
+        <v>104.9</v>
+      </c>
       <c r="FQ61" t="n">
         <v>101.18</v>
       </c>
       <c r="FS61" t="n">
         <v>136740</v>
+      </c>
+      <c r="FU61" t="n">
+        <v>99.59999999999998</v>
+      </c>
+      <c r="FV61" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="FX61" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="FY61" t="n">
+        <v>25.80099999999999</v>
+      </c>
+      <c r="FZ61" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="GA61" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GB61" t="n">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GB59"/>
+  <dimension ref="A1:GD60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1347,6 +1347,16 @@
           <t>AEC3D</t>
         </is>
       </c>
+      <c r="GC1" t="inlineStr">
+        <is>
+          <t>X29E7</t>
+        </is>
+      </c>
+      <c r="GD1" t="inlineStr">
+        <is>
+          <t>D30O6</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -28909,6 +28919,520 @@
         <v>101</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>126.04</v>
+      </c>
+      <c r="I60" t="n">
+        <v>113.993</v>
+      </c>
+      <c r="J60" t="n">
+        <v>128.51</v>
+      </c>
+      <c r="K60" t="n">
+        <v>120.36</v>
+      </c>
+      <c r="L60" t="n">
+        <v>144.65</v>
+      </c>
+      <c r="M60" t="n">
+        <v>130.25</v>
+      </c>
+      <c r="N60" t="n">
+        <v>122.51</v>
+      </c>
+      <c r="O60" t="n">
+        <v>125.45</v>
+      </c>
+      <c r="P60" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="S60" t="n">
+        <v>169.25</v>
+      </c>
+      <c r="T60" t="n">
+        <v>297.05</v>
+      </c>
+      <c r="U60" t="n">
+        <v>217.9</v>
+      </c>
+      <c r="V60" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="W60" t="n">
+        <v>385</v>
+      </c>
+      <c r="X60" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>272.65</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>344</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>118.05</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>148000</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>146610</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>126280</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>102</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>94.80000000000001</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>53.67000000000001</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>70.47</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>74</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>67</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>96</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>166.75</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>105.063</v>
+      </c>
+      <c r="BK60" t="n">
+        <v>146460</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>149110</v>
+      </c>
+      <c r="BR60" t="n">
+        <v>120000</v>
+      </c>
+      <c r="BS60" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="BT60" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="BU60" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="BV60" t="n">
+        <v>102.965</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="BX60" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY60" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ60" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA60" t="n">
+        <v>91.73999999999999</v>
+      </c>
+      <c r="CB60" t="n">
+        <v>117.55</v>
+      </c>
+      <c r="CC60" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="CE60" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="CF60" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="CG60" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="CH60" t="n">
+        <v>48.699</v>
+      </c>
+      <c r="CI60" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="CJ60" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="CL60" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="CM60" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="CN60" t="n">
+        <v>105</v>
+      </c>
+      <c r="CO60" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="CP60" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="CQ60" t="n">
+        <v>110</v>
+      </c>
+      <c r="CR60" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="CS60" t="n">
+        <v>111</v>
+      </c>
+      <c r="CT60" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="CU60" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="CV60" t="n">
+        <v>84.65000000000001</v>
+      </c>
+      <c r="CW60" t="n">
+        <v>51.63999999999999</v>
+      </c>
+      <c r="CX60" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="CY60" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="CZ60" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="DA60" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="DB60" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="DC60" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DD60" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DE60" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="DF60" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="DG60" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="DH60" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="DI60" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="DJ60" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="DK60" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="DL60" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="DM60" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="DN60" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="DO60" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="DP60" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="DQ60" t="n">
+        <v>114</v>
+      </c>
+      <c r="DR60" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DS60" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="DT60" t="n">
+        <v>110</v>
+      </c>
+      <c r="DU60" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DV60" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="DW60" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="DX60" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DY60" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="DZ60" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="EA60" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="EB60" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="EC60" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="ED60" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="EE60" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EF60" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="EG60" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="EH60" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="EI60" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="EJ60" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="EK60" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="EL60" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="EM60" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="EN60" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="EO60" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EQ60" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="ER60" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="ES60" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="ET60" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="EU60" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EV60" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="EW60" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="EX60" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="EY60" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="EZ60" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="FA60" t="n">
+        <v>104</v>
+      </c>
+      <c r="FB60" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="FC60" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="FD60" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="FE60" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="FF60" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="FG60" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FH60" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="FI60" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="FJ60" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FK60" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="FL60" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FM60" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="FN60" t="n">
+        <v>105</v>
+      </c>
+      <c r="FP60" t="n">
+        <v>101</v>
+      </c>
+      <c r="FQ60" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="FR60" t="n">
+        <v>149000</v>
+      </c>
+      <c r="FS60" t="n">
+        <v>136580</v>
+      </c>
+      <c r="FU60" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="FV60" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="FW60" t="n">
+        <v>102</v>
+      </c>
+      <c r="FX60" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FY60" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="FZ60" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="GA60" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GB60" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="GC60" t="n">
+        <v>97.84999999999999</v>
+      </c>
+      <c r="GD60" t="n">
+        <v>147920</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GD60"/>
+  <dimension ref="A1:GM61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1357,6 +1357,51 @@
           <t>D30O6</t>
         </is>
       </c>
+      <c r="GE1" t="inlineStr">
+        <is>
+          <t>PNXCD</t>
+        </is>
+      </c>
+      <c r="GF1" t="inlineStr">
+        <is>
+          <t>TTC9D</t>
+        </is>
+      </c>
+      <c r="GG1" t="inlineStr">
+        <is>
+          <t>CP40D</t>
+        </is>
+      </c>
+      <c r="GH1" t="inlineStr">
+        <is>
+          <t>PLC3D</t>
+        </is>
+      </c>
+      <c r="GI1" t="inlineStr">
+        <is>
+          <t>HJCKD</t>
+        </is>
+      </c>
+      <c r="GJ1" t="inlineStr">
+        <is>
+          <t>YM41D</t>
+        </is>
+      </c>
+      <c r="GK1" t="inlineStr">
+        <is>
+          <t>EMC1D</t>
+        </is>
+      </c>
+      <c r="GL1" t="inlineStr">
+        <is>
+          <t>MR45D</t>
+        </is>
+      </c>
+      <c r="GM1" t="inlineStr">
+        <is>
+          <t>VSCYD</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -29433,6 +29478,544 @@
         <v>147920</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="I61" t="n">
+        <v>113.99</v>
+      </c>
+      <c r="J61" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="L61" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="M61" t="n">
+        <v>129.67</v>
+      </c>
+      <c r="N61" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="O61" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="P61" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="S61" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="T61" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="U61" t="n">
+        <v>217.25</v>
+      </c>
+      <c r="V61" t="n">
+        <v>120</v>
+      </c>
+      <c r="W61" t="n">
+        <v>384.05</v>
+      </c>
+      <c r="X61" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>270</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>342.75</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>128.825</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>118.65</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>113</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>148350</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>146600</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>124740</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>102</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>94.25999999999999</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>53.45</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>92.62</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>55.40999999999999</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>77.97</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>57.22000000000001</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>79.23999999999999</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>73.84999999999999</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>92.30000000000001</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>146400</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>102</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="BQ61" t="n">
+        <v>149100</v>
+      </c>
+      <c r="BR61" t="n">
+        <v>117700</v>
+      </c>
+      <c r="BS61" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="BT61" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="BU61" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="BV61" t="n">
+        <v>102.865</v>
+      </c>
+      <c r="BW61" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="BX61" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="BY61" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="BZ61" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA61" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="CB61" t="n">
+        <v>118</v>
+      </c>
+      <c r="CC61" t="n">
+        <v>122</v>
+      </c>
+      <c r="CE61" t="n">
+        <v>114.05</v>
+      </c>
+      <c r="CF61" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="CG61" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="CH61" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="CI61" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="CJ61" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="CL61" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="CM61" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="CN61" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="CO61" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="CP61" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="CQ61" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="CR61" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="CS61" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="CT61" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="CU61" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="CV61" t="n">
+        <v>84.58</v>
+      </c>
+      <c r="CW61" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="CX61" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="CY61" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="CZ61" t="n">
+        <v>104</v>
+      </c>
+      <c r="DA61" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="DB61" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="DC61" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="DD61" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DE61" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="DF61" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="DG61" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="DH61" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="DI61" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="DJ61" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="DK61" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="DL61" t="n">
+        <v>109</v>
+      </c>
+      <c r="DM61" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="DN61" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DO61" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="DP61" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="DQ61" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="DR61" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="DS61" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="DT61" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="DU61" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="DV61" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DW61" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DX61" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="DY61" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="DZ61" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="EA61" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="EB61" t="n">
+        <v>106</v>
+      </c>
+      <c r="EC61" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="ED61" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="EE61" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="EF61" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="EG61" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="EH61" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="EI61" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="EJ61" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="EK61" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EL61" t="n">
+        <v>105</v>
+      </c>
+      <c r="EM61" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="EN61" t="n">
+        <v>111</v>
+      </c>
+      <c r="EP61" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="EQ61" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="ER61" t="n">
+        <v>104</v>
+      </c>
+      <c r="ES61" t="n">
+        <v>102</v>
+      </c>
+      <c r="ET61" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="EU61" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EV61" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EW61" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EX61" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="EY61" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="EZ61" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="FA61" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="FB61" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="FC61" t="n">
+        <v>104</v>
+      </c>
+      <c r="FD61" t="n">
+        <v>99.84999999999998</v>
+      </c>
+      <c r="FE61" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="FF61" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="FG61" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="FH61" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="FI61" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FJ61" t="n">
+        <v>102</v>
+      </c>
+      <c r="FK61" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="FL61" t="n">
+        <v>102</v>
+      </c>
+      <c r="FM61" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="FN61" t="n">
+        <v>106</v>
+      </c>
+      <c r="FP61" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="FQ61" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="FR61" t="n">
+        <v>149000</v>
+      </c>
+      <c r="FS61" t="n">
+        <v>135900</v>
+      </c>
+      <c r="FU61" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="FV61" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="FW61" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FX61" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="FY61" t="n">
+        <v>26</v>
+      </c>
+      <c r="FZ61" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="GA61" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GB61" t="n">
+        <v>100</v>
+      </c>
+      <c r="GC61" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="GD61" t="n">
+        <v>148140</v>
+      </c>
+      <c r="GE61" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="GF61" t="n">
+        <v>106</v>
+      </c>
+      <c r="GG61" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="GH61" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="GI61" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GJ61" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="GK61" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GL61" t="n">
+        <v>31.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1800,6 +1800,21 @@
       <c r="FM2" t="n">
         <v>103.9</v>
       </c>
+      <c r="GE2" t="n">
+        <v>109</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>106.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2230,6 +2245,27 @@
       <c r="FZ3" t="n">
         <v>108.8</v>
       </c>
+      <c r="GE3" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="GF3" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="GG3" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="GH3" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="GI3" t="n">
+        <v>105</v>
+      </c>
+      <c r="GJ3" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="GK3" t="n">
+        <v>105.8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2660,6 +2696,27 @@
       <c r="FZ4" t="n">
         <v>108.45</v>
       </c>
+      <c r="GE4" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>105</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GH4" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="GI4" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="GJ4" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="GK4" t="n">
+        <v>105.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3093,6 +3150,27 @@
       <c r="FZ5" t="n">
         <v>108.4</v>
       </c>
+      <c r="GE5" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GH5" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="GI5" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="GJ5" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="GK5" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3541,6 +3619,27 @@
       <c r="FZ6" t="n">
         <v>109</v>
       </c>
+      <c r="GE6" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>104</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="GH6" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="GI6" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="GJ6" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="GK6" t="n">
+        <v>105.75</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4001,6 +4100,27 @@
       <c r="FZ7" t="n">
         <v>109</v>
       </c>
+      <c r="GE7" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>104</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>104</v>
+      </c>
+      <c r="GH7" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="GI7" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GJ7" t="n">
+        <v>102</v>
+      </c>
+      <c r="GK7" t="n">
+        <v>105.15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4455,6 +4575,27 @@
       <c r="FZ8" t="n">
         <v>109</v>
       </c>
+      <c r="GE8" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>104</v>
+      </c>
+      <c r="GH8" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="GI8" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="GJ8" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GK8" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4915,6 +5056,27 @@
       <c r="FZ9" t="n">
         <v>110</v>
       </c>
+      <c r="GE9" t="n">
+        <v>112.85</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="GH9" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="GI9" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="GJ9" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GK9" t="n">
+        <v>105.55</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5378,6 +5540,27 @@
       <c r="FZ10" t="n">
         <v>110.2</v>
       </c>
+      <c r="GE10" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="GH10" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="GI10" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="GJ10" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="GK10" t="n">
+        <v>105.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5829,6 +6012,27 @@
       <c r="FN11" t="n">
         <v>101.5</v>
       </c>
+      <c r="GE11" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>104</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="GH11" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="GI11" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="GJ11" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GK11" t="n">
+        <v>104.65</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6277,6 +6481,27 @@
       <c r="FN12" t="n">
         <v>102.25</v>
       </c>
+      <c r="GE12" t="n">
+        <v>113</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GH12" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="GI12" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="GJ12" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="GK12" t="n">
+        <v>105.25</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6740,6 +6965,27 @@
       <c r="FZ13" t="n">
         <v>111.65</v>
       </c>
+      <c r="GE13" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GH13" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="GI13" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="GJ13" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="GK13" t="n">
+        <v>105.25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7203,6 +7449,27 @@
       <c r="FZ14" t="n">
         <v>110</v>
       </c>
+      <c r="GE14" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="GH14" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="GI14" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="GJ14" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GK14" t="n">
+        <v>105.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7654,6 +7921,30 @@
       <c r="FO15" t="n">
         <v>98.75</v>
       </c>
+      <c r="FW15" t="n">
+        <v>99</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="GH15" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="GI15" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GJ15" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="GK15" t="n">
+        <v>105.85</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8123,8 +8414,32 @@
       <c r="FN16" t="n">
         <v>102.75</v>
       </c>
+      <c r="FW16" t="n">
+        <v>99.20000000000002</v>
+      </c>
       <c r="FZ16" t="n">
         <v>112.55</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="GH16" t="n">
+        <v>107</v>
+      </c>
+      <c r="GI16" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="GJ16" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GK16" t="n">
+        <v>105.9</v>
       </c>
     </row>
     <row r="17">
@@ -8592,8 +8907,32 @@
       <c r="FN17" t="n">
         <v>102.7</v>
       </c>
+      <c r="FW17" t="n">
+        <v>100</v>
+      </c>
       <c r="FZ17" t="n">
         <v>113.5</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="GH17" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="GI17" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="GJ17" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GK17" t="n">
+        <v>105.85</v>
       </c>
     </row>
     <row r="18">
@@ -9058,6 +9397,30 @@
       <c r="FN18" t="n">
         <v>102.75</v>
       </c>
+      <c r="FW18" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="GG18" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="GH18" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="GI18" t="n">
+        <v>105</v>
+      </c>
+      <c r="GJ18" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GK18" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9530,6 +9893,30 @@
       <c r="FN19" t="n">
         <v>102.75</v>
       </c>
+      <c r="FW19" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="GE19" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="GF19" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="GG19" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="GH19" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="GI19" t="n">
+        <v>106</v>
+      </c>
+      <c r="GJ19" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="GK19" t="n">
+        <v>105.9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9996,8 +10383,32 @@
       <c r="FN20" t="n">
         <v>102.6</v>
       </c>
+      <c r="FW20" t="n">
+        <v>100.5</v>
+      </c>
       <c r="FZ20" t="n">
         <v>113</v>
+      </c>
+      <c r="GE20" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="GF20" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="GG20" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GH20" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="GI20" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="GJ20" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GK20" t="n">
+        <v>105.95</v>
       </c>
     </row>
     <row r="21">
@@ -10468,6 +10879,30 @@
       <c r="FN21" t="n">
         <v>102</v>
       </c>
+      <c r="FW21" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="GE21" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="GF21" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="GG21" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GH21" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="GI21" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="GJ21" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GK21" t="n">
+        <v>105.95</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10940,8 +11375,35 @@
       <c r="FN22" t="n">
         <v>102.5</v>
       </c>
+      <c r="FT22" t="n">
+        <v>95</v>
+      </c>
+      <c r="FW22" t="n">
+        <v>100.15</v>
+      </c>
       <c r="FZ22" t="n">
         <v>112.55</v>
+      </c>
+      <c r="GE22" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="GF22" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="GG22" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GH22" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="GI22" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="GJ22" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="GK22" t="n">
+        <v>106.3</v>
       </c>
     </row>
     <row r="23">
@@ -11412,8 +11874,32 @@
       <c r="FN23" t="n">
         <v>102.7</v>
       </c>
+      <c r="FW23" t="n">
+        <v>100.5</v>
+      </c>
       <c r="FZ23" t="n">
         <v>112.55</v>
+      </c>
+      <c r="GE23" t="n">
+        <v>112</v>
+      </c>
+      <c r="GF23" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="GG23" t="n">
+        <v>103</v>
+      </c>
+      <c r="GH23" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="GI23" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="GJ23" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GK23" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="24">
@@ -11887,8 +12373,32 @@
       <c r="FN24" t="n">
         <v>103</v>
       </c>
+      <c r="FW24" t="n">
+        <v>100.25</v>
+      </c>
       <c r="FZ24" t="n">
         <v>112.3</v>
+      </c>
+      <c r="GE24" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="GF24" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="GG24" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="GH24" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="GI24" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="GJ24" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="GK24" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="25">
@@ -12359,8 +12869,32 @@
       <c r="FN25" t="n">
         <v>102.9</v>
       </c>
+      <c r="FW25" t="n">
+        <v>100</v>
+      </c>
       <c r="FZ25" t="n">
         <v>112.45</v>
+      </c>
+      <c r="GE25" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="GF25" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="GG25" t="n">
+        <v>104</v>
+      </c>
+      <c r="GH25" t="n">
+        <v>107</v>
+      </c>
+      <c r="GI25" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="GJ25" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GK25" t="n">
+        <v>104.05</v>
       </c>
     </row>
     <row r="26">
@@ -12825,8 +13359,32 @@
       <c r="FN26" t="n">
         <v>103</v>
       </c>
+      <c r="FW26" t="n">
+        <v>100.15</v>
+      </c>
       <c r="FZ26" t="n">
         <v>112.55</v>
+      </c>
+      <c r="GE26" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="GF26" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="GG26" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GH26" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="GI26" t="n">
+        <v>106</v>
+      </c>
+      <c r="GJ26" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="GK26" t="n">
+        <v>106.7</v>
       </c>
     </row>
     <row r="27">
@@ -13294,8 +13852,32 @@
       <c r="FN27" t="n">
         <v>103</v>
       </c>
+      <c r="FW27" t="n">
+        <v>100.2</v>
+      </c>
       <c r="FZ27" t="n">
         <v>112.15</v>
+      </c>
+      <c r="GE27" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="GF27" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GG27" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="GH27" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="GI27" t="n">
+        <v>107</v>
+      </c>
+      <c r="GJ27" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="GK27" t="n">
+        <v>106.7</v>
       </c>
     </row>
     <row r="28">
@@ -13769,6 +14351,30 @@
       <c r="FN28" t="n">
         <v>103</v>
       </c>
+      <c r="FW28" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="GE28" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="GF28" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GG28" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="GH28" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="GI28" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="GJ28" t="n">
+        <v>103</v>
+      </c>
+      <c r="GK28" t="n">
+        <v>106.1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14247,8 +14853,32 @@
       <c r="FN29" t="n">
         <v>102.5</v>
       </c>
+      <c r="FW29" t="n">
+        <v>100.2</v>
+      </c>
       <c r="FZ29" t="n">
         <v>112.85</v>
+      </c>
+      <c r="GE29" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="GF29" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="GG29" t="n">
+        <v>104</v>
+      </c>
+      <c r="GH29" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="GI29" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="GJ29" t="n">
+        <v>103</v>
+      </c>
+      <c r="GK29" t="n">
+        <v>106.7</v>
       </c>
     </row>
     <row r="30">
@@ -14731,8 +15361,29 @@
       <c r="FP30" t="n">
         <v>100.1</v>
       </c>
+      <c r="FW30" t="n">
+        <v>100.6</v>
+      </c>
       <c r="FZ30" t="n">
         <v>112.8</v>
+      </c>
+      <c r="GE30" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="GF30" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="GG30" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="GH30" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="GI30" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="GJ30" t="n">
+        <v>102.65</v>
       </c>
     </row>
     <row r="31">
@@ -15218,8 +15869,32 @@
       <c r="FN31" t="n">
         <v>103</v>
       </c>
+      <c r="FW31" t="n">
+        <v>100.45</v>
+      </c>
       <c r="FZ31" t="n">
         <v>112.8</v>
+      </c>
+      <c r="GE31" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="GF31" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="GG31" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GH31" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="GI31" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="GJ31" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="GK31" t="n">
+        <v>102.45</v>
       </c>
     </row>
     <row r="32">
@@ -15696,8 +16371,32 @@
       <c r="FN32" t="n">
         <v>103</v>
       </c>
+      <c r="FW32" t="n">
+        <v>100.5</v>
+      </c>
       <c r="FZ32" t="n">
         <v>111.85</v>
+      </c>
+      <c r="GE32" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="GF32" t="n">
+        <v>105</v>
+      </c>
+      <c r="GG32" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="GH32" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="GI32" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="GJ32" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GK32" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="33">
@@ -16183,8 +16882,32 @@
       <c r="FN33" t="n">
         <v>103</v>
       </c>
+      <c r="FW33" t="n">
+        <v>100.9</v>
+      </c>
       <c r="FZ33" t="n">
         <v>112.8</v>
+      </c>
+      <c r="GE33" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="GF33" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="GG33" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="GH33" t="n">
+        <v>108</v>
+      </c>
+      <c r="GI33" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="GJ33" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="GK33" t="n">
+        <v>102.5</v>
       </c>
     </row>
     <row r="34">
@@ -16610,6 +17333,24 @@
       <c r="FN34" t="n">
         <v>107</v>
       </c>
+      <c r="GE34" t="n">
+        <v>113</v>
+      </c>
+      <c r="GF34" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="GG34" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GH34" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="GJ34" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GK34" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -17097,6 +17838,27 @@
       <c r="FZ35" t="n">
         <v>112.8</v>
       </c>
+      <c r="GE35" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="GF35" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="GG35" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="GH35" t="n">
+        <v>107</v>
+      </c>
+      <c r="GI35" t="n">
+        <v>106</v>
+      </c>
+      <c r="GJ35" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="GK35" t="n">
+        <v>102.8</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -17581,8 +18343,32 @@
       <c r="FP36" t="n">
         <v>100.4</v>
       </c>
+      <c r="FW36" t="n">
+        <v>100.5</v>
+      </c>
       <c r="FZ36" t="n">
         <v>112.85</v>
+      </c>
+      <c r="GE36" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="GF36" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GG36" t="n">
+        <v>105</v>
+      </c>
+      <c r="GH36" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="GI36" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="GJ36" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="GK36" t="n">
+        <v>102.7</v>
       </c>
     </row>
     <row r="37">
@@ -18065,8 +18851,29 @@
       <c r="FN37" t="n">
         <v>103</v>
       </c>
+      <c r="FW37" t="n">
+        <v>100.75</v>
+      </c>
       <c r="FZ37" t="n">
         <v>112.9</v>
+      </c>
+      <c r="GE37" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="GF37" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="GG37" t="n">
+        <v>105</v>
+      </c>
+      <c r="GH37" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="GJ37" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="GK37" t="n">
+        <v>103.3</v>
       </c>
     </row>
     <row r="38">
@@ -18549,8 +19356,32 @@
       <c r="FP38" t="n">
         <v>100</v>
       </c>
+      <c r="FW38" t="n">
+        <v>100.5</v>
+      </c>
       <c r="FZ38" t="n">
         <v>112.9</v>
+      </c>
+      <c r="GE38" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="GF38" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="GG38" t="n">
+        <v>105</v>
+      </c>
+      <c r="GH38" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="GI38" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="GJ38" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="GK38" t="n">
+        <v>102.55</v>
       </c>
     </row>
     <row r="39">
@@ -19042,8 +19873,35 @@
       <c r="FP39" t="n">
         <v>100.4</v>
       </c>
+      <c r="FW39" t="n">
+        <v>100.7</v>
+      </c>
       <c r="FZ39" t="n">
         <v>113.65</v>
+      </c>
+      <c r="GE39" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="GF39" t="n">
+        <v>107</v>
+      </c>
+      <c r="GG39" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="GH39" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="GI39" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="GJ39" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="GK39" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="GM39" t="n">
+        <v>104.05</v>
       </c>
     </row>
     <row r="40">
@@ -19529,8 +20387,35 @@
       <c r="FP40" t="n">
         <v>100.35</v>
       </c>
+      <c r="FW40" t="n">
+        <v>101.3</v>
+      </c>
       <c r="FZ40" t="n">
         <v>113.95</v>
+      </c>
+      <c r="GE40" t="n">
+        <v>115.15</v>
+      </c>
+      <c r="GF40" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="GG40" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="GH40" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="GI40" t="n">
+        <v>103</v>
+      </c>
+      <c r="GJ40" t="n">
+        <v>102</v>
+      </c>
+      <c r="GK40" t="n">
+        <v>103</v>
+      </c>
+      <c r="GM40" t="n">
+        <v>103.7</v>
       </c>
     </row>
     <row r="41">
@@ -20022,6 +20907,27 @@
       <c r="FP41" t="n">
         <v>100.4</v>
       </c>
+      <c r="FW41" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="GE41" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="GF41" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="GH41" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="GI41" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="GJ41" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="GK41" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -20509,6 +21415,33 @@
       <c r="FP42" t="n">
         <v>100.05</v>
       </c>
+      <c r="FW42" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="GE42" t="n">
+        <v>113.95</v>
+      </c>
+      <c r="GF42" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="GG42" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GH42" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="GI42" t="n">
+        <v>103</v>
+      </c>
+      <c r="GJ42" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="GK42" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="GM42" t="n">
+        <v>102.05</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -20996,8 +21929,32 @@
       <c r="FO43" t="n">
         <v>103.9</v>
       </c>
+      <c r="FW43" t="n">
+        <v>100.75</v>
+      </c>
       <c r="FZ43" t="n">
         <v>114.2</v>
+      </c>
+      <c r="GE43" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="GF43" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="GG43" t="n">
+        <v>106</v>
+      </c>
+      <c r="GH43" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="GI43" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="GJ43" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GK43" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="44">
@@ -21489,8 +22446,35 @@
       <c r="FP44" t="n">
         <v>100.05</v>
       </c>
+      <c r="FW44" t="n">
+        <v>101</v>
+      </c>
       <c r="FZ44" t="n">
         <v>114.4</v>
+      </c>
+      <c r="GE44" t="n">
+        <v>115.05</v>
+      </c>
+      <c r="GF44" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="GG44" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="GH44" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="GI44" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GJ44" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="GK44" t="n">
+        <v>103</v>
+      </c>
+      <c r="GM44" t="n">
+        <v>101</v>
       </c>
     </row>
     <row r="45">
@@ -21982,8 +22966,35 @@
       <c r="FP45" t="n">
         <v>100.55</v>
       </c>
+      <c r="FW45" t="n">
+        <v>101.3</v>
+      </c>
       <c r="FZ45" t="n">
         <v>114.45</v>
+      </c>
+      <c r="GE45" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="GF45" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="GG45" t="n">
+        <v>105</v>
+      </c>
+      <c r="GH45" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="GI45" t="n">
+        <v>103</v>
+      </c>
+      <c r="GJ45" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="GK45" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="GM45" t="n">
+        <v>102.05</v>
       </c>
     </row>
     <row r="46">
@@ -22475,8 +23486,32 @@
       <c r="FP46" t="n">
         <v>100.75</v>
       </c>
+      <c r="FW46" t="n">
+        <v>101.75</v>
+      </c>
       <c r="FZ46" t="n">
         <v>111.45</v>
+      </c>
+      <c r="GE46" t="n">
+        <v>115</v>
+      </c>
+      <c r="GF46" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="GG46" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="GH46" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="GI46" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="GJ46" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="GK46" t="n">
+        <v>103.3</v>
       </c>
     </row>
     <row r="47">
@@ -22971,8 +24006,32 @@
       <c r="FP47" t="n">
         <v>100.75</v>
       </c>
+      <c r="FW47" t="n">
+        <v>102</v>
+      </c>
       <c r="FZ47" t="n">
         <v>111.4</v>
+      </c>
+      <c r="GE47" t="n">
+        <v>113.95</v>
+      </c>
+      <c r="GF47" t="n">
+        <v>107</v>
+      </c>
+      <c r="GG47" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="GH47" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="GI47" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="GJ47" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="GK47" t="n">
+        <v>102.15</v>
       </c>
     </row>
     <row r="48">
@@ -23450,8 +24509,35 @@
       <c r="FN48" t="n">
         <v>103.75</v>
       </c>
+      <c r="FW48" t="n">
+        <v>101.2</v>
+      </c>
       <c r="FZ48" t="n">
         <v>110.95</v>
+      </c>
+      <c r="GE48" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="GF48" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="GG48" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="GH48" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="GI48" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="GJ48" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="GK48" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="GM48" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="49">
@@ -23929,11 +25015,44 @@
       <c r="FP49" t="n">
         <v>100.6</v>
       </c>
+      <c r="FR49" t="n">
+        <v>147500</v>
+      </c>
+      <c r="FT49" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="FW49" t="n">
+        <v>101.5</v>
+      </c>
       <c r="FZ49" t="n">
         <v>110.95</v>
       </c>
       <c r="GA49" t="n">
         <v>103</v>
+      </c>
+      <c r="GE49" t="n">
+        <v>113.95</v>
+      </c>
+      <c r="GF49" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="GG49" t="n">
+        <v>105</v>
+      </c>
+      <c r="GH49" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="GI49" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="GJ49" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="GK49" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GM49" t="n">
+        <v>101.5</v>
       </c>
     </row>
     <row r="50">
@@ -24446,6 +25565,33 @@
       <c r="GA50" t="n">
         <v>104</v>
       </c>
+      <c r="GE50" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="GF50" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="GG50" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GH50" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="GI50" t="n">
+        <v>104</v>
+      </c>
+      <c r="GJ50" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="GK50" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="GL50" t="n">
+        <v>33</v>
+      </c>
+      <c r="GM50" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -24948,6 +26094,30 @@
       <c r="GA51" t="n">
         <v>103.1</v>
       </c>
+      <c r="GE51" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="GF51" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="GG51" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GH51" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="GI51" t="n">
+        <v>104</v>
+      </c>
+      <c r="GJ51" t="n">
+        <v>101</v>
+      </c>
+      <c r="GK51" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GL51" t="n">
+        <v>29.8</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -25450,6 +26620,33 @@
       <c r="GA52" t="n">
         <v>104</v>
       </c>
+      <c r="GE52" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="GF52" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="GG52" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="GH52" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="GI52" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GJ52" t="n">
+        <v>101</v>
+      </c>
+      <c r="GK52" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GL52" t="n">
+        <v>29.006</v>
+      </c>
+      <c r="GM52" t="n">
+        <v>101.95</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -25953,6 +27150,36 @@
       <c r="GA53" t="n">
         <v>104.05</v>
       </c>
+      <c r="GB53" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="GE53" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="GF53" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="GG53" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="GH53" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="GI53" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GJ53" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GK53" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GL53" t="n">
+        <v>30.712</v>
+      </c>
+      <c r="GM53" t="n">
+        <v>99.99999999999999</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -26455,6 +27682,36 @@
       </c>
       <c r="GA54" t="n">
         <v>104.25</v>
+      </c>
+      <c r="GB54" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="GE54" t="n">
+        <v>113.95</v>
+      </c>
+      <c r="GF54" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="GG54" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="GH54" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="GI54" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="GJ54" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="GK54" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GL54" t="n">
+        <v>34</v>
+      </c>
+      <c r="GM54" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="55">
@@ -26931,6 +28188,9 @@
       <c r="FQ55" t="n">
         <v>100.69</v>
       </c>
+      <c r="FR55" t="n">
+        <v>147950</v>
+      </c>
       <c r="FS55" t="n">
         <v>137100</v>
       </c>
@@ -26957,6 +28217,30 @@
       </c>
       <c r="GB55" t="n">
         <v>101</v>
+      </c>
+      <c r="GE55" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="GF55" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="GG55" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="GH55" t="n">
+        <v>104</v>
+      </c>
+      <c r="GI55" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="GJ55" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="GK55" t="n">
+        <v>103</v>
+      </c>
+      <c r="GM55" t="n">
+        <v>100.55</v>
       </c>
     </row>
     <row r="56">
@@ -27439,6 +28723,9 @@
       <c r="FQ56" t="n">
         <v>100.77</v>
       </c>
+      <c r="FR56" t="n">
+        <v>148000</v>
+      </c>
       <c r="FS56" t="n">
         <v>136900</v>
       </c>
@@ -27465,6 +28752,33 @@
       </c>
       <c r="GB56" t="n">
         <v>100.85</v>
+      </c>
+      <c r="GE56" t="n">
+        <v>114</v>
+      </c>
+      <c r="GF56" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="GG56" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="GH56" t="n">
+        <v>104</v>
+      </c>
+      <c r="GI56" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="GJ56" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="GK56" t="n">
+        <v>103</v>
+      </c>
+      <c r="GL56" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="GM56" t="n">
+        <v>102.1</v>
       </c>
     </row>
     <row r="57">
@@ -27944,6 +29258,9 @@
       <c r="FQ57" t="n">
         <v>100.9</v>
       </c>
+      <c r="FR57" t="n">
+        <v>148000</v>
+      </c>
       <c r="FS57" t="n">
         <v>136890</v>
       </c>
@@ -27953,6 +29270,9 @@
       <c r="FV57" t="n">
         <v>100.3</v>
       </c>
+      <c r="FW57" t="n">
+        <v>102.1</v>
+      </c>
       <c r="FX57" t="n">
         <v>103.65</v>
       </c>
@@ -27967,6 +29287,30 @@
       </c>
       <c r="GB57" t="n">
         <v>100.85</v>
+      </c>
+      <c r="GE57" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="GF57" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="GG57" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="GH57" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="GI57" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="GJ57" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="GK57" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="GM57" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="58">
@@ -28443,6 +29787,9 @@
       <c r="FQ58" t="n">
         <v>100.999</v>
       </c>
+      <c r="FR58" t="n">
+        <v>149000</v>
+      </c>
       <c r="FS58" t="n">
         <v>136690</v>
       </c>
@@ -28466,6 +29813,33 @@
       </c>
       <c r="GB58" t="n">
         <v>100.45</v>
+      </c>
+      <c r="GE58" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="GF58" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="GG58" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="GH58" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="GI58" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="GJ58" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="GK58" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="GL58" t="n">
+        <v>32</v>
+      </c>
+      <c r="GM58" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="59">
@@ -28939,6 +30313,9 @@
       <c r="FQ59" t="n">
         <v>101.18</v>
       </c>
+      <c r="FR59" t="n">
+        <v>149000</v>
+      </c>
       <c r="FS59" t="n">
         <v>136740</v>
       </c>
@@ -28948,6 +30325,9 @@
       <c r="FV59" t="n">
         <v>99.95</v>
       </c>
+      <c r="FW59" t="n">
+        <v>102.75</v>
+      </c>
       <c r="FX59" t="n">
         <v>103.95</v>
       </c>
@@ -28962,6 +30342,39 @@
       </c>
       <c r="GB59" t="n">
         <v>101</v>
+      </c>
+      <c r="GC59" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="GD59" t="n">
+        <v>147690</v>
+      </c>
+      <c r="GE59" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="GF59" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="GG59" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="GH59" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="GI59" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="GJ59" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="GK59" t="n">
+        <v>103</v>
+      </c>
+      <c r="GL59" t="n">
+        <v>31</v>
+      </c>
+      <c r="GM59" t="n">
+        <v>100.15</v>
       </c>
     </row>
     <row r="60">
@@ -29477,6 +30890,33 @@
       <c r="GD60" t="n">
         <v>147920</v>
       </c>
+      <c r="GE60" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="GF60" t="n">
+        <v>106</v>
+      </c>
+      <c r="GG60" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GH60" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="GI60" t="n">
+        <v>104</v>
+      </c>
+      <c r="GJ60" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="GK60" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GL60" t="n">
+        <v>30.204</v>
+      </c>
+      <c r="GM60" t="n">
+        <v>100.15</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GM61"/>
+  <dimension ref="A1:GM62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -31456,6 +31456,538 @@
         <v>31.2</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>126.236</v>
+      </c>
+      <c r="I62" t="n">
+        <v>114.28</v>
+      </c>
+      <c r="J62" t="n">
+        <v>128.814</v>
+      </c>
+      <c r="K62" t="n">
+        <v>120.98</v>
+      </c>
+      <c r="L62" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>131.54</v>
+      </c>
+      <c r="N62" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="P62" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="S62" t="n">
+        <v>169.4</v>
+      </c>
+      <c r="T62" t="n">
+        <v>296.9</v>
+      </c>
+      <c r="U62" t="n">
+        <v>218.35</v>
+      </c>
+      <c r="V62" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="W62" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="X62" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>271</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>129</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>119.45</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>148500</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>147050</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>124000</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>93.89</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>92</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>55.67999999999999</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>78.06</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>72.92</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>67</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>91</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>167.2</v>
+      </c>
+      <c r="BI62" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="BK62" t="n">
+        <v>146000</v>
+      </c>
+      <c r="BM62" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BN62" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="BO62" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="BP62" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="BQ62" t="n">
+        <v>149200</v>
+      </c>
+      <c r="BR62" t="n">
+        <v>119000</v>
+      </c>
+      <c r="BS62" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="BT62" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="BU62" t="n">
+        <v>80.58</v>
+      </c>
+      <c r="BV62" t="n">
+        <v>103.34</v>
+      </c>
+      <c r="BW62" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="BX62" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="BY62" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="BZ62" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA62" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="CB62" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="CC62" t="n">
+        <v>122.35</v>
+      </c>
+      <c r="CE62" t="n">
+        <v>114.29</v>
+      </c>
+      <c r="CF62" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="CG62" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="CH62" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="CI62" t="n">
+        <v>64.51000000000001</v>
+      </c>
+      <c r="CJ62" t="n">
+        <v>111</v>
+      </c>
+      <c r="CL62" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="CM62" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="CN62" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="CO62" t="n">
+        <v>76.58</v>
+      </c>
+      <c r="CP62" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="CQ62" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="CR62" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="CS62" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="CT62" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="CU62" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="CV62" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="CW62" t="n">
+        <v>51.11000000000001</v>
+      </c>
+      <c r="CX62" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="CY62" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="CZ62" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="DB62" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="DC62" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="DD62" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="DE62" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="DF62" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="DG62" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DH62" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DI62" t="n">
+        <v>113.15</v>
+      </c>
+      <c r="DJ62" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="DK62" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="DL62" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DM62" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="DN62" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DO62" t="n">
+        <v>110</v>
+      </c>
+      <c r="DP62" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="DQ62" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="DR62" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="DS62" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="DT62" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="DU62" t="n">
+        <v>106</v>
+      </c>
+      <c r="DV62" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="DW62" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="DX62" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DY62" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="DZ62" t="n">
+        <v>107</v>
+      </c>
+      <c r="EA62" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="EB62" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="EC62" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="ED62" t="n">
+        <v>106</v>
+      </c>
+      <c r="EE62" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="EF62" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="EG62" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="EH62" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="EI62" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="EJ62" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EK62" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="EL62" t="n">
+        <v>105</v>
+      </c>
+      <c r="EM62" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="EN62" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="EO62" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EQ62" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="ER62" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="ES62" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="ET62" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="EU62" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EV62" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EW62" t="n">
+        <v>103</v>
+      </c>
+      <c r="EX62" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EY62" t="n">
+        <v>111.05</v>
+      </c>
+      <c r="EZ62" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="FA62" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="FB62" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="FC62" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FD62" t="n">
+        <v>99.50000000000001</v>
+      </c>
+      <c r="FE62" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="FF62" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FG62" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FH62" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FI62" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="FJ62" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="FK62" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FL62" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="FM62" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="FN62" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="FP62" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="FQ62" t="n">
+        <v>101.325</v>
+      </c>
+      <c r="FR62" t="n">
+        <v>149000</v>
+      </c>
+      <c r="FS62" t="n">
+        <v>135950</v>
+      </c>
+      <c r="FU62" t="n">
+        <v>99.49000000000001</v>
+      </c>
+      <c r="FV62" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="FX62" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="FY62" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="GA62" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="GB62" t="n">
+        <v>100</v>
+      </c>
+      <c r="GC62" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="GD62" t="n">
+        <v>148000</v>
+      </c>
+      <c r="GE62" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="GF62" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="GG62" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GH62" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="GI62" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="GJ62" t="n">
+        <v>101</v>
+      </c>
+      <c r="GK62" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GL62" t="n">
+        <v>31</v>
+      </c>
+      <c r="GM62" t="n">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GM62"/>
+  <dimension ref="A1:GM63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -31988,6 +31988,544 @@
         <v>101</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>126.492</v>
+      </c>
+      <c r="I63" t="n">
+        <v>114.64</v>
+      </c>
+      <c r="J63" t="n">
+        <v>129.306</v>
+      </c>
+      <c r="K63" t="n">
+        <v>121.435</v>
+      </c>
+      <c r="L63" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="M63" t="n">
+        <v>131.94</v>
+      </c>
+      <c r="N63" t="n">
+        <v>124.35</v>
+      </c>
+      <c r="O63" t="n">
+        <v>126</v>
+      </c>
+      <c r="P63" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="S63" t="n">
+        <v>169.85</v>
+      </c>
+      <c r="T63" t="n">
+        <v>297.9</v>
+      </c>
+      <c r="U63" t="n">
+        <v>219.1</v>
+      </c>
+      <c r="V63" t="n">
+        <v>120.95</v>
+      </c>
+      <c r="W63" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="X63" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>272.25</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>96.45999999999999</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>345.9</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>93.86</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>129.31</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>148800</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>146750</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>123590</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>53.34999999999999</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>92.29999999999998</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>78.18000000000001</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>69.95999999999999</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>57.00999999999999</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>79.89</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>92</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>96.45999999999999</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>167.4</v>
+      </c>
+      <c r="BI63" t="n">
+        <v>105.63</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>146000</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>108</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>149550</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>117400</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>83.95</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>103.56</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>91</v>
+      </c>
+      <c r="CB63" t="n">
+        <v>119</v>
+      </c>
+      <c r="CC63" t="n">
+        <v>122.65</v>
+      </c>
+      <c r="CE63" t="n">
+        <v>115.198</v>
+      </c>
+      <c r="CF63" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="CG63" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="CH63" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="CI63" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="CJ63" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="CL63" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="CM63" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="CN63" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="CO63" t="n">
+        <v>77.27</v>
+      </c>
+      <c r="CP63" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="CQ63" t="n">
+        <v>110</v>
+      </c>
+      <c r="CR63" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="CS63" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="CT63" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="CU63" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="CV63" t="n">
+        <v>81.68000000000001</v>
+      </c>
+      <c r="CW63" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="CX63" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="CY63" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="CZ63" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="DA63" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="DB63" t="n">
+        <v>109</v>
+      </c>
+      <c r="DC63" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="DD63" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DE63" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="DF63" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="DG63" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="DH63" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DI63" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="DJ63" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="DK63" t="n">
+        <v>111</v>
+      </c>
+      <c r="DL63" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="DM63" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="DN63" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DO63" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="DP63" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="DQ63" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="DR63" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="DS63" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DT63" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="DU63" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="DV63" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DW63" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="DX63" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DY63" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="DZ63" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="EA63" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="EB63" t="n">
+        <v>106</v>
+      </c>
+      <c r="EC63" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="ED63" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="EE63" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EF63" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="EG63" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="EH63" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="EI63" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EJ63" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EK63" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EL63" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="EM63" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="EN63" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="EO63" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EQ63" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="ER63" t="n">
+        <v>103</v>
+      </c>
+      <c r="ES63" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="ET63" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="EU63" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EV63" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EW63" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EX63" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="EY63" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="EZ63" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="FA63" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="FB63" t="n">
+        <v>104</v>
+      </c>
+      <c r="FC63" t="n">
+        <v>104</v>
+      </c>
+      <c r="FD63" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="FE63" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="FF63" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="FG63" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FH63" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="FI63" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FJ63" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="FK63" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FL63" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="FM63" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="FN63" t="n">
+        <v>106</v>
+      </c>
+      <c r="FQ63" t="n">
+        <v>101.579</v>
+      </c>
+      <c r="FR63" t="n">
+        <v>149000</v>
+      </c>
+      <c r="FS63" t="n">
+        <v>136650</v>
+      </c>
+      <c r="FU63" t="n">
+        <v>99.45000000000002</v>
+      </c>
+      <c r="FV63" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="FW63" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="FX63" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="FY63" t="n">
+        <v>25.521</v>
+      </c>
+      <c r="FZ63" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="GA63" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="GB63" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="GC63" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="GD63" t="n">
+        <v>148400</v>
+      </c>
+      <c r="GE63" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="GF63" t="n">
+        <v>106</v>
+      </c>
+      <c r="GG63" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="GH63" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="GI63" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="GJ63" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="GK63" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GL63" t="n">
+        <v>31</v>
+      </c>
+      <c r="GM63" t="n">
+        <v>100.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GM63"/>
+  <dimension ref="A1:GM64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -32595,6 +32595,502 @@
         <v>100.1</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>126.575</v>
+      </c>
+      <c r="I64" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="J64" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="K64" t="n">
+        <v>121.52</v>
+      </c>
+      <c r="L64" t="n">
+        <v>146.08</v>
+      </c>
+      <c r="M64" t="n">
+        <v>132.34</v>
+      </c>
+      <c r="N64" t="n">
+        <v>124.63</v>
+      </c>
+      <c r="O64" t="n">
+        <v>126</v>
+      </c>
+      <c r="P64" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>110</v>
+      </c>
+      <c r="S64" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="T64" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="U64" t="n">
+        <v>219.2</v>
+      </c>
+      <c r="V64" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="W64" t="n">
+        <v>387.5</v>
+      </c>
+      <c r="X64" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>272.45</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>345.7</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>93.84</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>116</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>149650</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>147500</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>125360</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>94.34</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>92.59000000000002</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>55.16</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>75.18000000000001</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>53.90000000000001</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>76.77</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>91.40000000000002</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="BI64" t="n">
+        <v>105.769</v>
+      </c>
+      <c r="BK64" t="n">
+        <v>147390</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="BQ64" t="n">
+        <v>150550</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>119010</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>84</v>
+      </c>
+      <c r="BU64" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="BV64" t="n">
+        <v>103.717</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="BY64" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="BZ64" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA64" t="n">
+        <v>91.11000000000001</v>
+      </c>
+      <c r="CB64" t="n">
+        <v>119</v>
+      </c>
+      <c r="CC64" t="n">
+        <v>122.8</v>
+      </c>
+      <c r="CE64" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="CF64" t="n">
+        <v>103</v>
+      </c>
+      <c r="CG64" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="CM64" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="CN64" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="CO64" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="CR64" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="CS64" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="CT64" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="CU64" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="CV64" t="n">
+        <v>78.39</v>
+      </c>
+      <c r="CW64" t="n">
+        <v>50</v>
+      </c>
+      <c r="CX64" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="CY64" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="CZ64" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="DB64" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="DC64" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="DD64" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="DE64" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="DF64" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="DG64" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="DH64" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="DI64" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="DJ64" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="DL64" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="DM64" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DO64" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DP64" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="DQ64" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DR64" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="DS64" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="DT64" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="DU64" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DV64" t="n">
+        <v>105</v>
+      </c>
+      <c r="DW64" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="DX64" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="DY64" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DZ64" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="EA64" t="n">
+        <v>108</v>
+      </c>
+      <c r="EB64" t="n">
+        <v>103</v>
+      </c>
+      <c r="EC64" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="ED64" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="EE64" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="EF64" t="n">
+        <v>106</v>
+      </c>
+      <c r="EG64" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="EH64" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="EI64" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="EJ64" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EK64" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EL64" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="EM64" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="EN64" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="EO64" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EQ64" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="ER64" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="ES64" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="ET64" t="n">
+        <v>102</v>
+      </c>
+      <c r="EU64" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EV64" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="EW64" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="EX64" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="EY64" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EZ64" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="FA64" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="FB64" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="FC64" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FD64" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="FE64" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="FF64" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FG64" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="FH64" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="FI64" t="n">
+        <v>104</v>
+      </c>
+      <c r="FJ64" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="FK64" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FL64" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="FM64" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="FN64" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="FQ64" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="FR64" t="n">
+        <v>149000</v>
+      </c>
+      <c r="FS64" t="n">
+        <v>137100</v>
+      </c>
+      <c r="FU64" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="FV64" t="n">
+        <v>99.48999999999998</v>
+      </c>
+      <c r="FX64" t="n">
+        <v>102</v>
+      </c>
+      <c r="FY64" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="GA64" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="GB64" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="GC64" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="GD64" t="n">
+        <v>149200</v>
+      </c>
+      <c r="GF64" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="GG64" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="GH64" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="GI64" t="n">
+        <v>104</v>
+      </c>
+      <c r="GJ64" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="GK64" t="n">
+        <v>103</v>
+      </c>
+      <c r="GM64" t="n">
+        <v>101.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1633,28 +1633,28 @@
         <v>99.11999999999999</v>
       </c>
       <c r="CH2" t="n">
-        <v>53.60000000000001</v>
+        <v>52.2094</v>
       </c>
       <c r="CI2" t="n">
         <v>69.01000000000001</v>
       </c>
       <c r="CJ2" t="n">
-        <v>109</v>
+        <v>106.1722</v>
       </c>
       <c r="CO2" t="n">
         <v>72.66</v>
       </c>
       <c r="CP2" t="n">
-        <v>71</v>
+        <v>69.158</v>
       </c>
       <c r="CS2" t="n">
-        <v>103.6</v>
+        <v>100.9123</v>
       </c>
       <c r="CT2" t="n">
         <v>102</v>
       </c>
       <c r="CW2" t="n">
-        <v>68.73</v>
+        <v>66.9469</v>
       </c>
       <c r="CX2" t="n">
         <v>102.1</v>
@@ -1663,13 +1663,13 @@
         <v>98.18000000000001</v>
       </c>
       <c r="DA2" t="n">
-        <v>108.4</v>
+        <v>105.5877</v>
       </c>
       <c r="DB2" t="n">
-        <v>103.25</v>
+        <v>100.5713</v>
       </c>
       <c r="DC2" t="n">
-        <v>102.8</v>
+        <v>100.133</v>
       </c>
       <c r="DE2" t="n">
         <v>100.7</v>
@@ -1681,19 +1681,19 @@
         <v>101.1</v>
       </c>
       <c r="DI2" t="n">
-        <v>112.2</v>
+        <v>109.2892</v>
       </c>
       <c r="DK2" t="n">
-        <v>109.4</v>
+        <v>106.5618</v>
       </c>
       <c r="DL2" t="n">
-        <v>104</v>
+        <v>101.3019</v>
       </c>
       <c r="DM2" t="n">
         <v>103.25</v>
       </c>
       <c r="DN2" t="n">
-        <v>102.8</v>
+        <v>100.133</v>
       </c>
       <c r="DP2" t="n">
         <v>106.95</v>
@@ -1708,7 +1708,7 @@
         <v>108.65</v>
       </c>
       <c r="DT2" t="n">
-        <v>104.5</v>
+        <v>101.7889</v>
       </c>
       <c r="DU2" t="n">
         <v>104.7</v>
@@ -1717,7 +1717,7 @@
         <v>101.4</v>
       </c>
       <c r="DX2" t="n">
-        <v>104</v>
+        <v>101.3019</v>
       </c>
       <c r="DY2" t="n">
         <v>105.85</v>
@@ -1729,7 +1729,7 @@
         <v>103.95</v>
       </c>
       <c r="EB2" t="n">
-        <v>104.7</v>
+        <v>101.9837</v>
       </c>
       <c r="ED2" t="n">
         <v>102</v>
@@ -1777,7 +1777,7 @@
         <v>100</v>
       </c>
       <c r="EY2" t="n">
-        <v>106.45</v>
+        <v>103.6883</v>
       </c>
       <c r="FA2" t="n">
         <v>95.3</v>
@@ -1801,7 +1801,7 @@
         <v>103.9</v>
       </c>
       <c r="GE2" t="n">
-        <v>109</v>
+        <v>106.1722</v>
       </c>
       <c r="GF2" t="n">
         <v>103.6</v>
@@ -2024,10 +2024,10 @@
         <v>44.11</v>
       </c>
       <c r="CI3" t="n">
-        <v>63.4</v>
+        <v>61.1383</v>
       </c>
       <c r="CJ3" t="n">
-        <v>113.05</v>
+        <v>109.0171</v>
       </c>
       <c r="CM3" t="n">
         <v>100.2</v>
@@ -2039,13 +2039,13 @@
         <v>72.8</v>
       </c>
       <c r="CP3" t="n">
-        <v>75.59</v>
+        <v>72.8934</v>
       </c>
       <c r="CQ3" t="n">
-        <v>107.9</v>
+        <v>104.0508</v>
       </c>
       <c r="CR3" t="n">
-        <v>109.8</v>
+        <v>105.883</v>
       </c>
       <c r="CS3" t="n">
         <v>108.9</v>
@@ -2066,13 +2066,13 @@
         <v>105.65</v>
       </c>
       <c r="DA3" t="n">
-        <v>111.6</v>
+        <v>107.6188</v>
       </c>
       <c r="DB3" t="n">
-        <v>110.6</v>
+        <v>106.6545</v>
       </c>
       <c r="DC3" t="n">
-        <v>105.5</v>
+        <v>101.7364</v>
       </c>
       <c r="DD3" t="n">
         <v>105.6</v>
@@ -2102,7 +2102,7 @@
         <v>110.25</v>
       </c>
       <c r="DN3" t="n">
-        <v>110.9</v>
+        <v>106.9438</v>
       </c>
       <c r="DO3" t="n">
         <v>103.85</v>
@@ -2144,7 +2144,7 @@
         <v>106.1</v>
       </c>
       <c r="EB3" t="n">
-        <v>108.25</v>
+        <v>104.3883</v>
       </c>
       <c r="EC3" t="n">
         <v>100.75</v>
@@ -2204,7 +2204,7 @@
         <v>105.85</v>
       </c>
       <c r="EY3" t="n">
-        <v>107.85</v>
+        <v>104.0026</v>
       </c>
       <c r="EZ3" t="n">
         <v>99.99999999999999</v>
@@ -2478,16 +2478,16 @@
         <v>100.6</v>
       </c>
       <c r="CH4" t="n">
-        <v>47.5</v>
+        <v>45.842</v>
       </c>
       <c r="CI4" t="n">
-        <v>63.41</v>
+        <v>61.1966</v>
       </c>
       <c r="CJ4" t="n">
-        <v>113.5</v>
+        <v>109.5381</v>
       </c>
       <c r="CM4" t="n">
-        <v>103.9</v>
+        <v>100.2732</v>
       </c>
       <c r="CN4" t="n">
         <v>97.79000000000001</v>
@@ -2499,10 +2499,10 @@
         <v>75</v>
       </c>
       <c r="CQ4" t="n">
-        <v>108</v>
+        <v>104.2301</v>
       </c>
       <c r="CR4" t="n">
-        <v>111.15</v>
+        <v>107.2702</v>
       </c>
       <c r="CS4" t="n">
         <v>103</v>
@@ -2514,7 +2514,7 @@
         <v>100.85</v>
       </c>
       <c r="CW4" t="n">
-        <v>70.55</v>
+        <v>68.0874</v>
       </c>
       <c r="CX4" t="n">
         <v>106.2</v>
@@ -2523,10 +2523,10 @@
         <v>105.7</v>
       </c>
       <c r="DB4" t="n">
-        <v>110.7</v>
+        <v>106.8359</v>
       </c>
       <c r="DC4" t="n">
-        <v>105.2</v>
+        <v>101.5279</v>
       </c>
       <c r="DD4" t="n">
         <v>105.85</v>
@@ -2547,7 +2547,7 @@
         <v>105.5</v>
       </c>
       <c r="DK4" t="n">
-        <v>113.55</v>
+        <v>109.5864</v>
       </c>
       <c r="DL4" t="n">
         <v>102.75</v>
@@ -2574,7 +2574,7 @@
         <v>109.5</v>
       </c>
       <c r="DT4" t="n">
-        <v>107.2</v>
+        <v>103.4581</v>
       </c>
       <c r="DU4" t="n">
         <v>108</v>
@@ -2598,7 +2598,7 @@
         <v>106</v>
       </c>
       <c r="EB4" t="n">
-        <v>108.55</v>
+        <v>104.7609</v>
       </c>
       <c r="EC4" t="n">
         <v>100.85</v>
@@ -2706,7 +2706,7 @@
         <v>104.5</v>
       </c>
       <c r="GE4" t="n">
-        <v>112.9</v>
+        <v>108.9591</v>
       </c>
       <c r="GF4" t="n">
         <v>105</v>
@@ -2929,13 +2929,13 @@
         <v>100.55</v>
       </c>
       <c r="CH5" t="n">
-        <v>46.8</v>
+        <v>45.2142</v>
       </c>
       <c r="CI5" t="n">
         <v>61.50000000000001</v>
       </c>
       <c r="CJ5" t="n">
-        <v>112.75</v>
+        <v>108.9296</v>
       </c>
       <c r="CK5" t="n">
         <v>98.75</v>
@@ -2950,10 +2950,10 @@
         <v>72.42</v>
       </c>
       <c r="CP5" t="n">
-        <v>75.98999999999999</v>
+        <v>73.4152</v>
       </c>
       <c r="CQ5" t="n">
-        <v>107.7</v>
+        <v>104.0507</v>
       </c>
       <c r="CR5" t="n">
         <v>107.15</v>
@@ -2968,7 +2968,7 @@
         <v>100.9</v>
       </c>
       <c r="CW5" t="n">
-        <v>70.65000000000001</v>
+        <v>68.2561</v>
       </c>
       <c r="CX5" t="n">
         <v>105.25</v>
@@ -2977,13 +2977,13 @@
         <v>105.7</v>
       </c>
       <c r="DA5" t="n">
-        <v>111.05</v>
+        <v>107.2872</v>
       </c>
       <c r="DB5" t="n">
         <v>106.8</v>
       </c>
       <c r="DC5" t="n">
-        <v>105.3</v>
+        <v>101.7321</v>
       </c>
       <c r="DD5" t="n">
         <v>106.15</v>
@@ -3004,7 +3004,7 @@
         <v>105.45</v>
       </c>
       <c r="DK5" t="n">
-        <v>113.85</v>
+        <v>109.9924</v>
       </c>
       <c r="DL5" t="n">
         <v>102.9</v>
@@ -3389,7 +3389,7 @@
         <v>108.9</v>
       </c>
       <c r="BP6" t="n">
-        <v>109</v>
+        <v>105.3115</v>
       </c>
       <c r="CB6" t="n">
         <v>114.35</v>
@@ -3410,13 +3410,13 @@
         <v>100.6</v>
       </c>
       <c r="CH6" t="n">
-        <v>47.69</v>
+        <v>46.0762</v>
       </c>
       <c r="CI6" t="n">
-        <v>63.41</v>
+        <v>61.2642</v>
       </c>
       <c r="CM6" t="n">
-        <v>103.85</v>
+        <v>100.3357</v>
       </c>
       <c r="CN6" t="n">
         <v>97.90000000000001</v>
@@ -3425,16 +3425,16 @@
         <v>72.69</v>
       </c>
       <c r="CP6" t="n">
-        <v>75</v>
+        <v>72.462</v>
       </c>
       <c r="CQ6" t="n">
-        <v>107.45</v>
+        <v>103.8139</v>
       </c>
       <c r="CR6" t="n">
         <v>107.15</v>
       </c>
       <c r="CS6" t="n">
-        <v>107.9</v>
+        <v>104.2487</v>
       </c>
       <c r="CT6" t="n">
         <v>103.85</v>
@@ -3443,7 +3443,7 @@
         <v>100.7</v>
       </c>
       <c r="CW6" t="n">
-        <v>70.89</v>
+        <v>68.4911</v>
       </c>
       <c r="CX6" t="n">
         <v>105.1</v>
@@ -3452,16 +3452,16 @@
         <v>105.75</v>
       </c>
       <c r="DA6" t="n">
-        <v>111</v>
+        <v>107.2438</v>
       </c>
       <c r="DB6" t="n">
-        <v>110.7</v>
+        <v>106.9539</v>
       </c>
       <c r="DC6" t="n">
-        <v>105.2</v>
+        <v>101.6401</v>
       </c>
       <c r="DD6" t="n">
-        <v>109.95</v>
+        <v>106.2293</v>
       </c>
       <c r="DE6" t="n">
         <v>104.55</v>
@@ -3632,10 +3632,10 @@
         <v>101.4</v>
       </c>
       <c r="FZ6" t="n">
-        <v>109</v>
+        <v>105.3115</v>
       </c>
       <c r="GE6" t="n">
-        <v>112.2</v>
+        <v>108.4032</v>
       </c>
       <c r="GF6" t="n">
         <v>104</v>
@@ -3882,13 +3882,13 @@
         <v>45.25000000000001</v>
       </c>
       <c r="CI7" t="n">
-        <v>63.5</v>
+        <v>61.3286</v>
       </c>
       <c r="CJ7" t="n">
-        <v>112</v>
+        <v>108.1702</v>
       </c>
       <c r="CK7" t="n">
-        <v>102.45</v>
+        <v>98.94670000000001</v>
       </c>
       <c r="CM7" t="n">
         <v>100.6</v>
@@ -3900,16 +3900,16 @@
         <v>72.59</v>
       </c>
       <c r="CP7" t="n">
-        <v>75</v>
+        <v>72.4354</v>
       </c>
       <c r="CQ7" t="n">
-        <v>107.9</v>
+        <v>104.2104</v>
       </c>
       <c r="CR7" t="n">
-        <v>109.65</v>
+        <v>105.9005</v>
       </c>
       <c r="CS7" t="n">
-        <v>107.3</v>
+        <v>103.6309</v>
       </c>
       <c r="CT7" t="n">
         <v>104</v>
@@ -3963,7 +3963,7 @@
         <v>110.55</v>
       </c>
       <c r="DN7" t="n">
-        <v>110.5</v>
+        <v>106.7215</v>
       </c>
       <c r="DO7" t="n">
         <v>104.35</v>
@@ -4363,10 +4363,10 @@
         <v>45.24999999999999</v>
       </c>
       <c r="CI8" t="n">
-        <v>63.72</v>
+        <v>61.4484</v>
       </c>
       <c r="CJ8" t="n">
-        <v>112.3</v>
+        <v>108.2965</v>
       </c>
       <c r="CM8" t="n">
         <v>100.6</v>
@@ -4378,7 +4378,7 @@
         <v>73.25</v>
       </c>
       <c r="CP8" t="n">
-        <v>76.34</v>
+        <v>73.6185</v>
       </c>
       <c r="CQ8" t="n">
         <v>104.15</v>
@@ -4387,7 +4387,7 @@
         <v>104.8</v>
       </c>
       <c r="CS8" t="n">
-        <v>107.9</v>
+        <v>104.0534</v>
       </c>
       <c r="CT8" t="n">
         <v>104.3</v>
@@ -4411,7 +4411,7 @@
         <v>106.85</v>
       </c>
       <c r="DC8" t="n">
-        <v>105.4</v>
+        <v>101.6425</v>
       </c>
       <c r="DD8" t="n">
         <v>106.7</v>
@@ -4441,7 +4441,7 @@
         <v>110.7</v>
       </c>
       <c r="DN8" t="n">
-        <v>110.7</v>
+        <v>106.7536</v>
       </c>
       <c r="DO8" t="n">
         <v>104.55</v>
@@ -4471,7 +4471,7 @@
         <v>104.25</v>
       </c>
       <c r="DX8" t="n">
-        <v>107.25</v>
+        <v>103.4266</v>
       </c>
       <c r="DY8" t="n">
         <v>107.65</v>
@@ -4483,7 +4483,7 @@
         <v>107.25</v>
       </c>
       <c r="EB8" t="n">
-        <v>107.1</v>
+        <v>103.2819</v>
       </c>
       <c r="EC8" t="n">
         <v>100.6</v>
@@ -4546,7 +4546,7 @@
         <v>104.55</v>
       </c>
       <c r="EY8" t="n">
-        <v>108.3</v>
+        <v>104.4391</v>
       </c>
       <c r="EZ8" t="n">
         <v>100.5</v>
@@ -4588,7 +4588,7 @@
         <v>101.3</v>
       </c>
       <c r="FZ8" t="n">
-        <v>109</v>
+        <v>105.1142</v>
       </c>
       <c r="GE8" t="n">
         <v>108.35</v>
@@ -4838,10 +4838,10 @@
         <v>45.25</v>
       </c>
       <c r="CI9" t="n">
-        <v>64.19</v>
+        <v>61.9226</v>
       </c>
       <c r="CJ9" t="n">
-        <v>112.7</v>
+        <v>108.719</v>
       </c>
       <c r="CM9" t="n">
         <v>100.65</v>
@@ -4853,16 +4853,16 @@
         <v>72.93000000000001</v>
       </c>
       <c r="CP9" t="n">
-        <v>76.5</v>
+        <v>73.79770000000001</v>
       </c>
       <c r="CQ9" t="n">
-        <v>108.1</v>
+        <v>104.2815</v>
       </c>
       <c r="CR9" t="n">
-        <v>110.4</v>
+        <v>106.5003</v>
       </c>
       <c r="CS9" t="n">
-        <v>108</v>
+        <v>104.1851</v>
       </c>
       <c r="CT9" t="n">
         <v>104</v>
@@ -4880,10 +4880,10 @@
         <v>106.5</v>
       </c>
       <c r="DA9" t="n">
-        <v>111.35</v>
+        <v>107.4167</v>
       </c>
       <c r="DB9" t="n">
-        <v>111.1</v>
+        <v>107.1755</v>
       </c>
       <c r="DC9" t="n">
         <v>101.55</v>
@@ -5069,7 +5069,7 @@
         <v>101.95</v>
       </c>
       <c r="FZ9" t="n">
-        <v>110</v>
+        <v>106.1144</v>
       </c>
       <c r="GE9" t="n">
         <v>108.8</v>
@@ -5319,13 +5319,13 @@
         <v>45.24999999999999</v>
       </c>
       <c r="CI10" t="n">
-        <v>63.7</v>
+        <v>61.4124</v>
       </c>
       <c r="CJ10" t="n">
         <v>110</v>
       </c>
       <c r="CK10" t="n">
-        <v>102.8</v>
+        <v>99.1083</v>
       </c>
       <c r="CM10" t="n">
         <v>100.75</v>
@@ -5400,7 +5400,7 @@
         <v>113</v>
       </c>
       <c r="DN10" t="n">
-        <v>111</v>
+        <v>107.0138</v>
       </c>
       <c r="DO10" t="n">
         <v>104.7</v>
@@ -5553,10 +5553,10 @@
         <v>102</v>
       </c>
       <c r="FZ10" t="n">
-        <v>110.2</v>
+        <v>106.2425</v>
       </c>
       <c r="GE10" t="n">
-        <v>112.8</v>
+        <v>108.7492</v>
       </c>
       <c r="GF10" t="n">
         <v>103.75</v>
@@ -5800,13 +5800,13 @@
         <v>45.4</v>
       </c>
       <c r="CI11" t="n">
-        <v>64.01000000000001</v>
+        <v>61.7302</v>
       </c>
       <c r="CK11" t="n">
-        <v>103</v>
+        <v>99.33150000000001</v>
       </c>
       <c r="CM11" t="n">
-        <v>104.9</v>
+        <v>101.1638</v>
       </c>
       <c r="CN11" t="n">
         <v>98</v>
@@ -5815,7 +5815,7 @@
         <v>72.97</v>
       </c>
       <c r="CP11" t="n">
-        <v>76.59999999999999</v>
+        <v>73.87179999999999</v>
       </c>
       <c r="CQ11" t="n">
         <v>104.55</v>
@@ -5842,13 +5842,13 @@
         <v>100.6</v>
       </c>
       <c r="DA11" t="n">
-        <v>111.7</v>
+        <v>107.7216</v>
       </c>
       <c r="DB11" t="n">
         <v>107.2</v>
       </c>
       <c r="DC11" t="n">
-        <v>105.9</v>
+        <v>102.1282</v>
       </c>
       <c r="DD11" t="n">
         <v>106.6</v>
@@ -5878,7 +5878,7 @@
         <v>111</v>
       </c>
       <c r="DN11" t="n">
-        <v>112</v>
+        <v>108.0109</v>
       </c>
       <c r="DO11" t="n">
         <v>104.5</v>
@@ -6028,7 +6028,7 @@
         <v>101.5</v>
       </c>
       <c r="GE11" t="n">
-        <v>112.65</v>
+        <v>108.6378</v>
       </c>
       <c r="GF11" t="n">
         <v>104</v>
@@ -6269,13 +6269,13 @@
         <v>102</v>
       </c>
       <c r="CH12" t="n">
-        <v>46.61</v>
+        <v>44.8958</v>
       </c>
       <c r="CI12" t="n">
-        <v>64.5</v>
+        <v>62.1278</v>
       </c>
       <c r="CJ12" t="n">
-        <v>113.3</v>
+        <v>109.1331</v>
       </c>
       <c r="CM12" t="n">
         <v>100.95</v>
@@ -6287,7 +6287,7 @@
         <v>72.90000000000001</v>
       </c>
       <c r="CP12" t="n">
-        <v>76.40000000000001</v>
+        <v>73.5902</v>
       </c>
       <c r="CQ12" t="n">
         <v>104.25</v>
@@ -6305,7 +6305,7 @@
         <v>101.05</v>
       </c>
       <c r="CW12" t="n">
-        <v>71.2</v>
+        <v>68.5814</v>
       </c>
       <c r="CX12" t="n">
         <v>105.25</v>
@@ -6320,7 +6320,7 @@
         <v>107.05</v>
       </c>
       <c r="DC12" t="n">
-        <v>105.85</v>
+        <v>101.9571</v>
       </c>
       <c r="DD12" t="n">
         <v>106.6</v>
@@ -6350,7 +6350,7 @@
         <v>111.05</v>
       </c>
       <c r="DN12" t="n">
-        <v>111.85</v>
+        <v>107.7364</v>
       </c>
       <c r="DO12" t="n">
         <v>104.6</v>
@@ -6738,10 +6738,10 @@
         <v>101.95</v>
       </c>
       <c r="CH13" t="n">
-        <v>46.65</v>
+        <v>44.9863</v>
       </c>
       <c r="CI13" t="n">
-        <v>63.8</v>
+        <v>61.5247</v>
       </c>
       <c r="CJ13" t="n">
         <v>109.5</v>
@@ -6759,13 +6759,13 @@
         <v>72.90000000000001</v>
       </c>
       <c r="CP13" t="n">
-        <v>75.47</v>
+        <v>72.77849999999999</v>
       </c>
       <c r="CQ13" t="n">
         <v>104.85</v>
       </c>
       <c r="CR13" t="n">
-        <v>110.1</v>
+        <v>106.1735</v>
       </c>
       <c r="CS13" t="n">
         <v>105.5</v>
@@ -6789,7 +6789,7 @@
         <v>107.25</v>
       </c>
       <c r="DB13" t="n">
-        <v>111.65</v>
+        <v>107.6682</v>
       </c>
       <c r="DC13" t="n">
         <v>102.2</v>
@@ -6813,16 +6813,16 @@
         <v>107.6</v>
       </c>
       <c r="DK13" t="n">
-        <v>114.3</v>
+        <v>110.2237</v>
       </c>
       <c r="DL13" t="n">
         <v>104.2</v>
       </c>
       <c r="DM13" t="n">
-        <v>111</v>
+        <v>107.0414</v>
       </c>
       <c r="DN13" t="n">
-        <v>107.3</v>
+        <v>103.4733</v>
       </c>
       <c r="DO13" t="n">
         <v>104.65</v>
@@ -6978,7 +6978,7 @@
         <v>98.55</v>
       </c>
       <c r="FZ13" t="n">
-        <v>111.65</v>
+        <v>107.6682</v>
       </c>
       <c r="GE13" t="n">
         <v>108.75</v>
@@ -7225,7 +7225,7 @@
         <v>44.5</v>
       </c>
       <c r="CI14" t="n">
-        <v>64.59999999999999</v>
+        <v>62.2715</v>
       </c>
       <c r="CJ14" t="n">
         <v>110</v>
@@ -7243,7 +7243,7 @@
         <v>72.8</v>
       </c>
       <c r="CP14" t="n">
-        <v>76.36</v>
+        <v>73.60769999999999</v>
       </c>
       <c r="CQ14" t="n">
         <v>104.3</v>
@@ -7261,7 +7261,7 @@
         <v>101.25</v>
       </c>
       <c r="CW14" t="n">
-        <v>71.7</v>
+        <v>69.1156</v>
       </c>
       <c r="CX14" t="n">
         <v>106.9</v>
@@ -7270,10 +7270,10 @@
         <v>101.65</v>
       </c>
       <c r="DA14" t="n">
-        <v>111.8</v>
+        <v>107.7702</v>
       </c>
       <c r="DB14" t="n">
-        <v>111</v>
+        <v>106.9991</v>
       </c>
       <c r="DC14" t="n">
         <v>102</v>
@@ -7288,7 +7288,7 @@
         <v>105.6</v>
       </c>
       <c r="DH14" t="n">
-        <v>107.7</v>
+        <v>103.818</v>
       </c>
       <c r="DI14" t="n">
         <v>111.55</v>
@@ -7306,7 +7306,7 @@
         <v>107.75</v>
       </c>
       <c r="DN14" t="n">
-        <v>107.3</v>
+        <v>103.4324</v>
       </c>
       <c r="DO14" t="n">
         <v>104.8</v>
@@ -7336,7 +7336,7 @@
         <v>104.95</v>
       </c>
       <c r="DX14" t="n">
-        <v>109.45</v>
+        <v>105.5049</v>
       </c>
       <c r="DY14" t="n">
         <v>108.4</v>
@@ -7465,7 +7465,7 @@
         <v>107</v>
       </c>
       <c r="GE14" t="n">
-        <v>113.35</v>
+        <v>109.2644</v>
       </c>
       <c r="GF14" t="n">
         <v>104.95</v>
@@ -7706,7 +7706,7 @@
         <v>45.00000000000001</v>
       </c>
       <c r="CI15" t="n">
-        <v>64.14</v>
+        <v>62.1385</v>
       </c>
       <c r="CK15" t="n">
         <v>99.84999999999999</v>
@@ -7724,13 +7724,13 @@
         <v>75</v>
       </c>
       <c r="CQ15" t="n">
-        <v>107.8</v>
+        <v>104.436</v>
       </c>
       <c r="CR15" t="n">
-        <v>110.15</v>
+        <v>106.7127</v>
       </c>
       <c r="CS15" t="n">
-        <v>108</v>
+        <v>104.6298</v>
       </c>
       <c r="CT15" t="n">
         <v>105</v>
@@ -7748,10 +7748,10 @@
         <v>102.45</v>
       </c>
       <c r="DA15" t="n">
-        <v>111.15</v>
+        <v>107.6815</v>
       </c>
       <c r="DB15" t="n">
-        <v>111.2</v>
+        <v>107.7299</v>
       </c>
       <c r="DC15" t="n">
         <v>102.4</v>
@@ -7775,7 +7775,7 @@
         <v>108</v>
       </c>
       <c r="DK15" t="n">
-        <v>114.1</v>
+        <v>110.5394</v>
       </c>
       <c r="DL15" t="n">
         <v>104.8</v>
@@ -7784,7 +7784,7 @@
         <v>107.3</v>
       </c>
       <c r="DN15" t="n">
-        <v>107.7</v>
+        <v>104.3391</v>
       </c>
       <c r="DO15" t="n">
         <v>105.9</v>
@@ -7940,7 +7940,7 @@
         <v>98.75</v>
       </c>
       <c r="FW15" t="n">
-        <v>99</v>
+        <v>95.9106</v>
       </c>
       <c r="GE15" t="n">
         <v>109.25</v>
@@ -8196,13 +8196,13 @@
         <v>101.85</v>
       </c>
       <c r="CH16" t="n">
-        <v>47</v>
+        <v>45.5918</v>
       </c>
       <c r="CI16" t="n">
         <v>62.00000000000001</v>
       </c>
       <c r="CJ16" t="n">
-        <v>114.4</v>
+        <v>110.9723</v>
       </c>
       <c r="CM16" t="n">
         <v>103</v>
@@ -8214,13 +8214,13 @@
         <v>74.76000000000001</v>
       </c>
       <c r="CP16" t="n">
-        <v>77.59999999999999</v>
+        <v>75.2749</v>
       </c>
       <c r="CQ16" t="n">
         <v>104.4</v>
       </c>
       <c r="CR16" t="n">
-        <v>110.3</v>
+        <v>106.9951</v>
       </c>
       <c r="CS16" t="n">
         <v>105</v>
@@ -8241,7 +8241,7 @@
         <v>101.8</v>
       </c>
       <c r="DA16" t="n">
-        <v>111.1</v>
+        <v>107.7712</v>
       </c>
       <c r="DB16" t="n">
         <v>106.05</v>
@@ -8277,7 +8277,7 @@
         <v>109</v>
       </c>
       <c r="DN16" t="n">
-        <v>109.9</v>
+        <v>106.6071</v>
       </c>
       <c r="DO16" t="n">
         <v>106.25</v>
@@ -8295,7 +8295,7 @@
         <v>111</v>
       </c>
       <c r="DT16" t="n">
-        <v>108.35</v>
+        <v>105.1036</v>
       </c>
       <c r="DU16" t="n">
         <v>105.15</v>
@@ -8436,7 +8436,7 @@
         <v>95.95</v>
       </c>
       <c r="FZ16" t="n">
-        <v>112.55</v>
+        <v>109.1777</v>
       </c>
       <c r="GE16" t="n">
         <v>109.6</v>
@@ -8695,13 +8695,13 @@
         <v>45.3</v>
       </c>
       <c r="CI17" t="n">
-        <v>63.01999999999999</v>
+        <v>61.2561</v>
       </c>
       <c r="CJ17" t="n">
-        <v>114.25</v>
+        <v>111.0523</v>
       </c>
       <c r="CM17" t="n">
-        <v>106.2</v>
+        <v>103.2276</v>
       </c>
       <c r="CN17" t="n">
         <v>99.34999999999999</v>
@@ -8710,16 +8710,16 @@
         <v>75.54000000000001</v>
       </c>
       <c r="CP17" t="n">
-        <v>77.2</v>
+        <v>75.0393</v>
       </c>
       <c r="CQ17" t="n">
-        <v>107.7</v>
+        <v>104.6856</v>
       </c>
       <c r="CR17" t="n">
-        <v>109.6</v>
+        <v>106.5324</v>
       </c>
       <c r="CS17" t="n">
-        <v>109</v>
+        <v>105.9492</v>
       </c>
       <c r="CT17" t="n">
         <v>106.45</v>
@@ -8737,7 +8737,7 @@
         <v>103.95</v>
       </c>
       <c r="DA17" t="n">
-        <v>111.1</v>
+        <v>107.9904</v>
       </c>
       <c r="DB17" t="n">
         <v>106.05</v>
@@ -8764,7 +8764,7 @@
         <v>109.5</v>
       </c>
       <c r="DK17" t="n">
-        <v>114</v>
+        <v>110.8093</v>
       </c>
       <c r="DL17" t="n">
         <v>105.6</v>
@@ -8773,7 +8773,7 @@
         <v>108.9</v>
       </c>
       <c r="DN17" t="n">
-        <v>108.75</v>
+        <v>105.7062</v>
       </c>
       <c r="DO17" t="n">
         <v>107</v>
@@ -8803,7 +8803,7 @@
         <v>105.6</v>
       </c>
       <c r="DX17" t="n">
-        <v>107.9</v>
+        <v>104.88</v>
       </c>
       <c r="DY17" t="n">
         <v>109</v>
@@ -8929,7 +8929,7 @@
         <v>97.00000000000001</v>
       </c>
       <c r="FZ17" t="n">
-        <v>113.5</v>
+        <v>110.3233</v>
       </c>
       <c r="GE17" t="n">
         <v>109.2</v>
@@ -9188,10 +9188,10 @@
         <v>45.3</v>
       </c>
       <c r="CI18" t="n">
-        <v>63.27</v>
+        <v>61.5151</v>
       </c>
       <c r="CM18" t="n">
-        <v>106.3</v>
+        <v>103.3516</v>
       </c>
       <c r="CN18" t="n">
         <v>99.39</v>
@@ -9200,10 +9200,10 @@
         <v>75.64</v>
       </c>
       <c r="CP18" t="n">
-        <v>78</v>
+        <v>75.8365</v>
       </c>
       <c r="CQ18" t="n">
-        <v>107.6</v>
+        <v>104.6155</v>
       </c>
       <c r="CR18" t="n">
         <v>106.5</v>
@@ -9218,7 +9218,7 @@
         <v>103.2</v>
       </c>
       <c r="CW18" t="n">
-        <v>71.84</v>
+        <v>69.84739999999999</v>
       </c>
       <c r="CX18" t="n">
         <v>106.2</v>
@@ -9230,13 +9230,13 @@
         <v>100.35</v>
       </c>
       <c r="DA18" t="n">
-        <v>111.1</v>
+        <v>108.0184</v>
       </c>
       <c r="DB18" t="n">
         <v>104.75</v>
       </c>
       <c r="DC18" t="n">
-        <v>106.9</v>
+        <v>103.9349</v>
       </c>
       <c r="DD18" t="n">
         <v>107.35</v>
@@ -9266,7 +9266,7 @@
         <v>108.45</v>
       </c>
       <c r="DN18" t="n">
-        <v>108.3</v>
+        <v>105.2961</v>
       </c>
       <c r="DO18" t="n">
         <v>106.4</v>
@@ -9639,7 +9639,7 @@
         <v>108.3</v>
       </c>
       <c r="BP19" t="n">
-        <v>106.35</v>
+        <v>103.4125</v>
       </c>
       <c r="BQ19" t="n">
         <v>144390</v>
@@ -9675,13 +9675,13 @@
         <v>101.9</v>
       </c>
       <c r="CH19" t="n">
-        <v>47.1</v>
+        <v>45.799</v>
       </c>
       <c r="CI19" t="n">
-        <v>63.12</v>
+        <v>61.3765</v>
       </c>
       <c r="CJ19" t="n">
-        <v>114.5</v>
+        <v>111.3374</v>
       </c>
       <c r="CK19" t="n">
         <v>100.55</v>
@@ -9690,22 +9690,22 @@
         <v>103.25</v>
       </c>
       <c r="CN19" t="n">
-        <v>102.25</v>
+        <v>99.42570000000001</v>
       </c>
       <c r="CO19" t="n">
         <v>75.45</v>
       </c>
       <c r="CP19" t="n">
-        <v>78.5</v>
+        <v>76.3317</v>
       </c>
       <c r="CQ19" t="n">
         <v>104.75</v>
       </c>
       <c r="CR19" t="n">
-        <v>109.45</v>
+        <v>106.4269</v>
       </c>
       <c r="CS19" t="n">
-        <v>108.25</v>
+        <v>105.26</v>
       </c>
       <c r="CT19" t="n">
         <v>106.6</v>
@@ -9714,7 +9714,7 @@
         <v>103.85</v>
       </c>
       <c r="CW19" t="n">
-        <v>71</v>
+        <v>69.0389</v>
       </c>
       <c r="CX19" t="n">
         <v>106.4</v>
@@ -9726,13 +9726,13 @@
         <v>99.99999999999999</v>
       </c>
       <c r="DA19" t="n">
-        <v>111.05</v>
+        <v>107.9827</v>
       </c>
       <c r="DB19" t="n">
         <v>104.75</v>
       </c>
       <c r="DC19" t="n">
-        <v>106.95</v>
+        <v>103.9959</v>
       </c>
       <c r="DD19" t="n">
         <v>107.1</v>
@@ -9753,7 +9753,7 @@
         <v>109</v>
       </c>
       <c r="DK19" t="n">
-        <v>113.25</v>
+        <v>110.1219</v>
       </c>
       <c r="DL19" t="n">
         <v>105.5</v>
@@ -9762,7 +9762,7 @@
         <v>107.8</v>
       </c>
       <c r="DN19" t="n">
-        <v>108.2</v>
+        <v>105.2114</v>
       </c>
       <c r="DO19" t="n">
         <v>106.5</v>
@@ -9792,7 +9792,7 @@
         <v>104.75</v>
       </c>
       <c r="DX19" t="n">
-        <v>107.75</v>
+        <v>104.7738</v>
       </c>
       <c r="DY19" t="n">
         <v>108.65</v>
@@ -9804,7 +9804,7 @@
         <v>107.9</v>
       </c>
       <c r="EB19" t="n">
-        <v>107.9</v>
+        <v>104.9197</v>
       </c>
       <c r="EC19" t="n">
         <v>102.2</v>
@@ -9870,7 +9870,7 @@
         <v>105.45</v>
       </c>
       <c r="EY19" t="n">
-        <v>108.45</v>
+        <v>105.4545</v>
       </c>
       <c r="EZ19" t="n">
         <v>101.15</v>
@@ -9918,7 +9918,7 @@
         <v>97.72000000000001</v>
       </c>
       <c r="GE19" t="n">
-        <v>112.55</v>
+        <v>109.4412</v>
       </c>
       <c r="GF19" t="n">
         <v>105.95</v>
@@ -10171,13 +10171,13 @@
         <v>101.8</v>
       </c>
       <c r="CH20" t="n">
-        <v>46.75</v>
+        <v>45.4251</v>
       </c>
       <c r="CI20" t="n">
-        <v>63.3</v>
+        <v>61.5061</v>
       </c>
       <c r="CJ20" t="n">
-        <v>114.5</v>
+        <v>111.2551</v>
       </c>
       <c r="CK20" t="n">
         <v>100.85</v>
@@ -10186,13 +10186,13 @@
         <v>104</v>
       </c>
       <c r="CN20" t="n">
-        <v>102.15</v>
+        <v>99.2551</v>
       </c>
       <c r="CO20" t="n">
         <v>75.61</v>
       </c>
       <c r="CP20" t="n">
-        <v>78.40000000000001</v>
+        <v>76.1781</v>
       </c>
       <c r="CQ20" t="n">
         <v>105</v>
@@ -10201,7 +10201,7 @@
         <v>106.45</v>
       </c>
       <c r="CS20" t="n">
-        <v>109.4</v>
+        <v>106.2996</v>
       </c>
       <c r="CT20" t="n">
         <v>105.9</v>
@@ -10210,7 +10210,7 @@
         <v>103.4</v>
       </c>
       <c r="CW20" t="n">
-        <v>51.2</v>
+        <v>49.749</v>
       </c>
       <c r="CX20" t="n">
         <v>104.6</v>
@@ -10222,7 +10222,7 @@
         <v>100</v>
       </c>
       <c r="DA20" t="n">
-        <v>110.95</v>
+        <v>107.8057</v>
       </c>
       <c r="DB20" t="n">
         <v>105</v>
@@ -10249,7 +10249,7 @@
         <v>109.2</v>
       </c>
       <c r="DK20" t="n">
-        <v>113.8</v>
+        <v>110.5749</v>
       </c>
       <c r="DL20" t="n">
         <v>104.95</v>
@@ -10258,7 +10258,7 @@
         <v>108</v>
       </c>
       <c r="DN20" t="n">
-        <v>108</v>
+        <v>104.9393</v>
       </c>
       <c r="DO20" t="n">
         <v>106.55</v>
@@ -10300,7 +10300,7 @@
         <v>107.9</v>
       </c>
       <c r="EB20" t="n">
-        <v>107.6</v>
+        <v>104.5506</v>
       </c>
       <c r="EC20" t="n">
         <v>102.15</v>
@@ -10363,7 +10363,7 @@
         <v>106.5</v>
       </c>
       <c r="EY20" t="n">
-        <v>107.55</v>
+        <v>104.502</v>
       </c>
       <c r="EZ20" t="n">
         <v>101.05</v>
@@ -10405,13 +10405,13 @@
         <v>102.6</v>
       </c>
       <c r="FW20" t="n">
-        <v>100.5</v>
+        <v>97.65179999999999</v>
       </c>
       <c r="FZ20" t="n">
-        <v>113</v>
+        <v>109.7976</v>
       </c>
       <c r="GE20" t="n">
-        <v>112.35</v>
+        <v>109.166</v>
       </c>
       <c r="GF20" t="n">
         <v>105.2</v>
@@ -10664,13 +10664,13 @@
         <v>101.85</v>
       </c>
       <c r="CH21" t="n">
-        <v>46.8</v>
+        <v>45.4278</v>
       </c>
       <c r="CI21" t="n">
         <v>64</v>
       </c>
       <c r="CJ21" t="n">
-        <v>115</v>
+        <v>111.6282</v>
       </c>
       <c r="CM21" t="n">
         <v>103.35</v>
@@ -10682,16 +10682,16 @@
         <v>75.5</v>
       </c>
       <c r="CP21" t="n">
-        <v>78</v>
+        <v>75.71299999999999</v>
       </c>
       <c r="CQ21" t="n">
-        <v>107.3</v>
+        <v>104.1539</v>
       </c>
       <c r="CR21" t="n">
         <v>106.45</v>
       </c>
       <c r="CS21" t="n">
-        <v>108.5</v>
+        <v>105.3187</v>
       </c>
       <c r="CT21" t="n">
         <v>106.1</v>
@@ -10700,7 +10700,7 @@
         <v>103</v>
       </c>
       <c r="CW21" t="n">
-        <v>51.24999999999999</v>
+        <v>49.7473</v>
       </c>
       <c r="CX21" t="n">
         <v>105.65</v>
@@ -10712,10 +10712,10 @@
         <v>99.81</v>
       </c>
       <c r="DA21" t="n">
-        <v>111.1</v>
+        <v>107.8425</v>
       </c>
       <c r="DB21" t="n">
-        <v>108</v>
+        <v>104.8334</v>
       </c>
       <c r="DC21" t="n">
         <v>102.95</v>
@@ -10856,7 +10856,7 @@
         <v>103.2</v>
       </c>
       <c r="EY21" t="n">
-        <v>108</v>
+        <v>104.8334</v>
       </c>
       <c r="EZ21" t="n">
         <v>101.05</v>
@@ -11157,16 +11157,16 @@
         <v>101.85</v>
       </c>
       <c r="CH22" t="n">
-        <v>46.8</v>
+        <v>45.3538</v>
       </c>
       <c r="CI22" t="n">
         <v>60.5</v>
       </c>
       <c r="CJ22" t="n">
-        <v>114.4</v>
+        <v>110.8649</v>
       </c>
       <c r="CK22" t="n">
-        <v>103.95</v>
+        <v>100.7378</v>
       </c>
       <c r="CM22" t="n">
         <v>102.6</v>
@@ -11178,7 +11178,7 @@
         <v>76.13</v>
       </c>
       <c r="CP22" t="n">
-        <v>78</v>
+        <v>75.58969999999999</v>
       </c>
       <c r="CQ22" t="n">
         <v>104.85</v>
@@ -11208,7 +11208,7 @@
         <v>99.7</v>
       </c>
       <c r="DA22" t="n">
-        <v>111.2</v>
+        <v>107.7638</v>
       </c>
       <c r="DB22" t="n">
         <v>104.95</v>
@@ -11403,7 +11403,7 @@
         <v>97</v>
       </c>
       <c r="FZ22" t="n">
-        <v>112.55</v>
+        <v>109.0721</v>
       </c>
       <c r="GE22" t="n">
         <v>108.5</v>
@@ -11662,22 +11662,22 @@
         <v>45.2</v>
       </c>
       <c r="CI23" t="n">
-        <v>64.2</v>
+        <v>62.1918</v>
       </c>
       <c r="CJ23" t="n">
-        <v>114.1</v>
+        <v>110.531</v>
       </c>
       <c r="CM23" t="n">
         <v>103</v>
       </c>
       <c r="CN23" t="n">
-        <v>102.45</v>
+        <v>99.2454</v>
       </c>
       <c r="CO23" t="n">
         <v>75.31999999999999</v>
       </c>
       <c r="CP23" t="n">
-        <v>77.59999999999999</v>
+        <v>75.17270000000001</v>
       </c>
       <c r="CQ23" t="n">
         <v>104.8</v>
@@ -11686,7 +11686,7 @@
         <v>106.25</v>
       </c>
       <c r="CS23" t="n">
-        <v>108.9</v>
+        <v>105.4936</v>
       </c>
       <c r="CT23" t="n">
         <v>105.65</v>
@@ -11707,7 +11707,7 @@
         <v>99.75</v>
       </c>
       <c r="DA23" t="n">
-        <v>111.3</v>
+        <v>107.8185</v>
       </c>
       <c r="DB23" t="n">
         <v>104.7</v>
@@ -11773,7 +11773,7 @@
         <v>104.8</v>
       </c>
       <c r="DX23" t="n">
-        <v>108.4</v>
+        <v>105.0093</v>
       </c>
       <c r="DY23" t="n">
         <v>109.05</v>
@@ -11902,7 +11902,7 @@
         <v>97</v>
       </c>
       <c r="FZ23" t="n">
-        <v>112.55</v>
+        <v>109.0294</v>
       </c>
       <c r="GE23" t="n">
         <v>109</v>
@@ -12158,13 +12158,13 @@
         <v>102.25</v>
       </c>
       <c r="CH24" t="n">
-        <v>46.8</v>
+        <v>45.4175</v>
       </c>
       <c r="CI24" t="n">
         <v>60.5</v>
       </c>
       <c r="CJ24" t="n">
-        <v>115</v>
+        <v>111.6027</v>
       </c>
       <c r="CM24" t="n">
         <v>103.3</v>
@@ -12176,7 +12176,7 @@
         <v>75.58</v>
       </c>
       <c r="CP24" t="n">
-        <v>78</v>
+        <v>75.69580000000001</v>
       </c>
       <c r="CQ24" t="n">
         <v>104.65</v>
@@ -12185,7 +12185,7 @@
         <v>107.1</v>
       </c>
       <c r="CS24" t="n">
-        <v>108.9</v>
+        <v>105.6829</v>
       </c>
       <c r="CT24" t="n">
         <v>105.7</v>
@@ -12194,7 +12194,7 @@
         <v>102.55</v>
       </c>
       <c r="CV24" t="n">
-        <v>74</v>
+        <v>71.8139</v>
       </c>
       <c r="CW24" t="n">
         <v>49.545</v>
@@ -12275,7 +12275,7 @@
         <v>105.4</v>
       </c>
       <c r="DX24" t="n">
-        <v>108</v>
+        <v>104.8095</v>
       </c>
       <c r="DY24" t="n">
         <v>109.45</v>
@@ -12401,7 +12401,7 @@
         <v>97</v>
       </c>
       <c r="FZ24" t="n">
-        <v>112.3</v>
+        <v>108.9825</v>
       </c>
       <c r="GE24" t="n">
         <v>109</v>
@@ -12657,10 +12657,10 @@
         <v>102</v>
       </c>
       <c r="CH25" t="n">
-        <v>47.1</v>
+        <v>45.7642</v>
       </c>
       <c r="CI25" t="n">
-        <v>63.63999999999999</v>
+        <v>61.8351</v>
       </c>
       <c r="CJ25" t="n">
         <v>113</v>
@@ -12675,7 +12675,7 @@
         <v>75.39</v>
       </c>
       <c r="CP25" t="n">
-        <v>77.90000000000001</v>
+        <v>75.6906</v>
       </c>
       <c r="CQ25" t="n">
         <v>104.6</v>
@@ -12741,10 +12741,10 @@
         <v>104.1</v>
       </c>
       <c r="DM25" t="n">
-        <v>110.35</v>
+        <v>107.2203</v>
       </c>
       <c r="DN25" t="n">
-        <v>107.35</v>
+        <v>104.3054</v>
       </c>
       <c r="DO25" t="n">
         <v>105.35</v>
@@ -12894,7 +12894,7 @@
         <v>102.9</v>
       </c>
       <c r="FW25" t="n">
-        <v>100</v>
+        <v>97.1639</v>
       </c>
       <c r="FZ25" t="n">
         <v>109.1</v>
@@ -13144,13 +13144,13 @@
         <v>46.00000000000001</v>
       </c>
       <c r="CI26" t="n">
-        <v>63.49999999999999</v>
+        <v>61.6382</v>
       </c>
       <c r="CJ26" t="n">
-        <v>115</v>
+        <v>111.6282</v>
       </c>
       <c r="CM26" t="n">
-        <v>106.8</v>
+        <v>103.6686</v>
       </c>
       <c r="CN26" t="n">
         <v>99.42</v>
@@ -13159,10 +13159,10 @@
         <v>75.3</v>
       </c>
       <c r="CP26" t="n">
-        <v>79.5</v>
+        <v>77.169</v>
       </c>
       <c r="CQ26" t="n">
-        <v>107.6</v>
+        <v>104.4451</v>
       </c>
       <c r="CR26" t="n">
         <v>105.9</v>
@@ -13195,7 +13195,7 @@
         <v>107.7</v>
       </c>
       <c r="DB26" t="n">
-        <v>107.35</v>
+        <v>104.2025</v>
       </c>
       <c r="DC26" t="n">
         <v>103.75</v>
@@ -13384,7 +13384,7 @@
         <v>103</v>
       </c>
       <c r="FW26" t="n">
-        <v>100.15</v>
+        <v>97.2136</v>
       </c>
       <c r="FZ26" t="n">
         <v>109.25</v>
@@ -13646,10 +13646,10 @@
         <v>46</v>
       </c>
       <c r="CI27" t="n">
-        <v>63.6</v>
+        <v>61.7045</v>
       </c>
       <c r="CJ27" t="n">
-        <v>115</v>
+        <v>111.5727</v>
       </c>
       <c r="CM27" t="n">
         <v>104.5</v>
@@ -13661,10 +13661,10 @@
         <v>75</v>
       </c>
       <c r="CP27" t="n">
-        <v>78.34999999999999</v>
+        <v>76.0149</v>
       </c>
       <c r="CQ27" t="n">
-        <v>108.05</v>
+        <v>104.8298</v>
       </c>
       <c r="CR27" t="n">
         <v>106.3</v>
@@ -13679,7 +13679,7 @@
         <v>102.35</v>
       </c>
       <c r="CV27" t="n">
-        <v>85.3</v>
+        <v>82.7578</v>
       </c>
       <c r="CW27" t="n">
         <v>49.957</v>
@@ -13694,10 +13694,10 @@
         <v>100.4</v>
       </c>
       <c r="DA27" t="n">
-        <v>110.7</v>
+        <v>107.4008</v>
       </c>
       <c r="DB27" t="n">
-        <v>107.4</v>
+        <v>104.1992</v>
       </c>
       <c r="DC27" t="n">
         <v>104</v>
@@ -13730,7 +13730,7 @@
         <v>107.05</v>
       </c>
       <c r="DN27" t="n">
-        <v>107.25</v>
+        <v>104.0536</v>
       </c>
       <c r="DO27" t="n">
         <v>105.55</v>
@@ -13877,7 +13877,7 @@
         <v>103</v>
       </c>
       <c r="FW27" t="n">
-        <v>100.2</v>
+        <v>97.21380000000001</v>
       </c>
       <c r="FZ27" t="n">
         <v>109.4</v>
@@ -14136,25 +14136,25 @@
         <v>102.1</v>
       </c>
       <c r="CH28" t="n">
-        <v>47.39000000000001</v>
+        <v>45.9623</v>
       </c>
       <c r="CI28" t="n">
-        <v>63.6</v>
+        <v>61.684</v>
       </c>
       <c r="CM28" t="n">
         <v>103.65</v>
       </c>
       <c r="CN28" t="n">
-        <v>102.5</v>
+        <v>99.4121</v>
       </c>
       <c r="CO28" t="n">
         <v>76.02</v>
       </c>
       <c r="CP28" t="n">
-        <v>79.3</v>
+        <v>76.911</v>
       </c>
       <c r="CQ28" t="n">
-        <v>107.4</v>
+        <v>104.1645</v>
       </c>
       <c r="CR28" t="n">
         <v>106.25</v>
@@ -14163,13 +14163,13 @@
         <v>104.2</v>
       </c>
       <c r="CT28" t="n">
-        <v>109.45</v>
+        <v>106.1527</v>
       </c>
       <c r="CU28" t="n">
         <v>102.3</v>
       </c>
       <c r="CV28" t="n">
-        <v>85</v>
+        <v>82.4393</v>
       </c>
       <c r="CW28" t="n">
         <v>49.788</v>
@@ -14187,7 +14187,7 @@
         <v>108.05</v>
       </c>
       <c r="DB28" t="n">
-        <v>107.5</v>
+        <v>104.2615</v>
       </c>
       <c r="DC28" t="n">
         <v>103.4</v>
@@ -14214,7 +14214,7 @@
         <v>109</v>
       </c>
       <c r="DK28" t="n">
-        <v>113.5</v>
+        <v>110.0807</v>
       </c>
       <c r="DL28" t="n">
         <v>103.75</v>
@@ -14253,7 +14253,7 @@
         <v>104.5</v>
       </c>
       <c r="DX28" t="n">
-        <v>109</v>
+        <v>105.7163</v>
       </c>
       <c r="DY28" t="n">
         <v>109.1</v>
@@ -14301,7 +14301,7 @@
         <v>101.9</v>
       </c>
       <c r="EN28" t="n">
-        <v>114.05</v>
+        <v>110.6141</v>
       </c>
       <c r="EO28" t="n">
         <v>103.35</v>
@@ -14376,7 +14376,7 @@
         <v>103</v>
       </c>
       <c r="FW28" t="n">
-        <v>100.2</v>
+        <v>97.1814</v>
       </c>
       <c r="GE28" t="n">
         <v>108.95</v>
@@ -14632,10 +14632,10 @@
         <v>102</v>
       </c>
       <c r="CH29" t="n">
-        <v>47</v>
+        <v>45.6238</v>
       </c>
       <c r="CI29" t="n">
-        <v>63.35999999999999</v>
+        <v>61.5048</v>
       </c>
       <c r="CJ29" t="n">
         <v>108</v>
@@ -14650,10 +14650,10 @@
         <v>75.92</v>
       </c>
       <c r="CP29" t="n">
-        <v>79.90000000000001</v>
+        <v>77.5605</v>
       </c>
       <c r="CQ29" t="n">
-        <v>107.95</v>
+        <v>104.7892</v>
       </c>
       <c r="CR29" t="n">
         <v>106.65</v>
@@ -14668,7 +14668,7 @@
         <v>103</v>
       </c>
       <c r="CV29" t="n">
-        <v>85.05</v>
+        <v>82.55970000000001</v>
       </c>
       <c r="CW29" t="n">
         <v>49.7</v>
@@ -14722,7 +14722,7 @@
         <v>107.3</v>
       </c>
       <c r="DN29" t="n">
-        <v>107.45</v>
+        <v>104.3038</v>
       </c>
       <c r="DO29" t="n">
         <v>105.75</v>
@@ -14752,7 +14752,7 @@
         <v>105.3</v>
       </c>
       <c r="DX29" t="n">
-        <v>108.3</v>
+        <v>105.129</v>
       </c>
       <c r="DY29" t="n">
         <v>109</v>
@@ -14878,13 +14878,13 @@
         <v>102.5</v>
       </c>
       <c r="FW29" t="n">
-        <v>100.2</v>
+        <v>97.26609999999999</v>
       </c>
       <c r="FZ29" t="n">
-        <v>112.85</v>
+        <v>109.5457</v>
       </c>
       <c r="GE29" t="n">
-        <v>111.85</v>
+        <v>108.575</v>
       </c>
       <c r="GF29" t="n">
         <v>104.95</v>
@@ -15140,7 +15140,7 @@
         <v>45.2</v>
       </c>
       <c r="CI30" t="n">
-        <v>63.4</v>
+        <v>61.5229</v>
       </c>
       <c r="CM30" t="n">
         <v>103.65</v>
@@ -15152,10 +15152,10 @@
         <v>75.91</v>
       </c>
       <c r="CP30" t="n">
-        <v>80.2</v>
+        <v>77.82550000000001</v>
       </c>
       <c r="CQ30" t="n">
-        <v>108</v>
+        <v>104.8025</v>
       </c>
       <c r="CR30" t="n">
         <v>106.75</v>
@@ -15173,7 +15173,7 @@
         <v>80.2</v>
       </c>
       <c r="CW30" t="n">
-        <v>50.95</v>
+        <v>49.4415</v>
       </c>
       <c r="CX30" t="n">
         <v>108.3</v>
@@ -15185,7 +15185,7 @@
         <v>99.79000000000001</v>
       </c>
       <c r="DA30" t="n">
-        <v>112</v>
+        <v>108.6841</v>
       </c>
       <c r="DB30" t="n">
         <v>104.6</v>
@@ -15194,7 +15194,7 @@
         <v>103.25</v>
       </c>
       <c r="DD30" t="n">
-        <v>112.1</v>
+        <v>108.7811</v>
       </c>
       <c r="DE30" t="n">
         <v>104.7</v>
@@ -15215,7 +15215,7 @@
         <v>108.9</v>
       </c>
       <c r="DK30" t="n">
-        <v>113.35</v>
+        <v>109.9941</v>
       </c>
       <c r="DL30" t="n">
         <v>104.75</v>
@@ -15224,7 +15224,7 @@
         <v>107.35</v>
       </c>
       <c r="DN30" t="n">
-        <v>107.6</v>
+        <v>104.4143</v>
       </c>
       <c r="DO30" t="n">
         <v>105.9</v>
@@ -15254,7 +15254,7 @@
         <v>104.55</v>
       </c>
       <c r="DX30" t="n">
-        <v>108.1</v>
+        <v>104.8995</v>
       </c>
       <c r="DY30" t="n">
         <v>109.2</v>
@@ -15335,7 +15335,7 @@
         <v>102.3</v>
       </c>
       <c r="EY30" t="n">
-        <v>108.75</v>
+        <v>105.5303</v>
       </c>
       <c r="EZ30" t="n">
         <v>101.05</v>
@@ -15350,7 +15350,7 @@
         <v>109.2</v>
       </c>
       <c r="FD30" t="n">
-        <v>100</v>
+        <v>97.0393</v>
       </c>
       <c r="FE30" t="n">
         <v>103.7</v>
@@ -15386,13 +15386,13 @@
         <v>100.1</v>
       </c>
       <c r="FW30" t="n">
-        <v>100.6</v>
+        <v>97.6216</v>
       </c>
       <c r="FZ30" t="n">
         <v>108.75</v>
       </c>
       <c r="GE30" t="n">
-        <v>111.85</v>
+        <v>108.5385</v>
       </c>
       <c r="GF30" t="n">
         <v>105.05</v>
@@ -15642,16 +15642,16 @@
         <v>101.95</v>
       </c>
       <c r="CH31" t="n">
-        <v>47</v>
+        <v>45.664</v>
       </c>
       <c r="CI31" t="n">
         <v>64</v>
       </c>
       <c r="CJ31" t="n">
-        <v>111</v>
+        <v>107.8447</v>
       </c>
       <c r="CK31" t="n">
-        <v>103.75</v>
+        <v>100.8008</v>
       </c>
       <c r="CM31" t="n">
         <v>103.95</v>
@@ -15663,10 +15663,10 @@
         <v>76.5</v>
       </c>
       <c r="CP31" t="n">
-        <v>79.8</v>
+        <v>77.5316</v>
       </c>
       <c r="CQ31" t="n">
-        <v>108.05</v>
+        <v>104.9786</v>
       </c>
       <c r="CR31" t="n">
         <v>106.8</v>
@@ -15681,7 +15681,7 @@
         <v>102.5</v>
       </c>
       <c r="CV31" t="n">
-        <v>85.15000000000001</v>
+        <v>82.7296</v>
       </c>
       <c r="CW31" t="n">
         <v>49.906</v>
@@ -15696,7 +15696,7 @@
         <v>100.4</v>
       </c>
       <c r="DA31" t="n">
-        <v>111.05</v>
+        <v>107.8933</v>
       </c>
       <c r="DB31" t="n">
         <v>104.7</v>
@@ -15735,7 +15735,7 @@
         <v>107.2</v>
       </c>
       <c r="DN31" t="n">
-        <v>107.75</v>
+        <v>104.6871</v>
       </c>
       <c r="DO31" t="n">
         <v>105.6</v>
@@ -15765,7 +15765,7 @@
         <v>105.4</v>
       </c>
       <c r="DX31" t="n">
-        <v>108.6</v>
+        <v>105.513</v>
       </c>
       <c r="DY31" t="n">
         <v>109.85</v>
@@ -15894,13 +15894,13 @@
         <v>103</v>
       </c>
       <c r="FW31" t="n">
-        <v>100.45</v>
+        <v>97.5946</v>
       </c>
       <c r="FZ31" t="n">
         <v>108.85</v>
       </c>
       <c r="GE31" t="n">
-        <v>112.35</v>
+        <v>109.1564</v>
       </c>
       <c r="GF31" t="n">
         <v>104.9</v>
@@ -16105,7 +16105,7 @@
         <v>108.5</v>
       </c>
       <c r="BP32" t="n">
-        <v>106.6</v>
+        <v>103.6493</v>
       </c>
       <c r="BQ32" t="n">
         <v>148350</v>
@@ -16153,13 +16153,13 @@
         <v>101.9</v>
       </c>
       <c r="CH32" t="n">
-        <v>47</v>
+        <v>45.699</v>
       </c>
       <c r="CI32" t="n">
-        <v>63.71999999999999</v>
+        <v>61.9562</v>
       </c>
       <c r="CJ32" t="n">
-        <v>111</v>
+        <v>107.9275</v>
       </c>
       <c r="CM32" t="n">
         <v>103.95</v>
@@ -16171,10 +16171,10 @@
         <v>76.5</v>
       </c>
       <c r="CP32" t="n">
-        <v>81</v>
+        <v>78.75790000000001</v>
       </c>
       <c r="CQ32" t="n">
-        <v>108.65</v>
+        <v>105.6425</v>
       </c>
       <c r="CR32" t="n">
         <v>106.4</v>
@@ -16189,7 +16189,7 @@
         <v>104</v>
       </c>
       <c r="CV32" t="n">
-        <v>85.2</v>
+        <v>82.8416</v>
       </c>
       <c r="CW32" t="n">
         <v>50.17</v>
@@ -16204,13 +16204,13 @@
         <v>101.9</v>
       </c>
       <c r="DA32" t="n">
-        <v>111.2</v>
+        <v>108.1219</v>
       </c>
       <c r="DB32" t="n">
         <v>104.95</v>
       </c>
       <c r="DC32" t="n">
-        <v>106.4</v>
+        <v>103.4548</v>
       </c>
       <c r="DD32" t="n">
         <v>107.7</v>
@@ -16234,7 +16234,7 @@
         <v>109</v>
       </c>
       <c r="DK32" t="n">
-        <v>113</v>
+        <v>109.8721</v>
       </c>
       <c r="DL32" t="n">
         <v>104.8</v>
@@ -16243,7 +16243,7 @@
         <v>107.5</v>
       </c>
       <c r="DN32" t="n">
-        <v>107.3</v>
+        <v>104.3299</v>
       </c>
       <c r="DO32" t="n">
         <v>105.35</v>
@@ -16273,7 +16273,7 @@
         <v>105.35</v>
       </c>
       <c r="DX32" t="n">
-        <v>108.3</v>
+        <v>105.3022</v>
       </c>
       <c r="DY32" t="n">
         <v>108.5</v>
@@ -16655,7 +16655,7 @@
         <v>101.85</v>
       </c>
       <c r="CH33" t="n">
-        <v>47.45</v>
+        <v>46.0622</v>
       </c>
       <c r="CI33" t="n">
         <v>61.14999999999999</v>
@@ -16670,16 +16670,16 @@
         <v>104.05</v>
       </c>
       <c r="CN33" t="n">
-        <v>102.25</v>
+        <v>99.2594</v>
       </c>
       <c r="CO33" t="n">
         <v>75.95999999999999</v>
       </c>
       <c r="CP33" t="n">
-        <v>80</v>
+        <v>77.6602</v>
       </c>
       <c r="CQ33" t="n">
-        <v>109.1</v>
+        <v>105.9091</v>
       </c>
       <c r="CR33" t="n">
         <v>106.9</v>
@@ -16694,10 +16694,10 @@
         <v>103</v>
       </c>
       <c r="CV33" t="n">
-        <v>84.40000000000001</v>
+        <v>81.9315</v>
       </c>
       <c r="CW33" t="n">
-        <v>51.3</v>
+        <v>49.7996</v>
       </c>
       <c r="CX33" t="n">
         <v>106.9</v>
@@ -16709,10 +16709,10 @@
         <v>100.25</v>
       </c>
       <c r="DA33" t="n">
-        <v>111.3</v>
+        <v>108.0447</v>
       </c>
       <c r="DB33" t="n">
-        <v>107.8</v>
+        <v>104.6471</v>
       </c>
       <c r="DC33" t="n">
         <v>103.4</v>
@@ -16748,7 +16748,7 @@
         <v>107.65</v>
       </c>
       <c r="DN33" t="n">
-        <v>107.25</v>
+        <v>104.1132</v>
       </c>
       <c r="DO33" t="n">
         <v>105.5</v>
@@ -16778,7 +16778,7 @@
         <v>105</v>
       </c>
       <c r="DX33" t="n">
-        <v>107.55</v>
+        <v>104.4044</v>
       </c>
       <c r="DY33" t="n">
         <v>109.2</v>
@@ -16907,13 +16907,13 @@
         <v>103</v>
       </c>
       <c r="FW33" t="n">
-        <v>100.9</v>
+        <v>97.94889999999999</v>
       </c>
       <c r="FZ33" t="n">
         <v>109</v>
       </c>
       <c r="GE33" t="n">
-        <v>112.6</v>
+        <v>109.3067</v>
       </c>
       <c r="GF33" t="n">
         <v>105.05</v>
@@ -17115,10 +17115,10 @@
         <v>106.5</v>
       </c>
       <c r="BO34" t="n">
-        <v>112.35</v>
+        <v>109.5958</v>
       </c>
       <c r="BP34" t="n">
-        <v>106.6</v>
+        <v>103.9867</v>
       </c>
       <c r="BQ34" t="n">
         <v>147900</v>
@@ -17166,10 +17166,10 @@
         <v>102</v>
       </c>
       <c r="CI34" t="n">
-        <v>63.8</v>
+        <v>62.236</v>
       </c>
       <c r="CL34" t="n">
-        <v>107.5</v>
+        <v>104.8647</v>
       </c>
       <c r="CO34" t="n">
         <v>77.43000000000001</v>
@@ -17178,22 +17178,22 @@
         <v>80</v>
       </c>
       <c r="CQ34" t="n">
-        <v>108</v>
+        <v>105.3524</v>
       </c>
       <c r="CS34" t="n">
         <v>104.5</v>
       </c>
       <c r="CT34" t="n">
-        <v>109</v>
+        <v>106.3279</v>
       </c>
       <c r="CU34" t="n">
         <v>104.1</v>
       </c>
       <c r="CV34" t="n">
-        <v>84.90000000000001</v>
+        <v>82.81870000000001</v>
       </c>
       <c r="CW34" t="n">
-        <v>51.4</v>
+        <v>50.14</v>
       </c>
       <c r="CX34" t="n">
         <v>107.9</v>
@@ -17208,31 +17208,31 @@
         <v>103.5</v>
       </c>
       <c r="DD34" t="n">
-        <v>110.05</v>
+        <v>107.3522</v>
       </c>
       <c r="DE34" t="n">
-        <v>108</v>
+        <v>105.3524</v>
       </c>
       <c r="DF34" t="n">
-        <v>109.35</v>
+        <v>106.6693</v>
       </c>
       <c r="DG34" t="n">
         <v>99.95</v>
       </c>
       <c r="DI34" t="n">
-        <v>117</v>
+        <v>114.1318</v>
       </c>
       <c r="DJ34" t="n">
         <v>110.85</v>
       </c>
       <c r="DL34" t="n">
-        <v>108.15</v>
+        <v>105.4988</v>
       </c>
       <c r="DM34" t="n">
-        <v>110.5</v>
+        <v>107.7911</v>
       </c>
       <c r="DO34" t="n">
-        <v>109</v>
+        <v>106.3279</v>
       </c>
       <c r="DP34" t="n">
         <v>90.5</v>
@@ -17247,7 +17247,7 @@
         <v>110.2</v>
       </c>
       <c r="DT34" t="n">
-        <v>108.3</v>
+        <v>105.6451</v>
       </c>
       <c r="DU34" t="n">
         <v>105.7</v>
@@ -17268,7 +17268,7 @@
         <v>107.9</v>
       </c>
       <c r="EB34" t="n">
-        <v>109.85</v>
+        <v>107.1571</v>
       </c>
       <c r="EC34" t="n">
         <v>102.65</v>
@@ -17319,7 +17319,7 @@
         <v>103.2</v>
       </c>
       <c r="EY34" t="n">
-        <v>108.85</v>
+        <v>106.1816</v>
       </c>
       <c r="EZ34" t="n">
         <v>101.9</v>
@@ -17334,7 +17334,7 @@
         <v>107.7</v>
       </c>
       <c r="FD34" t="n">
-        <v>100.2</v>
+        <v>97.7436</v>
       </c>
       <c r="FH34" t="n">
         <v>105.7</v>
@@ -17358,7 +17358,7 @@
         <v>107</v>
       </c>
       <c r="GE34" t="n">
-        <v>113</v>
+        <v>110.2299</v>
       </c>
       <c r="GF34" t="n">
         <v>105.6</v>
@@ -17560,7 +17560,7 @@
         <v>108.7</v>
       </c>
       <c r="BP35" t="n">
-        <v>106.3</v>
+        <v>103.2103</v>
       </c>
       <c r="BQ35" t="n">
         <v>147500</v>
@@ -17608,13 +17608,13 @@
         <v>101.95</v>
       </c>
       <c r="CH35" t="n">
-        <v>47.15</v>
+        <v>45.7796</v>
       </c>
       <c r="CI35" t="n">
         <v>62.4</v>
       </c>
       <c r="CJ35" t="n">
-        <v>112</v>
+        <v>108.7446</v>
       </c>
       <c r="CK35" t="n">
         <v>102.2</v>
@@ -17623,7 +17623,7 @@
         <v>102.25</v>
       </c>
       <c r="CM35" t="n">
-        <v>107.65</v>
+        <v>104.5211</v>
       </c>
       <c r="CN35" t="n">
         <v>99.44</v>
@@ -17632,13 +17632,13 @@
         <v>76.7</v>
       </c>
       <c r="CP35" t="n">
-        <v>81.5</v>
+        <v>79.1311</v>
       </c>
       <c r="CQ35" t="n">
-        <v>108.1</v>
+        <v>104.958</v>
       </c>
       <c r="CR35" t="n">
-        <v>110.45</v>
+        <v>107.2397</v>
       </c>
       <c r="CS35" t="n">
         <v>103.5</v>
@@ -17650,10 +17650,10 @@
         <v>102.25</v>
       </c>
       <c r="CV35" t="n">
-        <v>84.81999999999999</v>
+        <v>82.3546</v>
       </c>
       <c r="CW35" t="n">
-        <v>51.2</v>
+        <v>49.7118</v>
       </c>
       <c r="CX35" t="n">
         <v>106.45</v>
@@ -17668,7 +17668,7 @@
         <v>107.7</v>
       </c>
       <c r="DB35" t="n">
-        <v>108.3</v>
+        <v>105.1522</v>
       </c>
       <c r="DC35" t="n">
         <v>103.3</v>
@@ -17686,7 +17686,7 @@
         <v>98.75</v>
       </c>
       <c r="DH35" t="n">
-        <v>108.7</v>
+        <v>105.5406</v>
       </c>
       <c r="DI35" t="n">
         <v>113.6</v>
@@ -17722,7 +17722,7 @@
         <v>108.8</v>
       </c>
       <c r="DT35" t="n">
-        <v>108.5</v>
+        <v>105.3464</v>
       </c>
       <c r="DU35" t="n">
         <v>106.15</v>
@@ -18119,7 +18119,7 @@
         <v>102</v>
       </c>
       <c r="CH36" t="n">
-        <v>47.09999999999999</v>
+        <v>45.6655</v>
       </c>
       <c r="CI36" t="n">
         <v>62.3</v>
@@ -18140,7 +18140,7 @@
         <v>76.69</v>
       </c>
       <c r="CP36" t="n">
-        <v>81.5</v>
+        <v>79.01779999999999</v>
       </c>
       <c r="CQ36" t="n">
         <v>104.85</v>
@@ -18158,13 +18158,13 @@
         <v>102.75</v>
       </c>
       <c r="CV36" t="n">
-        <v>84.45</v>
+        <v>81.878</v>
       </c>
       <c r="CW36" t="n">
         <v>50</v>
       </c>
       <c r="CX36" t="n">
-        <v>110</v>
+        <v>106.6499</v>
       </c>
       <c r="CY36" t="n">
         <v>105.95</v>
@@ -18179,10 +18179,10 @@
         <v>105.35</v>
       </c>
       <c r="DC36" t="n">
-        <v>106.45</v>
+        <v>103.208</v>
       </c>
       <c r="DD36" t="n">
-        <v>106.75</v>
+        <v>103.4988</v>
       </c>
       <c r="DE36" t="n">
         <v>105.3</v>
@@ -18212,7 +18212,7 @@
         <v>107.2</v>
       </c>
       <c r="DN36" t="n">
-        <v>108.25</v>
+        <v>104.9532</v>
       </c>
       <c r="DO36" t="n">
         <v>105</v>
@@ -18242,7 +18242,7 @@
         <v>105.4</v>
       </c>
       <c r="DX36" t="n">
-        <v>108.1</v>
+        <v>104.8077</v>
       </c>
       <c r="DY36" t="n">
         <v>110.25</v>
@@ -18371,10 +18371,10 @@
         <v>100.4</v>
       </c>
       <c r="FW36" t="n">
-        <v>100.5</v>
+        <v>97.4392</v>
       </c>
       <c r="FZ36" t="n">
-        <v>112.85</v>
+        <v>109.4131</v>
       </c>
       <c r="GE36" t="n">
         <v>108.35</v>
@@ -18630,16 +18630,16 @@
         <v>102.15</v>
       </c>
       <c r="CH37" t="n">
-        <v>47.6</v>
+        <v>46.1092</v>
       </c>
       <c r="CI37" t="n">
-        <v>64.06999999999999</v>
+        <v>62.0634</v>
       </c>
       <c r="CJ37" t="n">
-        <v>112</v>
+        <v>108.4923</v>
       </c>
       <c r="CK37" t="n">
-        <v>104.85</v>
+        <v>101.5662</v>
       </c>
       <c r="CL37" t="n">
         <v>102.5</v>
@@ -18648,7 +18648,7 @@
         <v>104.4</v>
       </c>
       <c r="CN37" t="n">
-        <v>104</v>
+        <v>100.7428</v>
       </c>
       <c r="CO37" t="n">
         <v>77.33</v>
@@ -18672,7 +18672,7 @@
         <v>102.3</v>
       </c>
       <c r="CV37" t="n">
-        <v>84.56</v>
+        <v>81.9117</v>
       </c>
       <c r="CW37" t="n">
         <v>50</v>
@@ -18687,10 +18687,10 @@
         <v>99.90000000000001</v>
       </c>
       <c r="DA37" t="n">
-        <v>111.25</v>
+        <v>107.7658</v>
       </c>
       <c r="DB37" t="n">
-        <v>108.3</v>
+        <v>104.9082</v>
       </c>
       <c r="DC37" t="n">
         <v>103.35</v>
@@ -18726,7 +18726,7 @@
         <v>107.25</v>
       </c>
       <c r="DN37" t="n">
-        <v>107.55</v>
+        <v>104.1816</v>
       </c>
       <c r="DO37" t="n">
         <v>105.1</v>
@@ -18744,7 +18744,7 @@
         <v>109.7</v>
       </c>
       <c r="DT37" t="n">
-        <v>109.15</v>
+        <v>105.7315</v>
       </c>
       <c r="DU37" t="n">
         <v>107</v>
@@ -18756,7 +18756,7 @@
         <v>105.9</v>
       </c>
       <c r="DX37" t="n">
-        <v>108.3</v>
+        <v>104.9082</v>
       </c>
       <c r="DY37" t="n">
         <v>109.45</v>
@@ -18768,7 +18768,7 @@
         <v>108.6</v>
       </c>
       <c r="EB37" t="n">
-        <v>110.15</v>
+        <v>106.7002</v>
       </c>
       <c r="EC37" t="n">
         <v>102.5</v>
@@ -18879,7 +18879,7 @@
         <v>103</v>
       </c>
       <c r="FW37" t="n">
-        <v>100.75</v>
+        <v>97.5946</v>
       </c>
       <c r="FZ37" t="n">
         <v>109.25</v>
@@ -19135,16 +19135,16 @@
         <v>63.7</v>
       </c>
       <c r="CJ38" t="n">
-        <v>111.95</v>
+        <v>108.1507</v>
       </c>
       <c r="CK38" t="n">
-        <v>105.15</v>
+        <v>101.5815</v>
       </c>
       <c r="CL38" t="n">
         <v>101.55</v>
       </c>
       <c r="CM38" t="n">
-        <v>107.95</v>
+        <v>104.2865</v>
       </c>
       <c r="CN38" t="n">
         <v>99.3</v>
@@ -19171,10 +19171,10 @@
         <v>102.35</v>
       </c>
       <c r="CV38" t="n">
-        <v>85</v>
+        <v>82.1153</v>
       </c>
       <c r="CW38" t="n">
-        <v>51.5</v>
+        <v>49.7522</v>
       </c>
       <c r="CX38" t="n">
         <v>106</v>
@@ -19225,7 +19225,7 @@
         <v>106.9</v>
       </c>
       <c r="DN38" t="n">
-        <v>108.55</v>
+        <v>104.8661</v>
       </c>
       <c r="DO38" t="n">
         <v>105.45</v>
@@ -19255,7 +19255,7 @@
         <v>105.5</v>
       </c>
       <c r="DX38" t="n">
-        <v>108.95</v>
+        <v>105.2525</v>
       </c>
       <c r="DY38" t="n">
         <v>110.05</v>
@@ -19387,10 +19387,10 @@
         <v>96.97</v>
       </c>
       <c r="FZ38" t="n">
-        <v>112.9</v>
+        <v>109.0685</v>
       </c>
       <c r="GE38" t="n">
-        <v>112.7</v>
+        <v>108.8753</v>
       </c>
       <c r="GF38" t="n">
         <v>106.5</v>
@@ -19646,13 +19646,13 @@
         <v>102.4</v>
       </c>
       <c r="CH39" t="n">
-        <v>47.3</v>
+        <v>45.6017</v>
       </c>
       <c r="CI39" t="n">
-        <v>65</v>
+        <v>62.6662</v>
       </c>
       <c r="CJ39" t="n">
-        <v>111.95</v>
+        <v>107.9305</v>
       </c>
       <c r="CK39" t="n">
         <v>101.85</v>
@@ -19670,10 +19670,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="CP39" t="n">
-        <v>81.67</v>
+        <v>78.7377</v>
       </c>
       <c r="CQ39" t="n">
-        <v>108.8</v>
+        <v>104.8936</v>
       </c>
       <c r="CR39" t="n">
         <v>107.55</v>
@@ -19688,10 +19688,10 @@
         <v>101.65</v>
       </c>
       <c r="CV39" t="n">
-        <v>85.45999999999999</v>
+        <v>82.3916</v>
       </c>
       <c r="CW39" t="n">
-        <v>51.20999999999999</v>
+        <v>49.3714</v>
       </c>
       <c r="CX39" t="n">
         <v>106.45</v>
@@ -19703,13 +19703,13 @@
         <v>99.91999999999999</v>
       </c>
       <c r="DA39" t="n">
-        <v>111.85</v>
+        <v>107.8341</v>
       </c>
       <c r="DB39" t="n">
-        <v>108.95</v>
+        <v>105.0383</v>
       </c>
       <c r="DC39" t="n">
-        <v>107.3</v>
+        <v>103.4475</v>
       </c>
       <c r="DD39" t="n">
         <v>102.9</v>
@@ -19733,7 +19733,7 @@
         <v>104.65</v>
       </c>
       <c r="DK39" t="n">
-        <v>114.3</v>
+        <v>110.1962</v>
       </c>
       <c r="DL39" t="n">
         <v>104.6</v>
@@ -19742,7 +19742,7 @@
         <v>107.55</v>
       </c>
       <c r="DN39" t="n">
-        <v>108.55</v>
+        <v>104.6526</v>
       </c>
       <c r="DO39" t="n">
         <v>105.05</v>
@@ -19772,7 +19772,7 @@
         <v>106.15</v>
       </c>
       <c r="DX39" t="n">
-        <v>109</v>
+        <v>105.0865</v>
       </c>
       <c r="DY39" t="n">
         <v>110.65</v>
@@ -19904,13 +19904,13 @@
         <v>100.4</v>
       </c>
       <c r="FW39" t="n">
-        <v>100.7</v>
+        <v>97.08450000000001</v>
       </c>
       <c r="FZ39" t="n">
         <v>109.5</v>
       </c>
       <c r="GE39" t="n">
-        <v>112.8</v>
+        <v>108.75</v>
       </c>
       <c r="GF39" t="n">
         <v>107</v>
@@ -20169,10 +20169,10 @@
         <v>46</v>
       </c>
       <c r="CI40" t="n">
-        <v>64.90000000000001</v>
+        <v>62.3822</v>
       </c>
       <c r="CJ40" t="n">
-        <v>112.8</v>
+        <v>108.4239</v>
       </c>
       <c r="CL40" t="n">
         <v>101.65</v>
@@ -20187,7 +20187,7 @@
         <v>80.88</v>
       </c>
       <c r="CQ40" t="n">
-        <v>109.65</v>
+        <v>105.3961</v>
       </c>
       <c r="CR40" t="n">
         <v>107.6</v>
@@ -20202,10 +20202,10 @@
         <v>101.8</v>
       </c>
       <c r="CV40" t="n">
-        <v>85.3</v>
+        <v>81.99079999999999</v>
       </c>
       <c r="CW40" t="n">
-        <v>51.39999999999999</v>
+        <v>49.4059</v>
       </c>
       <c r="CX40" t="n">
         <v>105.7</v>
@@ -20220,7 +20220,7 @@
         <v>107.9</v>
       </c>
       <c r="DB40" t="n">
-        <v>109.5</v>
+        <v>105.2519</v>
       </c>
       <c r="DC40" t="n">
         <v>103.45</v>
@@ -20274,7 +20274,7 @@
         <v>105.7</v>
       </c>
       <c r="DT40" t="n">
-        <v>110.5</v>
+        <v>106.2131</v>
       </c>
       <c r="DU40" t="n">
         <v>106</v>
@@ -20418,10 +20418,10 @@
         <v>100.35</v>
       </c>
       <c r="FW40" t="n">
-        <v>101.3</v>
+        <v>97.37009999999999</v>
       </c>
       <c r="FZ40" t="n">
-        <v>113.95</v>
+        <v>109.5293</v>
       </c>
       <c r="GE40" t="n">
         <v>109.35</v>
@@ -20683,7 +20683,7 @@
         <v>45.2</v>
       </c>
       <c r="CI41" t="n">
-        <v>64.58</v>
+        <v>62.098</v>
       </c>
       <c r="CJ41" t="n">
         <v>107.3</v>
@@ -20704,10 +20704,10 @@
         <v>77.05</v>
       </c>
       <c r="CP41" t="n">
-        <v>81.59999999999999</v>
+        <v>78.4639</v>
       </c>
       <c r="CQ41" t="n">
-        <v>109.5</v>
+        <v>105.2916</v>
       </c>
       <c r="CR41" t="n">
         <v>107.65</v>
@@ -20725,7 +20725,7 @@
         <v>81.98</v>
       </c>
       <c r="CW41" t="n">
-        <v>51.4</v>
+        <v>49.4246</v>
       </c>
       <c r="CX41" t="n">
         <v>108.85</v>
@@ -20737,7 +20737,7 @@
         <v>100</v>
       </c>
       <c r="DA41" t="n">
-        <v>112.3</v>
+        <v>107.984</v>
       </c>
       <c r="DB41" t="n">
         <v>105.5</v>
@@ -20767,7 +20767,7 @@
         <v>104.7</v>
       </c>
       <c r="DK41" t="n">
-        <v>114.8</v>
+        <v>110.3879</v>
       </c>
       <c r="DL41" t="n">
         <v>104.85</v>
@@ -20776,7 +20776,7 @@
         <v>107.05</v>
       </c>
       <c r="DN41" t="n">
-        <v>108.8</v>
+        <v>104.6185</v>
       </c>
       <c r="DO41" t="n">
         <v>105.05</v>
@@ -20941,7 +20941,7 @@
         <v>100.4</v>
       </c>
       <c r="FW41" t="n">
-        <v>101.3</v>
+        <v>97.4068</v>
       </c>
       <c r="GE41" t="n">
         <v>109.45</v>
@@ -21197,7 +21197,7 @@
         <v>45.2</v>
       </c>
       <c r="CI42" t="n">
-        <v>64.90000000000001</v>
+        <v>62.3961</v>
       </c>
       <c r="CJ42" t="n">
         <v>107.75</v>
@@ -21218,7 +21218,7 @@
         <v>77.23999999999999</v>
       </c>
       <c r="CP42" t="n">
-        <v>81.51000000000001</v>
+        <v>78.3653</v>
       </c>
       <c r="CQ42" t="n">
         <v>108.15</v>
@@ -21236,7 +21236,7 @@
         <v>102.25</v>
       </c>
       <c r="CV42" t="n">
-        <v>85.2</v>
+        <v>81.913</v>
       </c>
       <c r="CW42" t="n">
         <v>49.768</v>
@@ -21251,10 +21251,10 @@
         <v>100.5</v>
       </c>
       <c r="DA42" t="n">
-        <v>112</v>
+        <v>107.679</v>
       </c>
       <c r="DB42" t="n">
-        <v>109.8</v>
+        <v>105.5639</v>
       </c>
       <c r="DC42" t="n">
         <v>103.75</v>
@@ -21281,7 +21281,7 @@
         <v>107.5</v>
       </c>
       <c r="DK42" t="n">
-        <v>114.95</v>
+        <v>110.5152</v>
       </c>
       <c r="DL42" t="n">
         <v>104.8</v>
@@ -21290,7 +21290,7 @@
         <v>106.95</v>
       </c>
       <c r="DN42" t="n">
-        <v>109.7</v>
+        <v>105.4677</v>
       </c>
       <c r="DO42" t="n">
         <v>105.35</v>
@@ -21320,7 +21320,7 @@
         <v>106</v>
       </c>
       <c r="DX42" t="n">
-        <v>108.9</v>
+        <v>104.6986</v>
       </c>
       <c r="DY42" t="n">
         <v>109.9</v>
@@ -21660,7 +21660,7 @@
         <v>110.8</v>
       </c>
       <c r="BP43" t="n">
-        <v>107.9</v>
+        <v>103.4874</v>
       </c>
       <c r="BQ43" t="n">
         <v>147640</v>
@@ -21711,13 +21711,13 @@
         <v>103.25</v>
       </c>
       <c r="CH43" t="n">
-        <v>47.29999999999999</v>
+        <v>45.3657</v>
       </c>
       <c r="CI43" t="n">
         <v>61.99999999999999</v>
       </c>
       <c r="CJ43" t="n">
-        <v>111.9</v>
+        <v>107.3239</v>
       </c>
       <c r="CL43" t="n">
         <v>101.7</v>
@@ -21726,7 +21726,7 @@
         <v>104.35</v>
       </c>
       <c r="CN43" t="n">
-        <v>104</v>
+        <v>99.7469</v>
       </c>
       <c r="CO43" t="n">
         <v>76.39</v>
@@ -21735,7 +21735,7 @@
         <v>78.5</v>
       </c>
       <c r="CQ43" t="n">
-        <v>110</v>
+        <v>105.5016</v>
       </c>
       <c r="CR43" t="n">
         <v>107.9</v>
@@ -21768,7 +21768,7 @@
         <v>107.3</v>
       </c>
       <c r="DB43" t="n">
-        <v>109.8</v>
+        <v>105.3097</v>
       </c>
       <c r="DC43" t="n">
         <v>103.5</v>
@@ -21834,7 +21834,7 @@
         <v>106.5</v>
       </c>
       <c r="DX43" t="n">
-        <v>109.5</v>
+        <v>105.022</v>
       </c>
       <c r="DY43" t="n">
         <v>109.75</v>
@@ -21966,13 +21966,13 @@
         <v>103.9</v>
       </c>
       <c r="FW43" t="n">
-        <v>100.75</v>
+        <v>96.6298</v>
       </c>
       <c r="FZ43" t="n">
         <v>109.5</v>
       </c>
       <c r="GE43" t="n">
-        <v>113.7</v>
+        <v>109.0503</v>
       </c>
       <c r="GF43" t="n">
         <v>106.25</v>
@@ -22228,7 +22228,7 @@
         <v>45.20000000000001</v>
       </c>
       <c r="CI44" t="n">
-        <v>63.9</v>
+        <v>61.273</v>
       </c>
       <c r="CJ44" t="n">
         <v>107.3</v>
@@ -22243,7 +22243,7 @@
         <v>104.3</v>
       </c>
       <c r="CN44" t="n">
-        <v>104</v>
+        <v>99.7244</v>
       </c>
       <c r="CO44" t="n">
         <v>75.70999999999999</v>
@@ -22267,7 +22267,7 @@
         <v>102.5</v>
       </c>
       <c r="CV44" t="n">
-        <v>85.15000000000001</v>
+        <v>81.6493</v>
       </c>
       <c r="CW44" t="n">
         <v>49.60000000000001</v>
@@ -22282,7 +22282,7 @@
         <v>100.7</v>
       </c>
       <c r="DA44" t="n">
-        <v>112.8</v>
+        <v>108.1626</v>
       </c>
       <c r="DB44" t="n">
         <v>105.15</v>
@@ -22291,7 +22291,7 @@
         <v>103.55</v>
       </c>
       <c r="DD44" t="n">
-        <v>108.3</v>
+        <v>103.8476</v>
       </c>
       <c r="DE44" t="n">
         <v>105.05</v>
@@ -22321,7 +22321,7 @@
         <v>107.55</v>
       </c>
       <c r="DN44" t="n">
-        <v>109</v>
+        <v>104.5188</v>
       </c>
       <c r="DO44" t="n">
         <v>105.75</v>
@@ -22339,7 +22339,7 @@
         <v>106.05</v>
       </c>
       <c r="DT44" t="n">
-        <v>111</v>
+        <v>106.4366</v>
       </c>
       <c r="DU44" t="n">
         <v>106.5</v>
@@ -22432,7 +22432,7 @@
         <v>103</v>
       </c>
       <c r="EY44" t="n">
-        <v>110.5</v>
+        <v>105.9572</v>
       </c>
       <c r="EZ44" t="n">
         <v>102</v>
@@ -22486,7 +22486,7 @@
         <v>100.05</v>
       </c>
       <c r="FW44" t="n">
-        <v>101</v>
+        <v>96.8477</v>
       </c>
       <c r="FZ44" t="n">
         <v>109.55</v>
@@ -22697,7 +22697,7 @@
         <v>109.4</v>
       </c>
       <c r="BP45" t="n">
-        <v>107.7</v>
+        <v>103.2451</v>
       </c>
       <c r="BQ45" t="n">
         <v>148520</v>
@@ -22748,7 +22748,7 @@
         <v>103.15</v>
       </c>
       <c r="CH45" t="n">
-        <v>47.54</v>
+        <v>45.5736</v>
       </c>
       <c r="CI45" t="n">
         <v>60.9</v>
@@ -22772,13 +22772,13 @@
         <v>76.47</v>
       </c>
       <c r="CP45" t="n">
-        <v>81.78</v>
+        <v>78.3973</v>
       </c>
       <c r="CQ45" t="n">
         <v>105.05</v>
       </c>
       <c r="CR45" t="n">
-        <v>108.1</v>
+        <v>103.6286</v>
       </c>
       <c r="CS45" t="n">
         <v>104.35</v>
@@ -22793,7 +22793,7 @@
         <v>81.65000000000001</v>
       </c>
       <c r="CW45" t="n">
-        <v>51.35000000000001</v>
+        <v>49.226</v>
       </c>
       <c r="CX45" t="n">
         <v>106.35</v>
@@ -22805,7 +22805,7 @@
         <v>100.1</v>
       </c>
       <c r="DA45" t="n">
-        <v>112.1</v>
+        <v>107.4631</v>
       </c>
       <c r="DB45" t="n">
         <v>105.45</v>
@@ -22835,7 +22835,7 @@
         <v>105.65</v>
       </c>
       <c r="DK45" t="n">
-        <v>110.75</v>
+        <v>106.169</v>
       </c>
       <c r="DL45" t="n">
         <v>104.65</v>
@@ -22844,7 +22844,7 @@
         <v>107.5</v>
       </c>
       <c r="DN45" t="n">
-        <v>109.2</v>
+        <v>104.6831</v>
       </c>
       <c r="DO45" t="n">
         <v>105.85</v>
@@ -23012,10 +23012,10 @@
         <v>97</v>
       </c>
       <c r="FZ45" t="n">
-        <v>114.45</v>
+        <v>109.7159</v>
       </c>
       <c r="GE45" t="n">
-        <v>113.6</v>
+        <v>108.9011</v>
       </c>
       <c r="GF45" t="n">
         <v>107.7</v>
@@ -23274,13 +23274,13 @@
         <v>45.99999999999999</v>
       </c>
       <c r="CI46" t="n">
-        <v>63.75999999999999</v>
+        <v>61.2527</v>
       </c>
       <c r="CJ46" t="n">
         <v>107.5</v>
       </c>
       <c r="CK46" t="n">
-        <v>105.5</v>
+        <v>101.3513</v>
       </c>
       <c r="CL46" t="n">
         <v>101.65</v>
@@ -23295,13 +23295,13 @@
         <v>76.52</v>
       </c>
       <c r="CP46" t="n">
-        <v>81.25</v>
+        <v>78.0549</v>
       </c>
       <c r="CQ46" t="n">
-        <v>109</v>
+        <v>104.7136</v>
       </c>
       <c r="CR46" t="n">
-        <v>108.5</v>
+        <v>104.2333</v>
       </c>
       <c r="CS46" t="n">
         <v>104.4</v>
@@ -23313,7 +23313,7 @@
         <v>102</v>
       </c>
       <c r="CV46" t="n">
-        <v>85.25</v>
+        <v>81.8976</v>
       </c>
       <c r="CW46" t="n">
         <v>49.09800000000001</v>
@@ -23367,7 +23367,7 @@
         <v>107.1</v>
       </c>
       <c r="DN46" t="n">
-        <v>108.9</v>
+        <v>104.6176</v>
       </c>
       <c r="DO46" t="n">
         <v>105.5</v>
@@ -23385,7 +23385,7 @@
         <v>107.8</v>
       </c>
       <c r="DT46" t="n">
-        <v>111.95</v>
+        <v>107.5476</v>
       </c>
       <c r="DU46" t="n">
         <v>106.9</v>
@@ -23478,7 +23478,7 @@
         <v>103.2</v>
       </c>
       <c r="EY46" t="n">
-        <v>110.85</v>
+        <v>106.4909</v>
       </c>
       <c r="EZ46" t="n">
         <v>102</v>
@@ -23532,10 +23532,10 @@
         <v>100.75</v>
       </c>
       <c r="FW46" t="n">
-        <v>101.75</v>
+        <v>97.7487</v>
       </c>
       <c r="FZ46" t="n">
-        <v>111.45</v>
+        <v>107.0673</v>
       </c>
       <c r="GE46" t="n">
         <v>108.75</v>
@@ -23740,7 +23740,7 @@
         <v>109.3</v>
       </c>
       <c r="BP47" t="n">
-        <v>107.8</v>
+        <v>103.5857</v>
       </c>
       <c r="BQ47" t="n">
         <v>148400</v>
@@ -23791,16 +23791,16 @@
         <v>103.05</v>
       </c>
       <c r="CH47" t="n">
-        <v>47.17000000000001</v>
+        <v>45.326</v>
       </c>
       <c r="CI47" t="n">
-        <v>64.28</v>
+        <v>61.7671</v>
       </c>
       <c r="CJ47" t="n">
         <v>107.7</v>
       </c>
       <c r="CK47" t="n">
-        <v>106.1</v>
+        <v>101.9522</v>
       </c>
       <c r="CL47" t="n">
         <v>101</v>
@@ -23818,7 +23818,7 @@
         <v>79.51000000000001</v>
       </c>
       <c r="CQ47" t="n">
-        <v>109.1</v>
+        <v>104.8349</v>
       </c>
       <c r="CR47" t="n">
         <v>103.85</v>
@@ -23917,7 +23917,7 @@
         <v>106.8</v>
       </c>
       <c r="DX47" t="n">
-        <v>108.55</v>
+        <v>104.3064</v>
       </c>
       <c r="DY47" t="n">
         <v>109.55</v>
@@ -23998,7 +23998,7 @@
         <v>103</v>
       </c>
       <c r="EY47" t="n">
-        <v>110.95</v>
+        <v>106.6126</v>
       </c>
       <c r="EZ47" t="n">
         <v>101.9</v>
@@ -24052,7 +24052,7 @@
         <v>100.75</v>
       </c>
       <c r="FW47" t="n">
-        <v>102</v>
+        <v>98.0125</v>
       </c>
       <c r="FZ47" t="n">
         <v>107.05</v>
@@ -24300,10 +24300,10 @@
         <v>102.9</v>
       </c>
       <c r="CH48" t="n">
-        <v>47.99999999999999</v>
+        <v>46.2295</v>
       </c>
       <c r="CI48" t="n">
-        <v>64.3</v>
+        <v>61.9283</v>
       </c>
       <c r="CJ48" t="n">
         <v>107.65</v>
@@ -24318,13 +24318,13 @@
         <v>104.2</v>
       </c>
       <c r="CN48" t="n">
-        <v>104</v>
+        <v>100.164</v>
       </c>
       <c r="CO48" t="n">
         <v>76.40000000000001</v>
       </c>
       <c r="CP48" t="n">
-        <v>80.64</v>
+        <v>77.6656</v>
       </c>
       <c r="CQ48" t="n">
         <v>105.15</v>
@@ -24345,7 +24345,7 @@
         <v>81.17</v>
       </c>
       <c r="CW48" t="n">
-        <v>51.25999999999999</v>
+        <v>49.3693</v>
       </c>
       <c r="CX48" t="n">
         <v>106.4</v>
@@ -24387,7 +24387,7 @@
         <v>105.95</v>
       </c>
       <c r="DK48" t="n">
-        <v>110.4</v>
+        <v>106.3279</v>
       </c>
       <c r="DL48" t="n">
         <v>104.3</v>
@@ -24414,7 +24414,7 @@
         <v>107.5</v>
       </c>
       <c r="DT48" t="n">
-        <v>110.5</v>
+        <v>106.4242</v>
       </c>
       <c r="DU48" t="n">
         <v>106.8</v>
@@ -24426,7 +24426,7 @@
         <v>105.5</v>
       </c>
       <c r="DX48" t="n">
-        <v>109.65</v>
+        <v>105.6055</v>
       </c>
       <c r="DY48" t="n">
         <v>109.7</v>
@@ -24555,13 +24555,13 @@
         <v>103.75</v>
       </c>
       <c r="FW48" t="n">
-        <v>101.2</v>
+        <v>97.46720000000001</v>
       </c>
       <c r="FX48" t="n">
         <v>99.05</v>
       </c>
       <c r="FZ48" t="n">
-        <v>110.95</v>
+        <v>106.8576</v>
       </c>
       <c r="GE48" t="n">
         <v>108.75</v>
@@ -24809,13 +24809,13 @@
         <v>102.65</v>
       </c>
       <c r="CH49" t="n">
-        <v>49.00000000000001</v>
+        <v>47.1848</v>
       </c>
       <c r="CI49" t="n">
-        <v>64.45</v>
+        <v>62.0625</v>
       </c>
       <c r="CJ49" t="n">
-        <v>111.7</v>
+        <v>107.5621</v>
       </c>
       <c r="CK49" t="n">
         <v>101.7</v>
@@ -24833,7 +24833,7 @@
         <v>76.7</v>
       </c>
       <c r="CP49" t="n">
-        <v>80.40000000000001</v>
+        <v>77.4216</v>
       </c>
       <c r="CQ49" t="n">
         <v>105.2</v>
@@ -24851,10 +24851,10 @@
         <v>102.6</v>
       </c>
       <c r="CV49" t="n">
-        <v>84.02</v>
+        <v>80.9075</v>
       </c>
       <c r="CW49" t="n">
-        <v>51.46000000000001</v>
+        <v>49.5537</v>
       </c>
       <c r="CX49" t="n">
         <v>106.5</v>
@@ -24866,7 +24866,7 @@
         <v>99.84999999999999</v>
       </c>
       <c r="DA49" t="n">
-        <v>112</v>
+        <v>107.851</v>
       </c>
       <c r="DB49" t="n">
         <v>105.3</v>
@@ -24899,13 +24899,13 @@
         <v>106.45</v>
       </c>
       <c r="DL49" t="n">
-        <v>108.9</v>
+        <v>104.8658</v>
       </c>
       <c r="DM49" t="n">
         <v>107.5</v>
       </c>
       <c r="DN49" t="n">
-        <v>108.7</v>
+        <v>104.6732</v>
       </c>
       <c r="DO49" t="n">
         <v>105.9</v>
@@ -24935,7 +24935,7 @@
         <v>107.9</v>
       </c>
       <c r="DX49" t="n">
-        <v>109</v>
+        <v>104.9621</v>
       </c>
       <c r="DY49" t="n">
         <v>109.7</v>
@@ -25284,7 +25284,7 @@
         <v>109.65</v>
       </c>
       <c r="BP50" t="n">
-        <v>107.6</v>
+        <v>103.7166</v>
       </c>
       <c r="BQ50" t="n">
         <v>148500</v>
@@ -25335,16 +25335,16 @@
         <v>102.45</v>
       </c>
       <c r="CH50" t="n">
-        <v>47.61</v>
+        <v>45.8917</v>
       </c>
       <c r="CI50" t="n">
-        <v>64.34999999999999</v>
+        <v>62.0275</v>
       </c>
       <c r="CJ50" t="n">
         <v>107.5</v>
       </c>
       <c r="CK50" t="n">
-        <v>105.65</v>
+        <v>101.8369</v>
       </c>
       <c r="CL50" t="n">
         <v>101.7</v>
@@ -25359,10 +25359,10 @@
         <v>77.34999999999999</v>
       </c>
       <c r="CP50" t="n">
-        <v>81.5</v>
+        <v>78.5585</v>
       </c>
       <c r="CQ50" t="n">
-        <v>109.2</v>
+        <v>105.2588</v>
       </c>
       <c r="CR50" t="n">
         <v>103.75</v>
@@ -25377,7 +25377,7 @@
         <v>102.85</v>
       </c>
       <c r="CV50" t="n">
-        <v>84.34999999999999</v>
+        <v>81.3057</v>
       </c>
       <c r="CW50" t="n">
         <v>49.845</v>
@@ -25392,10 +25392,10 @@
         <v>100.5</v>
       </c>
       <c r="DA50" t="n">
-        <v>111.7</v>
+        <v>107.6686</v>
       </c>
       <c r="DB50" t="n">
-        <v>109.25</v>
+        <v>105.307</v>
       </c>
       <c r="DC50" t="n">
         <v>103.5</v>
@@ -25431,7 +25431,7 @@
         <v>107.8</v>
       </c>
       <c r="DN50" t="n">
-        <v>108.9</v>
+        <v>104.9696</v>
       </c>
       <c r="DO50" t="n">
         <v>105.7</v>
@@ -25449,7 +25449,7 @@
         <v>106.5</v>
       </c>
       <c r="DT50" t="n">
-        <v>110.3</v>
+        <v>106.3191</v>
       </c>
       <c r="DU50" t="n">
         <v>106</v>
@@ -25461,7 +25461,7 @@
         <v>106.5</v>
       </c>
       <c r="DX50" t="n">
-        <v>106.45</v>
+        <v>102.6081</v>
       </c>
       <c r="DY50" t="n">
         <v>110</v>
@@ -25605,7 +25605,7 @@
         <v>100</v>
       </c>
       <c r="FW50" t="n">
-        <v>101.8</v>
+        <v>98.1259</v>
       </c>
       <c r="FX50" t="n">
         <v>99.54000000000001</v>
@@ -25614,7 +25614,7 @@
         <v>25.499</v>
       </c>
       <c r="FZ50" t="n">
-        <v>110.9</v>
+        <v>106.8975</v>
       </c>
       <c r="GA50" t="n">
         <v>99.5</v>
@@ -25641,7 +25641,7 @@
         <v>101.95</v>
       </c>
       <c r="GL50" t="n">
-        <v>33</v>
+        <v>31.809</v>
       </c>
       <c r="GM50" t="n">
         <v>101</v>
@@ -25822,7 +25822,7 @@
         <v>110</v>
       </c>
       <c r="BP51" t="n">
-        <v>108.1</v>
+        <v>104.2147</v>
       </c>
       <c r="BQ51" t="n">
         <v>148450</v>
@@ -25873,13 +25873,13 @@
         <v>102.4</v>
       </c>
       <c r="CH51" t="n">
-        <v>47.8</v>
+        <v>46.082</v>
       </c>
       <c r="CI51" t="n">
         <v>64</v>
       </c>
       <c r="CJ51" t="n">
-        <v>112.1</v>
+        <v>108.071</v>
       </c>
       <c r="CK51" t="n">
         <v>101.75</v>
@@ -25891,7 +25891,7 @@
         <v>100.55</v>
       </c>
       <c r="CN51" t="n">
-        <v>104.9</v>
+        <v>101.1297</v>
       </c>
       <c r="CO51" t="n">
         <v>77.23999999999999</v>
@@ -25900,10 +25900,10 @@
         <v>79.54000000000001</v>
       </c>
       <c r="CQ51" t="n">
-        <v>109.1</v>
+        <v>105.1788</v>
       </c>
       <c r="CR51" t="n">
-        <v>107.6</v>
+        <v>103.7327</v>
       </c>
       <c r="CS51" t="n">
         <v>104.7</v>
@@ -25915,7 +25915,7 @@
         <v>102.9</v>
       </c>
       <c r="CV51" t="n">
-        <v>85.5</v>
+        <v>82.42700000000001</v>
       </c>
       <c r="CW51" t="n">
         <v>49.822</v>
@@ -25930,7 +25930,7 @@
         <v>99.5</v>
       </c>
       <c r="DA51" t="n">
-        <v>111.8</v>
+        <v>107.7818</v>
       </c>
       <c r="DB51" t="n">
         <v>105.75</v>
@@ -25942,7 +25942,7 @@
         <v>103.55</v>
       </c>
       <c r="DE51" t="n">
-        <v>109.55</v>
+        <v>105.6126</v>
       </c>
       <c r="DF51" t="n">
         <v>107.3</v>
@@ -25984,7 +25984,7 @@
         <v>106.5</v>
       </c>
       <c r="DT51" t="n">
-        <v>111.25</v>
+        <v>107.2515</v>
       </c>
       <c r="DU51" t="n">
         <v>106.25</v>
@@ -25996,7 +25996,7 @@
         <v>106.4</v>
       </c>
       <c r="DX51" t="n">
-        <v>108.45</v>
+        <v>104.5522</v>
       </c>
       <c r="DY51" t="n">
         <v>110.3</v>
@@ -26077,7 +26077,7 @@
         <v>103.4</v>
       </c>
       <c r="EY51" t="n">
-        <v>109.85</v>
+        <v>105.9018</v>
       </c>
       <c r="EZ51" t="n">
         <v>102.2</v>
@@ -26173,7 +26173,7 @@
         <v>102.7</v>
       </c>
       <c r="GL51" t="n">
-        <v>29.8</v>
+        <v>28.7289</v>
       </c>
     </row>
     <row r="52">
@@ -26402,13 +26402,13 @@
         <v>102.45</v>
       </c>
       <c r="CH52" t="n">
-        <v>47.799</v>
+        <v>46.1232</v>
       </c>
       <c r="CI52" t="n">
         <v>62</v>
       </c>
       <c r="CJ52" t="n">
-        <v>112.1</v>
+        <v>108.1699</v>
       </c>
       <c r="CL52" t="n">
         <v>101.75</v>
@@ -26423,10 +26423,10 @@
         <v>77.36</v>
       </c>
       <c r="CP52" t="n">
-        <v>81</v>
+        <v>78.1602</v>
       </c>
       <c r="CQ52" t="n">
-        <v>109</v>
+        <v>105.1786</v>
       </c>
       <c r="CR52" t="n">
         <v>105.15</v>
@@ -26444,7 +26444,7 @@
         <v>82.02</v>
       </c>
       <c r="CW52" t="n">
-        <v>51.45000000000001</v>
+        <v>49.6462</v>
       </c>
       <c r="CX52" t="n">
         <v>106.45</v>
@@ -26456,7 +26456,7 @@
         <v>99.8</v>
       </c>
       <c r="DA52" t="n">
-        <v>112.25</v>
+        <v>108.3146</v>
       </c>
       <c r="DB52" t="n">
         <v>105.7</v>
@@ -26465,10 +26465,10 @@
         <v>103.6</v>
       </c>
       <c r="DD52" t="n">
-        <v>107.4</v>
+        <v>103.6347</v>
       </c>
       <c r="DE52" t="n">
-        <v>109.6</v>
+        <v>105.7576</v>
       </c>
       <c r="DF52" t="n">
         <v>107.8</v>
@@ -26489,7 +26489,7 @@
         <v>107.05</v>
       </c>
       <c r="DL52" t="n">
-        <v>108.65</v>
+        <v>104.8409</v>
       </c>
       <c r="DM52" t="n">
         <v>108.05</v>
@@ -26510,7 +26510,7 @@
         <v>106.5</v>
       </c>
       <c r="DT52" t="n">
-        <v>111.2</v>
+        <v>107.3015</v>
       </c>
       <c r="DU52" t="n">
         <v>106.4</v>
@@ -26522,7 +26522,7 @@
         <v>106.1</v>
       </c>
       <c r="DX52" t="n">
-        <v>108.45</v>
+        <v>104.6479</v>
       </c>
       <c r="DY52" t="n">
         <v>110</v>
@@ -26699,7 +26699,7 @@
         <v>102.8</v>
       </c>
       <c r="GL52" t="n">
-        <v>29.006</v>
+        <v>27.9891</v>
       </c>
       <c r="GM52" t="n">
         <v>101.95</v>
@@ -26932,7 +26932,7 @@
         <v>46</v>
       </c>
       <c r="CI53" t="n">
-        <v>64.40000000000001</v>
+        <v>62.1585</v>
       </c>
       <c r="CJ53" t="n">
         <v>108.5</v>
@@ -26947,16 +26947,16 @@
         <v>100.5</v>
       </c>
       <c r="CN53" t="n">
-        <v>104</v>
+        <v>100.3801</v>
       </c>
       <c r="CO53" t="n">
         <v>77.13</v>
       </c>
       <c r="CP53" t="n">
-        <v>81.01000000000001</v>
+        <v>78.19029999999999</v>
       </c>
       <c r="CQ53" t="n">
-        <v>109.25</v>
+        <v>105.4474</v>
       </c>
       <c r="CR53" t="n">
         <v>103.55</v>
@@ -26974,7 +26974,7 @@
         <v>82.05</v>
       </c>
       <c r="CW53" t="n">
-        <v>51.65</v>
+        <v>49.8522</v>
       </c>
       <c r="CX53" t="n">
         <v>106.55</v>
@@ -26986,10 +26986,10 @@
         <v>99.84999999999998</v>
       </c>
       <c r="DA53" t="n">
-        <v>112</v>
+        <v>108.1017</v>
       </c>
       <c r="DB53" t="n">
-        <v>109.45</v>
+        <v>105.6404</v>
       </c>
       <c r="DC53" t="n">
         <v>103.6</v>
@@ -27016,7 +27016,7 @@
         <v>105.4</v>
       </c>
       <c r="DK53" t="n">
-        <v>110.65</v>
+        <v>106.7987</v>
       </c>
       <c r="DL53" t="n">
         <v>105</v>
@@ -27043,7 +27043,7 @@
         <v>106.35</v>
       </c>
       <c r="DT53" t="n">
-        <v>110.6</v>
+        <v>106.7504</v>
       </c>
       <c r="DU53" t="n">
         <v>106.2</v>
@@ -27214,7 +27214,7 @@
         <v>100.05</v>
       </c>
       <c r="GE53" t="n">
-        <v>113.75</v>
+        <v>109.7908</v>
       </c>
       <c r="GF53" t="n">
         <v>106.5</v>
@@ -27235,7 +27235,7 @@
         <v>103.25</v>
       </c>
       <c r="GL53" t="n">
-        <v>30.712</v>
+        <v>29.643</v>
       </c>
       <c r="GM53" t="n">
         <v>99.99999999999999</v>
@@ -27414,7 +27414,7 @@
         <v>109.6</v>
       </c>
       <c r="BP54" t="n">
-        <v>108.2</v>
+        <v>104.4034</v>
       </c>
       <c r="BQ54" t="n">
         <v>148800</v>
@@ -27471,7 +27471,7 @@
         <v>108</v>
       </c>
       <c r="CK54" t="n">
-        <v>106.5</v>
+        <v>102.763</v>
       </c>
       <c r="CL54" t="n">
         <v>101.5</v>
@@ -27480,13 +27480,13 @@
         <v>100.65</v>
       </c>
       <c r="CN54" t="n">
-        <v>103.5</v>
+        <v>99.8683</v>
       </c>
       <c r="CO54" t="n">
         <v>76.72</v>
       </c>
       <c r="CP54" t="n">
-        <v>80.8</v>
+        <v>77.9648</v>
       </c>
       <c r="CQ54" t="n">
         <v>107.95</v>
@@ -27522,7 +27522,7 @@
         <v>108.15</v>
       </c>
       <c r="DB54" t="n">
-        <v>109.7</v>
+        <v>105.8508</v>
       </c>
       <c r="DC54" t="n">
         <v>103.9</v>
@@ -27558,7 +27558,7 @@
         <v>108.35</v>
       </c>
       <c r="DN54" t="n">
-        <v>109</v>
+        <v>105.1753</v>
       </c>
       <c r="DO54" t="n">
         <v>106.15</v>
@@ -27588,7 +27588,7 @@
         <v>106.1</v>
       </c>
       <c r="DX54" t="n">
-        <v>108.2</v>
+        <v>104.4034</v>
       </c>
       <c r="DY54" t="n">
         <v>110.5</v>
@@ -27669,7 +27669,7 @@
         <v>105.95</v>
       </c>
       <c r="EY54" t="n">
-        <v>110.8</v>
+        <v>106.9122</v>
       </c>
       <c r="EZ54" t="n">
         <v>102</v>
@@ -27738,7 +27738,7 @@
         <v>25.511</v>
       </c>
       <c r="FZ54" t="n">
-        <v>111.05</v>
+        <v>107.1534</v>
       </c>
       <c r="GA54" t="n">
         <v>100.45</v>
@@ -27768,7 +27768,7 @@
         <v>102.7</v>
       </c>
       <c r="GL54" t="n">
-        <v>34</v>
+        <v>32.807</v>
       </c>
       <c r="GM54" t="n">
         <v>102</v>
@@ -28000,10 +28000,10 @@
         <v>102.6</v>
       </c>
       <c r="CH55" t="n">
-        <v>48</v>
+        <v>46.2603</v>
       </c>
       <c r="CI55" t="n">
-        <v>63.93</v>
+        <v>61.6129</v>
       </c>
       <c r="CJ55" t="n">
         <v>108.1</v>
@@ -28021,10 +28021,10 @@
         <v>76.43000000000001</v>
       </c>
       <c r="CP55" t="n">
-        <v>80.2</v>
+        <v>77.2932</v>
       </c>
       <c r="CQ55" t="n">
-        <v>109.95</v>
+        <v>105.9649</v>
       </c>
       <c r="CR55" t="n">
         <v>104.1</v>
@@ -28042,7 +28042,7 @@
         <v>81.87</v>
       </c>
       <c r="CW55" t="n">
-        <v>51.82</v>
+        <v>49.9418</v>
       </c>
       <c r="CX55" t="n">
         <v>106.5</v>
@@ -28057,13 +28057,13 @@
         <v>107.65</v>
       </c>
       <c r="DB55" t="n">
-        <v>110</v>
+        <v>106.0131</v>
       </c>
       <c r="DC55" t="n">
         <v>103.8</v>
       </c>
       <c r="DD55" t="n">
-        <v>107.95</v>
+        <v>104.0374</v>
       </c>
       <c r="DE55" t="n">
         <v>105.8</v>
@@ -28084,7 +28084,7 @@
         <v>106.75</v>
       </c>
       <c r="DK55" t="n">
-        <v>111.4</v>
+        <v>107.3624</v>
       </c>
       <c r="DL55" t="n">
         <v>104.6</v>
@@ -28093,7 +28093,7 @@
         <v>107.85</v>
       </c>
       <c r="DN55" t="n">
-        <v>108.95</v>
+        <v>105.0012</v>
       </c>
       <c r="DO55" t="n">
         <v>106.6</v>
@@ -28123,7 +28123,7 @@
         <v>106.1</v>
       </c>
       <c r="DX55" t="n">
-        <v>105</v>
+        <v>101.1943</v>
       </c>
       <c r="DY55" t="n">
         <v>110.5</v>
@@ -28201,7 +28201,7 @@
         <v>105.4</v>
       </c>
       <c r="EY55" t="n">
-        <v>110.9</v>
+        <v>106.8805</v>
       </c>
       <c r="EZ55" t="n">
         <v>102.15</v>
@@ -28279,7 +28279,7 @@
         <v>107.3</v>
       </c>
       <c r="GA55" t="n">
-        <v>105.5</v>
+        <v>101.6762</v>
       </c>
       <c r="GB55" t="n">
         <v>101</v>
@@ -28538,7 +28538,7 @@
         <v>46</v>
       </c>
       <c r="CI56" t="n">
-        <v>64.2</v>
+        <v>61.791</v>
       </c>
       <c r="CJ56" t="n">
         <v>108.4</v>
@@ -28559,7 +28559,7 @@
         <v>79.5</v>
       </c>
       <c r="CQ56" t="n">
-        <v>110.05</v>
+        <v>105.9205</v>
       </c>
       <c r="CR56" t="n">
         <v>104.4</v>
@@ -28577,7 +28577,7 @@
         <v>81.77</v>
       </c>
       <c r="CW56" t="n">
-        <v>51.99</v>
+        <v>50.0392</v>
       </c>
       <c r="CX56" t="n">
         <v>106.3</v>
@@ -28589,7 +28589,7 @@
         <v>99.75</v>
       </c>
       <c r="DA56" t="n">
-        <v>112.25</v>
+        <v>108.038</v>
       </c>
       <c r="DB56" t="n">
         <v>105.95</v>
@@ -28628,7 +28628,7 @@
         <v>108.15</v>
       </c>
       <c r="DN56" t="n">
-        <v>109.2</v>
+        <v>105.1024</v>
       </c>
       <c r="DO56" t="n">
         <v>106.2</v>
@@ -28706,7 +28706,7 @@
         <v>101.55</v>
       </c>
       <c r="EN56" t="n">
-        <v>111.8</v>
+        <v>107.6049</v>
       </c>
       <c r="EO56" t="n">
         <v>103.35</v>
@@ -28736,7 +28736,7 @@
         <v>105</v>
       </c>
       <c r="EY56" t="n">
-        <v>111.95</v>
+        <v>107.7492</v>
       </c>
       <c r="EZ56" t="n">
         <v>102</v>
@@ -28802,10 +28802,10 @@
         <v>99.89999999999999</v>
       </c>
       <c r="FW56" t="n">
-        <v>102.2</v>
+        <v>98.3651</v>
       </c>
       <c r="FX56" t="n">
-        <v>103.7</v>
+        <v>99.80880000000001</v>
       </c>
       <c r="FY56" t="n">
         <v>26</v>
@@ -28841,7 +28841,7 @@
         <v>103</v>
       </c>
       <c r="GL56" t="n">
-        <v>31.5</v>
+        <v>30.318</v>
       </c>
       <c r="GM56" t="n">
         <v>102.1</v>
@@ -29079,7 +29079,7 @@
         <v>63</v>
       </c>
       <c r="CJ57" t="n">
-        <v>112.4</v>
+        <v>108.2595</v>
       </c>
       <c r="CL57" t="n">
         <v>101.9</v>
@@ -29097,7 +29097,7 @@
         <v>78.19</v>
       </c>
       <c r="CQ57" t="n">
-        <v>109.75</v>
+        <v>105.7071</v>
       </c>
       <c r="CR57" t="n">
         <v>105</v>
@@ -29115,7 +29115,7 @@
         <v>81.79000000000001</v>
       </c>
       <c r="CW57" t="n">
-        <v>51.46999999999998</v>
+        <v>49.574</v>
       </c>
       <c r="CX57" t="n">
         <v>106.35</v>
@@ -29127,10 +29127,10 @@
         <v>99.79000000000001</v>
       </c>
       <c r="DA57" t="n">
-        <v>112.35</v>
+        <v>108.2113</v>
       </c>
       <c r="DB57" t="n">
-        <v>110.5</v>
+        <v>106.4295</v>
       </c>
       <c r="DC57" t="n">
         <v>103.5</v>
@@ -29166,7 +29166,7 @@
         <v>108.05</v>
       </c>
       <c r="DN57" t="n">
-        <v>109.2</v>
+        <v>105.1774</v>
       </c>
       <c r="DO57" t="n">
         <v>105.6</v>
@@ -29337,7 +29337,7 @@
         <v>100.3</v>
       </c>
       <c r="FW57" t="n">
-        <v>102.1</v>
+        <v>98.3389</v>
       </c>
       <c r="FX57" t="n">
         <v>99.45</v>
@@ -29346,7 +29346,7 @@
         <v>25.85</v>
       </c>
       <c r="FZ57" t="n">
-        <v>111.75</v>
+        <v>107.6334</v>
       </c>
       <c r="GA57" t="n">
         <v>100.5</v>
@@ -29602,13 +29602,13 @@
         <v>102.85</v>
       </c>
       <c r="CH58" t="n">
-        <v>48</v>
+        <v>46.1842</v>
       </c>
       <c r="CI58" t="n">
         <v>63</v>
       </c>
       <c r="CJ58" t="n">
-        <v>112.4</v>
+        <v>108.1481</v>
       </c>
       <c r="CL58" t="n">
         <v>102.15</v>
@@ -29626,10 +29626,10 @@
         <v>77.81999999999999</v>
       </c>
       <c r="CQ58" t="n">
-        <v>110.4</v>
+        <v>106.2238</v>
       </c>
       <c r="CR58" t="n">
-        <v>108.6</v>
+        <v>104.4919</v>
       </c>
       <c r="CS58" t="n">
         <v>105.75</v>
@@ -29644,7 +29644,7 @@
         <v>78.8</v>
       </c>
       <c r="CW58" t="n">
-        <v>51.46999999999999</v>
+        <v>49.523</v>
       </c>
       <c r="CX58" t="n">
         <v>106.6</v>
@@ -29659,7 +29659,7 @@
         <v>108.1</v>
       </c>
       <c r="DB58" t="n">
-        <v>110</v>
+        <v>105.8389</v>
       </c>
       <c r="DC58" t="n">
         <v>103.6</v>
@@ -29695,7 +29695,7 @@
         <v>108.1</v>
       </c>
       <c r="DN58" t="n">
-        <v>109.2</v>
+        <v>105.0692</v>
       </c>
       <c r="DO58" t="n">
         <v>105.8</v>
@@ -29803,7 +29803,7 @@
         <v>105.5</v>
       </c>
       <c r="EY58" t="n">
-        <v>111.85</v>
+        <v>107.6189</v>
       </c>
       <c r="EZ58" t="n">
         <v>102.2</v>
@@ -29872,7 +29872,7 @@
         <v>25.7</v>
       </c>
       <c r="FZ58" t="n">
-        <v>109</v>
+        <v>104.8767</v>
       </c>
       <c r="GA58" t="n">
         <v>100.8</v>
@@ -29902,7 +29902,7 @@
         <v>103.3</v>
       </c>
       <c r="GL58" t="n">
-        <v>32</v>
+        <v>30.7895</v>
       </c>
       <c r="GM58" t="n">
         <v>100</v>
@@ -30134,7 +30134,7 @@
         <v>46.5</v>
       </c>
       <c r="CI59" t="n">
-        <v>64.2</v>
+        <v>61.8647</v>
       </c>
       <c r="CJ59" t="n">
         <v>108.25</v>
@@ -30155,7 +30155,7 @@
         <v>77.95</v>
       </c>
       <c r="CQ59" t="n">
-        <v>110</v>
+        <v>105.9986</v>
       </c>
       <c r="CR59" t="n">
         <v>104.9</v>
@@ -30173,7 +30173,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="CW59" t="n">
-        <v>51.66</v>
+        <v>49.7808</v>
       </c>
       <c r="CX59" t="n">
         <v>108.95</v>
@@ -30185,13 +30185,13 @@
         <v>99.93000000000001</v>
       </c>
       <c r="DA59" t="n">
-        <v>112.5</v>
+        <v>108.4077</v>
       </c>
       <c r="DB59" t="n">
-        <v>109.85</v>
+        <v>105.8541</v>
       </c>
       <c r="DC59" t="n">
-        <v>107.8</v>
+        <v>103.8787</v>
       </c>
       <c r="DD59" t="n">
         <v>104.1</v>
@@ -30224,7 +30224,7 @@
         <v>108.5</v>
       </c>
       <c r="DN59" t="n">
-        <v>109</v>
+        <v>105.035</v>
       </c>
       <c r="DO59" t="n">
         <v>106.2</v>
@@ -30329,7 +30329,7 @@
         <v>107</v>
       </c>
       <c r="EY59" t="n">
-        <v>110.95</v>
+        <v>106.9141</v>
       </c>
       <c r="EZ59" t="n">
         <v>102.1</v>
@@ -30392,19 +30392,19 @@
         <v>99.95</v>
       </c>
       <c r="FW59" t="n">
-        <v>102.75</v>
+        <v>99.0124</v>
       </c>
       <c r="FX59" t="n">
-        <v>103.95</v>
+        <v>100.1687</v>
       </c>
       <c r="FY59" t="n">
         <v>25.80099999999999</v>
       </c>
       <c r="FZ59" t="n">
-        <v>112.5</v>
+        <v>108.4077</v>
       </c>
       <c r="GA59" t="n">
-        <v>105.5</v>
+        <v>101.6623</v>
       </c>
       <c r="GB59" t="n">
         <v>101</v>
@@ -30416,7 +30416,7 @@
         <v>147690</v>
       </c>
       <c r="GE59" t="n">
-        <v>114.25</v>
+        <v>110.0941</v>
       </c>
       <c r="GF59" t="n">
         <v>106.25</v>
@@ -30437,7 +30437,7 @@
         <v>103</v>
       </c>
       <c r="GL59" t="n">
-        <v>31</v>
+        <v>29.8723</v>
       </c>
       <c r="GM59" t="n">
         <v>100.15</v>
@@ -30666,13 +30666,13 @@
         <v>102.6</v>
       </c>
       <c r="CH60" t="n">
-        <v>48.699</v>
+        <v>46.9223</v>
       </c>
       <c r="CI60" t="n">
-        <v>64.5</v>
+        <v>62.1468</v>
       </c>
       <c r="CJ60" t="n">
-        <v>111.65</v>
+        <v>107.5766</v>
       </c>
       <c r="CL60" t="n">
         <v>102</v>
@@ -30687,7 +30687,7 @@
         <v>74</v>
       </c>
       <c r="CP60" t="n">
-        <v>78.8</v>
+        <v>75.9251</v>
       </c>
       <c r="CQ60" t="n">
         <v>106.2</v>
@@ -30708,7 +30708,7 @@
         <v>81.54000000000001</v>
       </c>
       <c r="CW60" t="n">
-        <v>51.63999999999999</v>
+        <v>49.756</v>
       </c>
       <c r="CX60" t="n">
         <v>106.5</v>
@@ -30720,7 +30720,7 @@
         <v>99.90000000000001</v>
       </c>
       <c r="DA60" t="n">
-        <v>112.1</v>
+        <v>108.0102</v>
       </c>
       <c r="DB60" t="n">
         <v>105.9</v>
@@ -30732,7 +30732,7 @@
         <v>103.75</v>
       </c>
       <c r="DE60" t="n">
-        <v>109.7</v>
+        <v>105.6978</v>
       </c>
       <c r="DF60" t="n">
         <v>107.35</v>
@@ -30750,7 +30750,7 @@
         <v>105.5</v>
       </c>
       <c r="DK60" t="n">
-        <v>111.4</v>
+        <v>107.3357</v>
       </c>
       <c r="DL60" t="n">
         <v>105.3</v>
@@ -30777,7 +30777,7 @@
         <v>106.45</v>
       </c>
       <c r="DT60" t="n">
-        <v>110</v>
+        <v>105.9868</v>
       </c>
       <c r="DU60" t="n">
         <v>106.5</v>
@@ -30933,7 +30933,7 @@
         <v>99.26000000000001</v>
       </c>
       <c r="FW60" t="n">
-        <v>102</v>
+        <v>98.2787</v>
       </c>
       <c r="FX60" t="n">
         <v>100</v>
@@ -30942,7 +30942,7 @@
         <v>26.3</v>
       </c>
       <c r="FZ60" t="n">
-        <v>112.3</v>
+        <v>108.2029</v>
       </c>
       <c r="GA60" t="n">
         <v>106</v>
@@ -30957,7 +30957,7 @@
         <v>147920</v>
       </c>
       <c r="GE60" t="n">
-        <v>113.9</v>
+        <v>109.7445</v>
       </c>
       <c r="GF60" t="n">
         <v>106</v>
@@ -30978,7 +30978,7 @@
         <v>102.9</v>
       </c>
       <c r="GL60" t="n">
-        <v>30.204</v>
+        <v>29.1021</v>
       </c>
       <c r="GM60" t="n">
         <v>100.15</v>
@@ -31156,7 +31156,7 @@
         <v>109.6</v>
       </c>
       <c r="BP61" t="n">
-        <v>108.1</v>
+        <v>104.1782</v>
       </c>
       <c r="BQ61" t="n">
         <v>149100</v>
@@ -31207,7 +31207,7 @@
         <v>102.5</v>
       </c>
       <c r="CH61" t="n">
-        <v>48.6</v>
+        <v>46.8368</v>
       </c>
       <c r="CI61" t="n">
         <v>63.3</v>
@@ -31219,7 +31219,7 @@
         <v>101.55</v>
       </c>
       <c r="CM61" t="n">
-        <v>103.5</v>
+        <v>99.74509999999999</v>
       </c>
       <c r="CN61" t="n">
         <v>100.4</v>
@@ -31228,10 +31228,10 @@
         <v>74.05</v>
       </c>
       <c r="CP61" t="n">
-        <v>77.59999999999999</v>
+        <v>74.7848</v>
       </c>
       <c r="CQ61" t="n">
-        <v>109.75</v>
+        <v>105.7684</v>
       </c>
       <c r="CR61" t="n">
         <v>104</v>
@@ -31249,7 +31249,7 @@
         <v>81.56</v>
       </c>
       <c r="CW61" t="n">
-        <v>51.32</v>
+        <v>49.4582</v>
       </c>
       <c r="CX61" t="n">
         <v>106.3</v>
@@ -31270,7 +31270,7 @@
         <v>103.45</v>
       </c>
       <c r="DD61" t="n">
-        <v>107.9</v>
+        <v>103.9855</v>
       </c>
       <c r="DE61" t="n">
         <v>105.85</v>
@@ -31318,7 +31318,7 @@
         <v>106.5</v>
       </c>
       <c r="DT61" t="n">
-        <v>110.45</v>
+        <v>106.443</v>
       </c>
       <c r="DU61" t="n">
         <v>106.4</v>
@@ -31360,7 +31360,7 @@
         <v>108.5</v>
       </c>
       <c r="EH61" t="n">
-        <v>110.4</v>
+        <v>106.3948</v>
       </c>
       <c r="EI61" t="n">
         <v>101.7</v>
@@ -31408,7 +31408,7 @@
         <v>104.65</v>
       </c>
       <c r="EY61" t="n">
-        <v>110.4</v>
+        <v>106.3948</v>
       </c>
       <c r="EZ61" t="n">
         <v>101.3</v>
@@ -31474,7 +31474,7 @@
         <v>99.3</v>
       </c>
       <c r="FW61" t="n">
-        <v>101.9</v>
+        <v>98.2032</v>
       </c>
       <c r="FX61" t="n">
         <v>100</v>
@@ -31483,10 +31483,10 @@
         <v>26</v>
       </c>
       <c r="FZ61" t="n">
-        <v>112.4</v>
+        <v>108.3222</v>
       </c>
       <c r="GA61" t="n">
-        <v>105.5</v>
+        <v>101.6726</v>
       </c>
       <c r="GB61" t="n">
         <v>100</v>
@@ -31519,7 +31519,7 @@
         <v>102.4</v>
       </c>
       <c r="GL61" t="n">
-        <v>31.2</v>
+        <v>30.0681</v>
       </c>
     </row>
     <row r="62">
@@ -31748,7 +31748,7 @@
         <v>46.5</v>
       </c>
       <c r="CI62" t="n">
-        <v>64.51000000000001</v>
+        <v>62.1558</v>
       </c>
       <c r="CJ62" t="n">
         <v>107.8</v>
@@ -31760,16 +31760,16 @@
         <v>100</v>
       </c>
       <c r="CN62" t="n">
-        <v>104.5</v>
+        <v>100.6864</v>
       </c>
       <c r="CO62" t="n">
         <v>73.7</v>
       </c>
       <c r="CP62" t="n">
-        <v>77.8</v>
+        <v>74.96080000000001</v>
       </c>
       <c r="CQ62" t="n">
-        <v>109.8</v>
+        <v>105.793</v>
       </c>
       <c r="CR62" t="n">
         <v>103.9</v>
@@ -31787,7 +31787,7 @@
         <v>81.33</v>
       </c>
       <c r="CW62" t="n">
-        <v>51.11000000000001</v>
+        <v>49.2448</v>
       </c>
       <c r="CX62" t="n">
         <v>106</v>
@@ -31829,7 +31829,7 @@
         <v>104.8</v>
       </c>
       <c r="DK62" t="n">
-        <v>111.2</v>
+        <v>107.1419</v>
       </c>
       <c r="DL62" t="n">
         <v>105.15</v>
@@ -31880,7 +31880,7 @@
         <v>108.45</v>
       </c>
       <c r="EB62" t="n">
-        <v>105.9</v>
+        <v>102.0353</v>
       </c>
       <c r="EC62" t="n">
         <v>102.3</v>
@@ -32030,7 +32030,7 @@
         <v>148000</v>
       </c>
       <c r="GE62" t="n">
-        <v>114.3</v>
+        <v>110.1288</v>
       </c>
       <c r="GF62" t="n">
         <v>105.95</v>
@@ -32051,7 +32051,7 @@
         <v>102.4</v>
       </c>
       <c r="GL62" t="n">
-        <v>31</v>
+        <v>29.8687</v>
       </c>
       <c r="GM62" t="n">
         <v>101</v>
@@ -32190,7 +32190,7 @@
         <v>71.42</v>
       </c>
       <c r="AZ63" t="n">
-        <v>67.5</v>
+        <v>65.07859999999999</v>
       </c>
       <c r="BA63" t="n">
         <v>102.75</v>
@@ -32229,7 +32229,7 @@
         <v>109.7</v>
       </c>
       <c r="BP63" t="n">
-        <v>108</v>
+        <v>104.1257</v>
       </c>
       <c r="BQ63" t="n">
         <v>149550</v>
@@ -32280,13 +32280,13 @@
         <v>102.8</v>
       </c>
       <c r="CH63" t="n">
-        <v>48.25</v>
+        <v>46.5191</v>
       </c>
       <c r="CI63" t="n">
-        <v>64.59999999999999</v>
+        <v>62.2826</v>
       </c>
       <c r="CJ63" t="n">
-        <v>110.5</v>
+        <v>106.536</v>
       </c>
       <c r="CL63" t="n">
         <v>101.4</v>
@@ -32301,13 +32301,13 @@
         <v>74.5</v>
       </c>
       <c r="CP63" t="n">
-        <v>77.22</v>
+        <v>74.4499</v>
       </c>
       <c r="CQ63" t="n">
-        <v>110</v>
+        <v>106.054</v>
       </c>
       <c r="CR63" t="n">
-        <v>108.55</v>
+        <v>104.656</v>
       </c>
       <c r="CS63" t="n">
         <v>105.85</v>
@@ -32322,7 +32322,7 @@
         <v>79.37</v>
       </c>
       <c r="CW63" t="n">
-        <v>51.3</v>
+        <v>49.4597</v>
       </c>
       <c r="CX63" t="n">
         <v>106.2</v>
@@ -32334,7 +32334,7 @@
         <v>99.5</v>
       </c>
       <c r="DA63" t="n">
-        <v>112.1</v>
+        <v>108.0787</v>
       </c>
       <c r="DB63" t="n">
         <v>105.2</v>
@@ -32373,7 +32373,7 @@
         <v>108.4</v>
       </c>
       <c r="DN63" t="n">
-        <v>108.6</v>
+        <v>104.7042</v>
       </c>
       <c r="DO63" t="n">
         <v>107</v>
@@ -32481,7 +32481,7 @@
         <v>104.75</v>
       </c>
       <c r="EY63" t="n">
-        <v>110.15</v>
+        <v>106.1986</v>
       </c>
       <c r="EZ63" t="n">
         <v>101.6</v>
@@ -32544,16 +32544,16 @@
         <v>99.09999999999999</v>
       </c>
       <c r="FW63" t="n">
-        <v>102.5</v>
+        <v>98.82299999999999</v>
       </c>
       <c r="FX63" t="n">
-        <v>103.85</v>
+        <v>100.1246</v>
       </c>
       <c r="FY63" t="n">
         <v>25.521</v>
       </c>
       <c r="FZ63" t="n">
-        <v>112.4</v>
+        <v>108.3679</v>
       </c>
       <c r="GA63" t="n">
         <v>100.75</v>
@@ -32589,7 +32589,7 @@
         <v>102.7</v>
       </c>
       <c r="GL63" t="n">
-        <v>31</v>
+        <v>29.8879</v>
       </c>
       <c r="GM63" t="n">
         <v>100.1</v>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GM64"/>
+  <dimension ref="A1:GM65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -33091,6 +33091,496 @@
         <v>101.1</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>126.677</v>
+      </c>
+      <c r="I65" t="n">
+        <v>114.82</v>
+      </c>
+      <c r="J65" t="n">
+        <v>129.31</v>
+      </c>
+      <c r="K65" t="n">
+        <v>121.44</v>
+      </c>
+      <c r="L65" t="n">
+        <v>145.652</v>
+      </c>
+      <c r="M65" t="n">
+        <v>132.19</v>
+      </c>
+      <c r="N65" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="O65" t="n">
+        <v>125.34</v>
+      </c>
+      <c r="P65" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="S65" t="n">
+        <v>170.05</v>
+      </c>
+      <c r="T65" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="U65" t="n">
+        <v>219.4</v>
+      </c>
+      <c r="V65" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="W65" t="n">
+        <v>388.15</v>
+      </c>
+      <c r="X65" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>272.5</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>345.4</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>93.94</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>89.13</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>129.495</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>120.15</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>115.15</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>104</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>149900</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>147800</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>125640</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>94.42</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>53.67999999999999</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>92.99000000000001</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>55.11000000000001</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>53.53999999999999</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>55.27999999999999</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>80.43000000000001</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>91.88999999999999</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>105.805</v>
+      </c>
+      <c r="BK65" t="n">
+        <v>147000</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>150650</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>119100</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="BT65" t="n">
+        <v>83.94</v>
+      </c>
+      <c r="BU65" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="BV65" t="n">
+        <v>103.72</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="CB65" t="n">
+        <v>119.65</v>
+      </c>
+      <c r="CC65" t="n">
+        <v>122.8</v>
+      </c>
+      <c r="CE65" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="CF65" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="CG65" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="CL65" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="CN65" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="CO65" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="CQ65" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="CR65" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="CS65" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="CT65" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="CU65" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="CV65" t="n">
+        <v>80.69</v>
+      </c>
+      <c r="CX65" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="CY65" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="CZ65" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="DC65" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="DD65" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="DE65" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="DF65" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="DG65" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="DH65" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DI65" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DJ65" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="DM65" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DO65" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="DP65" t="n">
+        <v>90.19999999999999</v>
+      </c>
+      <c r="DQ65" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="DR65" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="DS65" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="DT65" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DU65" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="DV65" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="DW65" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="DX65" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="DY65" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DZ65" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="EA65" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="EB65" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="EC65" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="ED65" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="EE65" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EF65" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="EG65" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="EH65" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="EI65" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="EJ65" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EK65" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="EL65" t="n">
+        <v>105</v>
+      </c>
+      <c r="EM65" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="EN65" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="EO65" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EQ65" t="n">
+        <v>104</v>
+      </c>
+      <c r="ER65" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="ES65" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="ET65" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EU65" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EV65" t="n">
+        <v>102</v>
+      </c>
+      <c r="EW65" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EX65" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EY65" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EZ65" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FA65" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="FB65" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="FC65" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FD65" t="n">
+        <v>95.99000000000001</v>
+      </c>
+      <c r="FE65" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="FF65" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="FG65" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="FH65" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="FI65" t="n">
+        <v>104</v>
+      </c>
+      <c r="FJ65" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="FK65" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="FL65" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="FM65" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="FN65" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FP65" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="FQ65" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="FR65" t="n">
+        <v>149000</v>
+      </c>
+      <c r="FS65" t="n">
+        <v>137190</v>
+      </c>
+      <c r="FU65" t="n">
+        <v>99.58</v>
+      </c>
+      <c r="FV65" t="n">
+        <v>99.30000000000001</v>
+      </c>
+      <c r="FY65" t="n">
+        <v>25.571</v>
+      </c>
+      <c r="FZ65" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="GB65" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="GC65" t="n">
+        <v>98.38</v>
+      </c>
+      <c r="GD65" t="n">
+        <v>149450</v>
+      </c>
+      <c r="GF65" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="GG65" t="n">
+        <v>104</v>
+      </c>
+      <c r="GH65" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="GI65" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="GJ65" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="GK65" t="n">
+        <v>103</v>
+      </c>
+      <c r="GM65" t="n">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -33262,6 +33262,9 @@
       <c r="BO65" t="n">
         <v>109.5</v>
       </c>
+      <c r="BP65" t="n">
+        <v>104.0928</v>
+      </c>
       <c r="BQ65" t="n">
         <v>150650</v>
       </c>
@@ -33310,15 +33313,30 @@
       <c r="CG65" t="n">
         <v>103.35</v>
       </c>
+      <c r="CH65" t="n">
+        <v>46.2742</v>
+      </c>
+      <c r="CI65" t="n">
+        <v>61.7823</v>
+      </c>
+      <c r="CJ65" t="n">
+        <v>106.3055</v>
+      </c>
       <c r="CL65" t="n">
         <v>101.45</v>
       </c>
+      <c r="CM65" t="n">
+        <v>98.994</v>
+      </c>
       <c r="CN65" t="n">
         <v>100.9</v>
       </c>
       <c r="CO65" t="n">
         <v>74.3</v>
       </c>
+      <c r="CP65" t="n">
+        <v>75.0873</v>
+      </c>
       <c r="CQ65" t="n">
         <v>105.95</v>
       </c>
@@ -33337,6 +33355,9 @@
       <c r="CV65" t="n">
         <v>80.69</v>
       </c>
+      <c r="CW65" t="n">
+        <v>49.3142</v>
+      </c>
       <c r="CX65" t="n">
         <v>108.9</v>
       </c>
@@ -33346,6 +33367,12 @@
       <c r="CZ65" t="n">
         <v>99.90000000000001</v>
       </c>
+      <c r="DA65" t="n">
+        <v>108.1334</v>
+      </c>
+      <c r="DB65" t="n">
+        <v>105.0548</v>
+      </c>
       <c r="DC65" t="n">
         <v>103.2</v>
       </c>
@@ -33370,9 +33397,18 @@
       <c r="DJ65" t="n">
         <v>104.75</v>
       </c>
+      <c r="DK65" t="n">
+        <v>107.027</v>
+      </c>
+      <c r="DL65" t="n">
+        <v>105.0548</v>
+      </c>
       <c r="DM65" t="n">
         <v>107.85</v>
       </c>
+      <c r="DN65" t="n">
+        <v>104.5738</v>
+      </c>
       <c r="DO65" t="n">
         <v>105.9</v>
       </c>
@@ -33544,12 +33580,21 @@
       <c r="FV65" t="n">
         <v>99.30000000000001</v>
       </c>
+      <c r="FW65" t="n">
+        <v>98.5611</v>
+      </c>
+      <c r="FX65" t="n">
+        <v>99.5712</v>
+      </c>
       <c r="FY65" t="n">
         <v>25.571</v>
       </c>
       <c r="FZ65" t="n">
         <v>107.9</v>
       </c>
+      <c r="GA65" t="n">
+        <v>99.956</v>
+      </c>
       <c r="GB65" t="n">
         <v>100.2</v>
       </c>
@@ -33559,6 +33604,9 @@
       <c r="GD65" t="n">
         <v>149450</v>
       </c>
+      <c r="GE65" t="n">
+        <v>109.1916</v>
+      </c>
       <c r="GF65" t="n">
         <v>106.05</v>
       </c>
@@ -33576,6 +33624,9 @@
       </c>
       <c r="GK65" t="n">
         <v>103</v>
+      </c>
+      <c r="GL65" t="n">
+        <v>28.8131</v>
       </c>
       <c r="GM65" t="n">
         <v>101</v>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GM65"/>
+  <dimension ref="A1:GN65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1402,6 +1402,11 @@
           <t>VSCYD</t>
         </is>
       </c>
+      <c r="GN1" t="inlineStr">
+        <is>
+          <t>VSCPD</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -1814,6 +1819,9 @@
       </c>
       <c r="GK2" t="n">
         <v>106.5</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>103.2918</v>
       </c>
     </row>
     <row r="3">
@@ -2269,6 +2277,9 @@
       <c r="GK3" t="n">
         <v>105.8</v>
       </c>
+      <c r="GN3" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2726,6 +2737,9 @@
       <c r="GK4" t="n">
         <v>105.4</v>
       </c>
+      <c r="GN4" t="n">
+        <v>102.4735</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3186,6 +3200,9 @@
       <c r="GK5" t="n">
         <v>105</v>
       </c>
+      <c r="GN5" t="n">
+        <v>102.8845</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3655,6 +3672,9 @@
       <c r="GK6" t="n">
         <v>105.75</v>
       </c>
+      <c r="GN6" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4136,6 +4156,9 @@
       <c r="GK7" t="n">
         <v>105.15</v>
       </c>
+      <c r="GN7" t="n">
+        <v>103.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4611,6 +4634,9 @@
       <c r="GK8" t="n">
         <v>107</v>
       </c>
+      <c r="GN8" t="n">
+        <v>103.65</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5092,6 +5118,9 @@
       <c r="GK9" t="n">
         <v>105.55</v>
       </c>
+      <c r="GN9" t="n">
+        <v>102.9024</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5576,6 +5605,9 @@
       <c r="GK10" t="n">
         <v>105.5</v>
       </c>
+      <c r="GN10" t="n">
+        <v>102.9549</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6048,6 +6080,9 @@
       <c r="GK11" t="n">
         <v>104.65</v>
       </c>
+      <c r="GN11" t="n">
+        <v>102.9066</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6517,6 +6552,9 @@
       <c r="GK12" t="n">
         <v>105.25</v>
       </c>
+      <c r="GN12" t="n">
+        <v>102.8492</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7001,6 +7039,9 @@
       <c r="GK13" t="n">
         <v>105.25</v>
       </c>
+      <c r="GN13" t="n">
+        <v>102.65</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7485,6 +7526,9 @@
       <c r="GK14" t="n">
         <v>105.8</v>
       </c>
+      <c r="GN14" t="n">
+        <v>103.3492</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7963,6 +8007,9 @@
       <c r="GK15" t="n">
         <v>105.85</v>
       </c>
+      <c r="GN15" t="n">
+        <v>103.542</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8459,6 +8506,9 @@
       <c r="GK16" t="n">
         <v>105.9</v>
       </c>
+      <c r="GN16" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8952,6 +9002,9 @@
       <c r="GK17" t="n">
         <v>105.85</v>
       </c>
+      <c r="GN17" t="n">
+        <v>103.4884</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9442,6 +9495,9 @@
       <c r="GK18" t="n">
         <v>106</v>
       </c>
+      <c r="GN18" t="n">
+        <v>104.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9938,6 +9994,9 @@
       <c r="GK19" t="n">
         <v>105.9</v>
       </c>
+      <c r="GN19" t="n">
+        <v>103.8806</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10431,6 +10490,9 @@
       <c r="GK20" t="n">
         <v>105.95</v>
       </c>
+      <c r="GN20" t="n">
+        <v>103.3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10924,6 +10986,9 @@
       <c r="GK21" t="n">
         <v>105.95</v>
       </c>
+      <c r="GN21" t="n">
+        <v>103.1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11426,6 +11491,9 @@
       <c r="GK22" t="n">
         <v>106.3</v>
       </c>
+      <c r="GN22" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11925,6 +11993,9 @@
       <c r="GK23" t="n">
         <v>106</v>
       </c>
+      <c r="GN23" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12424,6 +12495,9 @@
       <c r="GK24" t="n">
         <v>106</v>
       </c>
+      <c r="GN24" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12920,6 +12994,9 @@
       <c r="GK25" t="n">
         <v>104.05</v>
       </c>
+      <c r="GN25" t="n">
+        <v>103.7279</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13410,6 +13487,9 @@
       <c r="GK26" t="n">
         <v>106.7</v>
       </c>
+      <c r="GN26" t="n">
+        <v>103.1765</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13903,6 +13983,9 @@
       <c r="GK27" t="n">
         <v>106.7</v>
       </c>
+      <c r="GN27" t="n">
+        <v>104.398</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14399,6 +14482,9 @@
       <c r="GK28" t="n">
         <v>106.1</v>
       </c>
+      <c r="GN28" t="n">
+        <v>105.1034</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14904,6 +14990,9 @@
       <c r="GK29" t="n">
         <v>106.7</v>
       </c>
+      <c r="GN29" t="n">
+        <v>102.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15409,6 +15498,9 @@
       <c r="GJ30" t="n">
         <v>102.65</v>
       </c>
+      <c r="GN30" t="n">
+        <v>105.8278</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15920,6 +16012,9 @@
       <c r="GK31" t="n">
         <v>102.45</v>
       </c>
+      <c r="GN31" t="n">
+        <v>106.7182</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -16422,6 +16517,9 @@
       <c r="GK32" t="n">
         <v>103</v>
       </c>
+      <c r="GN32" t="n">
+        <v>105.8376</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16933,6 +17031,9 @@
       <c r="GK33" t="n">
         <v>102.5</v>
       </c>
+      <c r="GN33" t="n">
+        <v>105.2667</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -17375,6 +17476,9 @@
       <c r="GK34" t="n">
         <v>103</v>
       </c>
+      <c r="GN34" t="n">
+        <v>106.842</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -17886,6 +17990,9 @@
       <c r="GK35" t="n">
         <v>102.8</v>
       </c>
+      <c r="GN35" t="n">
+        <v>105.9036</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -18397,6 +18504,9 @@
       <c r="GK36" t="n">
         <v>102.7</v>
       </c>
+      <c r="GN36" t="n">
+        <v>105.5374</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -18902,6 +19012,9 @@
       <c r="GK37" t="n">
         <v>103.3</v>
       </c>
+      <c r="GN37" t="n">
+        <v>104.8072</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -19410,6 +19523,9 @@
       <c r="GK38" t="n">
         <v>102.55</v>
       </c>
+      <c r="GN38" t="n">
+        <v>105.4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -19933,6 +20049,9 @@
       <c r="GM39" t="n">
         <v>104.05</v>
       </c>
+      <c r="GN39" t="n">
+        <v>105.25</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -20447,6 +20566,9 @@
       <c r="GM40" t="n">
         <v>103.7</v>
       </c>
+      <c r="GN40" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -20961,6 +21083,9 @@
       <c r="GK41" t="n">
         <v>103</v>
       </c>
+      <c r="GN41" t="n">
+        <v>104.25</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -21478,6 +21603,9 @@
       <c r="GM42" t="n">
         <v>102.05</v>
       </c>
+      <c r="GN42" t="n">
+        <v>104.9474</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -21992,6 +22120,9 @@
       <c r="GK43" t="n">
         <v>103</v>
       </c>
+      <c r="GN43" t="n">
+        <v>104.3575</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -22515,6 +22646,9 @@
       <c r="GM44" t="n">
         <v>101</v>
       </c>
+      <c r="GN44" t="n">
+        <v>105.0016</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -23038,6 +23172,9 @@
       <c r="GM45" t="n">
         <v>102.05</v>
       </c>
+      <c r="GN45" t="n">
+        <v>104.8694</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -23558,6 +23695,9 @@
       <c r="GK46" t="n">
         <v>103.3</v>
       </c>
+      <c r="GN46" t="n">
+        <v>105.2472</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -24078,6 +24218,9 @@
       <c r="GK47" t="n">
         <v>102.15</v>
       </c>
+      <c r="GN47" t="n">
+        <v>104.25</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -24587,6 +24730,9 @@
       <c r="GM48" t="n">
         <v>102</v>
       </c>
+      <c r="GN48" t="n">
+        <v>109.5</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -25107,6 +25253,9 @@
       </c>
       <c r="GM49" t="n">
         <v>101.5</v>
+      </c>
+      <c r="GN49" t="n">
+        <v>105.2</v>
       </c>
     </row>
     <row r="50">
@@ -25646,6 +25795,9 @@
       <c r="GM50" t="n">
         <v>101</v>
       </c>
+      <c r="GN50" t="n">
+        <v>104.543</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -26175,6 +26327,9 @@
       <c r="GL51" t="n">
         <v>28.7289</v>
       </c>
+      <c r="GN51" t="n">
+        <v>105.0811</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -26704,6 +26859,9 @@
       <c r="GM52" t="n">
         <v>101.95</v>
       </c>
+      <c r="GN52" t="n">
+        <v>104.95</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -27240,6 +27398,9 @@
       <c r="GM53" t="n">
         <v>99.99999999999999</v>
       </c>
+      <c r="GN53" t="n">
+        <v>104.9808</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -27772,6 +27933,9 @@
       </c>
       <c r="GM54" t="n">
         <v>102</v>
+      </c>
+      <c r="GN54" t="n">
+        <v>105.2294</v>
       </c>
     </row>
     <row r="55">
@@ -28308,6 +28472,9 @@
       <c r="GM55" t="n">
         <v>100.55</v>
       </c>
+      <c r="GN55" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -28846,6 +29013,9 @@
       <c r="GM56" t="n">
         <v>102.1</v>
       </c>
+      <c r="GN56" t="n">
+        <v>104.9704</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -29378,6 +29548,9 @@
       <c r="GM57" t="n">
         <v>102</v>
       </c>
+      <c r="GN57" t="n">
+        <v>104.8277</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -29907,6 +30080,9 @@
       <c r="GM58" t="n">
         <v>100</v>
       </c>
+      <c r="GN58" t="n">
+        <v>104.9327</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -30442,6 +30618,9 @@
       <c r="GM59" t="n">
         <v>100.15</v>
       </c>
+      <c r="GN59" t="n">
+        <v>104.6671</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -30983,6 +31162,9 @@
       <c r="GM60" t="n">
         <v>100.15</v>
       </c>
+      <c r="GN60" t="n">
+        <v>105.0621</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -31521,6 +31703,9 @@
       <c r="GL61" t="n">
         <v>30.0681</v>
       </c>
+      <c r="GN61" t="n">
+        <v>105.637</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -32056,6 +32241,9 @@
       <c r="GM62" t="n">
         <v>101</v>
       </c>
+      <c r="GN62" t="n">
+        <v>105.013</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -32594,6 +32782,9 @@
       <c r="GM63" t="n">
         <v>100.1</v>
       </c>
+      <c r="GN63" t="n">
+        <v>104.6313</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -33090,6 +33281,9 @@
       <c r="GM64" t="n">
         <v>101.1</v>
       </c>
+      <c r="GN64" t="n">
+        <v>104.7007</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -33631,6 +33825,9 @@
       <c r="GM65" t="n">
         <v>101</v>
       </c>
+      <c r="GN65" t="n">
+        <v>105.3139</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GN65"/>
+  <dimension ref="A1:GS65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1407,6 +1407,31 @@
           <t>VSCPD</t>
         </is>
       </c>
+      <c r="GO1" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="GP1" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="GQ1" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="GR1" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="GS1" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -1822,6 +1847,21 @@
       </c>
       <c r="GN2" t="n">
         <v>103.2918</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>1644</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>1163</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>43085</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>29700</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>37280</v>
       </c>
     </row>
     <row r="3">
@@ -2280,6 +2320,21 @@
       <c r="GN3" t="n">
         <v>102</v>
       </c>
+      <c r="GO3" t="n">
+        <v>1640</v>
+      </c>
+      <c r="GP3" t="n">
+        <v>1424</v>
+      </c>
+      <c r="GQ3" t="n">
+        <v>51760</v>
+      </c>
+      <c r="GR3" t="n">
+        <v>33420</v>
+      </c>
+      <c r="GS3" t="n">
+        <v>42060</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2740,6 +2795,21 @@
       <c r="GN4" t="n">
         <v>102.4735</v>
       </c>
+      <c r="GO4" t="n">
+        <v>1634</v>
+      </c>
+      <c r="GP4" t="n">
+        <v>1434</v>
+      </c>
+      <c r="GQ4" t="n">
+        <v>51800</v>
+      </c>
+      <c r="GR4" t="n">
+        <v>33580</v>
+      </c>
+      <c r="GS4" t="n">
+        <v>41985</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3203,6 +3273,21 @@
       <c r="GN5" t="n">
         <v>102.8845</v>
       </c>
+      <c r="GO5" t="n">
+        <v>1638.5</v>
+      </c>
+      <c r="GP5" t="n">
+        <v>1425</v>
+      </c>
+      <c r="GQ5" t="n">
+        <v>51940</v>
+      </c>
+      <c r="GR5" t="n">
+        <v>33570</v>
+      </c>
+      <c r="GS5" t="n">
+        <v>41900</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3675,6 +3760,21 @@
       <c r="GN6" t="n">
         <v>102</v>
       </c>
+      <c r="GO6" t="n">
+        <v>1639.5</v>
+      </c>
+      <c r="GP6" t="n">
+        <v>1421</v>
+      </c>
+      <c r="GQ6" t="n">
+        <v>52170.00000000001</v>
+      </c>
+      <c r="GR6" t="n">
+        <v>33630</v>
+      </c>
+      <c r="GS6" t="n">
+        <v>41865</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4159,6 +4259,21 @@
       <c r="GN7" t="n">
         <v>103.7</v>
       </c>
+      <c r="GO7" t="n">
+        <v>1650</v>
+      </c>
+      <c r="GP7" t="n">
+        <v>1430</v>
+      </c>
+      <c r="GQ7" t="n">
+        <v>52340</v>
+      </c>
+      <c r="GR7" t="n">
+        <v>33815</v>
+      </c>
+      <c r="GS7" t="n">
+        <v>41800</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4637,6 +4752,21 @@
       <c r="GN8" t="n">
         <v>103.65</v>
       </c>
+      <c r="GO8" t="n">
+        <v>1657</v>
+      </c>
+      <c r="GP8" t="n">
+        <v>1436</v>
+      </c>
+      <c r="GQ8" t="n">
+        <v>52750</v>
+      </c>
+      <c r="GR8" t="n">
+        <v>34170</v>
+      </c>
+      <c r="GS8" t="n">
+        <v>42150</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5121,6 +5251,21 @@
       <c r="GN9" t="n">
         <v>102.9024</v>
       </c>
+      <c r="GO9" t="n">
+        <v>1652</v>
+      </c>
+      <c r="GP9" t="n">
+        <v>1436</v>
+      </c>
+      <c r="GQ9" t="n">
+        <v>52850</v>
+      </c>
+      <c r="GR9" t="n">
+        <v>34840</v>
+      </c>
+      <c r="GS9" t="n">
+        <v>42900</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5608,6 +5753,21 @@
       <c r="GN10" t="n">
         <v>102.9549</v>
       </c>
+      <c r="GO10" t="n">
+        <v>1660</v>
+      </c>
+      <c r="GP10" t="n">
+        <v>1433.5</v>
+      </c>
+      <c r="GQ10" t="n">
+        <v>52800</v>
+      </c>
+      <c r="GR10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="GS10" t="n">
+        <v>42795</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6083,6 +6243,21 @@
       <c r="GN11" t="n">
         <v>102.9066</v>
       </c>
+      <c r="GO11" t="n">
+        <v>1670</v>
+      </c>
+      <c r="GP11" t="n">
+        <v>1442</v>
+      </c>
+      <c r="GQ11" t="n">
+        <v>52810</v>
+      </c>
+      <c r="GR11" t="n">
+        <v>34850</v>
+      </c>
+      <c r="GS11" t="n">
+        <v>43000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6555,6 +6730,21 @@
       <c r="GN12" t="n">
         <v>102.8492</v>
       </c>
+      <c r="GO12" t="n">
+        <v>1674.5</v>
+      </c>
+      <c r="GP12" t="n">
+        <v>1436</v>
+      </c>
+      <c r="GQ12" t="n">
+        <v>52800</v>
+      </c>
+      <c r="GR12" t="n">
+        <v>34840</v>
+      </c>
+      <c r="GS12" t="n">
+        <v>42705</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7042,6 +7232,21 @@
       <c r="GN13" t="n">
         <v>102.65</v>
       </c>
+      <c r="GO13" t="n">
+        <v>1670</v>
+      </c>
+      <c r="GP13" t="n">
+        <v>1439</v>
+      </c>
+      <c r="GQ13" t="n">
+        <v>52729.99999999999</v>
+      </c>
+      <c r="GR13" t="n">
+        <v>35000</v>
+      </c>
+      <c r="GS13" t="n">
+        <v>43100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7529,6 +7734,21 @@
       <c r="GN14" t="n">
         <v>103.3492</v>
       </c>
+      <c r="GO14" t="n">
+        <v>1675</v>
+      </c>
+      <c r="GP14" t="n">
+        <v>1438.5</v>
+      </c>
+      <c r="GQ14" t="n">
+        <v>52970.00000000001</v>
+      </c>
+      <c r="GR14" t="n">
+        <v>35125</v>
+      </c>
+      <c r="GS14" t="n">
+        <v>43550</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8010,6 +8230,21 @@
       <c r="GN15" t="n">
         <v>103.542</v>
       </c>
+      <c r="GO15" t="n">
+        <v>1680</v>
+      </c>
+      <c r="GP15" t="n">
+        <v>1440.5</v>
+      </c>
+      <c r="GQ15" t="n">
+        <v>53250</v>
+      </c>
+      <c r="GR15" t="n">
+        <v>35200</v>
+      </c>
+      <c r="GS15" t="n">
+        <v>44130</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8509,6 +8744,21 @@
       <c r="GN16" t="n">
         <v>104</v>
       </c>
+      <c r="GO16" t="n">
+        <v>1685</v>
+      </c>
+      <c r="GP16" t="n">
+        <v>1454</v>
+      </c>
+      <c r="GQ16" t="n">
+        <v>53500</v>
+      </c>
+      <c r="GR16" t="n">
+        <v>35245</v>
+      </c>
+      <c r="GS16" t="n">
+        <v>43700</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9005,6 +9255,21 @@
       <c r="GN17" t="n">
         <v>103.4884</v>
       </c>
+      <c r="GO17" t="n">
+        <v>1679</v>
+      </c>
+      <c r="GP17" t="n">
+        <v>1445</v>
+      </c>
+      <c r="GQ17" t="n">
+        <v>53320.00000000001</v>
+      </c>
+      <c r="GR17" t="n">
+        <v>34975</v>
+      </c>
+      <c r="GS17" t="n">
+        <v>43650</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9498,6 +9763,21 @@
       <c r="GN18" t="n">
         <v>104.25</v>
       </c>
+      <c r="GO18" t="n">
+        <v>1678</v>
+      </c>
+      <c r="GP18" t="n">
+        <v>1449.5</v>
+      </c>
+      <c r="GQ18" t="n">
+        <v>53329.99999999999</v>
+      </c>
+      <c r="GR18" t="n">
+        <v>35000</v>
+      </c>
+      <c r="GS18" t="n">
+        <v>44390</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9997,6 +10277,21 @@
       <c r="GN19" t="n">
         <v>103.8806</v>
       </c>
+      <c r="GO19" t="n">
+        <v>1672</v>
+      </c>
+      <c r="GP19" t="n">
+        <v>1447.5</v>
+      </c>
+      <c r="GQ19" t="n">
+        <v>53600</v>
+      </c>
+      <c r="GR19" t="n">
+        <v>35175</v>
+      </c>
+      <c r="GS19" t="n">
+        <v>44970</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10493,6 +10788,21 @@
       <c r="GN20" t="n">
         <v>103.3</v>
       </c>
+      <c r="GO20" t="n">
+        <v>1689</v>
+      </c>
+      <c r="GP20" t="n">
+        <v>1440</v>
+      </c>
+      <c r="GQ20" t="n">
+        <v>53590</v>
+      </c>
+      <c r="GR20" t="n">
+        <v>35450</v>
+      </c>
+      <c r="GS20" t="n">
+        <v>45600</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10989,6 +11299,21 @@
       <c r="GN21" t="n">
         <v>103.1</v>
       </c>
+      <c r="GO21" t="n">
+        <v>1676</v>
+      </c>
+      <c r="GP21" t="n">
+        <v>1442</v>
+      </c>
+      <c r="GQ21" t="n">
+        <v>53500</v>
+      </c>
+      <c r="GR21" t="n">
+        <v>35395</v>
+      </c>
+      <c r="GS21" t="n">
+        <v>45970</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11494,6 +11819,21 @@
       <c r="GN22" t="n">
         <v>103</v>
       </c>
+      <c r="GO22" t="n">
+        <v>1669</v>
+      </c>
+      <c r="GP22" t="n">
+        <v>1420</v>
+      </c>
+      <c r="GQ22" t="n">
+        <v>53210</v>
+      </c>
+      <c r="GR22" t="n">
+        <v>35355</v>
+      </c>
+      <c r="GS22" t="n">
+        <v>46000</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11996,6 +12336,21 @@
       <c r="GN23" t="n">
         <v>106</v>
       </c>
+      <c r="GO23" t="n">
+        <v>1661</v>
+      </c>
+      <c r="GP23" t="n">
+        <v>1428</v>
+      </c>
+      <c r="GQ23" t="n">
+        <v>52920.00000000001</v>
+      </c>
+      <c r="GR23" t="n">
+        <v>35640</v>
+      </c>
+      <c r="GS23" t="n">
+        <v>46160</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12498,6 +12853,21 @@
       <c r="GN24" t="n">
         <v>104</v>
       </c>
+      <c r="GO24" t="n">
+        <v>1651</v>
+      </c>
+      <c r="GP24" t="n">
+        <v>1421</v>
+      </c>
+      <c r="GQ24" t="n">
+        <v>52679.99999999999</v>
+      </c>
+      <c r="GR24" t="n">
+        <v>35360</v>
+      </c>
+      <c r="GS24" t="n">
+        <v>45935</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12997,6 +13367,21 @@
       <c r="GN25" t="n">
         <v>103.7279</v>
       </c>
+      <c r="GO25" t="n">
+        <v>1665</v>
+      </c>
+      <c r="GP25" t="n">
+        <v>1420</v>
+      </c>
+      <c r="GQ25" t="n">
+        <v>52560</v>
+      </c>
+      <c r="GR25" t="n">
+        <v>35500</v>
+      </c>
+      <c r="GS25" t="n">
+        <v>45900</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13490,6 +13875,21 @@
       <c r="GN26" t="n">
         <v>103.1765</v>
       </c>
+      <c r="GO26" t="n">
+        <v>1675.5</v>
+      </c>
+      <c r="GP26" t="n">
+        <v>1426</v>
+      </c>
+      <c r="GQ26" t="n">
+        <v>48100</v>
+      </c>
+      <c r="GR26" t="n">
+        <v>35450</v>
+      </c>
+      <c r="GS26" t="n">
+        <v>45945</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13986,6 +14386,21 @@
       <c r="GN27" t="n">
         <v>104.398</v>
       </c>
+      <c r="GO27" t="n">
+        <v>1675</v>
+      </c>
+      <c r="GP27" t="n">
+        <v>1434</v>
+      </c>
+      <c r="GQ27" t="n">
+        <v>48295</v>
+      </c>
+      <c r="GR27" t="n">
+        <v>35900</v>
+      </c>
+      <c r="GS27" t="n">
+        <v>46400</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14485,6 +14900,21 @@
       <c r="GN28" t="n">
         <v>105.1034</v>
       </c>
+      <c r="GO28" t="n">
+        <v>1673</v>
+      </c>
+      <c r="GP28" t="n">
+        <v>1439</v>
+      </c>
+      <c r="GQ28" t="n">
+        <v>48380</v>
+      </c>
+      <c r="GR28" t="n">
+        <v>36020</v>
+      </c>
+      <c r="GS28" t="n">
+        <v>46750</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14993,6 +15423,21 @@
       <c r="GN29" t="n">
         <v>102.55</v>
       </c>
+      <c r="GO29" t="n">
+        <v>1673</v>
+      </c>
+      <c r="GP29" t="n">
+        <v>1449.5</v>
+      </c>
+      <c r="GQ29" t="n">
+        <v>48425</v>
+      </c>
+      <c r="GR29" t="n">
+        <v>36205</v>
+      </c>
+      <c r="GS29" t="n">
+        <v>47340</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15501,6 +15946,21 @@
       <c r="GN30" t="n">
         <v>105.8278</v>
       </c>
+      <c r="GO30" t="n">
+        <v>1696</v>
+      </c>
+      <c r="GP30" t="n">
+        <v>1447</v>
+      </c>
+      <c r="GQ30" t="n">
+        <v>48600</v>
+      </c>
+      <c r="GR30" t="n">
+        <v>36555</v>
+      </c>
+      <c r="GS30" t="n">
+        <v>46980</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16015,6 +16475,21 @@
       <c r="GN31" t="n">
         <v>106.7182</v>
       </c>
+      <c r="GO31" t="n">
+        <v>1695.5</v>
+      </c>
+      <c r="GP31" t="n">
+        <v>1443.5</v>
+      </c>
+      <c r="GQ31" t="n">
+        <v>48450</v>
+      </c>
+      <c r="GR31" t="n">
+        <v>36945</v>
+      </c>
+      <c r="GS31" t="n">
+        <v>47000</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -16520,6 +16995,21 @@
       <c r="GN32" t="n">
         <v>105.8376</v>
       </c>
+      <c r="GO32" t="n">
+        <v>1688</v>
+      </c>
+      <c r="GP32" t="n">
+        <v>1452</v>
+      </c>
+      <c r="GQ32" t="n">
+        <v>48430</v>
+      </c>
+      <c r="GR32" t="n">
+        <v>37120</v>
+      </c>
+      <c r="GS32" t="n">
+        <v>46995</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -17034,6 +17524,21 @@
       <c r="GN33" t="n">
         <v>105.2667</v>
       </c>
+      <c r="GO33" t="n">
+        <v>1694.5</v>
+      </c>
+      <c r="GP33" t="n">
+        <v>1450</v>
+      </c>
+      <c r="GQ33" t="n">
+        <v>48510</v>
+      </c>
+      <c r="GR33" t="n">
+        <v>37400</v>
+      </c>
+      <c r="GS33" t="n">
+        <v>47070</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -17479,6 +17984,21 @@
       <c r="GN34" t="n">
         <v>106.842</v>
       </c>
+      <c r="GO34" t="n">
+        <v>1689</v>
+      </c>
+      <c r="GP34" t="n">
+        <v>1451.5</v>
+      </c>
+      <c r="GQ34" t="n">
+        <v>48490</v>
+      </c>
+      <c r="GR34" t="n">
+        <v>37480</v>
+      </c>
+      <c r="GS34" t="n">
+        <v>47200</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -17993,6 +18513,21 @@
       <c r="GN35" t="n">
         <v>105.9036</v>
       </c>
+      <c r="GO35" t="n">
+        <v>1695</v>
+      </c>
+      <c r="GP35" t="n">
+        <v>1445</v>
+      </c>
+      <c r="GQ35" t="n">
+        <v>48400</v>
+      </c>
+      <c r="GR35" t="n">
+        <v>37150</v>
+      </c>
+      <c r="GS35" t="n">
+        <v>46780</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -18507,6 +19042,21 @@
       <c r="GN36" t="n">
         <v>105.5374</v>
       </c>
+      <c r="GO36" t="n">
+        <v>1695</v>
+      </c>
+      <c r="GP36" t="n">
+        <v>1452.5</v>
+      </c>
+      <c r="GQ36" t="n">
+        <v>48620</v>
+      </c>
+      <c r="GR36" t="n">
+        <v>37240</v>
+      </c>
+      <c r="GS36" t="n">
+        <v>46370</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -19015,6 +19565,21 @@
       <c r="GN37" t="n">
         <v>104.8072</v>
       </c>
+      <c r="GO37" t="n">
+        <v>1680.5</v>
+      </c>
+      <c r="GP37" t="n">
+        <v>1457.5</v>
+      </c>
+      <c r="GQ37" t="n">
+        <v>48705</v>
+      </c>
+      <c r="GR37" t="n">
+        <v>37135</v>
+      </c>
+      <c r="GS37" t="n">
+        <v>46060</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -19526,6 +20091,21 @@
       <c r="GN38" t="n">
         <v>105.4</v>
       </c>
+      <c r="GO38" t="n">
+        <v>1699</v>
+      </c>
+      <c r="GP38" t="n">
+        <v>1457</v>
+      </c>
+      <c r="GQ38" t="n">
+        <v>48525</v>
+      </c>
+      <c r="GR38" t="n">
+        <v>36825</v>
+      </c>
+      <c r="GS38" t="n">
+        <v>46090</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -20052,6 +20632,21 @@
       <c r="GN39" t="n">
         <v>105.25</v>
       </c>
+      <c r="GO39" t="n">
+        <v>1699</v>
+      </c>
+      <c r="GP39" t="n">
+        <v>1454</v>
+      </c>
+      <c r="GQ39" t="n">
+        <v>48600</v>
+      </c>
+      <c r="GR39" t="n">
+        <v>37120</v>
+      </c>
+      <c r="GS39" t="n">
+        <v>46100</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -20569,6 +21164,21 @@
       <c r="GN40" t="n">
         <v>105</v>
       </c>
+      <c r="GO40" t="n">
+        <v>1709</v>
+      </c>
+      <c r="GP40" t="n">
+        <v>1456</v>
+      </c>
+      <c r="GQ40" t="n">
+        <v>48790</v>
+      </c>
+      <c r="GR40" t="n">
+        <v>37175</v>
+      </c>
+      <c r="GS40" t="n">
+        <v>46880</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -21086,6 +21696,21 @@
       <c r="GN41" t="n">
         <v>104.25</v>
       </c>
+      <c r="GO41" t="n">
+        <v>1710</v>
+      </c>
+      <c r="GP41" t="n">
+        <v>1457.5</v>
+      </c>
+      <c r="GQ41" t="n">
+        <v>48790</v>
+      </c>
+      <c r="GR41" t="n">
+        <v>37585</v>
+      </c>
+      <c r="GS41" t="n">
+        <v>47100</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -21606,6 +22231,21 @@
       <c r="GN42" t="n">
         <v>104.9474</v>
       </c>
+      <c r="GO42" t="n">
+        <v>1703</v>
+      </c>
+      <c r="GP42" t="n">
+        <v>1461.5</v>
+      </c>
+      <c r="GQ42" t="n">
+        <v>48760</v>
+      </c>
+      <c r="GR42" t="n">
+        <v>37345</v>
+      </c>
+      <c r="GS42" t="n">
+        <v>47010</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -22123,6 +22763,21 @@
       <c r="GN43" t="n">
         <v>104.3575</v>
       </c>
+      <c r="GO43" t="n">
+        <v>1699</v>
+      </c>
+      <c r="GP43" t="n">
+        <v>1460</v>
+      </c>
+      <c r="GQ43" t="n">
+        <v>48800</v>
+      </c>
+      <c r="GR43" t="n">
+        <v>36945</v>
+      </c>
+      <c r="GS43" t="n">
+        <v>47150</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -22649,6 +23304,21 @@
       <c r="GN44" t="n">
         <v>105.0016</v>
       </c>
+      <c r="GO44" t="n">
+        <v>1705</v>
+      </c>
+      <c r="GP44" t="n">
+        <v>1465</v>
+      </c>
+      <c r="GQ44" t="n">
+        <v>48920</v>
+      </c>
+      <c r="GR44" t="n">
+        <v>36900</v>
+      </c>
+      <c r="GS44" t="n">
+        <v>47150</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -23175,6 +23845,21 @@
       <c r="GN45" t="n">
         <v>104.8694</v>
       </c>
+      <c r="GO45" t="n">
+        <v>1709.5</v>
+      </c>
+      <c r="GP45" t="n">
+        <v>1462</v>
+      </c>
+      <c r="GQ45" t="n">
+        <v>49050</v>
+      </c>
+      <c r="GR45" t="n">
+        <v>36900</v>
+      </c>
+      <c r="GS45" t="n">
+        <v>47140</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -23698,6 +24383,21 @@
       <c r="GN46" t="n">
         <v>105.2472</v>
       </c>
+      <c r="GO46" t="n">
+        <v>1708</v>
+      </c>
+      <c r="GP46" t="n">
+        <v>1460</v>
+      </c>
+      <c r="GQ46" t="n">
+        <v>48930</v>
+      </c>
+      <c r="GR46" t="n">
+        <v>36755</v>
+      </c>
+      <c r="GS46" t="n">
+        <v>47250</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -24221,6 +24921,21 @@
       <c r="GN47" t="n">
         <v>104.25</v>
       </c>
+      <c r="GO47" t="n">
+        <v>1708.5</v>
+      </c>
+      <c r="GP47" t="n">
+        <v>1465</v>
+      </c>
+      <c r="GQ47" t="n">
+        <v>48805</v>
+      </c>
+      <c r="GR47" t="n">
+        <v>36690</v>
+      </c>
+      <c r="GS47" t="n">
+        <v>46800</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -24733,6 +25448,21 @@
       <c r="GN48" t="n">
         <v>109.5</v>
       </c>
+      <c r="GO48" t="n">
+        <v>1706</v>
+      </c>
+      <c r="GP48" t="n">
+        <v>1458</v>
+      </c>
+      <c r="GQ48" t="n">
+        <v>48605</v>
+      </c>
+      <c r="GR48" t="n">
+        <v>36200</v>
+      </c>
+      <c r="GS48" t="n">
+        <v>46195</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -25256,6 +25986,21 @@
       </c>
       <c r="GN49" t="n">
         <v>105.2</v>
+      </c>
+      <c r="GO49" t="n">
+        <v>1703</v>
+      </c>
+      <c r="GP49" t="n">
+        <v>1464</v>
+      </c>
+      <c r="GQ49" t="n">
+        <v>48885</v>
+      </c>
+      <c r="GR49" t="n">
+        <v>36240</v>
+      </c>
+      <c r="GS49" t="n">
+        <v>46200</v>
       </c>
     </row>
     <row r="50">
@@ -25798,6 +26543,21 @@
       <c r="GN50" t="n">
         <v>104.543</v>
       </c>
+      <c r="GO50" t="n">
+        <v>1706.5</v>
+      </c>
+      <c r="GP50" t="n">
+        <v>1462.5</v>
+      </c>
+      <c r="GQ50" t="n">
+        <v>48670</v>
+      </c>
+      <c r="GR50" t="n">
+        <v>36350</v>
+      </c>
+      <c r="GS50" t="n">
+        <v>46220</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -26330,6 +27090,21 @@
       <c r="GN51" t="n">
         <v>105.0811</v>
       </c>
+      <c r="GO51" t="n">
+        <v>1697.5</v>
+      </c>
+      <c r="GP51" t="n">
+        <v>1460</v>
+      </c>
+      <c r="GQ51" t="n">
+        <v>48740</v>
+      </c>
+      <c r="GR51" t="n">
+        <v>36290</v>
+      </c>
+      <c r="GS51" t="n">
+        <v>45995</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -26862,6 +27637,21 @@
       <c r="GN52" t="n">
         <v>104.95</v>
       </c>
+      <c r="GO52" t="n">
+        <v>1696.5</v>
+      </c>
+      <c r="GP52" t="n">
+        <v>1453</v>
+      </c>
+      <c r="GQ52" t="n">
+        <v>48500</v>
+      </c>
+      <c r="GR52" t="n">
+        <v>36245</v>
+      </c>
+      <c r="GS52" t="n">
+        <v>45840</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -27401,6 +28191,21 @@
       <c r="GN53" t="n">
         <v>104.9808</v>
       </c>
+      <c r="GO53" t="n">
+        <v>1694.5</v>
+      </c>
+      <c r="GP53" t="n">
+        <v>1452.5</v>
+      </c>
+      <c r="GQ53" t="n">
+        <v>48535</v>
+      </c>
+      <c r="GR53" t="n">
+        <v>35740</v>
+      </c>
+      <c r="GS53" t="n">
+        <v>44600</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -27936,6 +28741,21 @@
       </c>
       <c r="GN54" t="n">
         <v>105.2294</v>
+      </c>
+      <c r="GO54" t="n">
+        <v>1705.5</v>
+      </c>
+      <c r="GP54" t="n">
+        <v>1464</v>
+      </c>
+      <c r="GQ54" t="n">
+        <v>48730</v>
+      </c>
+      <c r="GR54" t="n">
+        <v>35550</v>
+      </c>
+      <c r="GS54" t="n">
+        <v>44110</v>
       </c>
     </row>
     <row r="55">
@@ -28475,6 +29295,21 @@
       <c r="GN55" t="n">
         <v>106</v>
       </c>
+      <c r="GO55" t="n">
+        <v>1710</v>
+      </c>
+      <c r="GP55" t="n">
+        <v>1469</v>
+      </c>
+      <c r="GQ55" t="n">
+        <v>48800</v>
+      </c>
+      <c r="GR55" t="n">
+        <v>35705</v>
+      </c>
+      <c r="GS55" t="n">
+        <v>43900</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -29016,6 +29851,21 @@
       <c r="GN56" t="n">
         <v>104.9704</v>
       </c>
+      <c r="GO56" t="n">
+        <v>1705.5</v>
+      </c>
+      <c r="GP56" t="n">
+        <v>1460</v>
+      </c>
+      <c r="GQ56" t="n">
+        <v>48770</v>
+      </c>
+      <c r="GR56" t="n">
+        <v>35450</v>
+      </c>
+      <c r="GS56" t="n">
+        <v>44200</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -29551,6 +30401,21 @@
       <c r="GN57" t="n">
         <v>104.8277</v>
       </c>
+      <c r="GO57" t="n">
+        <v>1710</v>
+      </c>
+      <c r="GP57" t="n">
+        <v>1460</v>
+      </c>
+      <c r="GQ57" t="n">
+        <v>48735</v>
+      </c>
+      <c r="GR57" t="n">
+        <v>35470</v>
+      </c>
+      <c r="GS57" t="n">
+        <v>43650</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -30083,6 +30948,21 @@
       <c r="GN58" t="n">
         <v>104.9327</v>
       </c>
+      <c r="GO58" t="n">
+        <v>1709</v>
+      </c>
+      <c r="GP58" t="n">
+        <v>1459</v>
+      </c>
+      <c r="GQ58" t="n">
+        <v>48750</v>
+      </c>
+      <c r="GR58" t="n">
+        <v>35800</v>
+      </c>
+      <c r="GS58" t="n">
+        <v>43750</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -30621,6 +31501,21 @@
       <c r="GN59" t="n">
         <v>104.6671</v>
       </c>
+      <c r="GO59" t="n">
+        <v>1712.5</v>
+      </c>
+      <c r="GP59" t="n">
+        <v>1460</v>
+      </c>
+      <c r="GQ59" t="n">
+        <v>48600</v>
+      </c>
+      <c r="GR59" t="n">
+        <v>35800</v>
+      </c>
+      <c r="GS59" t="n">
+        <v>43600</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -31165,6 +32060,21 @@
       <c r="GN60" t="n">
         <v>105.0621</v>
       </c>
+      <c r="GO60" t="n">
+        <v>1698.5</v>
+      </c>
+      <c r="GP60" t="n">
+        <v>1457.5</v>
+      </c>
+      <c r="GQ60" t="n">
+        <v>48290</v>
+      </c>
+      <c r="GR60" t="n">
+        <v>35670</v>
+      </c>
+      <c r="GS60" t="n">
+        <v>43000</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -31706,6 +32616,21 @@
       <c r="GN61" t="n">
         <v>105.637</v>
       </c>
+      <c r="GO61" t="n">
+        <v>1691</v>
+      </c>
+      <c r="GP61" t="n">
+        <v>1433</v>
+      </c>
+      <c r="GQ61" t="n">
+        <v>47970</v>
+      </c>
+      <c r="GR61" t="n">
+        <v>35100</v>
+      </c>
+      <c r="GS61" t="n">
+        <v>43385</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -32244,6 +33169,21 @@
       <c r="GN62" t="n">
         <v>105.013</v>
       </c>
+      <c r="GO62" t="n">
+        <v>1702</v>
+      </c>
+      <c r="GP62" t="n">
+        <v>1422.5</v>
+      </c>
+      <c r="GQ62" t="n">
+        <v>47230</v>
+      </c>
+      <c r="GR62" t="n">
+        <v>34250</v>
+      </c>
+      <c r="GS62" t="n">
+        <v>42495</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -32785,6 +33725,21 @@
       <c r="GN63" t="n">
         <v>104.6313</v>
       </c>
+      <c r="GO63" t="n">
+        <v>1707</v>
+      </c>
+      <c r="GP63" t="n">
+        <v>1421</v>
+      </c>
+      <c r="GQ63" t="n">
+        <v>47360</v>
+      </c>
+      <c r="GR63" t="n">
+        <v>34670</v>
+      </c>
+      <c r="GS63" t="n">
+        <v>42330</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -33284,6 +34239,21 @@
       <c r="GN64" t="n">
         <v>104.7007</v>
       </c>
+      <c r="GO64" t="n">
+        <v>1697</v>
+      </c>
+      <c r="GP64" t="n">
+        <v>1430</v>
+      </c>
+      <c r="GQ64" t="n">
+        <v>47360</v>
+      </c>
+      <c r="GR64" t="n">
+        <v>34600</v>
+      </c>
+      <c r="GS64" t="n">
+        <v>42470</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -33828,6 +34798,21 @@
       <c r="GN65" t="n">
         <v>105.3139</v>
       </c>
+      <c r="GO65" t="n">
+        <v>1707</v>
+      </c>
+      <c r="GP65" t="n">
+        <v>1427</v>
+      </c>
+      <c r="GQ65" t="n">
+        <v>47460</v>
+      </c>
+      <c r="GR65" t="n">
+        <v>34400</v>
+      </c>
+      <c r="GS65" t="n">
+        <v>42500</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historicos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GS65"/>
+  <dimension ref="A1:GS66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -34814,6 +34814,559 @@
         <v>42500</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>126.768</v>
+      </c>
+      <c r="I66" t="n">
+        <v>114.864</v>
+      </c>
+      <c r="J66" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>121.475</v>
+      </c>
+      <c r="L66" t="n">
+        <v>145.45</v>
+      </c>
+      <c r="M66" t="n">
+        <v>131.945</v>
+      </c>
+      <c r="N66" t="n">
+        <v>124.15</v>
+      </c>
+      <c r="O66" t="n">
+        <v>125.345</v>
+      </c>
+      <c r="P66" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="S66" t="n">
+        <v>170.1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="U66" t="n">
+        <v>219.25</v>
+      </c>
+      <c r="V66" t="n">
+        <v>121.45</v>
+      </c>
+      <c r="W66" t="n">
+        <v>388.05</v>
+      </c>
+      <c r="X66" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>272.6</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>345.95</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>94</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>129.58</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>120.35</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>107</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>150210</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>147860</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>125850</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>94.34999999999999</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>53.41</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>55.05</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>75</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>78.05</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>53.40000000000001</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>76.47</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>71.36</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>91.27</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="BI66" t="n">
+        <v>105.855</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>147200</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>151010</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>119110</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>91.48999999999999</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="BU66" t="n">
+        <v>81.19</v>
+      </c>
+      <c r="BV66" t="n">
+        <v>103.869</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>84.73999999999999</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>90.94</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="CC66" t="n">
+        <v>122.75</v>
+      </c>
+      <c r="CE66" t="n">
+        <v>114.87</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="CH66" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="CI66" t="n">
+        <v>62.2782</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>106.1036</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>101.3943</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>101.2021</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="CO66" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="CP66" t="n">
+        <v>74.48390000000001</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>106.488</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>103.4125</v>
+      </c>
+      <c r="CS66" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="CT66" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="CU66" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="CV66" t="n">
+        <v>77.3672</v>
+      </c>
+      <c r="CW66" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="CX66" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="CY66" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="CZ66" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="DA66" t="n">
+        <v>109</v>
+      </c>
+      <c r="DB66" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="DC66" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="DD66" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="DE66" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="DF66" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="DG66" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="DH66" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="DI66" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DJ66" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="DK66" t="n">
+        <v>106.8244</v>
+      </c>
+      <c r="DL66" t="n">
+        <v>104.9022</v>
+      </c>
+      <c r="DM66" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="DN66" t="n">
+        <v>104.71</v>
+      </c>
+      <c r="DO66" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="DP66" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="DQ66" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DR66" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="DS66" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DT66" t="n">
+        <v>106</v>
+      </c>
+      <c r="DU66" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="DV66" t="n">
+        <v>105</v>
+      </c>
+      <c r="DW66" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DX66" t="n">
+        <v>101.7787</v>
+      </c>
+      <c r="DY66" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="DZ66" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="EA66" t="n">
+        <v>108</v>
+      </c>
+      <c r="EB66" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="EC66" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="ED66" t="n">
+        <v>107</v>
+      </c>
+      <c r="EE66" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="EF66" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EG66" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="EH66" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="EI66" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EJ66" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="EK66" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EL66" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EM66" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="EN66" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="EO66" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EQ66" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="ER66" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="ES66" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="ET66" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="EU66" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EV66" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="EW66" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EX66" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EY66" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="EZ66" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="FA66" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="FB66" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="FC66" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="FD66" t="n">
+        <v>95.39999999999999</v>
+      </c>
+      <c r="FE66" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="FF66" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="FG66" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="FH66" t="n">
+        <v>105</v>
+      </c>
+      <c r="FI66" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="FJ66" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="FK66" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FM66" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="FN66" t="n">
+        <v>101</v>
+      </c>
+      <c r="FQ66" t="n">
+        <v>101.715</v>
+      </c>
+      <c r="FR66" t="n">
+        <v>149000</v>
+      </c>
+      <c r="FS66" t="n">
+        <v>137300</v>
+      </c>
+      <c r="FU66" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="FV66" t="n">
+        <v>99.14</v>
+      </c>
+      <c r="FW66" t="n">
+        <v>98.4149</v>
+      </c>
+      <c r="FX66" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="FY66" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="GA66" t="n">
+        <v>99.9526</v>
+      </c>
+      <c r="GB66" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="GC66" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="GD66" t="n">
+        <v>149990</v>
+      </c>
+      <c r="GE66" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="GF66" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="GG66" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="GH66" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="GI66" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GJ66" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GK66" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GL66" t="n">
+        <v>28.1703</v>
+      </c>
+      <c r="GM66" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="GN66" t="n">
+        <v>105.6711</v>
+      </c>
+      <c r="GO66" t="n">
+        <v>1702.5</v>
+      </c>
+      <c r="GP66" t="n">
+        <v>1428</v>
+      </c>
+      <c r="GQ66" t="n">
+        <v>47780</v>
+      </c>
+      <c r="GR66" t="n">
+        <v>34600</v>
+      </c>
+      <c r="GS66" t="n">
+        <v>42850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GS66"/>
+  <dimension ref="A1:GS67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -35367,6 +35367,562 @@
         <v>42850</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>126.816</v>
+      </c>
+      <c r="I67" t="n">
+        <v>114.92</v>
+      </c>
+      <c r="J67" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="K67" t="n">
+        <v>121.57</v>
+      </c>
+      <c r="L67" t="n">
+        <v>145.75</v>
+      </c>
+      <c r="M67" t="n">
+        <v>131.93</v>
+      </c>
+      <c r="N67" t="n">
+        <v>123.99</v>
+      </c>
+      <c r="O67" t="n">
+        <v>125.42</v>
+      </c>
+      <c r="P67" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="S67" t="n">
+        <v>170.2</v>
+      </c>
+      <c r="T67" t="n">
+        <v>298.4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>219.5</v>
+      </c>
+      <c r="V67" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="W67" t="n">
+        <v>388.8</v>
+      </c>
+      <c r="X67" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>272.75</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>345.95</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>94</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>129.655</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>149950</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>147800</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>125880</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>53.49999999999999</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>78.55</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>53.57999999999999</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>80.51000000000001</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>105.91</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>147100</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>151100</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>119450</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>81.44</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>103.914</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>84.69</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="CB67" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="CC67" t="n">
+        <v>123.12</v>
+      </c>
+      <c r="CE67" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="CF67" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="CG67" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="CH67" t="n">
+        <v>46.2973</v>
+      </c>
+      <c r="CI67" t="n">
+        <v>62.3694</v>
+      </c>
+      <c r="CJ67" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="CL67" t="n">
+        <v>101.5662</v>
+      </c>
+      <c r="CM67" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="CN67" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="CO67" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="CP67" t="n">
+        <v>75.515</v>
+      </c>
+      <c r="CQ67" t="n">
+        <v>105.98</v>
+      </c>
+      <c r="CR67" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="CS67" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="CT67" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="CU67" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="CV67" t="n">
+        <v>76.0427</v>
+      </c>
+      <c r="CW67" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="CX67" t="n">
+        <v>107</v>
+      </c>
+      <c r="CY67" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="CZ67" t="n">
+        <v>99.90000000000002</v>
+      </c>
+      <c r="DA67" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DB67" t="n">
+        <v>105.2124</v>
+      </c>
+      <c r="DC67" t="n">
+        <v>103</v>
+      </c>
+      <c r="DD67" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="DE67" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="DF67" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="DG67" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="DH67" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DI67" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="DJ67" t="n">
+        <v>106</v>
+      </c>
+      <c r="DK67" t="n">
+        <v>106.8436</v>
+      </c>
+      <c r="DL67" t="n">
+        <v>105</v>
+      </c>
+      <c r="DM67" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="DN67" t="n">
+        <v>104.6367</v>
+      </c>
+      <c r="DO67" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DP67" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="DQ67" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DR67" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="DS67" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DT67" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DU67" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="DV67" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="DW67" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="DX67" t="n">
+        <v>101.7101</v>
+      </c>
+      <c r="DY67" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="DZ67" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="EA67" t="n">
+        <v>109</v>
+      </c>
+      <c r="EB67" t="n">
+        <v>102.1899</v>
+      </c>
+      <c r="EC67" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="ED67" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="EE67" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EF67" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="EG67" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="EH67" t="n">
+        <v>105.5962</v>
+      </c>
+      <c r="EI67" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="EJ67" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EK67" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="EL67" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="EM67" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="EN67" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="EO67" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EQ67" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="ER67" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="ES67" t="n">
+        <v>102</v>
+      </c>
+      <c r="ET67" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="EU67" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EV67" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="EW67" t="n">
+        <v>103</v>
+      </c>
+      <c r="EX67" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EY67" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EZ67" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="FA67" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="FB67" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="FC67" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FD67" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="FE67" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="FF67" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="FG67" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="FH67" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="FI67" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="FJ67" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="FK67" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="FM67" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="FN67" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FP67" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="FQ67" t="n">
+        <v>101.835</v>
+      </c>
+      <c r="FR67" t="n">
+        <v>149000</v>
+      </c>
+      <c r="FS67" t="n">
+        <v>137000</v>
+      </c>
+      <c r="FU67" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="FV67" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="FW67" t="n">
+        <v>98.15989999999999</v>
+      </c>
+      <c r="FX67" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="FY67" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="FZ67" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="GA67" t="n">
+        <v>99.7911</v>
+      </c>
+      <c r="GB67" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="GC67" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="GD67" t="n">
+        <v>149780</v>
+      </c>
+      <c r="GE67" t="n">
+        <v>109.3864</v>
+      </c>
+      <c r="GF67" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="GG67" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="GH67" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="GI67" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="GJ67" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="GK67" t="n">
+        <v>105</v>
+      </c>
+      <c r="GL67" t="n">
+        <v>28.2581</v>
+      </c>
+      <c r="GM67" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="GN67" t="n">
+        <v>105.5483</v>
+      </c>
+      <c r="GO67" t="n">
+        <v>1701.5</v>
+      </c>
+      <c r="GP67" t="n">
+        <v>1434</v>
+      </c>
+      <c r="GQ67" t="n">
+        <v>47840</v>
+      </c>
+      <c r="GR67" t="n">
+        <v>34530</v>
+      </c>
+      <c r="GS67" t="n">
+        <v>42350</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GS67"/>
+  <dimension ref="A1:GS68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -35923,6 +35923,544 @@
         <v>42350</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>115.234</v>
+      </c>
+      <c r="J68" t="n">
+        <v>130.022</v>
+      </c>
+      <c r="K68" t="n">
+        <v>121.88</v>
+      </c>
+      <c r="L68" t="n">
+        <v>146.45</v>
+      </c>
+      <c r="M68" t="n">
+        <v>132.59</v>
+      </c>
+      <c r="N68" t="n">
+        <v>124.45</v>
+      </c>
+      <c r="O68" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="S68" t="n">
+        <v>170.75</v>
+      </c>
+      <c r="T68" t="n">
+        <v>299.35</v>
+      </c>
+      <c r="U68" t="n">
+        <v>220.25</v>
+      </c>
+      <c r="V68" t="n">
+        <v>121.65</v>
+      </c>
+      <c r="W68" t="n">
+        <v>389.5</v>
+      </c>
+      <c r="X68" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>273</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>345.95</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>94</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>89</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>150360</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>147390</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>125970</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>94.48</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>53.90000000000001</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>75.52</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>78.20999999999999</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>53.44</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>71.12</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>65</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>97.86</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>91</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>168.65</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>106.185</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>147500</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>103</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>119950</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>85</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>81.84999999999999</v>
+      </c>
+      <c r="BV68" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="BW68" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="BZ68" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA68" t="n">
+        <v>90.05999999999999</v>
+      </c>
+      <c r="CB68" t="n">
+        <v>119</v>
+      </c>
+      <c r="CC68" t="n">
+        <v>123.35</v>
+      </c>
+      <c r="CE68" t="n">
+        <v>115.44</v>
+      </c>
+      <c r="CF68" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="CG68" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="CH68" t="n">
+        <v>46.4108</v>
+      </c>
+      <c r="CI68" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="CJ68" t="n">
+        <v>106.3302</v>
+      </c>
+      <c r="CL68" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="CM68" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="CN68" t="n">
+        <v>103</v>
+      </c>
+      <c r="CO68" t="n">
+        <v>74.05</v>
+      </c>
+      <c r="CP68" t="n">
+        <v>75.2933</v>
+      </c>
+      <c r="CQ68" t="n">
+        <v>106.1387</v>
+      </c>
+      <c r="CR68" t="n">
+        <v>103.5043</v>
+      </c>
+      <c r="CS68" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="CT68" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="CU68" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="CV68" t="n">
+        <v>77.1613</v>
+      </c>
+      <c r="CW68" t="n">
+        <v>49.5154</v>
+      </c>
+      <c r="CX68" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="CY68" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="CZ68" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="DA68" t="n">
+        <v>108.2461</v>
+      </c>
+      <c r="DB68" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="DC68" t="n">
+        <v>103</v>
+      </c>
+      <c r="DD68" t="n">
+        <v>104</v>
+      </c>
+      <c r="DE68" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DF68" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="DG68" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="DH68" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="DI68" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DJ68" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="DK68" t="n">
+        <v>107.0008</v>
+      </c>
+      <c r="DL68" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="DM68" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="DN68" t="n">
+        <v>104.5102</v>
+      </c>
+      <c r="DO68" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DP68" t="n">
+        <v>89.61</v>
+      </c>
+      <c r="DQ68" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="DR68" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="DS68" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DT68" t="n">
+        <v>106.2344</v>
+      </c>
+      <c r="DU68" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="DV68" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="DW68" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="DX68" t="n">
+        <v>102</v>
+      </c>
+      <c r="DY68" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DZ68" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="EA68" t="n">
+        <v>109</v>
+      </c>
+      <c r="EB68" t="n">
+        <v>103</v>
+      </c>
+      <c r="EC68" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="ED68" t="n">
+        <v>106</v>
+      </c>
+      <c r="EE68" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="EF68" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="EG68" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="EH68" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="EI68" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="EJ68" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EK68" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EL68" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="EM68" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="EN68" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="EQ68" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="ER68" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="ES68" t="n">
+        <v>102</v>
+      </c>
+      <c r="EU68" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EV68" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="EW68" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="EX68" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="EY68" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EZ68" t="n">
+        <v>102</v>
+      </c>
+      <c r="FA68" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="FB68" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="FC68" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="FD68" t="n">
+        <v>95.98</v>
+      </c>
+      <c r="FE68" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FF68" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="FG68" t="n">
+        <v>100</v>
+      </c>
+      <c r="FH68" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="FI68" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="FJ68" t="n">
+        <v>101</v>
+      </c>
+      <c r="FK68" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="FM68" t="n">
+        <v>102</v>
+      </c>
+      <c r="FN68" t="n">
+        <v>102</v>
+      </c>
+      <c r="FP68" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="FQ68" t="n">
+        <v>102.13</v>
+      </c>
+      <c r="FR68" t="n">
+        <v>149000</v>
+      </c>
+      <c r="FS68" t="n">
+        <v>137510</v>
+      </c>
+      <c r="FU68" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="FV68" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="FW68" t="n">
+        <v>98.66679999999999</v>
+      </c>
+      <c r="FX68" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="FY68" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="FZ68" t="n">
+        <v>107.3361</v>
+      </c>
+      <c r="GA68" t="n">
+        <v>99.57680000000001</v>
+      </c>
+      <c r="GB68" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="GC68" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="GD68" t="n">
+        <v>149850</v>
+      </c>
+      <c r="GE68" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="GF68" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="GG68" t="n">
+        <v>104</v>
+      </c>
+      <c r="GH68" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GI68" t="n">
+        <v>104</v>
+      </c>
+      <c r="GJ68" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="GK68" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GL68" t="n">
+        <v>28.1631</v>
+      </c>
+      <c r="GN68" t="n">
+        <v>105.037</v>
+      </c>
+      <c r="GO68" t="n">
+        <v>1702</v>
+      </c>
+      <c r="GP68" t="n">
+        <v>1438</v>
+      </c>
+      <c r="GQ68" t="n">
+        <v>47800</v>
+      </c>
+      <c r="GR68" t="n">
+        <v>34580</v>
+      </c>
+      <c r="GS68" t="n">
+        <v>42560</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GS68"/>
+  <dimension ref="A1:GU69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1432,6 +1432,16 @@
           <t>CUAP</t>
         </is>
       </c>
+      <c r="GT1" t="inlineStr">
+        <is>
+          <t>S29E7</t>
+        </is>
+      </c>
+      <c r="GU1" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -36461,6 +36471,553 @@
         <v>42560</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>115.43</v>
+      </c>
+      <c r="J69" t="n">
+        <v>130.237</v>
+      </c>
+      <c r="K69" t="n">
+        <v>122.12</v>
+      </c>
+      <c r="L69" t="n">
+        <v>146.94</v>
+      </c>
+      <c r="M69" t="n">
+        <v>132.77</v>
+      </c>
+      <c r="N69" t="n">
+        <v>124.85</v>
+      </c>
+      <c r="O69" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="P69" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="S69" t="n">
+        <v>170.9</v>
+      </c>
+      <c r="T69" t="n">
+        <v>299.8</v>
+      </c>
+      <c r="U69" t="n">
+        <v>220.4</v>
+      </c>
+      <c r="V69" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="W69" t="n">
+        <v>389.65</v>
+      </c>
+      <c r="X69" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>273.3</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>121.15</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>150350</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>147300</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>125600</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>76</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>78.44</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>70.37</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>53.77</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>76.29000000000001</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>65.17</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>92.42</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>168.75</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>106.271</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>147400</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>119170</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>104.39</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>90.19999999999999</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>120.35</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>115.41</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>45.99999999999999</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>106</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>99.34999999999998</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>100.7846</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>68.78</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>72.18089999999999</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>106.0158</v>
+      </c>
+      <c r="CR69" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="CS69" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="CU69" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="CV69" t="n">
+        <v>79.1399</v>
+      </c>
+      <c r="CW69" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="CX69" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="CY69" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="CZ69" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>108.1754</v>
+      </c>
+      <c r="DB69" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DC69" t="n">
+        <v>103.2322</v>
+      </c>
+      <c r="DD69" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="DE69" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="DF69" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="DG69" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="DH69" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="DI69" t="n">
+        <v>108.3674</v>
+      </c>
+      <c r="DJ69" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="DK69" t="n">
+        <v>106.9276</v>
+      </c>
+      <c r="DL69" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DM69" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="DN69" t="n">
+        <v>104.9599</v>
+      </c>
+      <c r="DO69" t="n">
+        <v>106</v>
+      </c>
+      <c r="DP69" t="n">
+        <v>89.86999999999999</v>
+      </c>
+      <c r="DQ69" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="DR69" t="n">
+        <v>103</v>
+      </c>
+      <c r="DS69" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="DT69" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DU69" t="n">
+        <v>106</v>
+      </c>
+      <c r="DV69" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="DW69" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="DX69" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="DY69" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="DZ69" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="EA69" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="EB69" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="EC69" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="ED69" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="EE69" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EF69" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="EG69" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="EH69" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="EI69" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="EJ69" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EK69" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EL69" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="EM69" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="EN69" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="EQ69" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="ER69" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="ES69" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="EU69" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EV69" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="EW69" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EX69" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="EY69" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="EZ69" t="n">
+        <v>102</v>
+      </c>
+      <c r="FA69" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="FB69" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="FC69" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="FD69" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="FE69" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="FF69" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="FG69" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="FH69" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="FI69" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="FJ69" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="FK69" t="n">
+        <v>103</v>
+      </c>
+      <c r="FM69" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="FN69" t="n">
+        <v>102</v>
+      </c>
+      <c r="FP69" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="FQ69" t="n">
+        <v>102.28</v>
+      </c>
+      <c r="FR69" t="n">
+        <v>149000</v>
+      </c>
+      <c r="FS69" t="n">
+        <v>137900</v>
+      </c>
+      <c r="FU69" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="FV69" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="FW69" t="n">
+        <v>98.75000000000001</v>
+      </c>
+      <c r="FX69" t="n">
+        <v>102</v>
+      </c>
+      <c r="FY69" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="FZ69" t="n">
+        <v>107.5515</v>
+      </c>
+      <c r="GA69" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="GB69" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="GC69" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="GD69" t="n">
+        <v>150050</v>
+      </c>
+      <c r="GE69" t="n">
+        <v>109.4232</v>
+      </c>
+      <c r="GF69" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="GG69" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="GH69" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="GI69" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="GJ69" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="GK69" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GL69" t="n">
+        <v>27.8751</v>
+      </c>
+      <c r="GM69" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="GN69" t="n">
+        <v>105.7758</v>
+      </c>
+      <c r="GO69" t="n">
+        <v>1703.5</v>
+      </c>
+      <c r="GP69" t="n">
+        <v>1438</v>
+      </c>
+      <c r="GQ69" t="n">
+        <v>47895</v>
+      </c>
+      <c r="GR69" t="n">
+        <v>34590</v>
+      </c>
+      <c r="GS69" t="n">
+        <v>42580</v>
+      </c>
+      <c r="GT69" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="GU69" t="n">
+        <v>732.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GU69"/>
+  <dimension ref="A1:GU70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -37018,6 +37018,550 @@
         <v>732.8</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>115.455</v>
+      </c>
+      <c r="J70" t="n">
+        <v>130.29</v>
+      </c>
+      <c r="K70" t="n">
+        <v>122.265</v>
+      </c>
+      <c r="L70" t="n">
+        <v>147.3</v>
+      </c>
+      <c r="M70" t="n">
+        <v>133.05</v>
+      </c>
+      <c r="N70" t="n">
+        <v>124.99</v>
+      </c>
+      <c r="O70" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="P70" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>111</v>
+      </c>
+      <c r="S70" t="n">
+        <v>171.15</v>
+      </c>
+      <c r="T70" t="n">
+        <v>300</v>
+      </c>
+      <c r="U70" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="V70" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="W70" t="n">
+        <v>391.7</v>
+      </c>
+      <c r="X70" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>274</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>347.3</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>94.29000000000001</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>116</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>150400</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>147790</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>125510</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>94.83</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>92.36</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>78.54000000000001</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>53.56000000000001</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>55.89999999999999</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>76.55</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>80.51000000000001</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>71.13</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>92.97</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>106.331</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>147500</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>104</v>
+      </c>
+      <c r="BR70" t="n">
+        <v>119400</v>
+      </c>
+      <c r="BS70" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="BT70" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="BU70" t="n">
+        <v>82.34999999999999</v>
+      </c>
+      <c r="BV70" t="n">
+        <v>104.498</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="BX70" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>90.54000000000002</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>121.65</v>
+      </c>
+      <c r="CC70" t="n">
+        <v>123.699</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="CH70" t="n">
+        <v>46.5027</v>
+      </c>
+      <c r="CI70" t="n">
+        <v>62.4108</v>
+      </c>
+      <c r="CJ70" t="n">
+        <v>105.9897</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="CM70" t="n">
+        <v>99.44000000000001</v>
+      </c>
+      <c r="CO70" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="CP70" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="CQ70" t="n">
+        <v>106.134</v>
+      </c>
+      <c r="CR70" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="CS70" t="n">
+        <v>106</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>105.3165</v>
+      </c>
+      <c r="CU70" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="CV70" t="n">
+        <v>76.97</v>
+      </c>
+      <c r="CW70" t="n">
+        <v>49.3881</v>
+      </c>
+      <c r="CX70" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="CY70" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="CZ70" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="DB70" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="DC70" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="DD70" t="n">
+        <v>104.1142</v>
+      </c>
+      <c r="DE70" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="DF70" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="DG70" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="DH70" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DI70" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="DJ70" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="DK70" t="n">
+        <v>106.8553</v>
+      </c>
+      <c r="DL70" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DM70" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="DN70" t="n">
+        <v>105.2203</v>
+      </c>
+      <c r="DO70" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DP70" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="DQ70" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="DR70" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="DS70" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="DT70" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DU70" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="DV70" t="n">
+        <v>106</v>
+      </c>
+      <c r="DW70" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="DX70" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="DY70" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="DZ70" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="EA70" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="EB70" t="n">
+        <v>103</v>
+      </c>
+      <c r="EC70" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="ED70" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="EE70" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="EF70" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EG70" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="EH70" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="EI70" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EJ70" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EK70" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EL70" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="EM70" t="n">
+        <v>101</v>
+      </c>
+      <c r="EN70" t="n">
+        <v>107.0477</v>
+      </c>
+      <c r="EQ70" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="ER70" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="ES70" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="EU70" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EV70" t="n">
+        <v>101</v>
+      </c>
+      <c r="EW70" t="n">
+        <v>103</v>
+      </c>
+      <c r="EX70" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EY70" t="n">
+        <v>103</v>
+      </c>
+      <c r="EZ70" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FA70" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="FB70" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="FC70" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="FD70" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="FE70" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="FF70" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="FG70" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FH70" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="FI70" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="FJ70" t="n">
+        <v>102</v>
+      </c>
+      <c r="FK70" t="n">
+        <v>103</v>
+      </c>
+      <c r="FM70" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="FN70" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="FO70" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="FP70" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="FQ70" t="n">
+        <v>102.34</v>
+      </c>
+      <c r="FR70" t="n">
+        <v>148700</v>
+      </c>
+      <c r="FS70" t="n">
+        <v>138490</v>
+      </c>
+      <c r="FU70" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="FV70" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="FX70" t="n">
+        <v>100</v>
+      </c>
+      <c r="FY70" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="FZ70" t="n">
+        <v>107.769</v>
+      </c>
+      <c r="GA70" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="GB70" t="n">
+        <v>100</v>
+      </c>
+      <c r="GC70" t="n">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="GD70" t="n">
+        <v>149950</v>
+      </c>
+      <c r="GE70" t="n">
+        <v>109.6926</v>
+      </c>
+      <c r="GF70" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="GG70" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="GH70" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="GI70" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GJ70" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="GK70" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="GL70" t="n">
+        <v>28.0757</v>
+      </c>
+      <c r="GM70" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="GN70" t="n">
+        <v>104.8356</v>
+      </c>
+      <c r="GO70" t="n">
+        <v>1709</v>
+      </c>
+      <c r="GP70" t="n">
+        <v>1440</v>
+      </c>
+      <c r="GQ70" t="n">
+        <v>48195</v>
+      </c>
+      <c r="GR70" t="n">
+        <v>34700</v>
+      </c>
+      <c r="GS70" t="n">
+        <v>42645</v>
+      </c>
+      <c r="GT70" t="n">
+        <v>100.91</v>
+      </c>
+      <c r="GU70" t="n">
+        <v>734.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GU70"/>
+  <dimension ref="A1:GZ71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1442,6 +1442,31 @@
           <t>TX26</t>
         </is>
       </c>
+      <c r="GV1" t="inlineStr">
+        <is>
+          <t>TTD26</t>
+        </is>
+      </c>
+      <c r="GW1" t="inlineStr">
+        <is>
+          <t>MTC2D</t>
+        </is>
+      </c>
+      <c r="GX1" t="inlineStr">
+        <is>
+          <t>LOC6D</t>
+        </is>
+      </c>
+      <c r="GY1" t="inlineStr">
+        <is>
+          <t>CIC8D</t>
+        </is>
+      </c>
+      <c r="GZ1" t="inlineStr">
+        <is>
+          <t>TTCBD</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -37562,6 +37587,568 @@
         <v>734.5</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>115.545</v>
+      </c>
+      <c r="J71" t="n">
+        <v>130.45</v>
+      </c>
+      <c r="K71" t="n">
+        <v>122.38</v>
+      </c>
+      <c r="L71" t="n">
+        <v>147.199</v>
+      </c>
+      <c r="M71" t="n">
+        <v>133.25</v>
+      </c>
+      <c r="N71" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="O71" t="n">
+        <v>126.55</v>
+      </c>
+      <c r="P71" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="S71" t="n">
+        <v>171.25</v>
+      </c>
+      <c r="T71" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="U71" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="V71" t="n">
+        <v>121.95</v>
+      </c>
+      <c r="W71" t="n">
+        <v>393.55</v>
+      </c>
+      <c r="X71" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>348.3</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>94.48</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>115.55</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>150320</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>147600</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>125100</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>55.67999999999999</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>71</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>53.67999999999999</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>55.50999999999999</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>80.56</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>93.00000000000001</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>92.48999999999999</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>92</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>168.95</v>
+      </c>
+      <c r="BI71" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="BK71" t="n">
+        <v>147480</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="BR71" t="n">
+        <v>119190</v>
+      </c>
+      <c r="BS71" t="n">
+        <v>93</v>
+      </c>
+      <c r="BT71" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="BU71" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="BV71" t="n">
+        <v>104.53</v>
+      </c>
+      <c r="BW71" t="n">
+        <v>96.34999999999999</v>
+      </c>
+      <c r="BX71" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY71" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="BZ71" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA71" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="CB71" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="CC71" t="n">
+        <v>123.91</v>
+      </c>
+      <c r="CE71" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="CF71" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="CG71" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="CH71" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="CI71" t="n">
+        <v>62.6181</v>
+      </c>
+      <c r="CJ71" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="CL71" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="CM71" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="CN71" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="CO71" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="CP71" t="n">
+        <v>73.1587</v>
+      </c>
+      <c r="CQ71" t="n">
+        <v>106.369</v>
+      </c>
+      <c r="CR71" t="n">
+        <v>104.2031</v>
+      </c>
+      <c r="CS71" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="CT71" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="CU71" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="CV71" t="n">
+        <v>78.21250000000001</v>
+      </c>
+      <c r="CW71" t="n">
+        <v>49.5747</v>
+      </c>
+      <c r="CX71" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="CY71" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="CZ71" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="DA71" t="n">
+        <v>108.2461</v>
+      </c>
+      <c r="DB71" t="n">
+        <v>105.4545</v>
+      </c>
+      <c r="DC71" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="DD71" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="DE71" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="DF71" t="n">
+        <v>106.7059</v>
+      </c>
+      <c r="DG71" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="DH71" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="DI71" t="n">
+        <v>108.4386</v>
+      </c>
+      <c r="DJ71" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="DK71" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="DL71" t="n">
+        <v>105</v>
+      </c>
+      <c r="DM71" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="DN71" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="DO71" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="DP71" t="n">
+        <v>90.27000000000001</v>
+      </c>
+      <c r="DQ71" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="DR71" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="DS71" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="DT71" t="n">
+        <v>105.8876</v>
+      </c>
+      <c r="DU71" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="DV71" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="DW71" t="n">
+        <v>102</v>
+      </c>
+      <c r="DX71" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="DY71" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DZ71" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="EA71" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="EB71" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="EC71" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="ED71" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="EE71" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="EF71" t="n">
+        <v>105</v>
+      </c>
+      <c r="EG71" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="EH71" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="EI71" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="EJ71" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EK71" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EL71" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="EM71" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="EN71" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="EQ71" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="ER71" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="ES71" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="EU71" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EV71" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="EW71" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="EX71" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="EY71" t="n">
+        <v>103</v>
+      </c>
+      <c r="EZ71" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="FA71" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="FB71" t="n">
+        <v>104</v>
+      </c>
+      <c r="FC71" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="FD71" t="n">
+        <v>96</v>
+      </c>
+      <c r="FE71" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FF71" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="FG71" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="FH71" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="FI71" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FJ71" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="FK71" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="FM71" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="FN71" t="n">
+        <v>101</v>
+      </c>
+      <c r="FP71" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="FQ71" t="n">
+        <v>102.21</v>
+      </c>
+      <c r="FR71" t="n">
+        <v>148720</v>
+      </c>
+      <c r="FS71" t="n">
+        <v>138720</v>
+      </c>
+      <c r="FU71" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="FV71" t="n">
+        <v>99.89999999999999</v>
+      </c>
+      <c r="FW71" t="n">
+        <v>98.5718</v>
+      </c>
+      <c r="FX71" t="n">
+        <v>100.0638</v>
+      </c>
+      <c r="FY71" t="n">
+        <v>24.261</v>
+      </c>
+      <c r="FZ71" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="GA71" t="n">
+        <v>99.35000000000001</v>
+      </c>
+      <c r="GB71" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="GC71" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="GD71" t="n">
+        <v>149700</v>
+      </c>
+      <c r="GE71" t="n">
+        <v>109.9306</v>
+      </c>
+      <c r="GF71" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="GG71" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="GH71" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="GI71" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="GJ71" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="GK71" t="n">
+        <v>103</v>
+      </c>
+      <c r="GL71" t="n">
+        <v>28.3971</v>
+      </c>
+      <c r="GM71" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GN71" t="n">
+        <v>104.8769</v>
+      </c>
+      <c r="GO71" t="n">
+        <v>1714</v>
+      </c>
+      <c r="GP71" t="n">
+        <v>1447</v>
+      </c>
+      <c r="GQ71" t="n">
+        <v>48455</v>
+      </c>
+      <c r="GR71" t="n">
+        <v>34950</v>
+      </c>
+      <c r="GS71" t="n">
+        <v>42485</v>
+      </c>
+      <c r="GT71" t="n">
+        <v>100.979</v>
+      </c>
+      <c r="GU71" t="n">
+        <v>734.6</v>
+      </c>
+      <c r="GV71" t="n">
+        <v>168.85</v>
+      </c>
+      <c r="GW71" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GX71" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GY71" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="GZ71" t="n">
+        <v>104.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GZ71"/>
+  <dimension ref="A1:GZ72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -38149,6 +38149,568 @@
         <v>104.3</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="J72" t="n">
+        <v>130.45</v>
+      </c>
+      <c r="K72" t="n">
+        <v>122.489</v>
+      </c>
+      <c r="L72" t="n">
+        <v>147.38</v>
+      </c>
+      <c r="M72" t="n">
+        <v>133.35</v>
+      </c>
+      <c r="N72" t="n">
+        <v>125.53</v>
+      </c>
+      <c r="O72" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="P72" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>111</v>
+      </c>
+      <c r="S72" t="n">
+        <v>171.45</v>
+      </c>
+      <c r="T72" t="n">
+        <v>301.4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="V72" t="n">
+        <v>122.35</v>
+      </c>
+      <c r="W72" t="n">
+        <v>395.6</v>
+      </c>
+      <c r="X72" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>276.25</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>350.25</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>90.19</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>121.55</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>150050</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>147700</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>125100</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>55.82</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>78.81</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>53.94999999999999</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>55.67999999999999</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>80.70999999999999</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>71.78</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>93.20000000000002</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>93.23</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>99</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>92.03</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>169.1</v>
+      </c>
+      <c r="BI72" t="n">
+        <v>106.485</v>
+      </c>
+      <c r="BK72" t="n">
+        <v>147580</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="BR72" t="n">
+        <v>119000</v>
+      </c>
+      <c r="BS72" t="n">
+        <v>93</v>
+      </c>
+      <c r="BT72" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="BU72" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="BV72" t="n">
+        <v>104.63</v>
+      </c>
+      <c r="BW72" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BX72" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="BY72" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ72" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA72" t="n">
+        <v>90.69</v>
+      </c>
+      <c r="CB72" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="CC72" t="n">
+        <v>124.05</v>
+      </c>
+      <c r="CE72" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="CF72" t="n">
+        <v>104</v>
+      </c>
+      <c r="CG72" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="CH72" t="n">
+        <v>46.312</v>
+      </c>
+      <c r="CI72" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="CJ72" t="n">
+        <v>105.801</v>
+      </c>
+      <c r="CK72" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="CL72" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="CM72" t="n">
+        <v>99.18000000000002</v>
+      </c>
+      <c r="CN72" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="CO72" t="n">
+        <v>68.95999999999999</v>
+      </c>
+      <c r="CP72" t="n">
+        <v>70</v>
+      </c>
+      <c r="CQ72" t="n">
+        <v>106.2338</v>
+      </c>
+      <c r="CR72" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="CS72" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="CT72" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="CU72" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="CV72" t="n">
+        <v>78.6005</v>
+      </c>
+      <c r="CW72" t="n">
+        <v>49.3994</v>
+      </c>
+      <c r="CX72" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="CY72" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="CZ72" t="n">
+        <v>101</v>
+      </c>
+      <c r="DA72" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="DB72" t="n">
+        <v>105</v>
+      </c>
+      <c r="DC72" t="n">
+        <v>103</v>
+      </c>
+      <c r="DD72" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="DE72" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="DF72" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="DG72" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="DH72" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="DI72" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="DJ72" t="n">
+        <v>105</v>
+      </c>
+      <c r="DK72" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="DL72" t="n">
+        <v>105</v>
+      </c>
+      <c r="DM72" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="DN72" t="n">
+        <v>105.1758</v>
+      </c>
+      <c r="DO72" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="DP72" t="n">
+        <v>89.87</v>
+      </c>
+      <c r="DQ72" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DR72" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="DS72" t="n">
+        <v>105</v>
+      </c>
+      <c r="DT72" t="n">
+        <v>106</v>
+      </c>
+      <c r="DU72" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="DV72" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="DW72" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="DX72" t="n">
+        <v>102</v>
+      </c>
+      <c r="DY72" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="DZ72" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="EA72" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="EB72" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EC72" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="ED72" t="n">
+        <v>106</v>
+      </c>
+      <c r="EE72" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="EF72" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="EG72" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="EH72" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="EI72" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EJ72" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EK72" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="EL72" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EM72" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="EN72" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="EQ72" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="ER72" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="ES72" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="EU72" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EV72" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="EW72" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="EX72" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EY72" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EZ72" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="FA72" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FB72" t="n">
+        <v>104</v>
+      </c>
+      <c r="FC72" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="FD72" t="n">
+        <v>95.00000000000001</v>
+      </c>
+      <c r="FE72" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FF72" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="FG72" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="FH72" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="FI72" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="FJ72" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="FK72" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="FM72" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="FN72" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="FP72" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="FQ72" t="n">
+        <v>102.465</v>
+      </c>
+      <c r="FR72" t="n">
+        <v>148720</v>
+      </c>
+      <c r="FS72" t="n">
+        <v>138860</v>
+      </c>
+      <c r="FU72" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="FV72" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="FX72" t="n">
+        <v>100.03</v>
+      </c>
+      <c r="FY72" t="n">
+        <v>24.158</v>
+      </c>
+      <c r="FZ72" t="n">
+        <v>106.859</v>
+      </c>
+      <c r="GA72" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="GB72" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="GC72" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="GD72" t="n">
+        <v>149700</v>
+      </c>
+      <c r="GE72" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="GF72" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="GG72" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="GH72" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="GI72" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="GJ72" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GK72" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GL72" t="n">
+        <v>27.893</v>
+      </c>
+      <c r="GM72" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="GN72" t="n">
+        <v>104.6949</v>
+      </c>
+      <c r="GO72" t="n">
+        <v>1719</v>
+      </c>
+      <c r="GP72" t="n">
+        <v>1459</v>
+      </c>
+      <c r="GQ72" t="n">
+        <v>48850</v>
+      </c>
+      <c r="GR72" t="n">
+        <v>35000</v>
+      </c>
+      <c r="GS72" t="n">
+        <v>42620</v>
+      </c>
+      <c r="GT72" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="GU72" t="n">
+        <v>735.8</v>
+      </c>
+      <c r="GV72" t="n">
+        <v>169</v>
+      </c>
+      <c r="GW72" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GX72" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GY72" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GZ72" t="n">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1898,6 +1898,9 @@
       <c r="GS2" t="n">
         <v>37280</v>
       </c>
+      <c r="GZ2" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2370,6 +2373,15 @@
       <c r="GS3" t="n">
         <v>42060</v>
       </c>
+      <c r="GX3" t="n">
+        <v>104</v>
+      </c>
+      <c r="GY3" t="n">
+        <v>99</v>
+      </c>
+      <c r="GZ3" t="n">
+        <v>104.75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2845,6 +2857,15 @@
       <c r="GS4" t="n">
         <v>41985</v>
       </c>
+      <c r="GX4" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GY4" t="n">
+        <v>100</v>
+      </c>
+      <c r="GZ4" t="n">
+        <v>103.85</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3323,6 +3344,15 @@
       <c r="GS5" t="n">
         <v>41900</v>
       </c>
+      <c r="GX5" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="GY5" t="n">
+        <v>97.01000000000001</v>
+      </c>
+      <c r="GZ5" t="n">
+        <v>104.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3810,6 +3840,15 @@
       <c r="GS6" t="n">
         <v>41865</v>
       </c>
+      <c r="GX6" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="GY6" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="GZ6" t="n">
+        <v>104.05</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4309,6 +4348,15 @@
       <c r="GS7" t="n">
         <v>41800</v>
       </c>
+      <c r="GX7" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="GY7" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="GZ7" t="n">
+        <v>104.15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4802,6 +4850,15 @@
       <c r="GS8" t="n">
         <v>42150</v>
       </c>
+      <c r="GX8" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="GY8" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="GZ8" t="n">
+        <v>104.25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5301,6 +5358,12 @@
       <c r="GS9" t="n">
         <v>42900</v>
       </c>
+      <c r="GX9" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="GZ9" t="n">
+        <v>104.45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5803,6 +5866,15 @@
       <c r="GS10" t="n">
         <v>42795</v>
       </c>
+      <c r="GX10" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="GY10" t="n">
+        <v>98.00000000000001</v>
+      </c>
+      <c r="GZ10" t="n">
+        <v>104.8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6293,6 +6365,12 @@
       <c r="GS11" t="n">
         <v>43000</v>
       </c>
+      <c r="GX11" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="GZ11" t="n">
+        <v>104.25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6780,6 +6858,12 @@
       <c r="GS12" t="n">
         <v>42705</v>
       </c>
+      <c r="GX12" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="GZ12" t="n">
+        <v>104.2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7282,6 +7366,12 @@
       <c r="GS13" t="n">
         <v>43100</v>
       </c>
+      <c r="GX13" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="GZ13" t="n">
+        <v>104.35</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7784,6 +7874,12 @@
       <c r="GS14" t="n">
         <v>43550</v>
       </c>
+      <c r="GX14" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="GZ14" t="n">
+        <v>104.35</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8280,6 +8376,12 @@
       <c r="GS15" t="n">
         <v>44130</v>
       </c>
+      <c r="GX15" t="n">
+        <v>104</v>
+      </c>
+      <c r="GZ15" t="n">
+        <v>104.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8794,6 +8896,12 @@
       <c r="GS16" t="n">
         <v>43700</v>
       </c>
+      <c r="GX16" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="GZ16" t="n">
+        <v>104.15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9305,6 +9413,12 @@
       <c r="GS17" t="n">
         <v>43650</v>
       </c>
+      <c r="GX17" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="GZ17" t="n">
+        <v>104.35</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9813,6 +9927,12 @@
       <c r="GS18" t="n">
         <v>44390</v>
       </c>
+      <c r="GX18" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="GZ18" t="n">
+        <v>105.35</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10327,6 +10447,12 @@
       <c r="GS19" t="n">
         <v>44970</v>
       </c>
+      <c r="GX19" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="GZ19" t="n">
+        <v>104.35</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10838,6 +10964,12 @@
       <c r="GS20" t="n">
         <v>45600</v>
       </c>
+      <c r="GX20" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="GZ20" t="n">
+        <v>104.45</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11349,6 +11481,15 @@
       <c r="GS21" t="n">
         <v>45970</v>
       </c>
+      <c r="GX21" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="GY21" t="n">
+        <v>101</v>
+      </c>
+      <c r="GZ21" t="n">
+        <v>104.45</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11869,6 +12010,18 @@
       <c r="GS22" t="n">
         <v>46000</v>
       </c>
+      <c r="GW22" t="n">
+        <v>101</v>
+      </c>
+      <c r="GX22" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="GY22" t="n">
+        <v>97.56</v>
+      </c>
+      <c r="GZ22" t="n">
+        <v>104.3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12386,6 +12539,15 @@
       <c r="GS23" t="n">
         <v>46160</v>
       </c>
+      <c r="GW23" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="GX23" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="GZ23" t="n">
+        <v>104.1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12903,6 +13065,18 @@
       <c r="GS24" t="n">
         <v>45935</v>
       </c>
+      <c r="GW24" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="GX24" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="GY24" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="GZ24" t="n">
+        <v>103.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13417,6 +13591,18 @@
       <c r="GS25" t="n">
         <v>45900</v>
       </c>
+      <c r="GW25" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="GX25" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="GY25" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="GZ25" t="n">
+        <v>104.3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13925,6 +14111,15 @@
       <c r="GS26" t="n">
         <v>45945</v>
       </c>
+      <c r="GW26" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="GX26" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="GZ26" t="n">
+        <v>105.2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14436,6 +14631,18 @@
       <c r="GS27" t="n">
         <v>46400</v>
       </c>
+      <c r="GW27" t="n">
+        <v>101</v>
+      </c>
+      <c r="GX27" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="GY27" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="GZ27" t="n">
+        <v>104.95</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14950,6 +15157,18 @@
       <c r="GS28" t="n">
         <v>46750</v>
       </c>
+      <c r="GW28" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="GX28" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="GY28" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="GZ28" t="n">
+        <v>104.6</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15473,6 +15692,18 @@
       <c r="GS29" t="n">
         <v>47340</v>
       </c>
+      <c r="GW29" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="GX29" t="n">
+        <v>105</v>
+      </c>
+      <c r="GY29" t="n">
+        <v>102</v>
+      </c>
+      <c r="GZ29" t="n">
+        <v>104.15</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15996,6 +16227,15 @@
       <c r="GS30" t="n">
         <v>46980</v>
       </c>
+      <c r="GW30" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="GX30" t="n">
+        <v>105</v>
+      </c>
+      <c r="GZ30" t="n">
+        <v>104.65</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16525,6 +16765,18 @@
       <c r="GS31" t="n">
         <v>47000</v>
       </c>
+      <c r="GW31" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="GX31" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="GY31" t="n">
+        <v>103</v>
+      </c>
+      <c r="GZ31" t="n">
+        <v>104.75</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17045,6 +17297,18 @@
       <c r="GS32" t="n">
         <v>46995</v>
       </c>
+      <c r="GW32" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="GX32" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="GY32" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="GZ32" t="n">
+        <v>104.8</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -17574,6 +17838,15 @@
       <c r="GS33" t="n">
         <v>47070</v>
       </c>
+      <c r="GW33" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="GX33" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="GZ33" t="n">
+        <v>104.6</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18034,6 +18307,18 @@
       <c r="GS34" t="n">
         <v>47200</v>
       </c>
+      <c r="GW34" t="n">
+        <v>102</v>
+      </c>
+      <c r="GX34" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="GY34" t="n">
+        <v>103</v>
+      </c>
+      <c r="GZ34" t="n">
+        <v>104.35</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -18563,6 +18848,18 @@
       <c r="GS35" t="n">
         <v>46780</v>
       </c>
+      <c r="GW35" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="GX35" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="GY35" t="n">
+        <v>103</v>
+      </c>
+      <c r="GZ35" t="n">
+        <v>104.45</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -19092,6 +19389,15 @@
       <c r="GS36" t="n">
         <v>46370</v>
       </c>
+      <c r="GW36" t="n">
+        <v>102</v>
+      </c>
+      <c r="GX36" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="GZ36" t="n">
+        <v>104.75</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -19615,6 +19921,18 @@
       <c r="GS37" t="n">
         <v>46060</v>
       </c>
+      <c r="GW37" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="GX37" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="GY37" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="GZ37" t="n">
+        <v>104.6</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20141,6 +20459,18 @@
       <c r="GS38" t="n">
         <v>46090</v>
       </c>
+      <c r="GW38" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="GX38" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="GY38" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GZ38" t="n">
+        <v>104.8</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -20682,6 +21012,18 @@
       <c r="GS39" t="n">
         <v>46100</v>
       </c>
+      <c r="GW39" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GX39" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="GY39" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GZ39" t="n">
+        <v>105.4</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -21214,6 +21556,18 @@
       <c r="GS40" t="n">
         <v>46880</v>
       </c>
+      <c r="GW40" t="n">
+        <v>101</v>
+      </c>
+      <c r="GX40" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="GY40" t="n">
+        <v>103</v>
+      </c>
+      <c r="GZ40" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -21746,6 +22100,18 @@
       <c r="GS41" t="n">
         <v>47100</v>
       </c>
+      <c r="GW41" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GX41" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="GY41" t="n">
+        <v>103</v>
+      </c>
+      <c r="GZ41" t="n">
+        <v>104.85</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -22281,6 +22647,15 @@
       <c r="GS42" t="n">
         <v>47010</v>
       </c>
+      <c r="GW42" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="GX42" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="GZ42" t="n">
+        <v>104.95</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -22813,6 +23188,15 @@
       <c r="GS43" t="n">
         <v>47150</v>
       </c>
+      <c r="GW43" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="GX43" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="GZ43" t="n">
+        <v>104.9</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -23354,6 +23738,18 @@
       <c r="GS44" t="n">
         <v>47150</v>
       </c>
+      <c r="GW44" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="GX44" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GY44" t="n">
+        <v>102</v>
+      </c>
+      <c r="GZ44" t="n">
+        <v>105.4</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -23895,6 +24291,18 @@
       <c r="GS45" t="n">
         <v>47140</v>
       </c>
+      <c r="GW45" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="GX45" t="n">
+        <v>103</v>
+      </c>
+      <c r="GY45" t="n">
+        <v>103</v>
+      </c>
+      <c r="GZ45" t="n">
+        <v>104.9</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -24433,6 +24841,18 @@
       <c r="GS46" t="n">
         <v>47250</v>
       </c>
+      <c r="GW46" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="GX46" t="n">
+        <v>103</v>
+      </c>
+      <c r="GY46" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GZ46" t="n">
+        <v>104.95</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -24971,6 +25391,18 @@
       <c r="GS47" t="n">
         <v>46800</v>
       </c>
+      <c r="GW47" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="GX47" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GY47" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GZ47" t="n">
+        <v>104.95</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -25498,6 +25930,18 @@
       <c r="GS48" t="n">
         <v>46195</v>
       </c>
+      <c r="GW48" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="GX48" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="GY48" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GZ48" t="n">
+        <v>104.6</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -26036,6 +26480,18 @@
       </c>
       <c r="GS49" t="n">
         <v>46200</v>
+      </c>
+      <c r="GW49" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="GX49" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="GY49" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="GZ49" t="n">
+        <v>104.95</v>
       </c>
     </row>
     <row r="50">
@@ -26593,6 +27049,18 @@
       <c r="GS50" t="n">
         <v>46220</v>
       </c>
+      <c r="GW50" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GX50" t="n">
+        <v>103</v>
+      </c>
+      <c r="GY50" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="GZ50" t="n">
+        <v>104.95</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -27140,6 +27608,18 @@
       <c r="GS51" t="n">
         <v>45995</v>
       </c>
+      <c r="GW51" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="GX51" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="GY51" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GZ51" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -27687,6 +28167,18 @@
       <c r="GS52" t="n">
         <v>45840</v>
       </c>
+      <c r="GW52" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="GX52" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="GY52" t="n">
+        <v>103</v>
+      </c>
+      <c r="GZ52" t="n">
+        <v>104.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -28241,6 +28733,18 @@
       <c r="GS53" t="n">
         <v>44600</v>
       </c>
+      <c r="GW53" t="n">
+        <v>102</v>
+      </c>
+      <c r="GX53" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="GY53" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="GZ53" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -28791,6 +29295,18 @@
       </c>
       <c r="GS54" t="n">
         <v>44110</v>
+      </c>
+      <c r="GW54" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GX54" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GY54" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GZ54" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="55">
@@ -29345,6 +29861,18 @@
       <c r="GS55" t="n">
         <v>43900</v>
       </c>
+      <c r="GW55" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="GX55" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="GY55" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GZ55" t="n">
+        <v>105.45</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -29901,6 +30429,18 @@
       <c r="GS56" t="n">
         <v>44200</v>
       </c>
+      <c r="GW56" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="GX56" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="GY56" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GZ56" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -30451,6 +30991,18 @@
       <c r="GS57" t="n">
         <v>43650</v>
       </c>
+      <c r="GW57" t="n">
+        <v>102</v>
+      </c>
+      <c r="GX57" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GY57" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GZ57" t="n">
+        <v>105.1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -30998,6 +31550,18 @@
       <c r="GS58" t="n">
         <v>43750</v>
       </c>
+      <c r="GW58" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="GX58" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="GY58" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GZ58" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -31551,6 +32115,18 @@
       <c r="GS59" t="n">
         <v>43600</v>
       </c>
+      <c r="GW59" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GX59" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GY59" t="n">
+        <v>103</v>
+      </c>
+      <c r="GZ59" t="n">
+        <v>105.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -32110,6 +32686,18 @@
       <c r="GS60" t="n">
         <v>43000</v>
       </c>
+      <c r="GW60" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="GX60" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="GY60" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="GZ60" t="n">
+        <v>105.5</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -32666,6 +33254,18 @@
       <c r="GS61" t="n">
         <v>43385</v>
       </c>
+      <c r="GW61" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="GX61" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="GY61" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GZ61" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -33219,6 +33819,18 @@
       <c r="GS62" t="n">
         <v>42495</v>
       </c>
+      <c r="GW62" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="GX62" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="GY62" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GZ62" t="n">
+        <v>105.15</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -33775,6 +34387,18 @@
       <c r="GS63" t="n">
         <v>42330</v>
       </c>
+      <c r="GW63" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="GX63" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="GY63" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="GZ63" t="n">
+        <v>105.75</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -34289,6 +34913,18 @@
       <c r="GS64" t="n">
         <v>42470</v>
       </c>
+      <c r="GW64" t="n">
+        <v>102</v>
+      </c>
+      <c r="GX64" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="GY64" t="n">
+        <v>103</v>
+      </c>
+      <c r="GZ64" t="n">
+        <v>104.15</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -34848,6 +35484,18 @@
       <c r="GS65" t="n">
         <v>42500</v>
       </c>
+      <c r="GW65" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="GX65" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="GY65" t="n">
+        <v>103</v>
+      </c>
+      <c r="GZ65" t="n">
+        <v>104.15</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -35401,6 +36049,18 @@
       <c r="GS66" t="n">
         <v>42850</v>
       </c>
+      <c r="GW66" t="n">
+        <v>102</v>
+      </c>
+      <c r="GX66" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GY66" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GZ66" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -35957,6 +36617,18 @@
       <c r="GS67" t="n">
         <v>42350</v>
       </c>
+      <c r="GW67" t="n">
+        <v>102</v>
+      </c>
+      <c r="GX67" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="GY67" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GZ67" t="n">
+        <v>105.9</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -36495,6 +37167,18 @@
       <c r="GS68" t="n">
         <v>42560</v>
       </c>
+      <c r="GW68" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="GX68" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GY68" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GZ68" t="n">
+        <v>104.35</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -37042,6 +37726,18 @@
       <c r="GU69" t="n">
         <v>732.8</v>
       </c>
+      <c r="GW69" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="GX69" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GY69" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GZ69" t="n">
+        <v>104.45</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -37586,6 +38282,18 @@
       <c r="GU70" t="n">
         <v>734.5</v>
       </c>
+      <c r="GW70" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="GX70" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="GY70" t="n">
+        <v>103</v>
+      </c>
+      <c r="GZ70" t="n">
+        <v>104.6</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GZ72"/>
+  <dimension ref="A1:HE73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1467,6 +1467,31 @@
           <t>TTCBD</t>
         </is>
       </c>
+      <c r="HA1" t="inlineStr">
+        <is>
+          <t>TTC8D</t>
+        </is>
+      </c>
+      <c r="HB1" t="inlineStr">
+        <is>
+          <t>TTCAD</t>
+        </is>
+      </c>
+      <c r="HC1" t="inlineStr">
+        <is>
+          <t>CS53D</t>
+        </is>
+      </c>
+      <c r="HD1" t="inlineStr">
+        <is>
+          <t>TLCQD</t>
+        </is>
+      </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>GN47D</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -39419,6 +39444,577 @@
         <v>104</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>115.82</v>
+      </c>
+      <c r="J73" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="K73" t="n">
+        <v>122.77</v>
+      </c>
+      <c r="L73" t="n">
+        <v>147.67</v>
+      </c>
+      <c r="M73" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="N73" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="O73" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="P73" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="S73" t="n">
+        <v>171.8</v>
+      </c>
+      <c r="T73" t="n">
+        <v>302</v>
+      </c>
+      <c r="U73" t="n">
+        <v>223</v>
+      </c>
+      <c r="V73" t="n">
+        <v>123</v>
+      </c>
+      <c r="W73" t="n">
+        <v>395.3</v>
+      </c>
+      <c r="X73" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>352</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>95.48999999999999</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>150190</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>147500</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>125000</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>94.93000000000002</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>54.40000000000001</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>76.98</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>54</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>77.02</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>65.87</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="BH73" t="n">
+        <v>169.38</v>
+      </c>
+      <c r="BI73" t="n">
+        <v>106.675</v>
+      </c>
+      <c r="BK73" t="n">
+        <v>147540</v>
+      </c>
+      <c r="BM73" t="n">
+        <v>101</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>105</v>
+      </c>
+      <c r="BR73" t="n">
+        <v>118850</v>
+      </c>
+      <c r="BS73" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="BT73" t="n">
+        <v>85.89</v>
+      </c>
+      <c r="BU73" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="BV73" t="n">
+        <v>104.84</v>
+      </c>
+      <c r="BW73" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="BX73" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="BY73" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="BZ73" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA73" t="n">
+        <v>90.58999999999999</v>
+      </c>
+      <c r="CB73" t="n">
+        <v>120.75</v>
+      </c>
+      <c r="CC73" t="n">
+        <v>124.45</v>
+      </c>
+      <c r="CE73" t="n">
+        <v>115.82</v>
+      </c>
+      <c r="CF73" t="n">
+        <v>104</v>
+      </c>
+      <c r="CG73" t="n">
+        <v>104</v>
+      </c>
+      <c r="CH73" t="n">
+        <v>46.3517</v>
+      </c>
+      <c r="CI73" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="CJ73" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="CL73" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="CM73" t="n">
+        <v>99.13979999999999</v>
+      </c>
+      <c r="CN73" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="CO73" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="CP73" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="CQ73" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="CR73" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="CS73" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="CT73" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="CU73" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="CV73" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="CW73" t="n">
+        <v>49.349</v>
+      </c>
+      <c r="CX73" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="CY73" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="CZ73" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="DA73" t="n">
+        <v>107.7858</v>
+      </c>
+      <c r="DB73" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="DC73" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="DD73" t="n">
+        <v>103.799</v>
+      </c>
+      <c r="DE73" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DF73" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="DG73" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="DH73" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="DI73" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="DJ73" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="DK73" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="DL73" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DM73" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="DN73" t="n">
+        <v>105.192</v>
+      </c>
+      <c r="DO73" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="DP73" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="DQ73" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="DR73" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="DS73" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DT73" t="n">
+        <v>106</v>
+      </c>
+      <c r="DU73" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="DV73" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="DW73" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="DX73" t="n">
+        <v>102</v>
+      </c>
+      <c r="DY73" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="DZ73" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="EA73" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="EB73" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="EC73" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="ED73" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="EE73" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="EF73" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="EG73" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="EH73" t="n">
+        <v>105</v>
+      </c>
+      <c r="EI73" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="EJ73" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="EK73" t="n">
+        <v>104</v>
+      </c>
+      <c r="EL73" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="EM73" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="EN73" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="EQ73" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="ER73" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="ES73" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="EU73" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EV73" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="EW73" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EX73" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EY73" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EZ73" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="FA73" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FB73" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="FC73" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="FD73" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="FE73" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="FF73" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="FG73" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FH73" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="FI73" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="FJ73" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="FK73" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="FM73" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="FN73" t="n">
+        <v>101</v>
+      </c>
+      <c r="FP73" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="FQ73" t="n">
+        <v>102.66</v>
+      </c>
+      <c r="FR73" t="n">
+        <v>152000</v>
+      </c>
+      <c r="FS73" t="n">
+        <v>139390</v>
+      </c>
+      <c r="FU73" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="FV73" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="FX73" t="n">
+        <v>100.3407</v>
+      </c>
+      <c r="FY73" t="n">
+        <v>23.765</v>
+      </c>
+      <c r="GA73" t="n">
+        <v>98.99999999999999</v>
+      </c>
+      <c r="GB73" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="GC73" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="GD73" t="n">
+        <v>149900</v>
+      </c>
+      <c r="GE73" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="GF73" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="GG73" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="GH73" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="GI73" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="GJ73" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="GK73" t="n">
+        <v>103</v>
+      </c>
+      <c r="GL73" t="n">
+        <v>28.3394</v>
+      </c>
+      <c r="GM73" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="GN73" t="n">
+        <v>105.5282</v>
+      </c>
+      <c r="GO73" t="n">
+        <v>1728.5</v>
+      </c>
+      <c r="GP73" t="n">
+        <v>1462</v>
+      </c>
+      <c r="GQ73" t="n">
+        <v>48895</v>
+      </c>
+      <c r="GR73" t="n">
+        <v>35150</v>
+      </c>
+      <c r="GS73" t="n">
+        <v>43350</v>
+      </c>
+      <c r="GT73" t="n">
+        <v>101.244</v>
+      </c>
+      <c r="GU73" t="n">
+        <v>737.1</v>
+      </c>
+      <c r="GV73" t="n">
+        <v>169.15</v>
+      </c>
+      <c r="GW73" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="GX73" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="GY73" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GZ73" t="n">
+        <v>105</v>
+      </c>
+      <c r="HA73" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="HB73" t="n">
+        <v>104.0392</v>
+      </c>
+      <c r="HC73" t="n">
+        <v>103</v>
+      </c>
+      <c r="HD73" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="HE73" t="n">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1926,6 +1926,18 @@
       <c r="GZ2" t="n">
         <v>102</v>
       </c>
+      <c r="HA2" t="n">
+        <v>100</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2407,6 +2419,18 @@
       <c r="GZ3" t="n">
         <v>104.75</v>
       </c>
+      <c r="HA3" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="HC3" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="HD3" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="HE3" t="n">
+        <v>100.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2891,6 +2915,18 @@
       <c r="GZ4" t="n">
         <v>103.85</v>
       </c>
+      <c r="HA4" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="HC4" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="HD4" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="HE4" t="n">
+        <v>100.8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3378,6 +3414,18 @@
       <c r="GZ5" t="n">
         <v>104.1</v>
       </c>
+      <c r="HA5" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="HC5" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="HD5" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="HE5" t="n">
+        <v>100.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3874,6 +3922,18 @@
       <c r="GZ6" t="n">
         <v>104.05</v>
       </c>
+      <c r="HA6" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="HC6" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="HD6" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="HE6" t="n">
+        <v>101.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4382,6 +4442,18 @@
       <c r="GZ7" t="n">
         <v>104.15</v>
       </c>
+      <c r="HA7" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="HC7" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="HD7" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="HE7" t="n">
+        <v>100.8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4884,6 +4956,18 @@
       <c r="GZ8" t="n">
         <v>104.25</v>
       </c>
+      <c r="HA8" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="HC8" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="HD8" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="HE8" t="n">
+        <v>100.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5389,6 +5473,21 @@
       <c r="GZ9" t="n">
         <v>104.45</v>
       </c>
+      <c r="HA9" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="HB9" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="HC9" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="HD9" t="n">
+        <v>105</v>
+      </c>
+      <c r="HE9" t="n">
+        <v>100.4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5900,6 +5999,21 @@
       <c r="GZ10" t="n">
         <v>104.8</v>
       </c>
+      <c r="HA10" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="HB10" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="HC10" t="n">
+        <v>101</v>
+      </c>
+      <c r="HD10" t="n">
+        <v>105</v>
+      </c>
+      <c r="HE10" t="n">
+        <v>100.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6396,6 +6510,18 @@
       <c r="GZ11" t="n">
         <v>104.25</v>
       </c>
+      <c r="HA11" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="HC11" t="n">
+        <v>101</v>
+      </c>
+      <c r="HD11" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="HE11" t="n">
+        <v>101.2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6889,6 +7015,18 @@
       <c r="GZ12" t="n">
         <v>104.2</v>
       </c>
+      <c r="HA12" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="HC12" t="n">
+        <v>101</v>
+      </c>
+      <c r="HD12" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="HE12" t="n">
+        <v>100.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7397,6 +7535,18 @@
       <c r="GZ13" t="n">
         <v>104.35</v>
       </c>
+      <c r="HA13" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="HC13" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="HD13" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="HE13" t="n">
+        <v>100.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7905,6 +8055,18 @@
       <c r="GZ14" t="n">
         <v>104.35</v>
       </c>
+      <c r="HA14" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="HC14" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="HD14" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="HE14" t="n">
+        <v>102.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8407,6 +8569,18 @@
       <c r="GZ15" t="n">
         <v>104.5</v>
       </c>
+      <c r="HA15" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="HC15" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="HD15" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="HE15" t="n">
+        <v>103.25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8927,6 +9101,18 @@
       <c r="GZ16" t="n">
         <v>104.15</v>
       </c>
+      <c r="HA16" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="HC16" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="HD16" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="HE16" t="n">
+        <v>103.35</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9444,6 +9630,18 @@
       <c r="GZ17" t="n">
         <v>104.35</v>
       </c>
+      <c r="HA17" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="HC17" t="n">
+        <v>102</v>
+      </c>
+      <c r="HD17" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="HE17" t="n">
+        <v>102.85</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9958,6 +10156,21 @@
       <c r="GZ18" t="n">
         <v>105.35</v>
       </c>
+      <c r="HA18" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="HB18" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="HC18" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="HD18" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="HE18" t="n">
+        <v>102.75</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10478,6 +10691,15 @@
       <c r="GZ19" t="n">
         <v>104.35</v>
       </c>
+      <c r="HA19" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="HD19" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="HE19" t="n">
+        <v>101.8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10995,6 +11217,18 @@
       <c r="GZ20" t="n">
         <v>104.45</v>
       </c>
+      <c r="HA20" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="HC20" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="HD20" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="HE20" t="n">
+        <v>101.7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11515,6 +11749,18 @@
       <c r="GZ21" t="n">
         <v>104.45</v>
       </c>
+      <c r="HA21" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="HC21" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="HD21" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="HE21" t="n">
+        <v>103.7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12047,6 +12293,21 @@
       <c r="GZ22" t="n">
         <v>104.3</v>
       </c>
+      <c r="HA22" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="HB22" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="HC22" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="HD22" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="HE22" t="n">
+        <v>101.9</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12573,6 +12834,18 @@
       <c r="GZ23" t="n">
         <v>104.1</v>
       </c>
+      <c r="HA23" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="HC23" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="HD23" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="HE23" t="n">
+        <v>103.25</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13102,6 +13375,18 @@
       <c r="GZ24" t="n">
         <v>103.5</v>
       </c>
+      <c r="HA24" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="HC24" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="HD24" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="HE24" t="n">
+        <v>103.2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13628,6 +13913,18 @@
       <c r="GZ25" t="n">
         <v>104.3</v>
       </c>
+      <c r="HA25" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="HC25" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="HD25" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="HE25" t="n">
+        <v>102.7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14145,6 +14442,18 @@
       <c r="GZ26" t="n">
         <v>105.2</v>
       </c>
+      <c r="HA26" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="HC26" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="HD26" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="HE26" t="n">
+        <v>104.2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14668,6 +14977,18 @@
       <c r="GZ27" t="n">
         <v>104.95</v>
       </c>
+      <c r="HA27" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="HC27" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="HD27" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="HE27" t="n">
+        <v>103.2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15194,6 +15515,18 @@
       <c r="GZ28" t="n">
         <v>104.6</v>
       </c>
+      <c r="HA28" t="n">
+        <v>103</v>
+      </c>
+      <c r="HC28" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="HD28" t="n">
+        <v>105</v>
+      </c>
+      <c r="HE28" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15729,6 +16062,18 @@
       <c r="GZ29" t="n">
         <v>104.15</v>
       </c>
+      <c r="HA29" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="HC29" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="HD29" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="HE29" t="n">
+        <v>104.1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16261,6 +16606,18 @@
       <c r="GZ30" t="n">
         <v>104.65</v>
       </c>
+      <c r="HA30" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="HC30" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="HD30" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="HE30" t="n">
+        <v>102.6</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16802,6 +17159,18 @@
       <c r="GZ31" t="n">
         <v>104.75</v>
       </c>
+      <c r="HA31" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="HC31" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="HD31" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="HE31" t="n">
+        <v>102.8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17334,6 +17703,18 @@
       <c r="GZ32" t="n">
         <v>104.8</v>
       </c>
+      <c r="HA32" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="HC32" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="HD32" t="n">
+        <v>103</v>
+      </c>
+      <c r="HE32" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -17872,6 +18253,18 @@
       <c r="GZ33" t="n">
         <v>104.6</v>
       </c>
+      <c r="HA33" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="HC33" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="HD33" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HE33" t="n">
+        <v>103.25</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18344,6 +18737,15 @@
       <c r="GZ34" t="n">
         <v>104.35</v>
       </c>
+      <c r="HC34" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="HD34" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="HE34" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -18885,6 +19287,18 @@
       <c r="GZ35" t="n">
         <v>104.45</v>
       </c>
+      <c r="HA35" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="HC35" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="HD35" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="HE35" t="n">
+        <v>102.75</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -19423,6 +19837,18 @@
       <c r="GZ36" t="n">
         <v>104.75</v>
       </c>
+      <c r="HA36" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="HC36" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="HD36" t="n">
+        <v>104</v>
+      </c>
+      <c r="HE36" t="n">
+        <v>102.65</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -19958,6 +20384,21 @@
       <c r="GZ37" t="n">
         <v>104.6</v>
       </c>
+      <c r="HA37" t="n">
+        <v>103</v>
+      </c>
+      <c r="HB37" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="HC37" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="HD37" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HE37" t="n">
+        <v>102.9</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20496,6 +20937,21 @@
       <c r="GZ38" t="n">
         <v>104.8</v>
       </c>
+      <c r="HA38" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="HB38" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="HC38" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="HD38" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="HE38" t="n">
+        <v>102.5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -21049,6 +21505,18 @@
       <c r="GZ39" t="n">
         <v>105.4</v>
       </c>
+      <c r="HA39" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="HC39" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="HD39" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="HE39" t="n">
+        <v>102.85</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -21593,6 +22061,18 @@
       <c r="GZ40" t="n">
         <v>105</v>
       </c>
+      <c r="HA40" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HC40" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="HD40" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="HE40" t="n">
+        <v>102.8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -22137,6 +22617,18 @@
       <c r="GZ41" t="n">
         <v>104.85</v>
       </c>
+      <c r="HA41" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="HC41" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="HD41" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="HE41" t="n">
+        <v>103.3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -22681,6 +23173,21 @@
       <c r="GZ42" t="n">
         <v>104.95</v>
       </c>
+      <c r="HA42" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="HB42" t="n">
+        <v>104</v>
+      </c>
+      <c r="HC42" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="HD42" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="HE42" t="n">
+        <v>102.25</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -23222,6 +23729,18 @@
       <c r="GZ43" t="n">
         <v>104.9</v>
       </c>
+      <c r="HA43" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="HC43" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="HD43" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="HE43" t="n">
+        <v>102.7</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -23775,6 +24294,21 @@
       <c r="GZ44" t="n">
         <v>105.4</v>
       </c>
+      <c r="HA44" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="HB44" t="n">
+        <v>104</v>
+      </c>
+      <c r="HC44" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="HD44" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="HE44" t="n">
+        <v>103.4</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -24328,6 +24862,21 @@
       <c r="GZ45" t="n">
         <v>104.9</v>
       </c>
+      <c r="HA45" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="HB45" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="HC45" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="HD45" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="HE45" t="n">
+        <v>103.5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -24878,6 +25427,21 @@
       <c r="GZ46" t="n">
         <v>104.95</v>
       </c>
+      <c r="HA46" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="HB46" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="HC46" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="HD46" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="HE46" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -25428,6 +25992,21 @@
       <c r="GZ47" t="n">
         <v>104.95</v>
       </c>
+      <c r="HA47" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="HB47" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="HC47" t="n">
+        <v>105</v>
+      </c>
+      <c r="HD47" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="HE47" t="n">
+        <v>103.5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -25967,6 +26546,21 @@
       <c r="GZ48" t="n">
         <v>104.6</v>
       </c>
+      <c r="HA48" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="HB48" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="HC48" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="HD48" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="HE48" t="n">
+        <v>104.35</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -26517,6 +27111,18 @@
       </c>
       <c r="GZ49" t="n">
         <v>104.95</v>
+      </c>
+      <c r="HA49" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="HB49" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="HD49" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="HE49" t="n">
+        <v>103.45</v>
       </c>
     </row>
     <row r="50">
@@ -27086,6 +27692,18 @@
       <c r="GZ50" t="n">
         <v>104.95</v>
       </c>
+      <c r="HA50" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="HC50" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="HD50" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="HE50" t="n">
+        <v>104.15</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -27645,6 +28263,21 @@
       <c r="GZ51" t="n">
         <v>105</v>
       </c>
+      <c r="HA51" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HB51" t="n">
+        <v>105</v>
+      </c>
+      <c r="HC51" t="n">
+        <v>104</v>
+      </c>
+      <c r="HD51" t="n">
+        <v>105</v>
+      </c>
+      <c r="HE51" t="n">
+        <v>102.9</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -28204,6 +28837,18 @@
       <c r="GZ52" t="n">
         <v>104.85</v>
       </c>
+      <c r="HA52" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="HC52" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="HD52" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="HE52" t="n">
+        <v>102.5</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -28770,6 +29415,18 @@
       <c r="GZ53" t="n">
         <v>105</v>
       </c>
+      <c r="HA53" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="HC53" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="HD53" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="HE53" t="n">
+        <v>102.6</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -29332,6 +29989,18 @@
       </c>
       <c r="GZ54" t="n">
         <v>105</v>
+      </c>
+      <c r="HA54" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="HC54" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="HD54" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="HE54" t="n">
+        <v>102.35</v>
       </c>
     </row>
     <row r="55">
@@ -29898,6 +30567,18 @@
       <c r="GZ55" t="n">
         <v>105.45</v>
       </c>
+      <c r="HA55" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="HC55" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="HD55" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="HE55" t="n">
+        <v>102.8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -30466,6 +31147,18 @@
       <c r="GZ56" t="n">
         <v>105</v>
       </c>
+      <c r="HA56" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HC56" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="HD56" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="HE56" t="n">
+        <v>104.45</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -31028,6 +31721,18 @@
       <c r="GZ57" t="n">
         <v>105.1</v>
       </c>
+      <c r="HA57" t="n">
+        <v>103</v>
+      </c>
+      <c r="HC57" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="HD57" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="HE57" t="n">
+        <v>104.45</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -31587,6 +32292,21 @@
       <c r="GZ58" t="n">
         <v>105</v>
       </c>
+      <c r="HA58" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="HB58" t="n">
+        <v>105</v>
+      </c>
+      <c r="HC58" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="HD58" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="HE58" t="n">
+        <v>103.15</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -32152,6 +32872,18 @@
       <c r="GZ59" t="n">
         <v>105.2</v>
       </c>
+      <c r="HA59" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="HC59" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="HD59" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="HE59" t="n">
+        <v>103.15</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -32723,6 +33455,18 @@
       <c r="GZ60" t="n">
         <v>105.5</v>
       </c>
+      <c r="HA60" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="HC60" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="HD60" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="HE60" t="n">
+        <v>103.2</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -33291,6 +34035,21 @@
       <c r="GZ61" t="n">
         <v>105</v>
       </c>
+      <c r="HA61" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="HB61" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="HC61" t="n">
+        <v>103</v>
+      </c>
+      <c r="HD61" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="HE61" t="n">
+        <v>102.6</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -33856,6 +34615,21 @@
       <c r="GZ62" t="n">
         <v>105.15</v>
       </c>
+      <c r="HA62" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="HB62" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="HC62" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="HD62" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="HE62" t="n">
+        <v>102.35</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -34424,6 +35198,18 @@
       <c r="GZ63" t="n">
         <v>105.75</v>
       </c>
+      <c r="HA63" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="HC63" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="HD63" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="HE63" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -34950,6 +35736,18 @@
       <c r="GZ64" t="n">
         <v>104.15</v>
       </c>
+      <c r="HA64" t="n">
+        <v>103</v>
+      </c>
+      <c r="HC64" t="n">
+        <v>103</v>
+      </c>
+      <c r="HD64" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HE64" t="n">
+        <v>102.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -35521,6 +36319,18 @@
       <c r="GZ65" t="n">
         <v>104.15</v>
       </c>
+      <c r="HA65" t="n">
+        <v>103</v>
+      </c>
+      <c r="HC65" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="HD65" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="HE65" t="n">
+        <v>102.95</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -36086,6 +36896,21 @@
       <c r="GZ66" t="n">
         <v>104</v>
       </c>
+      <c r="HA66" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="HB66" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="HC66" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="HD66" t="n">
+        <v>104</v>
+      </c>
+      <c r="HE66" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -36654,6 +37479,21 @@
       <c r="GZ67" t="n">
         <v>105.9</v>
       </c>
+      <c r="HA67" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="HB67" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="HC67" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="HD67" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="HE67" t="n">
+        <v>102.65</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -37204,6 +38044,21 @@
       <c r="GZ68" t="n">
         <v>104.35</v>
       </c>
+      <c r="HA68" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="HB68" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="HC68" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="HD68" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="HE68" t="n">
+        <v>102.85</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -37763,6 +38618,18 @@
       <c r="GZ69" t="n">
         <v>104.45</v>
       </c>
+      <c r="HA69" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="HC69" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="HD69" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="HE69" t="n">
+        <v>103.05</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -38319,6 +39186,18 @@
       <c r="GZ70" t="n">
         <v>104.6</v>
       </c>
+      <c r="HA70" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="HC70" t="n">
+        <v>103</v>
+      </c>
+      <c r="HD70" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HE70" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -38881,6 +39760,18 @@
       <c r="GZ71" t="n">
         <v>104.3</v>
       </c>
+      <c r="HA71" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="HC71" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="HD71" t="n">
+        <v>104</v>
+      </c>
+      <c r="HE71" t="n">
+        <v>102.95</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -39443,6 +40334,18 @@
       <c r="GZ72" t="n">
         <v>104</v>
       </c>
+      <c r="HA72" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="HC72" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="HD72" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="HE72" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HE73"/>
+  <dimension ref="A1:HE74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -40918,6 +40918,580 @@
         <v>103</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="J74" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="K74" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="L74" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="M74" t="n">
+        <v>133.72</v>
+      </c>
+      <c r="N74" t="n">
+        <v>125.803</v>
+      </c>
+      <c r="O74" t="n">
+        <v>126.901</v>
+      </c>
+      <c r="P74" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>111.05</v>
+      </c>
+      <c r="S74" t="n">
+        <v>172</v>
+      </c>
+      <c r="T74" t="n">
+        <v>302.3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>223.3</v>
+      </c>
+      <c r="V74" t="n">
+        <v>123</v>
+      </c>
+      <c r="W74" t="n">
+        <v>395.75</v>
+      </c>
+      <c r="X74" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>277.35</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>150420</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>148000</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>125300</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>54.28999999999999</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>92.76000000000002</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>77</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>79.06999999999999</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>71.31</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>53.99999999999999</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>80.45</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>71.45999999999999</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>65.93000000000001</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>93.42</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="BI74" t="n">
+        <v>106.737</v>
+      </c>
+      <c r="BK74" t="n">
+        <v>147800</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>104</v>
+      </c>
+      <c r="BR74" t="n">
+        <v>118650</v>
+      </c>
+      <c r="BS74" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="BT74" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="BU74" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="BV74" t="n">
+        <v>104.93</v>
+      </c>
+      <c r="BW74" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="BX74" t="n">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="BY74" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="BZ74" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA74" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="CB74" t="n">
+        <v>121</v>
+      </c>
+      <c r="CC74" t="n">
+        <v>124.43</v>
+      </c>
+      <c r="CE74" t="n">
+        <v>116.147</v>
+      </c>
+      <c r="CF74" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="CG74" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="CH74" t="n">
+        <v>46.3052</v>
+      </c>
+      <c r="CI74" t="n">
+        <v>62.4593</v>
+      </c>
+      <c r="CJ74" t="n">
+        <v>105.4569</v>
+      </c>
+      <c r="CL74" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="CM74" t="n">
+        <v>98.84000000000002</v>
+      </c>
+      <c r="CN74" t="n">
+        <v>100.6634</v>
+      </c>
+      <c r="CO74" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="CP74" t="n">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="CQ74" t="n">
+        <v>106.7991</v>
+      </c>
+      <c r="CR74" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="CS74" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="CT74" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="CU74" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="CV74" t="n">
+        <v>78.18000000000001</v>
+      </c>
+      <c r="CW74" t="n">
+        <v>49.1813</v>
+      </c>
+      <c r="CX74" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="CY74" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="CZ74" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="DA74" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="DB74" t="n">
+        <v>105.2652</v>
+      </c>
+      <c r="DC74" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="DD74" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="DE74" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DF74" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="DG74" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="DH74" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="DI74" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="DJ74" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="DK74" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="DL74" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="DM74" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DN74" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="DO74" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DP74" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="DQ74" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DR74" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="DS74" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="DT74" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="DU74" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="DV74" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="DW74" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="DX74" t="n">
+        <v>102</v>
+      </c>
+      <c r="DY74" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="DZ74" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="EA74" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="EB74" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EC74" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="ED74" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="EE74" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EF74" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="EG74" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="EH74" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="EI74" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="EJ74" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EK74" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="EL74" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EM74" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="EN74" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="EQ74" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="ER74" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="ES74" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="EU74" t="n">
+        <v>104</v>
+      </c>
+      <c r="EV74" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EW74" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="EX74" t="n">
+        <v>104</v>
+      </c>
+      <c r="EY74" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="EZ74" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="FA74" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="FB74" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="FC74" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="FD74" t="n">
+        <v>95</v>
+      </c>
+      <c r="FE74" t="n">
+        <v>102</v>
+      </c>
+      <c r="FF74" t="n">
+        <v>103</v>
+      </c>
+      <c r="FG74" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="FH74" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="FI74" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="FJ74" t="n">
+        <v>102</v>
+      </c>
+      <c r="FK74" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="FM74" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="FN74" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="FP74" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="FQ74" t="n">
+        <v>102.755</v>
+      </c>
+      <c r="FR74" t="n">
+        <v>152000</v>
+      </c>
+      <c r="FS74" t="n">
+        <v>139680</v>
+      </c>
+      <c r="FU74" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="FV74" t="n">
+        <v>99.84999999999998</v>
+      </c>
+      <c r="FX74" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="FY74" t="n">
+        <v>23.55399999999999</v>
+      </c>
+      <c r="FZ74" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="GA74" t="n">
+        <v>99.08159999999999</v>
+      </c>
+      <c r="GB74" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="GC74" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="GD74" t="n">
+        <v>149900</v>
+      </c>
+      <c r="GE74" t="n">
+        <v>111.4488</v>
+      </c>
+      <c r="GF74" t="n">
+        <v>106</v>
+      </c>
+      <c r="GG74" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="GH74" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="GI74" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="GJ74" t="n">
+        <v>102</v>
+      </c>
+      <c r="GK74" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="GL74" t="n">
+        <v>28.7514</v>
+      </c>
+      <c r="GM74" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="GN74" t="n">
+        <v>105</v>
+      </c>
+      <c r="GO74" t="n">
+        <v>1736.5</v>
+      </c>
+      <c r="GP74" t="n">
+        <v>1465.5</v>
+      </c>
+      <c r="GQ74" t="n">
+        <v>48845</v>
+      </c>
+      <c r="GR74" t="n">
+        <v>35090</v>
+      </c>
+      <c r="GS74" t="n">
+        <v>43200</v>
+      </c>
+      <c r="GT74" t="n">
+        <v>101.31</v>
+      </c>
+      <c r="GU74" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="GV74" t="n">
+        <v>169.23</v>
+      </c>
+      <c r="GW74" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="GX74" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="GY74" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="GZ74" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="HA74" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="HB74" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="HC74" t="n">
+        <v>103</v>
+      </c>
+      <c r="HD74" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="HE74" t="n">
+        <v>103.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HE74"/>
+  <dimension ref="A1:HJ75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1492,6 +1492,31 @@
           <t>GN47D</t>
         </is>
       </c>
+      <c r="HF1" t="inlineStr">
+        <is>
+          <t>BDC33</t>
+        </is>
+      </c>
+      <c r="HG1" t="inlineStr">
+        <is>
+          <t>MGCUD</t>
+        </is>
+      </c>
+      <c r="HH1" t="inlineStr">
+        <is>
+          <t>PVC5D</t>
+        </is>
+      </c>
+      <c r="HI1" t="inlineStr">
+        <is>
+          <t>MSSFD</t>
+        </is>
+      </c>
+      <c r="HJ1" t="inlineStr">
+        <is>
+          <t>IRCOD</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -41492,6 +41517,595 @@
         <v>103.9</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>115.978</v>
+      </c>
+      <c r="J75" t="n">
+        <v>130.993</v>
+      </c>
+      <c r="K75" t="n">
+        <v>122.89</v>
+      </c>
+      <c r="L75" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>133.75</v>
+      </c>
+      <c r="N75" t="n">
+        <v>125.75</v>
+      </c>
+      <c r="O75" t="n">
+        <v>127.05</v>
+      </c>
+      <c r="P75" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="S75" t="n">
+        <v>172.15</v>
+      </c>
+      <c r="T75" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="U75" t="n">
+        <v>223.35</v>
+      </c>
+      <c r="V75" t="n">
+        <v>123</v>
+      </c>
+      <c r="W75" t="n">
+        <v>397.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>277.6</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>352.4</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>150510</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>147880</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>124600</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>95.07000000000001</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>54.40999999999999</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>76.55</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>53.77000000000001</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>55.95999999999999</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>76.93000000000001</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>80.53</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>65.86</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>169.625</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>106.81</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>147600</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>101</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>101</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>104</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>118000</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>86</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>104.981</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>84.91</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>90.84</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>121.05</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>124.452</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>116.01</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>104</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>46.2947</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>63</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>97.90900000000001</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>101</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>100</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>68.84999999999999</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="CU75" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="CV75" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="CW75" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="CX75" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="CY75" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="CZ75" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="DA75" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="DB75" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="DC75" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="DD75" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="DE75" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DF75" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="DG75" t="n">
+        <v>99</v>
+      </c>
+      <c r="DH75" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="DI75" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="DJ75" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="DK75" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="DL75" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="DM75" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="DN75" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="DO75" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="DP75" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="DQ75" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="DR75" t="n">
+        <v>102</v>
+      </c>
+      <c r="DS75" t="n">
+        <v>104</v>
+      </c>
+      <c r="DT75" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="DU75" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DV75" t="n">
+        <v>106</v>
+      </c>
+      <c r="DW75" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="DX75" t="n">
+        <v>102</v>
+      </c>
+      <c r="DY75" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="DZ75" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="EA75" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="EB75" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="EC75" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="ED75" t="n">
+        <v>106</v>
+      </c>
+      <c r="EE75" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="EF75" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="EG75" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="EH75" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="EI75" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="EJ75" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="EK75" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="EL75" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="EM75" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EN75" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="EQ75" t="n">
+        <v>103</v>
+      </c>
+      <c r="ER75" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="ES75" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EU75" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="EV75" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EW75" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="EX75" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EY75" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="EZ75" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="FA75" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="FB75" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="FC75" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="FD75" t="n">
+        <v>95.28</v>
+      </c>
+      <c r="FE75" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="FF75" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="FG75" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FH75" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="FI75" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="FJ75" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="FK75" t="n">
+        <v>103</v>
+      </c>
+      <c r="FM75" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="FN75" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="FQ75" t="n">
+        <v>102.835</v>
+      </c>
+      <c r="FR75" t="n">
+        <v>150000</v>
+      </c>
+      <c r="FS75" t="n">
+        <v>140000</v>
+      </c>
+      <c r="FU75" t="n">
+        <v>100</v>
+      </c>
+      <c r="FV75" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="FX75" t="n">
+        <v>100.1135</v>
+      </c>
+      <c r="FY75" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="FZ75" t="n">
+        <v>104.9539</v>
+      </c>
+      <c r="GA75" t="n">
+        <v>98.532</v>
+      </c>
+      <c r="GB75" t="n">
+        <v>100</v>
+      </c>
+      <c r="GC75" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="GD75" t="n">
+        <v>150090</v>
+      </c>
+      <c r="GE75" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="GF75" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="GG75" t="n">
+        <v>104</v>
+      </c>
+      <c r="GH75" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="GI75" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="GJ75" t="n">
+        <v>102</v>
+      </c>
+      <c r="GK75" t="n">
+        <v>103</v>
+      </c>
+      <c r="GL75" t="n">
+        <v>27.796</v>
+      </c>
+      <c r="GM75" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="GN75" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="GO75" t="n">
+        <v>1735</v>
+      </c>
+      <c r="GP75" t="n">
+        <v>1464</v>
+      </c>
+      <c r="GQ75" t="n">
+        <v>48945</v>
+      </c>
+      <c r="GR75" t="n">
+        <v>35120</v>
+      </c>
+      <c r="GS75" t="n">
+        <v>43295</v>
+      </c>
+      <c r="GT75" t="n">
+        <v>101.314</v>
+      </c>
+      <c r="GU75" t="n">
+        <v>738.5</v>
+      </c>
+      <c r="GV75" t="n">
+        <v>169.29</v>
+      </c>
+      <c r="GW75" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GX75" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="GY75" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="GZ75" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="HA75" t="n">
+        <v>103</v>
+      </c>
+      <c r="HB75" t="n">
+        <v>102.6535</v>
+      </c>
+      <c r="HC75" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="HD75" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="HE75" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="HF75" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="HG75" t="n">
+        <v>100</v>
+      </c>
+      <c r="HH75" t="n">
+        <v>99.51000000000001</v>
+      </c>
+      <c r="HI75" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="HJ75" t="n">
+        <v>104.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -1963,6 +1963,12 @@
       <c r="HE2" t="n">
         <v>99</v>
       </c>
+      <c r="HI2" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>105.35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2456,6 +2462,12 @@
       <c r="HE3" t="n">
         <v>100.5</v>
       </c>
+      <c r="HI3" t="n">
+        <v>103</v>
+      </c>
+      <c r="HJ3" t="n">
+        <v>106.75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2952,6 +2964,12 @@
       <c r="HE4" t="n">
         <v>100.8</v>
       </c>
+      <c r="HI4" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="HJ4" t="n">
+        <v>106.15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3451,6 +3469,12 @@
       <c r="HE5" t="n">
         <v>100.2</v>
       </c>
+      <c r="HI5" t="n">
+        <v>102</v>
+      </c>
+      <c r="HJ5" t="n">
+        <v>106.4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3959,6 +3983,12 @@
       <c r="HE6" t="n">
         <v>101.2</v>
       </c>
+      <c r="HI6" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="HJ6" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4479,6 +4509,12 @@
       <c r="HE7" t="n">
         <v>100.8</v>
       </c>
+      <c r="HI7" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="HJ7" t="n">
+        <v>106.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4993,6 +5029,12 @@
       <c r="HE8" t="n">
         <v>100.8</v>
       </c>
+      <c r="HI8" t="n">
+        <v>103</v>
+      </c>
+      <c r="HJ8" t="n">
+        <v>105.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5513,6 +5555,12 @@
       <c r="HE9" t="n">
         <v>100.4</v>
       </c>
+      <c r="HI9" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="HJ9" t="n">
+        <v>106.2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6039,6 +6087,12 @@
       <c r="HE10" t="n">
         <v>100.7</v>
       </c>
+      <c r="HI10" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="HJ10" t="n">
+        <v>106.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6547,6 +6601,12 @@
       <c r="HE11" t="n">
         <v>101.2</v>
       </c>
+      <c r="HI11" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="HJ11" t="n">
+        <v>106.85</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7052,6 +7112,12 @@
       <c r="HE12" t="n">
         <v>100.7</v>
       </c>
+      <c r="HI12" t="n">
+        <v>103</v>
+      </c>
+      <c r="HJ12" t="n">
+        <v>106.3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7572,6 +7638,12 @@
       <c r="HE13" t="n">
         <v>100.5</v>
       </c>
+      <c r="HI13" t="n">
+        <v>103</v>
+      </c>
+      <c r="HJ13" t="n">
+        <v>107.7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8092,6 +8164,12 @@
       <c r="HE14" t="n">
         <v>102.8</v>
       </c>
+      <c r="HI14" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="HJ14" t="n">
+        <v>107.2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8606,6 +8684,12 @@
       <c r="HE15" t="n">
         <v>103.25</v>
       </c>
+      <c r="HI15" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="HJ15" t="n">
+        <v>108.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9138,6 +9222,12 @@
       <c r="HE16" t="n">
         <v>103.35</v>
       </c>
+      <c r="HI16" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HJ16" t="n">
+        <v>108.45</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9667,6 +9757,12 @@
       <c r="HE17" t="n">
         <v>102.85</v>
       </c>
+      <c r="HI17" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="HJ17" t="n">
+        <v>107.5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10196,6 +10292,12 @@
       <c r="HE18" t="n">
         <v>102.75</v>
       </c>
+      <c r="HI18" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="HJ18" t="n">
+        <v>107.15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10725,6 +10827,12 @@
       <c r="HE19" t="n">
         <v>101.8</v>
       </c>
+      <c r="HI19" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="HJ19" t="n">
+        <v>106.9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11254,6 +11362,12 @@
       <c r="HE20" t="n">
         <v>101.7</v>
       </c>
+      <c r="HI20" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="HJ20" t="n">
+        <v>107.2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11786,6 +11900,12 @@
       <c r="HE21" t="n">
         <v>103.7</v>
       </c>
+      <c r="HI21" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="HJ21" t="n">
+        <v>106.9</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12333,6 +12453,12 @@
       <c r="HE22" t="n">
         <v>101.9</v>
       </c>
+      <c r="HI22" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="HJ22" t="n">
+        <v>107.7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12871,6 +12997,12 @@
       <c r="HE23" t="n">
         <v>103.25</v>
       </c>
+      <c r="HI23" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="HJ23" t="n">
+        <v>107.75</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13412,6 +13544,12 @@
       <c r="HE24" t="n">
         <v>103.2</v>
       </c>
+      <c r="HI24" t="n">
+        <v>103</v>
+      </c>
+      <c r="HJ24" t="n">
+        <v>107.8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13950,6 +14088,12 @@
       <c r="HE25" t="n">
         <v>102.7</v>
       </c>
+      <c r="HI25" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="HJ25" t="n">
+        <v>108.85</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14479,6 +14623,12 @@
       <c r="HE26" t="n">
         <v>104.2</v>
       </c>
+      <c r="HI26" t="n">
+        <v>103</v>
+      </c>
+      <c r="HJ26" t="n">
+        <v>107.75</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15014,6 +15164,12 @@
       <c r="HE27" t="n">
         <v>103.2</v>
       </c>
+      <c r="HI27" t="n">
+        <v>103</v>
+      </c>
+      <c r="HJ27" t="n">
+        <v>108.35</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15552,6 +15708,12 @@
       <c r="HE28" t="n">
         <v>103</v>
       </c>
+      <c r="HI28" t="n">
+        <v>103</v>
+      </c>
+      <c r="HJ28" t="n">
+        <v>107.9</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16099,6 +16261,12 @@
       <c r="HE29" t="n">
         <v>104.1</v>
       </c>
+      <c r="HI29" t="n">
+        <v>103</v>
+      </c>
+      <c r="HJ29" t="n">
+        <v>108.6</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16643,6 +16811,12 @@
       <c r="HE30" t="n">
         <v>102.6</v>
       </c>
+      <c r="HI30" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="HJ30" t="n">
+        <v>107.5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17196,6 +17370,12 @@
       <c r="HE31" t="n">
         <v>102.8</v>
       </c>
+      <c r="HI31" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="HJ31" t="n">
+        <v>107.2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17740,6 +17920,12 @@
       <c r="HE32" t="n">
         <v>103</v>
       </c>
+      <c r="HI32" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="HJ32" t="n">
+        <v>107.4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -18290,6 +18476,12 @@
       <c r="HE33" t="n">
         <v>103.25</v>
       </c>
+      <c r="HI33" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HJ33" t="n">
+        <v>107.25</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18771,6 +18963,12 @@
       <c r="HE34" t="n">
         <v>104</v>
       </c>
+      <c r="HI34" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="HJ34" t="n">
+        <v>107.5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -19324,6 +19522,15 @@
       <c r="HE35" t="n">
         <v>102.75</v>
       </c>
+      <c r="HF35" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="HI35" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HJ35" t="n">
+        <v>107.45</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -19874,6 +20081,15 @@
       <c r="HE36" t="n">
         <v>102.65</v>
       </c>
+      <c r="HF36" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="HI36" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="HJ36" t="n">
+        <v>107.7</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -20424,6 +20640,15 @@
       <c r="HE37" t="n">
         <v>102.9</v>
       </c>
+      <c r="HF37" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="HI37" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HJ37" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20977,6 +21202,15 @@
       <c r="HE38" t="n">
         <v>102.5</v>
       </c>
+      <c r="HH38" t="n">
+        <v>100</v>
+      </c>
+      <c r="HI38" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="HJ38" t="n">
+        <v>108.1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -21542,6 +21776,18 @@
       <c r="HE39" t="n">
         <v>102.85</v>
       </c>
+      <c r="HF39" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="HH39" t="n">
+        <v>100</v>
+      </c>
+      <c r="HI39" t="n">
+        <v>104</v>
+      </c>
+      <c r="HJ39" t="n">
+        <v>108.4</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -22098,6 +22344,12 @@
       <c r="HE40" t="n">
         <v>102.8</v>
       </c>
+      <c r="HI40" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="HJ40" t="n">
+        <v>108.1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -22654,6 +22906,12 @@
       <c r="HE41" t="n">
         <v>103.3</v>
       </c>
+      <c r="HI41" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="HJ41" t="n">
+        <v>108.35</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -23213,6 +23471,12 @@
       <c r="HE42" t="n">
         <v>102.25</v>
       </c>
+      <c r="HI42" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="HJ42" t="n">
+        <v>106.5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -23766,6 +24030,15 @@
       <c r="HE43" t="n">
         <v>102.7</v>
       </c>
+      <c r="HH43" t="n">
+        <v>96.99999999999999</v>
+      </c>
+      <c r="HI43" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="HJ43" t="n">
+        <v>107.4</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -24334,6 +24607,18 @@
       <c r="HE44" t="n">
         <v>103.4</v>
       </c>
+      <c r="HF44" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="HH44" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="HI44" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="HJ44" t="n">
+        <v>106.3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -24902,6 +25187,15 @@
       <c r="HE45" t="n">
         <v>103.5</v>
       </c>
+      <c r="HH45" t="n">
+        <v>98.00000000000001</v>
+      </c>
+      <c r="HI45" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="HJ45" t="n">
+        <v>105.2</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -25467,6 +25761,18 @@
       <c r="HE46" t="n">
         <v>104</v>
       </c>
+      <c r="HF46" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="HH46" t="n">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="HI46" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="HJ46" t="n">
+        <v>106.3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -26032,6 +26338,15 @@
       <c r="HE47" t="n">
         <v>103.5</v>
       </c>
+      <c r="HH47" t="n">
+        <v>100</v>
+      </c>
+      <c r="HI47" t="n">
+        <v>100</v>
+      </c>
+      <c r="HJ47" t="n">
+        <v>105.4</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -26586,6 +26901,12 @@
       <c r="HE48" t="n">
         <v>104.35</v>
       </c>
+      <c r="HI48" t="n">
+        <v>101</v>
+      </c>
+      <c r="HJ48" t="n">
+        <v>104.9</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -27148,6 +27469,12 @@
       </c>
       <c r="HE49" t="n">
         <v>103.45</v>
+      </c>
+      <c r="HI49" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="HJ49" t="n">
+        <v>105.05</v>
       </c>
     </row>
     <row r="50">
@@ -27729,6 +28056,15 @@
       <c r="HE50" t="n">
         <v>104.15</v>
       </c>
+      <c r="HF50" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="HI50" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="HJ50" t="n">
+        <v>105.9</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -28303,6 +28639,12 @@
       <c r="HE51" t="n">
         <v>102.9</v>
       </c>
+      <c r="HI51" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="HJ51" t="n">
+        <v>105.9</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -28874,6 +29216,15 @@
       <c r="HE52" t="n">
         <v>102.5</v>
       </c>
+      <c r="HF52" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="HI52" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="HJ52" t="n">
+        <v>105.75</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -29452,6 +29803,12 @@
       <c r="HE53" t="n">
         <v>102.6</v>
       </c>
+      <c r="HI53" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="HJ53" t="n">
+        <v>105.4</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -30026,6 +30383,15 @@
       </c>
       <c r="HE54" t="n">
         <v>102.35</v>
+      </c>
+      <c r="HF54" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="HI54" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="HJ54" t="n">
+        <v>106.65</v>
       </c>
     </row>
     <row r="55">
@@ -30604,6 +30970,12 @@
       <c r="HE55" t="n">
         <v>102.8</v>
       </c>
+      <c r="HI55" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="HJ55" t="n">
+        <v>105.8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -31184,6 +31556,15 @@
       <c r="HE56" t="n">
         <v>104.45</v>
       </c>
+      <c r="HF56" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="HI56" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="HJ56" t="n">
+        <v>105.45</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -31758,6 +32139,12 @@
       <c r="HE57" t="n">
         <v>104.45</v>
       </c>
+      <c r="HI57" t="n">
+        <v>102</v>
+      </c>
+      <c r="HJ57" t="n">
+        <v>104.8</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -32332,6 +32719,12 @@
       <c r="HE58" t="n">
         <v>103.15</v>
       </c>
+      <c r="HI58" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="HJ58" t="n">
+        <v>105.7</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -32909,6 +33302,18 @@
       <c r="HE59" t="n">
         <v>103.15</v>
       </c>
+      <c r="HF59" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="HH59" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="HI59" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="HJ59" t="n">
+        <v>105.4</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -33492,6 +33897,12 @@
       <c r="HE60" t="n">
         <v>103.2</v>
       </c>
+      <c r="HI60" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="HJ60" t="n">
+        <v>105.7</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -34075,6 +34486,15 @@
       <c r="HE61" t="n">
         <v>102.6</v>
       </c>
+      <c r="HF61" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="HI61" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="HJ61" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -34655,6 +35075,18 @@
       <c r="HE62" t="n">
         <v>102.35</v>
       </c>
+      <c r="HF62" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="HH62" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="HI62" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="HJ62" t="n">
+        <v>104.7</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -35235,6 +35667,18 @@
       <c r="HE63" t="n">
         <v>103</v>
       </c>
+      <c r="HF63" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="HG63" t="n">
+        <v>99.95000000000002</v>
+      </c>
+      <c r="HI63" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="HJ63" t="n">
+        <v>104.7</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -35773,6 +36217,15 @@
       <c r="HE64" t="n">
         <v>102.95</v>
       </c>
+      <c r="HG64" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="HI64" t="n">
+        <v>102</v>
+      </c>
+      <c r="HJ64" t="n">
+        <v>104.5</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -36356,6 +36809,21 @@
       <c r="HE65" t="n">
         <v>102.95</v>
       </c>
+      <c r="HF65" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="HG65" t="n">
+        <v>99.59999999999998</v>
+      </c>
+      <c r="HH65" t="n">
+        <v>99.20000000000002</v>
+      </c>
+      <c r="HI65" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="HJ65" t="n">
+        <v>104.1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -36936,6 +37404,15 @@
       <c r="HE66" t="n">
         <v>103</v>
       </c>
+      <c r="HG66" t="n">
+        <v>99.59999999999998</v>
+      </c>
+      <c r="HI66" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="HJ66" t="n">
+        <v>104.35</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -37519,6 +37996,18 @@
       <c r="HE67" t="n">
         <v>102.65</v>
       </c>
+      <c r="HG67" t="n">
+        <v>100</v>
+      </c>
+      <c r="HH67" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="HI67" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="HJ67" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -38084,6 +38573,18 @@
       <c r="HE68" t="n">
         <v>102.85</v>
       </c>
+      <c r="HF68" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="HG68" t="n">
+        <v>100</v>
+      </c>
+      <c r="HI68" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="HJ68" t="n">
+        <v>104.9</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -38655,6 +39156,18 @@
       <c r="HE69" t="n">
         <v>103.05</v>
       </c>
+      <c r="HF69" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="HG69" t="n">
+        <v>99.75000000000001</v>
+      </c>
+      <c r="HI69" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="HJ69" t="n">
+        <v>104.95</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -39223,6 +39736,21 @@
       <c r="HE70" t="n">
         <v>103</v>
       </c>
+      <c r="HF70" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="HG70" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="HH70" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="HI70" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="HJ70" t="n">
+        <v>104.9</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -39797,6 +40325,18 @@
       <c r="HE71" t="n">
         <v>102.95</v>
       </c>
+      <c r="HG71" t="n">
+        <v>100</v>
+      </c>
+      <c r="HH71" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="HI71" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="HJ71" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -40371,6 +40911,18 @@
       <c r="HE72" t="n">
         <v>104</v>
       </c>
+      <c r="HF72" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="HG72" t="n">
+        <v>100</v>
+      </c>
+      <c r="HI72" t="n">
+        <v>101</v>
+      </c>
+      <c r="HJ72" t="n">
+        <v>105.55</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -40942,6 +41494,21 @@
       <c r="HE73" t="n">
         <v>103</v>
       </c>
+      <c r="HF73" t="n">
+        <v>105</v>
+      </c>
+      <c r="HG73" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="HH73" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="HI73" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="HJ73" t="n">
+        <v>105.5</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -41516,6 +42083,18 @@
       <c r="HE74" t="n">
         <v>103.9</v>
       </c>
+      <c r="HG74" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="HH74" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="HI74" t="n">
+        <v>101</v>
+      </c>
+      <c r="HJ74" t="n">
+        <v>105.3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HJ75"/>
+  <dimension ref="A1:HJ76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -42685,6 +42685,592 @@
         <v>104.6</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>116.09</v>
+      </c>
+      <c r="J76" t="n">
+        <v>131.049</v>
+      </c>
+      <c r="K76" t="n">
+        <v>122.84</v>
+      </c>
+      <c r="L76" t="n">
+        <v>147.59</v>
+      </c>
+      <c r="M76" t="n">
+        <v>133.751</v>
+      </c>
+      <c r="N76" t="n">
+        <v>125.81</v>
+      </c>
+      <c r="O76" t="n">
+        <v>126.85</v>
+      </c>
+      <c r="P76" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="S76" t="n">
+        <v>172.05</v>
+      </c>
+      <c r="T76" t="n">
+        <v>302.2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>223.25</v>
+      </c>
+      <c r="V76" t="n">
+        <v>123</v>
+      </c>
+      <c r="W76" t="n">
+        <v>397</v>
+      </c>
+      <c r="X76" t="n">
+        <v>107</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>277.55</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>352.3</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>121.85</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>150750</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>147650</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>125050</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>94.97000000000001</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>92.69999999999999</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>56.07</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>76.56</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>79.04000000000001</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>71.72</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>65.93000000000001</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>93.18999999999998</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>169.72</v>
+      </c>
+      <c r="BI76" t="n">
+        <v>106.898</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>147800</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>118150</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>86.06</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>105</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>90.82999999999998</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>104</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>46.1877</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>62.9614</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>105.65</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>98</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>69.20999999999999</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>106.4095</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>78.98</v>
+      </c>
+      <c r="CW76" t="n">
+        <v>48.89999999999999</v>
+      </c>
+      <c r="CX76" t="n">
+        <v>105</v>
+      </c>
+      <c r="CY76" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="CZ76" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="DA76" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="DB76" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DC76" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="DD76" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="DE76" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="DF76" t="n">
+        <v>106</v>
+      </c>
+      <c r="DG76" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="DH76" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="DI76" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="DJ76" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="DK76" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="DL76" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DM76" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="DN76" t="n">
+        <v>104.7754</v>
+      </c>
+      <c r="DO76" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="DP76" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="DQ76" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="DR76" t="n">
+        <v>102</v>
+      </c>
+      <c r="DS76" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="DT76" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="DU76" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="DV76" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="DW76" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="DX76" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="DY76" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="DZ76" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="EA76" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="EB76" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="EC76" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="ED76" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="EE76" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="EF76" t="n">
+        <v>106.05</v>
+      </c>
+      <c r="EG76" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="EH76" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="EI76" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="EJ76" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EK76" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="EL76" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="EM76" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="EN76" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="EQ76" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="ER76" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="ES76" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="EU76" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EV76" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="EW76" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="EX76" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="EY76" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="EZ76" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="FA76" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="FB76" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="FC76" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="FD76" t="n">
+        <v>95</v>
+      </c>
+      <c r="FE76" t="n">
+        <v>102</v>
+      </c>
+      <c r="FF76" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="FG76" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="FH76" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="FI76" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="FJ76" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="FK76" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="FM76" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="FN76" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="FQ76" t="n">
+        <v>102.883</v>
+      </c>
+      <c r="FR76" t="n">
+        <v>150000</v>
+      </c>
+      <c r="FS76" t="n">
+        <v>140240</v>
+      </c>
+      <c r="FU76" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FV76" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="FX76" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="FY76" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="GA76" t="n">
+        <v>99.00790000000001</v>
+      </c>
+      <c r="GB76" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="GC76" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="GD76" t="n">
+        <v>150090</v>
+      </c>
+      <c r="GE76" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="GF76" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="GG76" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="GH76" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="GI76" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="GJ76" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="GK76" t="n">
+        <v>103</v>
+      </c>
+      <c r="GL76" t="n">
+        <v>27.3743</v>
+      </c>
+      <c r="GM76" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="GN76" t="n">
+        <v>104.7754</v>
+      </c>
+      <c r="GO76" t="n">
+        <v>1738</v>
+      </c>
+      <c r="GP76" t="n">
+        <v>1462.5</v>
+      </c>
+      <c r="GQ76" t="n">
+        <v>48920</v>
+      </c>
+      <c r="GR76" t="n">
+        <v>35100</v>
+      </c>
+      <c r="GS76" t="n">
+        <v>42970</v>
+      </c>
+      <c r="GT76" t="n">
+        <v>101.26</v>
+      </c>
+      <c r="GU76" t="n">
+        <v>738.6</v>
+      </c>
+      <c r="GV76" t="n">
+        <v>169.35</v>
+      </c>
+      <c r="GW76" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="GX76" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="GY76" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="GZ76" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="HA76" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="HB76" t="n">
+        <v>103</v>
+      </c>
+      <c r="HC76" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="HD76" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="HE76" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="HF76" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="HG76" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="HH76" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="HI76" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="HJ76" t="n">
+        <v>104.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HJ76"/>
+  <dimension ref="A1:HJ77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -43271,6 +43271,595 @@
         <v>104.3</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>116.13</v>
+      </c>
+      <c r="J77" t="n">
+        <v>131.17</v>
+      </c>
+      <c r="K77" t="n">
+        <v>123.037</v>
+      </c>
+      <c r="L77" t="n">
+        <v>148.04</v>
+      </c>
+      <c r="M77" t="n">
+        <v>134</v>
+      </c>
+      <c r="N77" t="n">
+        <v>126.05</v>
+      </c>
+      <c r="O77" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="P77" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="S77" t="n">
+        <v>172.302</v>
+      </c>
+      <c r="T77" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="U77" t="n">
+        <v>223.25</v>
+      </c>
+      <c r="V77" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="W77" t="n">
+        <v>396.5</v>
+      </c>
+      <c r="X77" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>277.9</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>90</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>150750</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>146450</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>125390</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>54.47000000000001</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>92.35000000000001</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>76</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>55.77000000000001</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>76.37</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>80.02</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>70.78</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>65.64</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>104</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>106.965</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>147100</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>118720</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>86.34</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>83.39</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>90.63</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="CC77" t="n">
+        <v>124.66</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>104</v>
+      </c>
+      <c r="CH77" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="CI77" t="n">
+        <v>62.4028</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>105.6048</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>98.00000000000001</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>98.8845</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="CO77" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="CP77" t="n">
+        <v>71.72</v>
+      </c>
+      <c r="CQ77" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>103.5887</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="CU77" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="CV77" t="n">
+        <v>79.194</v>
+      </c>
+      <c r="CW77" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="CX77" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="CY77" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="CZ77" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="DA77" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="DB77" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="DC77" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="DD77" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="DE77" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="DF77" t="n">
+        <v>106</v>
+      </c>
+      <c r="DG77" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="DH77" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="DI77" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="DJ77" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="DK77" t="n">
+        <v>107</v>
+      </c>
+      <c r="DL77" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="DM77" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="DN77" t="n">
+        <v>104.5967</v>
+      </c>
+      <c r="DO77" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="DP77" t="n">
+        <v>90.64</v>
+      </c>
+      <c r="DQ77" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DR77" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="DS77" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="DT77" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="DU77" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="DV77" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="DW77" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="DX77" t="n">
+        <v>103</v>
+      </c>
+      <c r="DY77" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="DZ77" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="EA77" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="EB77" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="EC77" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="ED77" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="EE77" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="EF77" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="EG77" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="EH77" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="EI77" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EJ77" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="EK77" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="EL77" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="EM77" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="EN77" t="n">
+        <v>106</v>
+      </c>
+      <c r="EQ77" t="n">
+        <v>104</v>
+      </c>
+      <c r="ER77" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="ES77" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="EU77" t="n">
+        <v>104</v>
+      </c>
+      <c r="EV77" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="EW77" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="EX77" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EY77" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="EZ77" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="FA77" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FB77" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FC77" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="FD77" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="FE77" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="FF77" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="FG77" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FH77" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="FI77" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="FJ77" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="FK77" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="FM77" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="FN77" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="FP77" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="FQ77" t="n">
+        <v>102.96</v>
+      </c>
+      <c r="FR77" t="n">
+        <v>149500</v>
+      </c>
+      <c r="FS77" t="n">
+        <v>140250</v>
+      </c>
+      <c r="FU77" t="n">
+        <v>100</v>
+      </c>
+      <c r="FV77" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="FX77" t="n">
+        <v>100.2285</v>
+      </c>
+      <c r="FY77" t="n">
+        <v>24.105</v>
+      </c>
+      <c r="FZ77" t="n">
+        <v>107.7649</v>
+      </c>
+      <c r="GA77" t="n">
+        <v>98.8845</v>
+      </c>
+      <c r="GB77" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="GC77" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="GD77" t="n">
+        <v>150100</v>
+      </c>
+      <c r="GE77" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="GF77" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="GG77" t="n">
+        <v>102</v>
+      </c>
+      <c r="GH77" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="GI77" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="GJ77" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="GK77" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="GL77" t="n">
+        <v>28.8013</v>
+      </c>
+      <c r="GM77" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="GN77" t="n">
+        <v>105.4128</v>
+      </c>
+      <c r="GO77" t="n">
+        <v>1735</v>
+      </c>
+      <c r="GP77" t="n">
+        <v>1462</v>
+      </c>
+      <c r="GQ77" t="n">
+        <v>49010</v>
+      </c>
+      <c r="GR77" t="n">
+        <v>35100</v>
+      </c>
+      <c r="GS77" t="n">
+        <v>43005</v>
+      </c>
+      <c r="GT77" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="GU77" t="n">
+        <v>739.2</v>
+      </c>
+      <c r="GV77" t="n">
+        <v>169.344</v>
+      </c>
+      <c r="GW77" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="GX77" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="GY77" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="GZ77" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="HA77" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="HB77" t="n">
+        <v>104</v>
+      </c>
+      <c r="HC77" t="n">
+        <v>103</v>
+      </c>
+      <c r="HD77" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="HE77" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="HF77" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="HG77" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="HI77" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="HJ77" t="n">
+        <v>104.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historicos.xlsx
+++ b/historicos.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HJ77"/>
+  <dimension ref="A1:HJ78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -43860,6 +43860,592 @@
         <v>104.8</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>116.33</v>
+      </c>
+      <c r="J78" t="n">
+        <v>131.35</v>
+      </c>
+      <c r="K78" t="n">
+        <v>123.29</v>
+      </c>
+      <c r="L78" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="M78" t="n">
+        <v>134.2</v>
+      </c>
+      <c r="N78" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="O78" t="n">
+        <v>127.499</v>
+      </c>
+      <c r="P78" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="S78" t="n">
+        <v>172.74</v>
+      </c>
+      <c r="T78" t="n">
+        <v>304.25</v>
+      </c>
+      <c r="U78" t="n">
+        <v>223.3</v>
+      </c>
+      <c r="V78" t="n">
+        <v>123</v>
+      </c>
+      <c r="W78" t="n">
+        <v>397.05</v>
+      </c>
+      <c r="X78" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>278.35</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>122</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>116.05</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>109</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>150600</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>146550</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>125490</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>94.62</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>54.56999999999999</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>92.44</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>55.69</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>70.04000000000001</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>53.92</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>55.77000000000001</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>76.48999999999999</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>70.76000000000001</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>104</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>93.08</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>170.173</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>107.151</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>147200</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>118600</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>94.11</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="BU78" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="BV78" t="n">
+        <v>105.28</v>
+      </c>
+      <c r="BW78" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="BY78" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="BZ78" t="n">
+        <v>150110</v>
+      </c>
+      <c r="CA78" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="CB78" t="n">
+        <v>121.05</v>
+      </c>
+      <c r="CC78" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="CE78" t="n">
+        <v>116.35</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="CG78" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="CH78" t="n">
+        <v>46.0423</v>
+      </c>
+      <c r="CI78" t="n">
+        <v>62.3969</v>
+      </c>
+      <c r="CJ78" t="n">
+        <v>105.9932</v>
+      </c>
+      <c r="CL78" t="n">
+        <v>100.4778</v>
+      </c>
+      <c r="CM78" t="n">
+        <v>98.31950000000001</v>
+      </c>
+      <c r="CN78" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="CO78" t="n">
+        <v>68.64</v>
+      </c>
+      <c r="CP78" t="n">
+        <v>72</v>
+      </c>
+      <c r="CQ78" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="CR78" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="CS78" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="CU78" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="CV78" t="n">
+        <v>76.7851</v>
+      </c>
+      <c r="CW78" t="n">
+        <v>49.1118</v>
+      </c>
+      <c r="CX78" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="CY78" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="CZ78" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="DA78" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="DB78" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="DC78" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="DD78" t="n">
+        <v>104</v>
+      </c>
+      <c r="DE78" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="DF78" t="n">
+        <v>105.9932</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="DI78" t="n">
+        <v>108</v>
+      </c>
+      <c r="DJ78" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="DK78" t="n">
+        <v>106.6647</v>
+      </c>
+      <c r="DL78" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="DM78" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="DN78" t="n">
+        <v>104.1707</v>
+      </c>
+      <c r="DO78" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="DP78" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="DQ78" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="DR78" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="DS78" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="DT78" t="n">
+        <v>105</v>
+      </c>
+      <c r="DU78" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="DV78" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="DW78" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DX78" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="DY78" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="DZ78" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="EA78" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="EB78" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="EC78" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="ED78" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="EE78" t="n">
+        <v>104</v>
+      </c>
+      <c r="EF78" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="EG78" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="EH78" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="EI78" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="EJ78" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="EK78" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="EL78" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="EM78" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="EN78" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="EQ78" t="n">
+        <v>105</v>
+      </c>
+      <c r="ER78" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="ES78" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="EU78" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="EV78" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="EW78" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="EX78" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="EY78" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="EZ78" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="FA78" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="FB78" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="FC78" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="FD78" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="FE78" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="FF78" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="FG78" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="FH78" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="FI78" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="FJ78" t="n">
+        <v>102</v>
+      </c>
+      <c r="FK78" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="FM78" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="FN78" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="FP78" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="FQ78" t="n">
+        <v>103.13</v>
+      </c>
+      <c r="FR78" t="n">
+        <v>150000</v>
+      </c>
+      <c r="FS78" t="n">
+        <v>140360</v>
+      </c>
+      <c r="FU78" t="n">
+        <v>101</v>
+      </c>
+      <c r="FV78" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="FX78" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="FY78" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="GA78" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="GB78" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="GC78" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="GD78" t="n">
+        <v>149950</v>
+      </c>
+      <c r="GE78" t="n">
+        <v>110</v>
+      </c>
+      <c r="GF78" t="n">
+        <v>106</v>
+      </c>
+      <c r="GG78" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="GH78" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="GI78" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="GJ78" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="GK78" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="GL78" t="n">
+        <v>27.0508</v>
+      </c>
+      <c r="GM78" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="GN78" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="GO78" t="n">
+        <v>1739.5</v>
+      </c>
+      <c r="GP78" t="n">
+        <v>1461.5</v>
+      </c>
+      <c r="GQ78" t="n">
+        <v>49050</v>
+      </c>
+      <c r="GR78" t="n">
+        <v>35100</v>
+      </c>
+      <c r="GS78" t="n">
+        <v>43010</v>
+      </c>
+      <c r="GT78" t="n">
+        <v>101.78</v>
+      </c>
+      <c r="GU78" t="n">
+        <v>741</v>
+      </c>
+      <c r="GV78" t="n">
+        <v>169.599</v>
+      </c>
+      <c r="GW78" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="GX78" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="GY78" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="GZ78" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="HA78" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="HB78" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="HC78" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="HD78" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="HE78" t="n">
+        <v>103</v>
+      </c>
+      <c r="HF78" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="HG78" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="HH78" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="HI78" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="HJ78" t="n">
+        <v>104.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
